--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,70 +641,78 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4309.5</v>
+        <v>4339</v>
       </c>
       <c r="C2" t="n">
-        <v>4345.8</v>
+        <v>4377</v>
       </c>
       <c r="D2" t="n">
-        <v>4309.5</v>
+        <v>4296</v>
       </c>
       <c r="E2" t="n">
-        <v>4330.9</v>
+        <v>4358.9</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>28</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0065</v>
       </c>
       <c r="H2" t="n">
-        <v>36.3</v>
+        <v>81</v>
       </c>
       <c r="I2" t="n">
-        <v>4176.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J2" t="n">
-        <v>4241.33</v>
+        <v>4296.23</v>
       </c>
       <c r="K2" t="n">
-        <v>4281.55</v>
+        <v>4312.75</v>
       </c>
       <c r="L2" t="n">
-        <v>4321.78</v>
+        <v>4329.27</v>
       </c>
       <c r="M2" t="n">
-        <v>4374.45</v>
+        <v>4349.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4427.12</v>
+        <v>4368.82</v>
       </c>
       <c r="O2" t="n">
-        <v>4454.9</v>
+        <v>4382.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -723,53 +731,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4339</v>
+        <v>4279.8</v>
       </c>
       <c r="C3" t="n">
-        <v>4377</v>
+        <v>4323.2</v>
       </c>
       <c r="D3" t="n">
-        <v>4296</v>
+        <v>4223.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>-134.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0309</v>
       </c>
       <c r="H3" t="n">
-        <v>81</v>
+        <v>99.5</v>
       </c>
       <c r="I3" t="n">
-        <v>4273.2</v>
+        <v>4215</v>
       </c>
       <c r="J3" t="n">
-        <v>4296.23</v>
+        <v>4289.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4312.75</v>
+        <v>4318.4</v>
       </c>
       <c r="L3" t="n">
-        <v>4329.27</v>
+        <v>4347.7</v>
       </c>
       <c r="M3" t="n">
-        <v>4349.05</v>
+        <v>4399.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4368.82</v>
+        <v>4451.1</v>
       </c>
       <c r="O3" t="n">
-        <v>4382.1</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
+        <v>4458</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
@@ -781,96 +791,84 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4279.8</v>
+        <v>4138.8</v>
       </c>
       <c r="C4" t="n">
-        <v>4323.2</v>
+        <v>4216.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4223.7</v>
+        <v>4134.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-134.8</v>
+        <v>-42.2</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0309</v>
+        <v>-0.01</v>
       </c>
       <c r="H4" t="n">
-        <v>99.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4215</v>
+        <v>4124.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4289.1</v>
+        <v>4099.93</v>
       </c>
       <c r="K4" t="n">
-        <v>4318.4</v>
+        <v>4174.35</v>
       </c>
       <c r="L4" t="n">
-        <v>4347.7</v>
+        <v>4248.78</v>
       </c>
       <c r="M4" t="n">
-        <v>4399.4</v>
+        <v>4273.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4451.1</v>
+        <v>4298.93</v>
       </c>
       <c r="O4" t="n">
-        <v>4458</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>4422.7</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -897,50 +895,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4138.8</v>
+        <v>4127.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4216.4</v>
+        <v>4135.2</v>
       </c>
       <c r="D5" t="n">
-        <v>4134.8</v>
+        <v>4118.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-42.2</v>
+        <v>-52</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0124</v>
       </c>
       <c r="H5" t="n">
-        <v>81.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4124.2</v>
+        <v>4053.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4099.93</v>
+        <v>4103.45</v>
       </c>
       <c r="K5" t="n">
-        <v>4174.35</v>
+        <v>4141.1</v>
       </c>
       <c r="L5" t="n">
-        <v>4248.78</v>
+        <v>4178.75</v>
       </c>
       <c r="M5" t="n">
-        <v>4273.85</v>
+        <v>4222.7</v>
       </c>
       <c r="N5" t="n">
-        <v>4298.93</v>
+        <v>4266.65</v>
       </c>
       <c r="O5" t="n">
-        <v>4422.7</v>
+        <v>4298</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -977,60 +975,64 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4127.1</v>
+        <v>4104.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4135.2</v>
+        <v>4104.7</v>
       </c>
       <c r="D6" t="n">
-        <v>4118.5</v>
+        <v>3963.3</v>
       </c>
       <c r="E6" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F6" t="n">
-        <v>-52</v>
+        <v>-139.6</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0338</v>
       </c>
       <c r="H6" t="n">
-        <v>16.7</v>
+        <v>141.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4053.2</v>
+        <v>4101.8</v>
       </c>
       <c r="J6" t="n">
-        <v>4103.45</v>
+        <v>4114.72</v>
       </c>
       <c r="K6" t="n">
-        <v>4141.1</v>
+        <v>4121.55</v>
       </c>
       <c r="L6" t="n">
-        <v>4178.75</v>
+        <v>4128.38</v>
       </c>
       <c r="M6" t="n">
-        <v>4222.7</v>
+        <v>4138.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4266.65</v>
+        <v>4148.12</v>
       </c>
       <c r="O6" t="n">
-        <v>4298</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>4151.9</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
@@ -1057,69 +1059,63 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4104.4</v>
+        <v>3988.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4104.7</v>
+        <v>4030.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3963.3</v>
+        <v>3986.7</v>
       </c>
       <c r="E7" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-139.6</v>
+        <v>40.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.0101</v>
       </c>
       <c r="H7" t="n">
-        <v>141.4</v>
+        <v>43.8</v>
       </c>
       <c r="I7" t="n">
-        <v>4101.8</v>
+        <v>3821.9</v>
       </c>
       <c r="J7" t="n">
-        <v>4114.72</v>
+        <v>3827.05</v>
       </c>
       <c r="K7" t="n">
-        <v>4121.55</v>
+        <v>3919.6</v>
       </c>
       <c r="L7" t="n">
-        <v>4128.38</v>
+        <v>4012.15</v>
       </c>
       <c r="M7" t="n">
-        <v>4138.25</v>
+        <v>4061</v>
       </c>
       <c r="N7" t="n">
-        <v>4148.12</v>
+        <v>4109.85</v>
       </c>
       <c r="O7" t="n">
-        <v>4151.9</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4246.1</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1136,55 +1132,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3988.4</v>
+        <v>4078.7</v>
       </c>
       <c r="C8" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="D8" t="n">
-        <v>3986.7</v>
+        <v>4078.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F8" t="n">
-        <v>40.2</v>
+        <v>48.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.012</v>
       </c>
       <c r="H8" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3821.9</v>
+        <v>3942.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3827.05</v>
+        <v>3997.65</v>
       </c>
       <c r="K8" t="n">
-        <v>3919.6</v>
+        <v>4008.6</v>
       </c>
       <c r="L8" t="n">
-        <v>4012.15</v>
+        <v>4019.55</v>
       </c>
       <c r="M8" t="n">
-        <v>4061</v>
+        <v>4052.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4109.85</v>
+        <v>4085.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4246.1</v>
+        <v>4074.3</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1197,17 +1197,21 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
@@ -1216,153 +1220,147 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4070</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4003.2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4022.3</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-56.4</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="H9" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I9" t="n">
         <v>4078.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="J9" t="n">
         <v>4078.7</v>
       </c>
-      <c r="D9" t="n">
+      <c r="K9" t="n">
         <v>4078.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="L9" t="n">
         <v>4078.7</v>
       </c>
-      <c r="F9" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3942.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3997.65</v>
-      </c>
-      <c r="K9" t="n">
-        <v>4008.6</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4019.55</v>
-      </c>
       <c r="M9" t="n">
-        <v>4052.4</v>
+        <v>4078.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4085.25</v>
+        <v>4078.7</v>
       </c>
       <c r="O9" t="n">
-        <v>4074.3</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4078.7</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4057.5</v>
+        <v>4002.6</v>
       </c>
       <c r="C10" t="n">
-        <v>4070</v>
+        <v>4049.7</v>
       </c>
       <c r="D10" t="n">
-        <v>4003.2</v>
+        <v>3962.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F10" t="n">
-        <v>-56.4</v>
+        <v>0.6</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0001</v>
       </c>
       <c r="H10" t="n">
-        <v>66.8</v>
+        <v>87.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4078.7</v>
+        <v>3936.4</v>
       </c>
       <c r="J10" t="n">
-        <v>4078.7</v>
+        <v>3948.35</v>
       </c>
       <c r="K10" t="n">
-        <v>4078.7</v>
+        <v>3988.9</v>
       </c>
       <c r="L10" t="n">
-        <v>4078.7</v>
+        <v>4029.45</v>
       </c>
       <c r="M10" t="n">
-        <v>4078.7</v>
+        <v>4055.7</v>
       </c>
       <c r="N10" t="n">
-        <v>4078.7</v>
+        <v>4081.95</v>
       </c>
       <c r="O10" t="n">
-        <v>4078.7</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4136.8</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1371,7 +1369,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1388,55 +1386,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4002.6</v>
+        <v>4013.1</v>
       </c>
       <c r="C11" t="n">
-        <v>4049.7</v>
+        <v>4100</v>
       </c>
       <c r="D11" t="n">
-        <v>3962.5</v>
+        <v>3963</v>
       </c>
       <c r="E11" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6</v>
+        <v>45.4</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0113</v>
       </c>
       <c r="H11" t="n">
-        <v>87.2</v>
+        <v>137</v>
       </c>
       <c r="I11" t="n">
-        <v>3936.4</v>
+        <v>3875.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3948.35</v>
+        <v>3944.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3988.9</v>
+        <v>3979.3</v>
       </c>
       <c r="L11" t="n">
-        <v>4029.45</v>
+        <v>4014.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4055.7</v>
+        <v>4066.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4081.95</v>
+        <v>4118.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4136.8</v>
+        <v>4136.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1449,13 +1451,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1470,57 +1474,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4013.1</v>
+        <v>4067.5</v>
       </c>
       <c r="C12" t="n">
-        <v>4100</v>
+        <v>4140.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3963</v>
+        <v>4062</v>
       </c>
       <c r="E12" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F12" t="n">
-        <v>45.4</v>
+        <v>44.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0109</v>
       </c>
       <c r="H12" t="n">
-        <v>137</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3875.3</v>
+        <v>3826</v>
       </c>
       <c r="J12" t="n">
-        <v>3944.1</v>
+        <v>3949.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3979.3</v>
+        <v>3999.8</v>
       </c>
       <c r="L12" t="n">
-        <v>4014.5</v>
+        <v>4049.9</v>
       </c>
       <c r="M12" t="n">
-        <v>4066.5</v>
+        <v>4136.8</v>
       </c>
       <c r="N12" t="n">
-        <v>4118.5</v>
+        <v>4223.7</v>
       </c>
       <c r="O12" t="n">
-        <v>4136.9</v>
+        <v>4237</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,10 +1532,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1563,50 +1565,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4067.5</v>
+        <v>4175.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4140.1</v>
+        <v>4199.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4062</v>
+        <v>4134.2</v>
       </c>
       <c r="E13" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F13" t="n">
-        <v>44.4</v>
+        <v>42.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0103</v>
       </c>
       <c r="H13" t="n">
-        <v>78.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3826</v>
+        <v>3983.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3949.7</v>
+        <v>4040.43</v>
       </c>
       <c r="K13" t="n">
-        <v>3999.8</v>
+        <v>4073.65</v>
       </c>
       <c r="L13" t="n">
-        <v>4049.9</v>
+        <v>4106.88</v>
       </c>
       <c r="M13" t="n">
-        <v>4136.8</v>
+        <v>4151.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4223.7</v>
+        <v>4196.63</v>
       </c>
       <c r="O13" t="n">
-        <v>4237</v>
+        <v>4218.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1627,8 +1629,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1647,50 +1651,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4175.4</v>
+        <v>4126.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4199.7</v>
+        <v>4167.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4134.2</v>
+        <v>4107.2</v>
       </c>
       <c r="E14" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F14" t="n">
-        <v>42.4</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0024</v>
       </c>
       <c r="H14" t="n">
-        <v>65.5</v>
+        <v>60</v>
       </c>
       <c r="I14" t="n">
-        <v>3983.9</v>
+        <v>4068.7</v>
       </c>
       <c r="J14" t="n">
-        <v>4040.43</v>
+        <v>4083.68</v>
       </c>
       <c r="K14" t="n">
-        <v>4073.65</v>
+        <v>4122.35</v>
       </c>
       <c r="L14" t="n">
-        <v>4106.88</v>
+        <v>4161.03</v>
       </c>
       <c r="M14" t="n">
-        <v>4151.75</v>
+        <v>4187.85</v>
       </c>
       <c r="N14" t="n">
-        <v>4196.63</v>
+        <v>4214.68</v>
       </c>
       <c r="O14" t="n">
-        <v>4218.2</v>
+        <v>4265.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1698,23 +1702,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1724,65 +1726,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4126.5</v>
+        <v>4116.3</v>
       </c>
       <c r="C15" t="n">
-        <v>4167.2</v>
+        <v>4120.3</v>
       </c>
       <c r="D15" t="n">
-        <v>4107.2</v>
+        <v>4053</v>
       </c>
       <c r="E15" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.800000000000001</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0179</v>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>67.3</v>
       </c>
       <c r="I15" t="n">
-        <v>4068.7</v>
+        <v>4047.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4083.68</v>
+        <v>4089.35</v>
       </c>
       <c r="K15" t="n">
-        <v>4122.35</v>
+        <v>4115.3</v>
       </c>
       <c r="L15" t="n">
-        <v>4161.03</v>
+        <v>4141.25</v>
       </c>
       <c r="M15" t="n">
-        <v>4187.85</v>
+        <v>4175.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4214.68</v>
+        <v>4209.35</v>
       </c>
       <c r="O15" t="n">
-        <v>4265.2</v>
+        <v>4227.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1813,81 +1813,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4116.3</v>
+        <v>4066.4</v>
       </c>
       <c r="C16" t="n">
-        <v>4120.3</v>
+        <v>4130.6</v>
       </c>
       <c r="D16" t="n">
-        <v>4053</v>
+        <v>4064.2</v>
       </c>
       <c r="E16" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F16" t="n">
-        <v>-74.40000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0147</v>
       </c>
       <c r="H16" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>4047.2</v>
+        <v>3985.7</v>
       </c>
       <c r="J16" t="n">
-        <v>4089.35</v>
+        <v>3995.73</v>
       </c>
       <c r="K16" t="n">
-        <v>4115.3</v>
+        <v>4037.25</v>
       </c>
       <c r="L16" t="n">
-        <v>4141.25</v>
+        <v>4078.77</v>
       </c>
       <c r="M16" t="n">
-        <v>4175.3</v>
+        <v>4104.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4209.35</v>
+        <v>4130.32</v>
       </c>
       <c r="O16" t="n">
-        <v>4227.2</v>
+        <v>4187.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1895,50 +1895,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4066.4</v>
+        <v>4122.3</v>
       </c>
       <c r="C17" t="n">
-        <v>4130.6</v>
+        <v>4125.8</v>
       </c>
       <c r="D17" t="n">
-        <v>4064.2</v>
+        <v>4090.6</v>
       </c>
       <c r="E17" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F17" t="n">
-        <v>59.7</v>
+        <v>-26.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0064</v>
       </c>
       <c r="H17" t="n">
-        <v>66.40000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3985.7</v>
+        <v>3997.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3995.73</v>
+        <v>4080.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4037.25</v>
+        <v>4097.4</v>
       </c>
       <c r="L17" t="n">
-        <v>4078.77</v>
+        <v>4114</v>
       </c>
       <c r="M17" t="n">
-        <v>4104.55</v>
+        <v>4163.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4130.32</v>
+        <v>4213.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4187.6</v>
+        <v>4197</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,24 +1946,22 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1972,65 +1970,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4122.3</v>
+        <v>4081</v>
       </c>
       <c r="C18" t="n">
-        <v>4125.8</v>
+        <v>4081</v>
       </c>
       <c r="D18" t="n">
-        <v>4090.6</v>
+        <v>3985.9</v>
       </c>
       <c r="E18" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F18" t="n">
-        <v>-26.5</v>
+        <v>-107.1</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0261</v>
       </c>
       <c r="H18" t="n">
-        <v>35.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3997.8</v>
+        <v>4055.4</v>
       </c>
       <c r="J18" t="n">
-        <v>4080.8</v>
+        <v>4066.85</v>
       </c>
       <c r="K18" t="n">
-        <v>4097.4</v>
+        <v>4086.5</v>
       </c>
       <c r="L18" t="n">
-        <v>4114</v>
+        <v>4106.15</v>
       </c>
       <c r="M18" t="n">
-        <v>4163.8</v>
+        <v>4121.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4213.6</v>
+        <v>4137.25</v>
       </c>
       <c r="O18" t="n">
-        <v>4197</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>4161</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
@@ -2047,91 +2053,85 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4081</v>
+        <v>3995.7</v>
       </c>
       <c r="C19" t="n">
-        <v>4081</v>
+        <v>4091.2</v>
       </c>
       <c r="D19" t="n">
-        <v>3985.9</v>
+        <v>3986.5</v>
       </c>
       <c r="E19" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-107.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.016</v>
       </c>
       <c r="H19" t="n">
-        <v>95.09999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="I19" t="n">
-        <v>4055.4</v>
+        <v>3890.8</v>
       </c>
       <c r="J19" t="n">
-        <v>4066.85</v>
+        <v>3883.67</v>
       </c>
       <c r="K19" t="n">
-        <v>4086.5</v>
+        <v>3949.45</v>
       </c>
       <c r="L19" t="n">
-        <v>4106.15</v>
+        <v>4015.22</v>
       </c>
       <c r="M19" t="n">
-        <v>4121.7</v>
+        <v>4044.55</v>
       </c>
       <c r="N19" t="n">
-        <v>4137.25</v>
+        <v>4073.88</v>
       </c>
       <c r="O19" t="n">
-        <v>4161</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>4176.1</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2140,55 +2140,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3995.7</v>
+        <v>4049.1</v>
       </c>
       <c r="C20" t="n">
-        <v>4091.2</v>
+        <v>4070.1</v>
       </c>
       <c r="D20" t="n">
-        <v>3986.5</v>
+        <v>4019.4</v>
       </c>
       <c r="E20" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F20" t="n">
-        <v>64.09999999999999</v>
+        <v>-17.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0042</v>
       </c>
       <c r="H20" t="n">
-        <v>104.7</v>
+        <v>50.7</v>
       </c>
       <c r="I20" t="n">
-        <v>3890.8</v>
+        <v>3881.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3883.67</v>
+        <v>3967.53</v>
       </c>
       <c r="K20" t="n">
-        <v>3949.45</v>
+        <v>4008.75</v>
       </c>
       <c r="L20" t="n">
-        <v>4015.22</v>
+        <v>4049.98</v>
       </c>
       <c r="M20" t="n">
-        <v>4044.55</v>
+        <v>4113.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4073.88</v>
+        <v>4176.93</v>
       </c>
       <c r="O20" t="n">
-        <v>4176.1</v>
+        <v>4195.9</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2199,20 +2203,16 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2224,70 +2224,74 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4049.1</v>
+        <v>4030.5</v>
       </c>
       <c r="C21" t="n">
-        <v>4070.1</v>
+        <v>4030.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4019.4</v>
+        <v>3972.6</v>
       </c>
       <c r="E21" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-17.1</v>
+        <v>-58.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0144</v>
       </c>
       <c r="H21" t="n">
-        <v>50.7</v>
+        <v>57.9</v>
       </c>
       <c r="I21" t="n">
-        <v>3881.8</v>
+        <v>3968.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3967.53</v>
+        <v>3992.92</v>
       </c>
       <c r="K21" t="n">
-        <v>4008.75</v>
+        <v>4018.65</v>
       </c>
       <c r="L21" t="n">
-        <v>4049.98</v>
+        <v>4044.38</v>
       </c>
       <c r="M21" t="n">
-        <v>4113.45</v>
+        <v>4069.35</v>
       </c>
       <c r="N21" t="n">
-        <v>4176.93</v>
+        <v>4094.33</v>
       </c>
       <c r="O21" t="n">
-        <v>4195.9</v>
+        <v>4120.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2304,81 +2308,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4030.5</v>
+        <v>3975.5</v>
       </c>
       <c r="C22" t="n">
-        <v>4030.5</v>
+        <v>4017.2</v>
       </c>
       <c r="D22" t="n">
-        <v>3972.6</v>
+        <v>3964.2</v>
       </c>
       <c r="E22" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F22" t="n">
-        <v>-58.4</v>
+        <v>27.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0068</v>
       </c>
       <c r="H22" t="n">
-        <v>57.9</v>
+        <v>53</v>
       </c>
       <c r="I22" t="n">
-        <v>3968.7</v>
+        <v>3914.7</v>
       </c>
       <c r="J22" t="n">
-        <v>3992.92</v>
+        <v>3919.73</v>
       </c>
       <c r="K22" t="n">
-        <v>4018.65</v>
+        <v>3956.65</v>
       </c>
       <c r="L22" t="n">
-        <v>4044.38</v>
+        <v>3993.58</v>
       </c>
       <c r="M22" t="n">
-        <v>4069.35</v>
+        <v>4014.55</v>
       </c>
       <c r="N22" t="n">
-        <v>4094.33</v>
+        <v>4035.53</v>
       </c>
       <c r="O22" t="n">
-        <v>4120.8</v>
+        <v>4088.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2390,55 +2388,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3975.5</v>
+        <v>4003.4</v>
       </c>
       <c r="C23" t="n">
-        <v>4017.2</v>
+        <v>4018.9</v>
       </c>
       <c r="D23" t="n">
-        <v>3964.2</v>
+        <v>4002.7</v>
       </c>
       <c r="E23" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F23" t="n">
-        <v>27.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>53</v>
+        <v>16.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3914.7</v>
+        <v>3911.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3919.73</v>
+        <v>3970.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3956.65</v>
+        <v>3986.2</v>
       </c>
       <c r="L23" t="n">
-        <v>3993.58</v>
+        <v>4001.7</v>
       </c>
       <c r="M23" t="n">
-        <v>4014.55</v>
+        <v>4039.2</v>
       </c>
       <c r="N23" t="n">
-        <v>4035.53</v>
+        <v>4076.7</v>
       </c>
       <c r="O23" t="n">
-        <v>4088.4</v>
+        <v>4070.2</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2451,13 +2453,11 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2472,57 +2472,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4003.4</v>
+        <v>4002.1</v>
       </c>
       <c r="C24" t="n">
-        <v>4018.9</v>
+        <v>4071.1</v>
       </c>
       <c r="D24" t="n">
-        <v>4002.7</v>
+        <v>3999.7</v>
       </c>
       <c r="E24" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4</v>
+        <v>60.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0152</v>
       </c>
       <c r="H24" t="n">
-        <v>16.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>3911.2</v>
+        <v>3986.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3970.7</v>
+        <v>3993.85</v>
       </c>
       <c r="K24" t="n">
-        <v>3986.2</v>
+        <v>4002.2</v>
       </c>
       <c r="L24" t="n">
-        <v>4001.7</v>
+        <v>4010.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4039.2</v>
+        <v>4018.4</v>
       </c>
       <c r="N24" t="n">
-        <v>4076.7</v>
+        <v>4026.25</v>
       </c>
       <c r="O24" t="n">
-        <v>4070.2</v>
+        <v>4035.1</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,81 +2530,89 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4002.1</v>
+        <v>4096.2</v>
       </c>
       <c r="C25" t="n">
-        <v>4071.1</v>
+        <v>4152.1</v>
       </c>
       <c r="D25" t="n">
-        <v>3999.7</v>
+        <v>4096.2</v>
       </c>
       <c r="E25" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F25" t="n">
-        <v>60.8</v>
+        <v>75.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0186</v>
       </c>
       <c r="H25" t="n">
-        <v>71.40000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I25" t="n">
-        <v>3986.5</v>
+        <v>3928.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3993.85</v>
+        <v>4017.55</v>
       </c>
       <c r="K25" t="n">
-        <v>4002.2</v>
+        <v>4035.4</v>
       </c>
       <c r="L25" t="n">
-        <v>4010.55</v>
+        <v>4053.25</v>
       </c>
       <c r="M25" t="n">
-        <v>4018.4</v>
+        <v>4106.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4026.25</v>
+        <v>4160.35</v>
       </c>
       <c r="O25" t="n">
-        <v>4035.1</v>
+        <v>4142.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2612,10 +2620,8 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2627,10 +2633,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="inlineStr">
         <is>
@@ -2642,90 +2646,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4096.2</v>
+        <v>4129.9</v>
       </c>
       <c r="C26" t="n">
-        <v>4152.1</v>
+        <v>4130.9</v>
       </c>
       <c r="D26" t="n">
-        <v>4096.2</v>
+        <v>4046.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F26" t="n">
-        <v>75.8</v>
+        <v>-100.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0242</v>
       </c>
       <c r="H26" t="n">
-        <v>55.9</v>
+        <v>84.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3928.3</v>
+        <v>4040.3</v>
       </c>
       <c r="J26" t="n">
-        <v>4017.55</v>
+        <v>4102.37</v>
       </c>
       <c r="K26" t="n">
-        <v>4035.4</v>
+        <v>4118.95</v>
       </c>
       <c r="L26" t="n">
-        <v>4053.25</v>
+        <v>4135.53</v>
       </c>
       <c r="M26" t="n">
-        <v>4106.8</v>
+        <v>4174.85</v>
       </c>
       <c r="N26" t="n">
-        <v>4160.35</v>
+        <v>4214.17</v>
       </c>
       <c r="O26" t="n">
-        <v>4142.5</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4208</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2733,69 +2735,63 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4129.9</v>
+        <v>4067.6</v>
       </c>
       <c r="C27" t="n">
-        <v>4130.9</v>
+        <v>4068</v>
       </c>
       <c r="D27" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="E27" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-100.3</v>
+        <v>21</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0052</v>
       </c>
       <c r="H27" t="n">
-        <v>84.3</v>
+        <v>0.4</v>
       </c>
       <c r="I27" t="n">
-        <v>4040.3</v>
+        <v>3962.3</v>
       </c>
       <c r="J27" t="n">
-        <v>4102.37</v>
+        <v>3941.23</v>
       </c>
       <c r="K27" t="n">
-        <v>4118.95</v>
+        <v>4004.45</v>
       </c>
       <c r="L27" t="n">
-        <v>4135.53</v>
+        <v>4067.68</v>
       </c>
       <c r="M27" t="n">
-        <v>4174.85</v>
+        <v>4088.75</v>
       </c>
       <c r="N27" t="n">
-        <v>4214.17</v>
+        <v>4109.82</v>
       </c>
       <c r="O27" t="n">
-        <v>4208</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4215.2</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2812,55 +2808,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4067.6</v>
+        <v>4090.1</v>
       </c>
       <c r="C28" t="n">
-        <v>4068</v>
+        <v>4107.9</v>
       </c>
       <c r="D28" t="n">
-        <v>4067.6</v>
+        <v>4072.7</v>
       </c>
       <c r="E28" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F28" t="n">
-        <v>21</v>
+        <v>6.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4</v>
+        <v>35.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3962.3</v>
+        <v>4067.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3941.23</v>
+        <v>4067.1</v>
       </c>
       <c r="K28" t="n">
-        <v>4004.45</v>
+        <v>4067.4</v>
       </c>
       <c r="L28" t="n">
-        <v>4067.68</v>
+        <v>4067.7</v>
       </c>
       <c r="M28" t="n">
-        <v>4088.75</v>
+        <v>4067.8</v>
       </c>
       <c r="N28" t="n">
-        <v>4109.82</v>
+        <v>4067.9</v>
       </c>
       <c r="O28" t="n">
-        <v>4215.2</v>
+        <v>4068.4</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,167 +2871,171 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4090.1</v>
+        <v>4025.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4107.9</v>
+        <v>4036.3</v>
       </c>
       <c r="D29" t="n">
-        <v>4072.7</v>
+        <v>4025.7</v>
       </c>
       <c r="E29" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F29" t="n">
-        <v>6.9</v>
+        <v>-38.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0094</v>
       </c>
       <c r="H29" t="n">
-        <v>35.2</v>
+        <v>10.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4067.2</v>
+        <v>4037.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4067.1</v>
+        <v>4031.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4067.4</v>
+        <v>4056.9</v>
       </c>
       <c r="L29" t="n">
-        <v>4067.7</v>
+        <v>4082.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4067.8</v>
+        <v>4092.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4067.9</v>
+        <v>4101.8</v>
       </c>
       <c r="O29" t="n">
-        <v>4068.4</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
+        <v>4143.1</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4025.7</v>
+        <v>4018.1</v>
       </c>
       <c r="C30" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="D30" t="n">
-        <v>4025.7</v>
+        <v>4017.9</v>
       </c>
       <c r="E30" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-38.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0004</v>
       </c>
       <c r="H30" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
       </c>
       <c r="I30" t="n">
-        <v>4037.5</v>
+        <v>4015.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4031.4</v>
+        <v>4028.35</v>
       </c>
       <c r="K30" t="n">
-        <v>4056.9</v>
+        <v>4031</v>
       </c>
       <c r="L30" t="n">
-        <v>4082.4</v>
+        <v>4033.65</v>
       </c>
       <c r="M30" t="n">
-        <v>4092.1</v>
+        <v>4041.6</v>
       </c>
       <c r="N30" t="n">
-        <v>4101.8</v>
+        <v>4049.55</v>
       </c>
       <c r="O30" t="n">
-        <v>4143.1</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4046.9</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
@@ -3043,9 +3047,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3071,237 +3075,233 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4018.1</v>
+        <v>4060.7</v>
       </c>
       <c r="C31" t="n">
-        <v>4034.7</v>
+        <v>4118.5</v>
       </c>
       <c r="D31" t="n">
-        <v>4017.9</v>
+        <v>4028.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0162</v>
       </c>
       <c r="H31" t="n">
-        <v>16.8</v>
+        <v>90</v>
       </c>
       <c r="I31" t="n">
-        <v>4015.1</v>
+        <v>4001.1</v>
       </c>
       <c r="J31" t="n">
-        <v>4028.35</v>
+        <v>4022.1</v>
       </c>
       <c r="K31" t="n">
-        <v>4031</v>
+        <v>4026.3</v>
       </c>
       <c r="L31" t="n">
-        <v>4033.65</v>
+        <v>4030.5</v>
       </c>
       <c r="M31" t="n">
-        <v>4041.6</v>
+        <v>4043.1</v>
       </c>
       <c r="N31" t="n">
-        <v>4049.55</v>
+        <v>4055.7</v>
       </c>
       <c r="O31" t="n">
-        <v>4046.9</v>
+        <v>4051.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4060.7</v>
+        <v>4102.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4118.5</v>
+        <v>4102.4</v>
       </c>
       <c r="D32" t="n">
-        <v>4028.5</v>
+        <v>4022.4</v>
       </c>
       <c r="E32" t="n">
-        <v>4100.1</v>
+        <v>4049.1</v>
       </c>
       <c r="F32" t="n">
-        <v>65.40000000000001</v>
+        <v>-51</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0162</v>
+        <v>-0.0124</v>
       </c>
       <c r="H32" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I32" t="n">
-        <v>4001.1</v>
+        <v>3938.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4022.1</v>
+        <v>4023.4</v>
       </c>
       <c r="K32" t="n">
-        <v>4026.3</v>
+        <v>4055.1</v>
       </c>
       <c r="L32" t="n">
-        <v>4030.5</v>
+        <v>4086.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4043.1</v>
+        <v>4145.1</v>
       </c>
       <c r="N32" t="n">
-        <v>4055.7</v>
+        <v>4203.4</v>
       </c>
       <c r="O32" t="n">
-        <v>4051.5</v>
+        <v>4208.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4102.4</v>
+        <v>4083.4</v>
       </c>
       <c r="C33" t="n">
-        <v>4102.4</v>
+        <v>4083.5</v>
       </c>
       <c r="D33" t="n">
-        <v>4022.4</v>
+        <v>4026.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4049.1</v>
+        <v>4033.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-51</v>
+        <v>-15.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0038</v>
       </c>
       <c r="H33" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="I33" t="n">
-        <v>3938.5</v>
+        <v>3942.4</v>
       </c>
       <c r="J33" t="n">
-        <v>4023.4</v>
+        <v>3962.45</v>
       </c>
       <c r="K33" t="n">
-        <v>4055.1</v>
+        <v>4009.1</v>
       </c>
       <c r="L33" t="n">
-        <v>4086.8</v>
+        <v>4055.75</v>
       </c>
       <c r="M33" t="n">
-        <v>4145.1</v>
+        <v>4089.1</v>
       </c>
       <c r="N33" t="n">
-        <v>4203.4</v>
+        <v>4122.45</v>
       </c>
       <c r="O33" t="n">
-        <v>4208.5</v>
+        <v>4182.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3320,57 +3320,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4083.4</v>
+        <v>4050.5</v>
       </c>
       <c r="C34" t="n">
-        <v>4083.5</v>
+        <v>4095.4</v>
       </c>
       <c r="D34" t="n">
-        <v>4026.5</v>
+        <v>4048.8</v>
       </c>
       <c r="E34" t="n">
-        <v>4033.7</v>
+        <v>4095.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-15.4</v>
+        <v>61.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.0153</v>
       </c>
       <c r="H34" t="n">
-        <v>57</v>
+        <v>46.6</v>
       </c>
       <c r="I34" t="n">
-        <v>3942.4</v>
+        <v>3969.5</v>
       </c>
       <c r="J34" t="n">
-        <v>3962.45</v>
+        <v>3966.05</v>
       </c>
       <c r="K34" t="n">
-        <v>4009.1</v>
+        <v>4005.2</v>
       </c>
       <c r="L34" t="n">
-        <v>4055.75</v>
+        <v>4044.35</v>
       </c>
       <c r="M34" t="n">
-        <v>4089.1</v>
+        <v>4062.2</v>
       </c>
       <c r="N34" t="n">
-        <v>4122.45</v>
+        <v>4080.05</v>
       </c>
       <c r="O34" t="n">
-        <v>4182.4</v>
+        <v>4140.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3381,16 +3381,20 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3400,59 +3404,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4050.5</v>
+        <v>4130</v>
       </c>
       <c r="C35" t="n">
-        <v>4095.4</v>
+        <v>4262.2</v>
       </c>
       <c r="D35" t="n">
-        <v>4048.8</v>
+        <v>4129.5</v>
       </c>
       <c r="E35" t="n">
-        <v>4095.4</v>
+        <v>4245.8</v>
       </c>
       <c r="F35" t="n">
-        <v>61.7</v>
+        <v>150.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0367</v>
       </c>
       <c r="H35" t="n">
-        <v>46.6</v>
+        <v>132.7</v>
       </c>
       <c r="I35" t="n">
-        <v>3969.5</v>
+        <v>4002.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3966.05</v>
+        <v>4060.45</v>
       </c>
       <c r="K35" t="n">
-        <v>4005.2</v>
+        <v>4072.1</v>
       </c>
       <c r="L35" t="n">
-        <v>4044.35</v>
+        <v>4083.75</v>
       </c>
       <c r="M35" t="n">
-        <v>4062.2</v>
+        <v>4118.7</v>
       </c>
       <c r="N35" t="n">
-        <v>4080.05</v>
+        <v>4153.65</v>
       </c>
       <c r="O35" t="n">
-        <v>4140.5</v>
+        <v>4142</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3478,8 +3478,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3491,50 +3493,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4130</v>
+        <v>4297</v>
       </c>
       <c r="C36" t="n">
-        <v>4262.2</v>
+        <v>4297</v>
       </c>
       <c r="D36" t="n">
-        <v>4129.5</v>
+        <v>4228</v>
       </c>
       <c r="E36" t="n">
-        <v>4245.8</v>
+        <v>4242</v>
       </c>
       <c r="F36" t="n">
-        <v>150.4</v>
+        <v>-3.8</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0009</v>
       </c>
       <c r="H36" t="n">
-        <v>132.7</v>
+        <v>69</v>
       </c>
       <c r="I36" t="n">
-        <v>4002.2</v>
+        <v>3996.8</v>
       </c>
       <c r="J36" t="n">
-        <v>4060.45</v>
+        <v>4138.07</v>
       </c>
       <c r="K36" t="n">
-        <v>4072.1</v>
+        <v>4179.45</v>
       </c>
       <c r="L36" t="n">
-        <v>4083.75</v>
+        <v>4220.82</v>
       </c>
       <c r="M36" t="n">
-        <v>4118.7</v>
+        <v>4312.15</v>
       </c>
       <c r="N36" t="n">
-        <v>4153.65</v>
+        <v>4403.47</v>
       </c>
       <c r="O36" t="n">
-        <v>4142</v>
+        <v>4394.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,78 +3549,76 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4297</v>
+        <v>4277</v>
       </c>
       <c r="C37" t="n">
-        <v>4297</v>
+        <v>4371.5</v>
       </c>
       <c r="D37" t="n">
-        <v>4228</v>
+        <v>4274</v>
       </c>
       <c r="E37" t="n">
-        <v>4242</v>
+        <v>4340.7</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.8</v>
+        <v>98.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0233</v>
       </c>
       <c r="H37" t="n">
-        <v>69</v>
+        <v>97.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3996.8</v>
+        <v>4159</v>
       </c>
       <c r="J37" t="n">
-        <v>4138.07</v>
+        <v>4162.75</v>
       </c>
       <c r="K37" t="n">
-        <v>4179.45</v>
+        <v>4207.5</v>
       </c>
       <c r="L37" t="n">
-        <v>4220.82</v>
+        <v>4252.25</v>
       </c>
       <c r="M37" t="n">
-        <v>4312.15</v>
+        <v>4276.5</v>
       </c>
       <c r="N37" t="n">
-        <v>4403.47</v>
+        <v>4300.75</v>
       </c>
       <c r="O37" t="n">
-        <v>4394.9</v>
+        <v>4366</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3631,76 +3631,78 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4277</v>
+        <v>4336.1</v>
       </c>
       <c r="C38" t="n">
-        <v>4371.5</v>
+        <v>4390.1</v>
       </c>
       <c r="D38" t="n">
-        <v>4274</v>
+        <v>4336.1</v>
       </c>
       <c r="E38" t="n">
-        <v>4340.7</v>
+        <v>4361.8</v>
       </c>
       <c r="F38" t="n">
-        <v>98.7</v>
+        <v>21.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0049</v>
       </c>
       <c r="H38" t="n">
-        <v>97.5</v>
+        <v>54</v>
       </c>
       <c r="I38" t="n">
-        <v>4159</v>
+        <v>4176.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4162.75</v>
+        <v>4252.18</v>
       </c>
       <c r="K38" t="n">
-        <v>4207.5</v>
+        <v>4291.95</v>
       </c>
       <c r="L38" t="n">
-        <v>4252.25</v>
+        <v>4331.73</v>
       </c>
       <c r="M38" t="n">
-        <v>4276.5</v>
+        <v>4389.45</v>
       </c>
       <c r="N38" t="n">
-        <v>4300.75</v>
+        <v>4447.18</v>
       </c>
       <c r="O38" t="n">
-        <v>4366</v>
+        <v>4469</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3718,18 +3720,14 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3741,50 +3739,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4336.1</v>
+        <v>4408.6</v>
       </c>
       <c r="C39" t="n">
-        <v>4390.1</v>
+        <v>4408.6</v>
       </c>
       <c r="D39" t="n">
-        <v>4336.1</v>
+        <v>4365.1</v>
       </c>
       <c r="E39" t="n">
-        <v>4361.8</v>
+        <v>4383</v>
       </c>
       <c r="F39" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>0.0049</v>
       </c>
       <c r="H39" t="n">
-        <v>54</v>
+        <v>43.5</v>
       </c>
       <c r="I39" t="n">
-        <v>4176.5</v>
+        <v>4282.1</v>
       </c>
       <c r="J39" t="n">
-        <v>4252.18</v>
+        <v>4307.15</v>
       </c>
       <c r="K39" t="n">
-        <v>4291.95</v>
+        <v>4334.8</v>
       </c>
       <c r="L39" t="n">
-        <v>4331.73</v>
+        <v>4362.45</v>
       </c>
       <c r="M39" t="n">
-        <v>4389.45</v>
+        <v>4388.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4447.18</v>
+        <v>4415.15</v>
       </c>
       <c r="O39" t="n">
-        <v>4469</v>
+        <v>4444.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3821,50 +3819,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4408.6</v>
+        <v>4406.5</v>
       </c>
       <c r="C40" t="n">
-        <v>4408.6</v>
+        <v>4434</v>
       </c>
       <c r="D40" t="n">
-        <v>4365.1</v>
+        <v>4406.3</v>
       </c>
       <c r="E40" t="n">
-        <v>4383</v>
+        <v>4408.9</v>
       </c>
       <c r="F40" t="n">
-        <v>21.2</v>
+        <v>25.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>43.5</v>
+        <v>27.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4282.1</v>
+        <v>4321.6</v>
       </c>
       <c r="J40" t="n">
-        <v>4307.15</v>
+        <v>4337.57</v>
       </c>
       <c r="K40" t="n">
-        <v>4334.8</v>
+        <v>4361.25</v>
       </c>
       <c r="L40" t="n">
-        <v>4362.45</v>
+        <v>4384.93</v>
       </c>
       <c r="M40" t="n">
-        <v>4388.8</v>
+        <v>4404.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4415.15</v>
+        <v>4424.57</v>
       </c>
       <c r="O40" t="n">
-        <v>4444.1</v>
+        <v>4452.1</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3885,8 +3883,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3901,68 +3901,74 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4406.5</v>
+        <v>4403.5</v>
       </c>
       <c r="C41" t="n">
-        <v>4434</v>
+        <v>4445</v>
       </c>
       <c r="D41" t="n">
-        <v>4406.3</v>
+        <v>4350</v>
       </c>
       <c r="E41" t="n">
-        <v>4408.9</v>
+        <v>4363.6</v>
       </c>
       <c r="F41" t="n">
-        <v>25.9</v>
+        <v>-45.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0103</v>
       </c>
       <c r="H41" t="n">
-        <v>27.7</v>
+        <v>95</v>
       </c>
       <c r="I41" t="n">
-        <v>4321.6</v>
+        <v>4378.6</v>
       </c>
       <c r="J41" t="n">
-        <v>4337.57</v>
+        <v>4375.57</v>
       </c>
       <c r="K41" t="n">
-        <v>4361.25</v>
+        <v>4395.05</v>
       </c>
       <c r="L41" t="n">
-        <v>4384.93</v>
+        <v>4414.52</v>
       </c>
       <c r="M41" t="n">
-        <v>4404.75</v>
+        <v>4422.75</v>
       </c>
       <c r="N41" t="n">
-        <v>4424.57</v>
+        <v>4430.98</v>
       </c>
       <c r="O41" t="n">
-        <v>4452.1</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>4461.7</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="inlineStr">
@@ -3973,70 +3979,70 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4403.5</v>
+        <v>4322.1</v>
       </c>
       <c r="C42" t="n">
-        <v>4445</v>
+        <v>4397.1</v>
       </c>
       <c r="D42" t="n">
-        <v>4350</v>
+        <v>4315</v>
       </c>
       <c r="E42" t="n">
-        <v>4363.6</v>
+        <v>4380.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-45.3</v>
+        <v>16.8</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0038</v>
       </c>
       <c r="H42" t="n">
-        <v>95</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>4378.6</v>
+        <v>4255</v>
       </c>
       <c r="J42" t="n">
-        <v>4375.57</v>
+        <v>4251.65</v>
       </c>
       <c r="K42" t="n">
-        <v>4395.05</v>
+        <v>4316.1</v>
       </c>
       <c r="L42" t="n">
-        <v>4414.52</v>
+        <v>4380.55</v>
       </c>
       <c r="M42" t="n">
-        <v>4422.75</v>
+        <v>4411.1</v>
       </c>
       <c r="N42" t="n">
-        <v>4430.98</v>
+        <v>4441.65</v>
       </c>
       <c r="O42" t="n">
-        <v>4461.7</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4540</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4045,18 +4051,14 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4075,50 +4077,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4322.1</v>
+        <v>4394.8</v>
       </c>
       <c r="C43" t="n">
-        <v>4397.1</v>
+        <v>4428.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4315</v>
+        <v>4386.5</v>
       </c>
       <c r="E43" t="n">
-        <v>4380.4</v>
+        <v>4417.8</v>
       </c>
       <c r="F43" t="n">
-        <v>16.8</v>
+        <v>37.4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>82.09999999999999</v>
+        <v>42</v>
       </c>
       <c r="I43" t="n">
-        <v>4255</v>
+        <v>4232.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4251.65</v>
+        <v>4310.47</v>
       </c>
       <c r="K43" t="n">
-        <v>4316.1</v>
+        <v>4339.35</v>
       </c>
       <c r="L43" t="n">
-        <v>4380.55</v>
+        <v>4368.22</v>
       </c>
       <c r="M43" t="n">
-        <v>4411.1</v>
+        <v>4421.45</v>
       </c>
       <c r="N43" t="n">
-        <v>4441.65</v>
+        <v>4474.67</v>
       </c>
       <c r="O43" t="n">
-        <v>4540</v>
+        <v>4479.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4126,18 +4128,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4152,77 +4154,81 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4394.8</v>
+        <v>4415.2</v>
       </c>
       <c r="C44" t="n">
-        <v>4428.5</v>
+        <v>4434.1</v>
       </c>
       <c r="D44" t="n">
-        <v>4386.5</v>
+        <v>4330.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4417.8</v>
+        <v>4366</v>
       </c>
       <c r="F44" t="n">
-        <v>37.4</v>
+        <v>-51.8</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0117</v>
       </c>
       <c r="H44" t="n">
-        <v>42</v>
+        <v>103.4</v>
       </c>
       <c r="I44" t="n">
-        <v>4232.9</v>
+        <v>4344.5</v>
       </c>
       <c r="J44" t="n">
-        <v>4310.47</v>
+        <v>4380.95</v>
       </c>
       <c r="K44" t="n">
-        <v>4339.35</v>
+        <v>4396.8</v>
       </c>
       <c r="L44" t="n">
-        <v>4368.22</v>
+        <v>4412.65</v>
       </c>
       <c r="M44" t="n">
-        <v>4421.45</v>
+        <v>4438.8</v>
       </c>
       <c r="N44" t="n">
-        <v>4474.67</v>
+        <v>4464.95</v>
       </c>
       <c r="O44" t="n">
-        <v>4479.2</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+        <v>4470.5</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4236,90 +4242,88 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4415.2</v>
+        <v>4339.8</v>
       </c>
       <c r="C45" t="n">
-        <v>4434.1</v>
+        <v>4524.1</v>
       </c>
       <c r="D45" t="n">
-        <v>4330.7</v>
+        <v>4327.6</v>
       </c>
       <c r="E45" t="n">
-        <v>4366</v>
+        <v>4489.4</v>
       </c>
       <c r="F45" t="n">
-        <v>-51.8</v>
+        <v>123.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0283</v>
       </c>
       <c r="H45" t="n">
-        <v>103.4</v>
+        <v>196.5</v>
       </c>
       <c r="I45" t="n">
-        <v>4344.5</v>
+        <v>4227.3</v>
       </c>
       <c r="J45" t="n">
-        <v>4380.95</v>
+        <v>4254.4</v>
       </c>
       <c r="K45" t="n">
-        <v>4396.8</v>
+        <v>4314.3</v>
       </c>
       <c r="L45" t="n">
-        <v>4412.65</v>
+        <v>4374.2</v>
       </c>
       <c r="M45" t="n">
-        <v>4438.8</v>
+        <v>4417.7</v>
       </c>
       <c r="N45" t="n">
-        <v>4464.95</v>
+        <v>4461.2</v>
       </c>
       <c r="O45" t="n">
-        <v>4470.5</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>4537.5</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
@@ -4331,50 +4335,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4339.8</v>
+        <v>4506.8</v>
       </c>
       <c r="C46" t="n">
-        <v>4524.1</v>
+        <v>4530</v>
       </c>
       <c r="D46" t="n">
-        <v>4327.6</v>
+        <v>4486</v>
       </c>
       <c r="E46" t="n">
-        <v>4489.4</v>
+        <v>4516.3</v>
       </c>
       <c r="F46" t="n">
-        <v>123.4</v>
+        <v>26.9</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.006</v>
       </c>
       <c r="H46" t="n">
-        <v>196.5</v>
+        <v>44</v>
       </c>
       <c r="I46" t="n">
-        <v>4227.3</v>
+        <v>4131.1</v>
       </c>
       <c r="J46" t="n">
-        <v>4254.4</v>
+        <v>4324.67</v>
       </c>
       <c r="K46" t="n">
-        <v>4314.3</v>
+        <v>4391.15</v>
       </c>
       <c r="L46" t="n">
-        <v>4374.2</v>
+        <v>4457.62</v>
       </c>
       <c r="M46" t="n">
-        <v>4417.7</v>
+        <v>4587.65</v>
       </c>
       <c r="N46" t="n">
-        <v>4461.2</v>
+        <v>4717.67</v>
       </c>
       <c r="O46" t="n">
-        <v>4537.5</v>
+        <v>4720.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4387,18 +4391,14 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4408,59 +4408,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4506.8</v>
+        <v>4560</v>
       </c>
       <c r="C47" t="n">
-        <v>4530</v>
+        <v>4624.1</v>
       </c>
       <c r="D47" t="n">
-        <v>4486</v>
+        <v>4560</v>
       </c>
       <c r="E47" t="n">
-        <v>4516.3</v>
+        <v>4624.1</v>
       </c>
       <c r="F47" t="n">
-        <v>26.9</v>
+        <v>107.8</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0239</v>
       </c>
       <c r="H47" t="n">
-        <v>44</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>4131.1</v>
+        <v>4442</v>
       </c>
       <c r="J47" t="n">
-        <v>4324.67</v>
+        <v>4476.45</v>
       </c>
       <c r="K47" t="n">
-        <v>4391.15</v>
+        <v>4494.3</v>
       </c>
       <c r="L47" t="n">
-        <v>4457.62</v>
+        <v>4512.15</v>
       </c>
       <c r="M47" t="n">
-        <v>4587.65</v>
+        <v>4538.3</v>
       </c>
       <c r="N47" t="n">
-        <v>4717.67</v>
+        <v>4564.45</v>
       </c>
       <c r="O47" t="n">
-        <v>4720.6</v>
+        <v>4574</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4473,17 +4469,23 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4495,50 +4497,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4560</v>
+        <v>4638</v>
       </c>
       <c r="C48" t="n">
-        <v>4624.1</v>
+        <v>4670.9</v>
       </c>
       <c r="D48" t="n">
-        <v>4560</v>
+        <v>4635.1</v>
       </c>
       <c r="E48" t="n">
-        <v>4624.1</v>
+        <v>4640.8</v>
       </c>
       <c r="F48" t="n">
-        <v>107.8</v>
+        <v>16.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0036</v>
       </c>
       <c r="H48" t="n">
-        <v>64.09999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4442</v>
+        <v>4495.9</v>
       </c>
       <c r="J48" t="n">
-        <v>4476.45</v>
+        <v>4576.03</v>
       </c>
       <c r="K48" t="n">
-        <v>4494.3</v>
+        <v>4592.05</v>
       </c>
       <c r="L48" t="n">
-        <v>4512.15</v>
+        <v>4608.08</v>
       </c>
       <c r="M48" t="n">
-        <v>4538.3</v>
+        <v>4656.15</v>
       </c>
       <c r="N48" t="n">
-        <v>4564.45</v>
+        <v>4704.23</v>
       </c>
       <c r="O48" t="n">
-        <v>4574</v>
+        <v>4688.2</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4556,18 +4558,14 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4579,50 +4577,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4638</v>
+        <v>4630.5</v>
       </c>
       <c r="C49" t="n">
-        <v>4670.9</v>
+        <v>4638.1</v>
       </c>
       <c r="D49" t="n">
-        <v>4635.1</v>
+        <v>4626.2</v>
       </c>
       <c r="E49" t="n">
-        <v>4640.8</v>
+        <v>4638.1</v>
       </c>
       <c r="F49" t="n">
-        <v>16.7</v>
+        <v>-2.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>35.8</v>
+        <v>11.9</v>
       </c>
       <c r="I49" t="n">
-        <v>4495.9</v>
+        <v>4599.3</v>
       </c>
       <c r="J49" t="n">
-        <v>4576.03</v>
+        <v>4598.9</v>
       </c>
       <c r="K49" t="n">
-        <v>4592.05</v>
+        <v>4622.9</v>
       </c>
       <c r="L49" t="n">
-        <v>4608.08</v>
+        <v>4646.9</v>
       </c>
       <c r="M49" t="n">
-        <v>4656.15</v>
+        <v>4658.7</v>
       </c>
       <c r="N49" t="n">
-        <v>4704.23</v>
+        <v>4670.5</v>
       </c>
       <c r="O49" t="n">
-        <v>4688.2</v>
+        <v>4706.7</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,15 +4631,13 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4654,68 +4650,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4630.5</v>
+        <v>4615.3</v>
       </c>
       <c r="C50" t="n">
-        <v>4638.1</v>
+        <v>4615.3</v>
       </c>
       <c r="D50" t="n">
-        <v>4626.2</v>
+        <v>4598.2</v>
       </c>
       <c r="E50" t="n">
-        <v>4638.1</v>
+        <v>4598.2</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.7</v>
+        <v>-39.9</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0086</v>
       </c>
       <c r="H50" t="n">
-        <v>11.9</v>
+        <v>17.1</v>
       </c>
       <c r="I50" t="n">
-        <v>4599.3</v>
+        <v>4614.3</v>
       </c>
       <c r="J50" t="n">
-        <v>4598.9</v>
+        <v>4629.18</v>
       </c>
       <c r="K50" t="n">
-        <v>4622.9</v>
+        <v>4632.15</v>
       </c>
       <c r="L50" t="n">
-        <v>4646.9</v>
+        <v>4635.13</v>
       </c>
       <c r="M50" t="n">
-        <v>4658.7</v>
+        <v>4644.05</v>
       </c>
       <c r="N50" t="n">
-        <v>4670.5</v>
+        <v>4652.97</v>
       </c>
       <c r="O50" t="n">
-        <v>4706.7</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>4650</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4727,91 +4733,85 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4615.3</v>
+        <v>4609.7</v>
       </c>
       <c r="C51" t="n">
-        <v>4615.3</v>
+        <v>4609.7</v>
       </c>
       <c r="D51" t="n">
-        <v>4598.2</v>
+        <v>4609.7</v>
       </c>
       <c r="E51" t="n">
-        <v>4598.2</v>
+        <v>4609.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-39.9</v>
+        <v>11.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0025</v>
       </c>
       <c r="H51" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>4614.3</v>
+        <v>4581.1</v>
       </c>
       <c r="J51" t="n">
-        <v>4629.18</v>
+        <v>4576.83</v>
       </c>
       <c r="K51" t="n">
-        <v>4632.15</v>
+        <v>4589.65</v>
       </c>
       <c r="L51" t="n">
-        <v>4635.13</v>
+        <v>4602.48</v>
       </c>
       <c r="M51" t="n">
-        <v>4644.05</v>
+        <v>4606.75</v>
       </c>
       <c r="N51" t="n">
-        <v>4652.97</v>
+        <v>4611.02</v>
       </c>
       <c r="O51" t="n">
-        <v>4650</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>4632.4</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4820,68 +4820,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
+        <v>4599.3</v>
+      </c>
+      <c r="C52" t="n">
+        <v>4625.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>4451.8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>4478.1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-131.6</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0285</v>
+      </c>
+      <c r="H52" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="I52" t="n">
         <v>4609.7</v>
       </c>
-      <c r="C52" t="n">
+      <c r="J52" t="n">
         <v>4609.7</v>
       </c>
-      <c r="D52" t="n">
+      <c r="K52" t="n">
         <v>4609.7</v>
       </c>
-      <c r="E52" t="n">
+      <c r="L52" t="n">
         <v>4609.7</v>
       </c>
-      <c r="F52" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>4581.1</v>
-      </c>
-      <c r="J52" t="n">
-        <v>4576.83</v>
-      </c>
-      <c r="K52" t="n">
-        <v>4589.65</v>
-      </c>
-      <c r="L52" t="n">
-        <v>4602.48</v>
-      </c>
       <c r="M52" t="n">
-        <v>4606.75</v>
+        <v>4609.7</v>
       </c>
       <c r="N52" t="n">
-        <v>4611.02</v>
+        <v>4609.7</v>
       </c>
       <c r="O52" t="n">
-        <v>4632.4</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>4609.7</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4891,11 +4901,13 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4904,161 +4916,151 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4599.3</v>
+        <v>4430</v>
       </c>
       <c r="C53" t="n">
-        <v>4625.5</v>
+        <v>4466.9</v>
       </c>
       <c r="D53" t="n">
-        <v>4451.8</v>
+        <v>4410.9</v>
       </c>
       <c r="E53" t="n">
-        <v>4478.1</v>
+        <v>4431.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-131.6</v>
+        <v>-47</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0105</v>
       </c>
       <c r="H53" t="n">
-        <v>173.7</v>
+        <v>56</v>
       </c>
       <c r="I53" t="n">
-        <v>4609.7</v>
+        <v>4278.1</v>
       </c>
       <c r="J53" t="n">
-        <v>4609.7</v>
+        <v>4274.12</v>
       </c>
       <c r="K53" t="n">
-        <v>4609.7</v>
+        <v>4391.25</v>
       </c>
       <c r="L53" t="n">
-        <v>4609.7</v>
+        <v>4508.38</v>
       </c>
       <c r="M53" t="n">
-        <v>4609.7</v>
+        <v>4564.95</v>
       </c>
       <c r="N53" t="n">
-        <v>4609.7</v>
+        <v>4621.53</v>
       </c>
       <c r="O53" t="n">
-        <v>4609.7</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
+        <v>4799.2</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4430</v>
+        <v>4402</v>
       </c>
       <c r="C54" t="n">
-        <v>4466.9</v>
+        <v>4402</v>
       </c>
       <c r="D54" t="n">
-        <v>4410.9</v>
+        <v>4329.1</v>
       </c>
       <c r="E54" t="n">
-        <v>4431.1</v>
+        <v>4348</v>
       </c>
       <c r="F54" t="n">
-        <v>-47</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.0188</v>
       </c>
       <c r="H54" t="n">
-        <v>56</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>4278.1</v>
+        <v>4354.9</v>
       </c>
       <c r="J54" t="n">
-        <v>4274.12</v>
+        <v>4371.2</v>
       </c>
       <c r="K54" t="n">
-        <v>4391.25</v>
+        <v>4403.1</v>
       </c>
       <c r="L54" t="n">
-        <v>4508.38</v>
+        <v>4435</v>
       </c>
       <c r="M54" t="n">
-        <v>4564.95</v>
+        <v>4459.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4621.53</v>
+        <v>4483.2</v>
       </c>
       <c r="O54" t="n">
-        <v>4799.2</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>4522.9</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5085,73 +5087,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4402</v>
+        <v>4328</v>
       </c>
       <c r="C55" t="n">
-        <v>4402</v>
+        <v>4390.2</v>
       </c>
       <c r="D55" t="n">
-        <v>4329.1</v>
+        <v>4292.2</v>
       </c>
       <c r="E55" t="n">
-        <v>4348</v>
+        <v>4366.3</v>
       </c>
       <c r="F55" t="n">
-        <v>-83.09999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0188</v>
+        <v>0.0042</v>
       </c>
       <c r="H55" t="n">
-        <v>72.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="I55" t="n">
-        <v>4354.9</v>
+        <v>4256.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4371.2</v>
+        <v>4266.33</v>
       </c>
       <c r="K55" t="n">
-        <v>4403.1</v>
+        <v>4311.55</v>
       </c>
       <c r="L55" t="n">
-        <v>4435</v>
+        <v>4356.78</v>
       </c>
       <c r="M55" t="n">
-        <v>4459.1</v>
+        <v>4384.45</v>
       </c>
       <c r="N55" t="n">
-        <v>4483.2</v>
+        <v>4412.12</v>
       </c>
       <c r="O55" t="n">
-        <v>4522.9</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4474.9</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5164,55 +5164,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4328</v>
+        <v>4426.3</v>
       </c>
       <c r="C56" t="n">
-        <v>4390.2</v>
+        <v>4510</v>
       </c>
       <c r="D56" t="n">
-        <v>4292.2</v>
+        <v>4426</v>
       </c>
       <c r="E56" t="n">
-        <v>4366.3</v>
+        <v>4491.7</v>
       </c>
       <c r="F56" t="n">
-        <v>18.3</v>
+        <v>125.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0287</v>
       </c>
       <c r="H56" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I56" t="n">
-        <v>4256.2</v>
+        <v>4194.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4266.33</v>
+        <v>4280.85</v>
       </c>
       <c r="K56" t="n">
-        <v>4311.55</v>
+        <v>4317.3</v>
       </c>
       <c r="L56" t="n">
-        <v>4356.78</v>
+        <v>4353.75</v>
       </c>
       <c r="M56" t="n">
-        <v>4384.45</v>
+        <v>4415.3</v>
       </c>
       <c r="N56" t="n">
-        <v>4412.12</v>
+        <v>4476.85</v>
       </c>
       <c r="O56" t="n">
-        <v>4474.9</v>
+        <v>4488.2</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5220,14 +5224,12 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5235,161 +5237,165 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4426.3</v>
+        <v>4429.8</v>
       </c>
       <c r="C57" t="n">
-        <v>4510</v>
+        <v>4429.8</v>
       </c>
       <c r="D57" t="n">
-        <v>4426</v>
+        <v>4429.8</v>
       </c>
       <c r="E57" t="n">
-        <v>4491.7</v>
+        <v>4429.8</v>
       </c>
       <c r="F57" t="n">
-        <v>125.4</v>
+        <v>-61.9</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0287</v>
+        <v>-0.0138</v>
       </c>
       <c r="H57" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>4194.2</v>
+        <v>4342</v>
       </c>
       <c r="J57" t="n">
-        <v>4280.85</v>
+        <v>4419.55</v>
       </c>
       <c r="K57" t="n">
-        <v>4317.3</v>
+        <v>4449.7</v>
       </c>
       <c r="L57" t="n">
-        <v>4353.75</v>
+        <v>4479.85</v>
       </c>
       <c r="M57" t="n">
-        <v>4415.3</v>
+        <v>4533.7</v>
       </c>
       <c r="N57" t="n">
-        <v>4476.85</v>
+        <v>4587.55</v>
       </c>
       <c r="O57" t="n">
-        <v>4488.2</v>
+        <v>4594</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
+        <v>4391.9</v>
+      </c>
+      <c r="C58" t="n">
+        <v>4406.1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>4384.4</v>
+      </c>
+      <c r="E58" t="n">
+        <v>4393.9</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="H58" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I58" t="n">
         <v>4429.8</v>
       </c>
-      <c r="C58" t="n">
+      <c r="J58" t="n">
         <v>4429.8</v>
       </c>
-      <c r="D58" t="n">
+      <c r="K58" t="n">
         <v>4429.8</v>
       </c>
-      <c r="E58" t="n">
+      <c r="L58" t="n">
         <v>4429.8</v>
       </c>
-      <c r="F58" t="n">
-        <v>-61.9</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0138</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>4342</v>
-      </c>
-      <c r="J58" t="n">
-        <v>4419.55</v>
-      </c>
-      <c r="K58" t="n">
-        <v>4449.7</v>
-      </c>
-      <c r="L58" t="n">
-        <v>4479.85</v>
-      </c>
       <c r="M58" t="n">
-        <v>4533.7</v>
+        <v>4429.8</v>
       </c>
       <c r="N58" t="n">
-        <v>4587.55</v>
+        <v>4429.8</v>
       </c>
       <c r="O58" t="n">
-        <v>4594</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>4429.8</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5411,97 +5417,91 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4391.9</v>
+        <v>4398.7</v>
       </c>
       <c r="C59" t="n">
-        <v>4406.1</v>
+        <v>4416</v>
       </c>
       <c r="D59" t="n">
-        <v>4384.4</v>
+        <v>4397.4</v>
       </c>
       <c r="E59" t="n">
-        <v>4393.9</v>
+        <v>4416</v>
       </c>
       <c r="F59" t="n">
-        <v>-35.9</v>
+        <v>22.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.005</v>
       </c>
       <c r="H59" t="n">
-        <v>21.7</v>
+        <v>18.6</v>
       </c>
       <c r="I59" t="n">
-        <v>4429.8</v>
+        <v>4362.7</v>
       </c>
       <c r="J59" t="n">
-        <v>4429.8</v>
+        <v>4371.52</v>
       </c>
       <c r="K59" t="n">
-        <v>4429.8</v>
+        <v>4383.05</v>
       </c>
       <c r="L59" t="n">
-        <v>4429.8</v>
+        <v>4394.57</v>
       </c>
       <c r="M59" t="n">
-        <v>4429.8</v>
+        <v>4404.75</v>
       </c>
       <c r="N59" t="n">
-        <v>4429.8</v>
+        <v>4414.93</v>
       </c>
       <c r="O59" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
+        <v>4427.8</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5509,156 +5509,158 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4398.7</v>
+        <v>4418.9</v>
       </c>
       <c r="C60" t="n">
-        <v>4416</v>
+        <v>4420</v>
       </c>
       <c r="D60" t="n">
-        <v>4397.4</v>
+        <v>4330.7</v>
       </c>
       <c r="E60" t="n">
-        <v>4416</v>
+        <v>4364.5</v>
       </c>
       <c r="F60" t="n">
-        <v>22.1</v>
+        <v>-51.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0117</v>
       </c>
       <c r="H60" t="n">
-        <v>18.6</v>
+        <v>89.3</v>
       </c>
       <c r="I60" t="n">
-        <v>4362.7</v>
+        <v>4378.8</v>
       </c>
       <c r="J60" t="n">
-        <v>4371.52</v>
+        <v>4402.05</v>
       </c>
       <c r="K60" t="n">
-        <v>4383.05</v>
+        <v>4406.7</v>
       </c>
       <c r="L60" t="n">
-        <v>4394.57</v>
+        <v>4411.35</v>
       </c>
       <c r="M60" t="n">
-        <v>4404.75</v>
+        <v>4425.3</v>
       </c>
       <c r="N60" t="n">
-        <v>4414.93</v>
+        <v>4439.25</v>
       </c>
       <c r="O60" t="n">
-        <v>4427.8</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
+        <v>4434.6</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="W60" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4418.9</v>
+        <v>4359.4</v>
       </c>
       <c r="C61" t="n">
-        <v>4420</v>
+        <v>4444.9</v>
       </c>
       <c r="D61" t="n">
-        <v>4330.7</v>
+        <v>4333</v>
       </c>
       <c r="E61" t="n">
-        <v>4364.5</v>
+        <v>4408.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-51.5</v>
+        <v>44.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0102</v>
       </c>
       <c r="H61" t="n">
-        <v>89.3</v>
+        <v>111.9</v>
       </c>
       <c r="I61" t="n">
-        <v>4378.8</v>
+        <v>4241.4</v>
       </c>
       <c r="J61" t="n">
-        <v>4402.05</v>
+        <v>4269.78</v>
       </c>
       <c r="K61" t="n">
-        <v>4406.7</v>
+        <v>4319.85</v>
       </c>
       <c r="L61" t="n">
-        <v>4411.35</v>
+        <v>4369.93</v>
       </c>
       <c r="M61" t="n">
-        <v>4425.3</v>
+        <v>4409.15</v>
       </c>
       <c r="N61" t="n">
-        <v>4439.25</v>
+        <v>4448.37</v>
       </c>
       <c r="O61" t="n">
-        <v>4434.6</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
+        <v>4509.3</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5672,119 +5674,35 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4359.4</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4444.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>4333</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4408.9</v>
-      </c>
-      <c r="F62" t="n">
-        <v>44.4</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0102</v>
-      </c>
-      <c r="H62" t="n">
-        <v>111.9</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4241.4</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4269.78</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4319.85</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4369.93</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4409.15</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4448.37</v>
-      </c>
-      <c r="O62" t="n">
-        <v>4509.3</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>4221.1</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>4306.97</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>4352.95</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>4398.92</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>4464.85</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>4530.77</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>4556.8</v>
       </c>
     </row>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,53 +641,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4339</v>
+        <v>4279.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4377</v>
+        <v>4323.2</v>
       </c>
       <c r="D2" t="n">
-        <v>4296</v>
+        <v>4223.7</v>
       </c>
       <c r="E2" t="n">
-        <v>4358.9</v>
+        <v>4224.1</v>
       </c>
       <c r="F2" t="n">
-        <v>28</v>
+        <v>-134.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0065</v>
+        <v>-0.0309</v>
       </c>
       <c r="H2" t="n">
-        <v>81</v>
+        <v>99.5</v>
       </c>
       <c r="I2" t="n">
-        <v>4273.2</v>
+        <v>4215</v>
       </c>
       <c r="J2" t="n">
-        <v>4296.23</v>
+        <v>4289.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4312.75</v>
+        <v>4318.4</v>
       </c>
       <c r="L2" t="n">
-        <v>4329.27</v>
+        <v>4347.7</v>
       </c>
       <c r="M2" t="n">
-        <v>4349.05</v>
+        <v>4399.4</v>
       </c>
       <c r="N2" t="n">
-        <v>4368.82</v>
+        <v>4451.1</v>
       </c>
       <c r="O2" t="n">
-        <v>4382.1</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>4458</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -701,97 +703,85 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4279.8</v>
+        <v>4138.8</v>
       </c>
       <c r="C3" t="n">
-        <v>4323.2</v>
+        <v>4216.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4223.7</v>
+        <v>4134.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4224.1</v>
+        <v>4181.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-134.8</v>
+        <v>-42.2</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0309</v>
+        <v>-0.01</v>
       </c>
       <c r="H3" t="n">
-        <v>99.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4215</v>
+        <v>4124.2</v>
       </c>
       <c r="J3" t="n">
-        <v>4289.1</v>
+        <v>4099.93</v>
       </c>
       <c r="K3" t="n">
-        <v>4318.4</v>
+        <v>4174.35</v>
       </c>
       <c r="L3" t="n">
-        <v>4347.7</v>
+        <v>4248.78</v>
       </c>
       <c r="M3" t="n">
-        <v>4399.4</v>
+        <v>4273.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4451.1</v>
+        <v>4298.93</v>
       </c>
       <c r="O3" t="n">
-        <v>4458</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>4422.7</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -805,7 +795,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -815,50 +805,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4138.8</v>
+        <v>4127.1</v>
       </c>
       <c r="C4" t="n">
-        <v>4216.4</v>
+        <v>4135.2</v>
       </c>
       <c r="D4" t="n">
-        <v>4134.8</v>
+        <v>4118.5</v>
       </c>
       <c r="E4" t="n">
-        <v>4181.9</v>
+        <v>4129.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-42.2</v>
+        <v>-52</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0124</v>
       </c>
       <c r="H4" t="n">
-        <v>81.59999999999999</v>
+        <v>16.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4124.2</v>
+        <v>4053.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4099.93</v>
+        <v>4103.45</v>
       </c>
       <c r="K4" t="n">
-        <v>4174.35</v>
+        <v>4141.1</v>
       </c>
       <c r="L4" t="n">
-        <v>4248.78</v>
+        <v>4178.75</v>
       </c>
       <c r="M4" t="n">
-        <v>4273.85</v>
+        <v>4222.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4298.93</v>
+        <v>4266.65</v>
       </c>
       <c r="O4" t="n">
-        <v>4422.7</v>
+        <v>4298</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -871,7 +861,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -885,7 +875,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -895,63 +885,67 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4127.1</v>
+        <v>4104.4</v>
       </c>
       <c r="C5" t="n">
-        <v>4135.2</v>
+        <v>4104.7</v>
       </c>
       <c r="D5" t="n">
-        <v>4118.5</v>
+        <v>3963.3</v>
       </c>
       <c r="E5" t="n">
-        <v>4129.9</v>
+        <v>3990.3</v>
       </c>
       <c r="F5" t="n">
-        <v>-52</v>
+        <v>-139.6</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0338</v>
       </c>
       <c r="H5" t="n">
-        <v>16.7</v>
+        <v>141.4</v>
       </c>
       <c r="I5" t="n">
-        <v>4053.2</v>
+        <v>4101.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4103.45</v>
+        <v>4114.72</v>
       </c>
       <c r="K5" t="n">
-        <v>4141.1</v>
+        <v>4121.55</v>
       </c>
       <c r="L5" t="n">
-        <v>4178.75</v>
+        <v>4128.38</v>
       </c>
       <c r="M5" t="n">
-        <v>4222.7</v>
+        <v>4138.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4266.65</v>
+        <v>4148.12</v>
       </c>
       <c r="O5" t="n">
-        <v>4298</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>4151.9</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -965,7 +959,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -975,69 +969,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4104.4</v>
+        <v>3988.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4104.7</v>
+        <v>4030.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3963.3</v>
+        <v>3986.7</v>
       </c>
       <c r="E6" t="n">
-        <v>3990.3</v>
+        <v>4030.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-139.6</v>
+        <v>40.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.0101</v>
       </c>
       <c r="H6" t="n">
-        <v>141.4</v>
+        <v>43.8</v>
       </c>
       <c r="I6" t="n">
-        <v>4101.8</v>
+        <v>3821.9</v>
       </c>
       <c r="J6" t="n">
-        <v>4114.72</v>
+        <v>3827.05</v>
       </c>
       <c r="K6" t="n">
-        <v>4121.55</v>
+        <v>3919.6</v>
       </c>
       <c r="L6" t="n">
-        <v>4128.38</v>
+        <v>4012.15</v>
       </c>
       <c r="M6" t="n">
-        <v>4138.25</v>
+        <v>4061</v>
       </c>
       <c r="N6" t="n">
-        <v>4148.12</v>
+        <v>4109.85</v>
       </c>
       <c r="O6" t="n">
-        <v>4151.9</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4246.1</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1049,60 +1037,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3988.4</v>
+        <v>4078.7</v>
       </c>
       <c r="C7" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="D7" t="n">
-        <v>3986.7</v>
+        <v>4078.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4030.5</v>
+        <v>4078.7</v>
       </c>
       <c r="F7" t="n">
-        <v>40.2</v>
+        <v>48.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.012</v>
       </c>
       <c r="H7" t="n">
-        <v>43.8</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>3821.9</v>
+        <v>3942.9</v>
       </c>
       <c r="J7" t="n">
-        <v>3827.05</v>
+        <v>3997.65</v>
       </c>
       <c r="K7" t="n">
-        <v>3919.6</v>
+        <v>4008.6</v>
       </c>
       <c r="L7" t="n">
-        <v>4012.15</v>
+        <v>4019.55</v>
       </c>
       <c r="M7" t="n">
-        <v>4061</v>
+        <v>4052.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4109.85</v>
+        <v>4085.25</v>
       </c>
       <c r="O7" t="n">
-        <v>4246.1</v>
+        <v>4074.3</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1113,183 +1105,181 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
+        <v>4057.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4070</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4003.2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>4022.3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-56.4</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="H8" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="I8" t="n">
         <v>4078.7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="J8" t="n">
         <v>4078.7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="K8" t="n">
         <v>4078.7</v>
       </c>
-      <c r="E8" t="n">
+      <c r="L8" t="n">
         <v>4078.7</v>
       </c>
-      <c r="F8" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3942.9</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3997.65</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4008.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>4019.55</v>
-      </c>
       <c r="M8" t="n">
-        <v>4052.4</v>
+        <v>4078.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4085.25</v>
+        <v>4078.7</v>
       </c>
       <c r="O8" t="n">
-        <v>4074.3</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>4078.7</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4057.5</v>
+        <v>4002.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4070</v>
+        <v>4049.7</v>
       </c>
       <c r="D9" t="n">
-        <v>4003.2</v>
+        <v>3962.5</v>
       </c>
       <c r="E9" t="n">
-        <v>4022.3</v>
+        <v>4022.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-56.4</v>
+        <v>0.6</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0001</v>
       </c>
       <c r="H9" t="n">
-        <v>66.8</v>
+        <v>87.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4078.7</v>
+        <v>3936.4</v>
       </c>
       <c r="J9" t="n">
-        <v>4078.7</v>
+        <v>3948.35</v>
       </c>
       <c r="K9" t="n">
-        <v>4078.7</v>
+        <v>3988.9</v>
       </c>
       <c r="L9" t="n">
-        <v>4078.7</v>
+        <v>4029.45</v>
       </c>
       <c r="M9" t="n">
-        <v>4078.7</v>
+        <v>4055.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4078.7</v>
+        <v>4081.95</v>
       </c>
       <c r="O9" t="n">
-        <v>4078.7</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4136.8</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1301,60 +1291,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4002.6</v>
+        <v>4013.1</v>
       </c>
       <c r="C10" t="n">
-        <v>4049.7</v>
+        <v>4100</v>
       </c>
       <c r="D10" t="n">
-        <v>3962.5</v>
+        <v>3963</v>
       </c>
       <c r="E10" t="n">
-        <v>4022.9</v>
+        <v>4068.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6</v>
+        <v>45.4</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0113</v>
       </c>
       <c r="H10" t="n">
-        <v>87.2</v>
+        <v>137</v>
       </c>
       <c r="I10" t="n">
-        <v>3936.4</v>
+        <v>3875.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3948.35</v>
+        <v>3944.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3988.9</v>
+        <v>3979.3</v>
       </c>
       <c r="L10" t="n">
-        <v>4029.45</v>
+        <v>4014.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4055.7</v>
+        <v>4066.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4081.95</v>
+        <v>4118.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4136.8</v>
+        <v>4136.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1369,11 +1363,13 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1381,64 +1377,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4013.1</v>
+        <v>4067.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4100</v>
+        <v>4140.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3963</v>
+        <v>4062</v>
       </c>
       <c r="E11" t="n">
-        <v>4068.3</v>
+        <v>4112.7</v>
       </c>
       <c r="F11" t="n">
-        <v>45.4</v>
+        <v>44.4</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0109</v>
       </c>
       <c r="H11" t="n">
-        <v>137</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3875.3</v>
+        <v>3826</v>
       </c>
       <c r="J11" t="n">
-        <v>3944.1</v>
+        <v>3949.7</v>
       </c>
       <c r="K11" t="n">
-        <v>3979.3</v>
+        <v>3999.8</v>
       </c>
       <c r="L11" t="n">
-        <v>4014.5</v>
+        <v>4049.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4066.5</v>
+        <v>4136.8</v>
       </c>
       <c r="N11" t="n">
-        <v>4118.5</v>
+        <v>4223.7</v>
       </c>
       <c r="O11" t="n">
-        <v>4136.9</v>
+        <v>4237</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,12 +1442,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1467,7 +1461,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1481,50 +1475,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4067.5</v>
+        <v>4175.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4140.1</v>
+        <v>4199.7</v>
       </c>
       <c r="D12" t="n">
-        <v>4062</v>
+        <v>4134.2</v>
       </c>
       <c r="E12" t="n">
-        <v>4112.7</v>
+        <v>4155.1</v>
       </c>
       <c r="F12" t="n">
-        <v>44.4</v>
+        <v>42.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0103</v>
       </c>
       <c r="H12" t="n">
-        <v>78.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3826</v>
+        <v>3983.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3949.7</v>
+        <v>4040.43</v>
       </c>
       <c r="K12" t="n">
-        <v>3999.8</v>
+        <v>4073.65</v>
       </c>
       <c r="L12" t="n">
-        <v>4049.9</v>
+        <v>4106.88</v>
       </c>
       <c r="M12" t="n">
-        <v>4136.8</v>
+        <v>4151.75</v>
       </c>
       <c r="N12" t="n">
-        <v>4223.7</v>
+        <v>4196.63</v>
       </c>
       <c r="O12" t="n">
-        <v>4237</v>
+        <v>4218.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,7 +1529,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1545,13 +1539,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1565,50 +1561,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4175.4</v>
+        <v>4126.5</v>
       </c>
       <c r="C13" t="n">
-        <v>4199.7</v>
+        <v>4167.2</v>
       </c>
       <c r="D13" t="n">
-        <v>4134.2</v>
+        <v>4107.2</v>
       </c>
       <c r="E13" t="n">
-        <v>4155.1</v>
+        <v>4145.3</v>
       </c>
       <c r="F13" t="n">
-        <v>42.4</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0024</v>
       </c>
       <c r="H13" t="n">
-        <v>65.5</v>
+        <v>60</v>
       </c>
       <c r="I13" t="n">
-        <v>3983.9</v>
+        <v>4068.7</v>
       </c>
       <c r="J13" t="n">
-        <v>4040.43</v>
+        <v>4083.68</v>
       </c>
       <c r="K13" t="n">
-        <v>4073.65</v>
+        <v>4122.35</v>
       </c>
       <c r="L13" t="n">
-        <v>4106.88</v>
+        <v>4161.03</v>
       </c>
       <c r="M13" t="n">
-        <v>4151.75</v>
+        <v>4187.85</v>
       </c>
       <c r="N13" t="n">
-        <v>4196.63</v>
+        <v>4214.68</v>
       </c>
       <c r="O13" t="n">
-        <v>4218.2</v>
+        <v>4265.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1616,100 +1612,96 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4126.5</v>
+        <v>4116.3</v>
       </c>
       <c r="C14" t="n">
-        <v>4167.2</v>
+        <v>4120.3</v>
       </c>
       <c r="D14" t="n">
-        <v>4107.2</v>
+        <v>4053</v>
       </c>
       <c r="E14" t="n">
-        <v>4145.3</v>
+        <v>4070.9</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.800000000000001</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.0179</v>
       </c>
       <c r="H14" t="n">
-        <v>60</v>
+        <v>67.3</v>
       </c>
       <c r="I14" t="n">
-        <v>4068.7</v>
+        <v>4047.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4083.68</v>
+        <v>4089.35</v>
       </c>
       <c r="K14" t="n">
-        <v>4122.35</v>
+        <v>4115.3</v>
       </c>
       <c r="L14" t="n">
-        <v>4161.03</v>
+        <v>4141.25</v>
       </c>
       <c r="M14" t="n">
-        <v>4187.85</v>
+        <v>4175.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4214.68</v>
+        <v>4209.35</v>
       </c>
       <c r="O14" t="n">
-        <v>4265.2</v>
+        <v>4227.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1721,7 +1713,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1731,81 +1723,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4116.3</v>
+        <v>4066.4</v>
       </c>
       <c r="C15" t="n">
-        <v>4120.3</v>
+        <v>4130.6</v>
       </c>
       <c r="D15" t="n">
-        <v>4053</v>
+        <v>4064.2</v>
       </c>
       <c r="E15" t="n">
-        <v>4070.9</v>
+        <v>4130.6</v>
       </c>
       <c r="F15" t="n">
-        <v>-74.40000000000001</v>
+        <v>59.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0147</v>
       </c>
       <c r="H15" t="n">
-        <v>67.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>4047.2</v>
+        <v>3985.7</v>
       </c>
       <c r="J15" t="n">
-        <v>4089.35</v>
+        <v>3995.73</v>
       </c>
       <c r="K15" t="n">
-        <v>4115.3</v>
+        <v>4037.25</v>
       </c>
       <c r="L15" t="n">
-        <v>4141.25</v>
+        <v>4078.77</v>
       </c>
       <c r="M15" t="n">
-        <v>4175.3</v>
+        <v>4104.55</v>
       </c>
       <c r="N15" t="n">
-        <v>4209.35</v>
+        <v>4130.32</v>
       </c>
       <c r="O15" t="n">
-        <v>4227.2</v>
+        <v>4187.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1813,50 +1805,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4066.4</v>
+        <v>4122.3</v>
       </c>
       <c r="C16" t="n">
-        <v>4130.6</v>
+        <v>4125.8</v>
       </c>
       <c r="D16" t="n">
-        <v>4064.2</v>
+        <v>4090.6</v>
       </c>
       <c r="E16" t="n">
-        <v>4130.6</v>
+        <v>4104.1</v>
       </c>
       <c r="F16" t="n">
-        <v>59.7</v>
+        <v>-26.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0064</v>
       </c>
       <c r="H16" t="n">
-        <v>66.40000000000001</v>
+        <v>35.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3985.7</v>
+        <v>3997.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3995.73</v>
+        <v>4080.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4037.25</v>
+        <v>4097.4</v>
       </c>
       <c r="L16" t="n">
-        <v>4078.77</v>
+        <v>4114</v>
       </c>
       <c r="M16" t="n">
-        <v>4104.55</v>
+        <v>4163.8</v>
       </c>
       <c r="N16" t="n">
-        <v>4130.32</v>
+        <v>4213.6</v>
       </c>
       <c r="O16" t="n">
-        <v>4187.6</v>
+        <v>4197</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1864,94 +1856,100 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4122.3</v>
+        <v>4081</v>
       </c>
       <c r="C17" t="n">
-        <v>4125.8</v>
+        <v>4081</v>
       </c>
       <c r="D17" t="n">
-        <v>4090.6</v>
+        <v>3985.9</v>
       </c>
       <c r="E17" t="n">
-        <v>4104.1</v>
+        <v>3997</v>
       </c>
       <c r="F17" t="n">
-        <v>-26.5</v>
+        <v>-107.1</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0261</v>
       </c>
       <c r="H17" t="n">
-        <v>35.2</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>3997.8</v>
+        <v>4055.4</v>
       </c>
       <c r="J17" t="n">
-        <v>4080.8</v>
+        <v>4066.85</v>
       </c>
       <c r="K17" t="n">
-        <v>4097.4</v>
+        <v>4086.5</v>
       </c>
       <c r="L17" t="n">
-        <v>4114</v>
+        <v>4106.15</v>
       </c>
       <c r="M17" t="n">
-        <v>4163.8</v>
+        <v>4121.7</v>
       </c>
       <c r="N17" t="n">
-        <v>4213.6</v>
+        <v>4137.25</v>
       </c>
       <c r="O17" t="n">
-        <v>4197</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>4161</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1967,146 +1965,144 @@
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4081</v>
+        <v>3995.7</v>
       </c>
       <c r="C18" t="n">
-        <v>4081</v>
+        <v>4091.2</v>
       </c>
       <c r="D18" t="n">
-        <v>3985.9</v>
+        <v>3986.5</v>
       </c>
       <c r="E18" t="n">
-        <v>3997</v>
+        <v>4061.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-107.1</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.016</v>
       </c>
       <c r="H18" t="n">
-        <v>95.09999999999999</v>
+        <v>104.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4055.4</v>
+        <v>3890.8</v>
       </c>
       <c r="J18" t="n">
-        <v>4066.85</v>
+        <v>3883.67</v>
       </c>
       <c r="K18" t="n">
-        <v>4086.5</v>
+        <v>3949.45</v>
       </c>
       <c r="L18" t="n">
-        <v>4106.15</v>
+        <v>4015.22</v>
       </c>
       <c r="M18" t="n">
-        <v>4121.7</v>
+        <v>4044.55</v>
       </c>
       <c r="N18" t="n">
-        <v>4137.25</v>
+        <v>4073.88</v>
       </c>
       <c r="O18" t="n">
-        <v>4161</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>4176.1</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3995.7</v>
+        <v>4049.1</v>
       </c>
       <c r="C19" t="n">
-        <v>4091.2</v>
+        <v>4070.1</v>
       </c>
       <c r="D19" t="n">
-        <v>3986.5</v>
+        <v>4019.4</v>
       </c>
       <c r="E19" t="n">
-        <v>4061.1</v>
+        <v>4044</v>
       </c>
       <c r="F19" t="n">
-        <v>64.09999999999999</v>
+        <v>-17.1</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0042</v>
       </c>
       <c r="H19" t="n">
-        <v>104.7</v>
+        <v>50.7</v>
       </c>
       <c r="I19" t="n">
-        <v>3890.8</v>
+        <v>3881.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3883.67</v>
+        <v>3967.53</v>
       </c>
       <c r="K19" t="n">
-        <v>3949.45</v>
+        <v>4008.75</v>
       </c>
       <c r="L19" t="n">
-        <v>4015.22</v>
+        <v>4049.98</v>
       </c>
       <c r="M19" t="n">
-        <v>4044.55</v>
+        <v>4113.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4073.88</v>
+        <v>4176.93</v>
       </c>
       <c r="O19" t="n">
-        <v>4176.1</v>
+        <v>4195.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,93 +2115,93 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4049.1</v>
+        <v>4030.5</v>
       </c>
       <c r="C20" t="n">
-        <v>4070.1</v>
+        <v>4030.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4019.4</v>
+        <v>3972.6</v>
       </c>
       <c r="E20" t="n">
-        <v>4044</v>
+        <v>3985.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-17.1</v>
+        <v>-58.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0144</v>
       </c>
       <c r="H20" t="n">
-        <v>50.7</v>
+        <v>57.9</v>
       </c>
       <c r="I20" t="n">
-        <v>3881.8</v>
+        <v>3968.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3967.53</v>
+        <v>3992.92</v>
       </c>
       <c r="K20" t="n">
-        <v>4008.75</v>
+        <v>4018.65</v>
       </c>
       <c r="L20" t="n">
-        <v>4049.98</v>
+        <v>4044.38</v>
       </c>
       <c r="M20" t="n">
-        <v>4113.45</v>
+        <v>4069.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4176.93</v>
+        <v>4094.33</v>
       </c>
       <c r="O20" t="n">
-        <v>4195.9</v>
+        <v>4120.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2217,146 +2213,144 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4030.5</v>
+        <v>3975.5</v>
       </c>
       <c r="C21" t="n">
-        <v>4030.5</v>
+        <v>4017.2</v>
       </c>
       <c r="D21" t="n">
-        <v>3972.6</v>
+        <v>3964.2</v>
       </c>
       <c r="E21" t="n">
-        <v>3985.6</v>
+        <v>4012.7</v>
       </c>
       <c r="F21" t="n">
-        <v>-58.4</v>
+        <v>27.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0068</v>
       </c>
       <c r="H21" t="n">
-        <v>57.9</v>
+        <v>53</v>
       </c>
       <c r="I21" t="n">
-        <v>3968.7</v>
+        <v>3914.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3992.92</v>
+        <v>3919.73</v>
       </c>
       <c r="K21" t="n">
-        <v>4018.65</v>
+        <v>3956.65</v>
       </c>
       <c r="L21" t="n">
-        <v>4044.38</v>
+        <v>3993.58</v>
       </c>
       <c r="M21" t="n">
-        <v>4069.35</v>
+        <v>4014.55</v>
       </c>
       <c r="N21" t="n">
-        <v>4094.33</v>
+        <v>4035.53</v>
       </c>
       <c r="O21" t="n">
-        <v>4120.8</v>
+        <v>4088.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3975.5</v>
+        <v>4003.4</v>
       </c>
       <c r="C22" t="n">
-        <v>4017.2</v>
+        <v>4018.9</v>
       </c>
       <c r="D22" t="n">
-        <v>3964.2</v>
+        <v>4002.7</v>
       </c>
       <c r="E22" t="n">
-        <v>4012.7</v>
+        <v>4010.3</v>
       </c>
       <c r="F22" t="n">
-        <v>27.1</v>
+        <v>-2.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>53</v>
+        <v>16.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3914.7</v>
+        <v>3911.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3919.73</v>
+        <v>3970.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3956.65</v>
+        <v>3986.2</v>
       </c>
       <c r="L22" t="n">
-        <v>3993.58</v>
+        <v>4001.7</v>
       </c>
       <c r="M22" t="n">
-        <v>4014.55</v>
+        <v>4039.2</v>
       </c>
       <c r="N22" t="n">
-        <v>4035.53</v>
+        <v>4076.7</v>
       </c>
       <c r="O22" t="n">
-        <v>4088.4</v>
+        <v>4070.2</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,15 +2361,13 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2383,64 +2375,64 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4003.4</v>
+        <v>4002.1</v>
       </c>
       <c r="C23" t="n">
-        <v>4018.9</v>
+        <v>4071.1</v>
       </c>
       <c r="D23" t="n">
-        <v>4002.7</v>
+        <v>3999.7</v>
       </c>
       <c r="E23" t="n">
-        <v>4010.3</v>
+        <v>4071.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4</v>
+        <v>60.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0152</v>
       </c>
       <c r="H23" t="n">
-        <v>16.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>3911.2</v>
+        <v>3986.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3970.7</v>
+        <v>3993.85</v>
       </c>
       <c r="K23" t="n">
-        <v>3986.2</v>
+        <v>4002.2</v>
       </c>
       <c r="L23" t="n">
-        <v>4001.7</v>
+        <v>4010.55</v>
       </c>
       <c r="M23" t="n">
-        <v>4039.2</v>
+        <v>4018.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4076.7</v>
+        <v>4026.25</v>
       </c>
       <c r="O23" t="n">
-        <v>4070.2</v>
+        <v>4035.1</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2448,81 +2440,89 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4002.1</v>
+        <v>4096.2</v>
       </c>
       <c r="C24" t="n">
-        <v>4071.1</v>
+        <v>4152.1</v>
       </c>
       <c r="D24" t="n">
-        <v>3999.7</v>
+        <v>4096.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4071.1</v>
+        <v>4146.9</v>
       </c>
       <c r="F24" t="n">
-        <v>60.8</v>
+        <v>75.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0186</v>
       </c>
       <c r="H24" t="n">
-        <v>71.40000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="I24" t="n">
-        <v>3986.5</v>
+        <v>3928.3</v>
       </c>
       <c r="J24" t="n">
-        <v>3993.85</v>
+        <v>4017.55</v>
       </c>
       <c r="K24" t="n">
-        <v>4002.2</v>
+        <v>4035.4</v>
       </c>
       <c r="L24" t="n">
-        <v>4010.55</v>
+        <v>4053.25</v>
       </c>
       <c r="M24" t="n">
-        <v>4018.4</v>
+        <v>4106.8</v>
       </c>
       <c r="N24" t="n">
-        <v>4026.25</v>
+        <v>4160.35</v>
       </c>
       <c r="O24" t="n">
-        <v>4035.1</v>
+        <v>4142.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,12 +2530,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2545,105 +2543,101 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4096.2</v>
+        <v>4129.9</v>
       </c>
       <c r="C25" t="n">
-        <v>4152.1</v>
+        <v>4130.9</v>
       </c>
       <c r="D25" t="n">
-        <v>4096.2</v>
+        <v>4046.6</v>
       </c>
       <c r="E25" t="n">
-        <v>4146.9</v>
+        <v>4046.6</v>
       </c>
       <c r="F25" t="n">
-        <v>75.8</v>
+        <v>-100.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0242</v>
       </c>
       <c r="H25" t="n">
-        <v>55.9</v>
+        <v>84.3</v>
       </c>
       <c r="I25" t="n">
-        <v>3928.3</v>
+        <v>4040.3</v>
       </c>
       <c r="J25" t="n">
-        <v>4017.55</v>
+        <v>4102.37</v>
       </c>
       <c r="K25" t="n">
-        <v>4035.4</v>
+        <v>4118.95</v>
       </c>
       <c r="L25" t="n">
-        <v>4053.25</v>
+        <v>4135.53</v>
       </c>
       <c r="M25" t="n">
-        <v>4106.8</v>
+        <v>4174.85</v>
       </c>
       <c r="N25" t="n">
-        <v>4160.35</v>
+        <v>4214.17</v>
       </c>
       <c r="O25" t="n">
-        <v>4142.5</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>4208</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2651,69 +2645,63 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4129.9</v>
+        <v>4067.6</v>
       </c>
       <c r="C26" t="n">
-        <v>4130.9</v>
+        <v>4068</v>
       </c>
       <c r="D26" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4046.6</v>
+        <v>4067.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-100.3</v>
+        <v>21</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0052</v>
       </c>
       <c r="H26" t="n">
-        <v>84.3</v>
+        <v>0.4</v>
       </c>
       <c r="I26" t="n">
-        <v>4040.3</v>
+        <v>3962.3</v>
       </c>
       <c r="J26" t="n">
-        <v>4102.37</v>
+        <v>3941.23</v>
       </c>
       <c r="K26" t="n">
-        <v>4118.95</v>
+        <v>4004.45</v>
       </c>
       <c r="L26" t="n">
-        <v>4135.53</v>
+        <v>4067.68</v>
       </c>
       <c r="M26" t="n">
-        <v>4174.85</v>
+        <v>4088.75</v>
       </c>
       <c r="N26" t="n">
-        <v>4214.17</v>
+        <v>4109.82</v>
       </c>
       <c r="O26" t="n">
-        <v>4208</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4215.2</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2725,60 +2713,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4067.6</v>
+        <v>4090.1</v>
       </c>
       <c r="C27" t="n">
-        <v>4068</v>
+        <v>4107.9</v>
       </c>
       <c r="D27" t="n">
-        <v>4067.6</v>
+        <v>4072.7</v>
       </c>
       <c r="E27" t="n">
-        <v>4067.6</v>
+        <v>4074.5</v>
       </c>
       <c r="F27" t="n">
-        <v>21</v>
+        <v>6.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0017</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4</v>
+        <v>35.2</v>
       </c>
       <c r="I27" t="n">
-        <v>3962.3</v>
+        <v>4067.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3941.23</v>
+        <v>4067.1</v>
       </c>
       <c r="K27" t="n">
-        <v>4004.45</v>
+        <v>4067.4</v>
       </c>
       <c r="L27" t="n">
-        <v>4067.68</v>
+        <v>4067.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4088.75</v>
+        <v>4067.8</v>
       </c>
       <c r="N27" t="n">
-        <v>4109.82</v>
+        <v>4067.9</v>
       </c>
       <c r="O27" t="n">
-        <v>4215.2</v>
+        <v>4068.4</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2791,165 +2783,169 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W27" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4090.1</v>
+        <v>4025.7</v>
       </c>
       <c r="C28" t="n">
-        <v>4107.9</v>
+        <v>4036.3</v>
       </c>
       <c r="D28" t="n">
-        <v>4072.7</v>
+        <v>4025.7</v>
       </c>
       <c r="E28" t="n">
-        <v>4074.5</v>
+        <v>4036.3</v>
       </c>
       <c r="F28" t="n">
-        <v>6.9</v>
+        <v>-38.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0094</v>
       </c>
       <c r="H28" t="n">
-        <v>35.2</v>
+        <v>10.6</v>
       </c>
       <c r="I28" t="n">
-        <v>4067.2</v>
+        <v>4037.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4067.1</v>
+        <v>4031.4</v>
       </c>
       <c r="K28" t="n">
-        <v>4067.4</v>
+        <v>4056.9</v>
       </c>
       <c r="L28" t="n">
-        <v>4067.7</v>
+        <v>4082.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4067.8</v>
+        <v>4092.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4067.9</v>
+        <v>4101.8</v>
       </c>
       <c r="O28" t="n">
-        <v>4068.4</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>4143.1</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4025.7</v>
+        <v>4018.1</v>
       </c>
       <c r="C29" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4025.7</v>
+        <v>4017.9</v>
       </c>
       <c r="E29" t="n">
-        <v>4036.3</v>
+        <v>4034.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-38.2</v>
+        <v>-1.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0004</v>
       </c>
       <c r="H29" t="n">
-        <v>10.6</v>
+        <v>16.8</v>
       </c>
       <c r="I29" t="n">
-        <v>4037.5</v>
+        <v>4015.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4031.4</v>
+        <v>4028.35</v>
       </c>
       <c r="K29" t="n">
-        <v>4056.9</v>
+        <v>4031</v>
       </c>
       <c r="L29" t="n">
-        <v>4082.4</v>
+        <v>4033.65</v>
       </c>
       <c r="M29" t="n">
-        <v>4092.1</v>
+        <v>4041.6</v>
       </c>
       <c r="N29" t="n">
-        <v>4101.8</v>
+        <v>4049.55</v>
       </c>
       <c r="O29" t="n">
-        <v>4143.1</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4046.9</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
@@ -2963,7 +2959,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2975,7 +2971,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2989,237 +2985,233 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4018.1</v>
+        <v>4060.7</v>
       </c>
       <c r="C30" t="n">
-        <v>4034.7</v>
+        <v>4118.5</v>
       </c>
       <c r="D30" t="n">
-        <v>4017.9</v>
+        <v>4028.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0162</v>
       </c>
       <c r="H30" t="n">
-        <v>16.8</v>
+        <v>90</v>
       </c>
       <c r="I30" t="n">
-        <v>4015.1</v>
+        <v>4001.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4028.35</v>
+        <v>4022.1</v>
       </c>
       <c r="K30" t="n">
-        <v>4031</v>
+        <v>4026.3</v>
       </c>
       <c r="L30" t="n">
-        <v>4033.65</v>
+        <v>4030.5</v>
       </c>
       <c r="M30" t="n">
-        <v>4041.6</v>
+        <v>4043.1</v>
       </c>
       <c r="N30" t="n">
-        <v>4049.55</v>
+        <v>4055.7</v>
       </c>
       <c r="O30" t="n">
-        <v>4046.9</v>
+        <v>4051.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4060.7</v>
+        <v>4102.4</v>
       </c>
       <c r="C31" t="n">
-        <v>4118.5</v>
+        <v>4102.4</v>
       </c>
       <c r="D31" t="n">
-        <v>4028.5</v>
+        <v>4022.4</v>
       </c>
       <c r="E31" t="n">
-        <v>4100.1</v>
+        <v>4049.1</v>
       </c>
       <c r="F31" t="n">
-        <v>65.40000000000001</v>
+        <v>-51</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0162</v>
+        <v>-0.0124</v>
       </c>
       <c r="H31" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I31" t="n">
-        <v>4001.1</v>
+        <v>3938.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4022.1</v>
+        <v>4023.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4026.3</v>
+        <v>4055.1</v>
       </c>
       <c r="L31" t="n">
-        <v>4030.5</v>
+        <v>4086.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4043.1</v>
+        <v>4145.1</v>
       </c>
       <c r="N31" t="n">
-        <v>4055.7</v>
+        <v>4203.4</v>
       </c>
       <c r="O31" t="n">
-        <v>4051.5</v>
+        <v>4208.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4102.4</v>
+        <v>4083.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4102.4</v>
+        <v>4083.5</v>
       </c>
       <c r="D32" t="n">
-        <v>4022.4</v>
+        <v>4026.5</v>
       </c>
       <c r="E32" t="n">
-        <v>4049.1</v>
+        <v>4033.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-51</v>
+        <v>-15.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0038</v>
       </c>
       <c r="H32" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>3938.5</v>
+        <v>3942.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4023.4</v>
+        <v>3962.45</v>
       </c>
       <c r="K32" t="n">
-        <v>4055.1</v>
+        <v>4009.1</v>
       </c>
       <c r="L32" t="n">
-        <v>4086.8</v>
+        <v>4055.75</v>
       </c>
       <c r="M32" t="n">
-        <v>4145.1</v>
+        <v>4089.1</v>
       </c>
       <c r="N32" t="n">
-        <v>4203.4</v>
+        <v>4122.45</v>
       </c>
       <c r="O32" t="n">
-        <v>4208.5</v>
+        <v>4182.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3231,64 +3223,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4083.4</v>
+        <v>4050.5</v>
       </c>
       <c r="C33" t="n">
-        <v>4083.5</v>
+        <v>4095.4</v>
       </c>
       <c r="D33" t="n">
-        <v>4026.5</v>
+        <v>4048.8</v>
       </c>
       <c r="E33" t="n">
-        <v>4033.7</v>
+        <v>4095.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-15.4</v>
+        <v>61.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.0153</v>
       </c>
       <c r="H33" t="n">
-        <v>57</v>
+        <v>46.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3942.4</v>
+        <v>3969.5</v>
       </c>
       <c r="J33" t="n">
-        <v>3962.45</v>
+        <v>3966.05</v>
       </c>
       <c r="K33" t="n">
-        <v>4009.1</v>
+        <v>4005.2</v>
       </c>
       <c r="L33" t="n">
-        <v>4055.75</v>
+        <v>4044.35</v>
       </c>
       <c r="M33" t="n">
-        <v>4089.1</v>
+        <v>4062.2</v>
       </c>
       <c r="N33" t="n">
-        <v>4122.45</v>
+        <v>4080.05</v>
       </c>
       <c r="O33" t="n">
-        <v>4182.4</v>
+        <v>4140.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3301,76 +3293,76 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4050.5</v>
+        <v>4130</v>
       </c>
       <c r="C34" t="n">
-        <v>4095.4</v>
+        <v>4262.2</v>
       </c>
       <c r="D34" t="n">
-        <v>4048.8</v>
+        <v>4129.5</v>
       </c>
       <c r="E34" t="n">
-        <v>4095.4</v>
+        <v>4245.8</v>
       </c>
       <c r="F34" t="n">
-        <v>61.7</v>
+        <v>150.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0367</v>
       </c>
       <c r="H34" t="n">
-        <v>46.6</v>
+        <v>132.7</v>
       </c>
       <c r="I34" t="n">
-        <v>3969.5</v>
+        <v>4002.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3966.05</v>
+        <v>4060.45</v>
       </c>
       <c r="K34" t="n">
-        <v>4005.2</v>
+        <v>4072.1</v>
       </c>
       <c r="L34" t="n">
-        <v>4044.35</v>
+        <v>4083.75</v>
       </c>
       <c r="M34" t="n">
-        <v>4062.2</v>
+        <v>4118.7</v>
       </c>
       <c r="N34" t="n">
-        <v>4080.05</v>
+        <v>4153.65</v>
       </c>
       <c r="O34" t="n">
-        <v>4140.5</v>
+        <v>4142</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3381,7 +3373,7 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3396,10 +3388,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3409,50 +3403,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4130</v>
+        <v>4297</v>
       </c>
       <c r="C35" t="n">
-        <v>4262.2</v>
+        <v>4297</v>
       </c>
       <c r="D35" t="n">
-        <v>4129.5</v>
+        <v>4228</v>
       </c>
       <c r="E35" t="n">
-        <v>4245.8</v>
+        <v>4242</v>
       </c>
       <c r="F35" t="n">
-        <v>150.4</v>
+        <v>-3.8</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0009</v>
       </c>
       <c r="H35" t="n">
-        <v>132.7</v>
+        <v>69</v>
       </c>
       <c r="I35" t="n">
-        <v>4002.2</v>
+        <v>3996.8</v>
       </c>
       <c r="J35" t="n">
-        <v>4060.45</v>
+        <v>4138.07</v>
       </c>
       <c r="K35" t="n">
-        <v>4072.1</v>
+        <v>4179.45</v>
       </c>
       <c r="L35" t="n">
-        <v>4083.75</v>
+        <v>4220.82</v>
       </c>
       <c r="M35" t="n">
-        <v>4118.7</v>
+        <v>4312.15</v>
       </c>
       <c r="N35" t="n">
-        <v>4153.65</v>
+        <v>4403.47</v>
       </c>
       <c r="O35" t="n">
-        <v>4142</v>
+        <v>4394.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3463,80 +3457,78 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4297</v>
+        <v>4277</v>
       </c>
       <c r="C36" t="n">
-        <v>4297</v>
+        <v>4371.5</v>
       </c>
       <c r="D36" t="n">
-        <v>4228</v>
+        <v>4274</v>
       </c>
       <c r="E36" t="n">
-        <v>4242</v>
+        <v>4340.7</v>
       </c>
       <c r="F36" t="n">
-        <v>-3.8</v>
+        <v>98.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0233</v>
       </c>
       <c r="H36" t="n">
-        <v>69</v>
+        <v>97.5</v>
       </c>
       <c r="I36" t="n">
-        <v>3996.8</v>
+        <v>4159</v>
       </c>
       <c r="J36" t="n">
-        <v>4138.07</v>
+        <v>4162.75</v>
       </c>
       <c r="K36" t="n">
-        <v>4179.45</v>
+        <v>4207.5</v>
       </c>
       <c r="L36" t="n">
-        <v>4220.82</v>
+        <v>4252.25</v>
       </c>
       <c r="M36" t="n">
-        <v>4312.15</v>
+        <v>4276.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4403.47</v>
+        <v>4300.75</v>
       </c>
       <c r="O36" t="n">
-        <v>4394.9</v>
+        <v>4366</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3547,78 +3539,80 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4277</v>
+        <v>4336.1</v>
       </c>
       <c r="C37" t="n">
-        <v>4371.5</v>
+        <v>4390.1</v>
       </c>
       <c r="D37" t="n">
-        <v>4274</v>
+        <v>4336.1</v>
       </c>
       <c r="E37" t="n">
-        <v>4340.7</v>
+        <v>4361.8</v>
       </c>
       <c r="F37" t="n">
-        <v>98.7</v>
+        <v>21.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0049</v>
       </c>
       <c r="H37" t="n">
-        <v>97.5</v>
+        <v>54</v>
       </c>
       <c r="I37" t="n">
-        <v>4159</v>
+        <v>4176.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4162.75</v>
+        <v>4252.18</v>
       </c>
       <c r="K37" t="n">
-        <v>4207.5</v>
+        <v>4291.95</v>
       </c>
       <c r="L37" t="n">
-        <v>4252.25</v>
+        <v>4331.73</v>
       </c>
       <c r="M37" t="n">
-        <v>4276.5</v>
+        <v>4389.45</v>
       </c>
       <c r="N37" t="n">
-        <v>4300.75</v>
+        <v>4447.18</v>
       </c>
       <c r="O37" t="n">
-        <v>4366</v>
+        <v>4469</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3629,27 +3623,23 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3659,50 +3649,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4336.1</v>
+        <v>4408.6</v>
       </c>
       <c r="C38" t="n">
-        <v>4390.1</v>
+        <v>4408.6</v>
       </c>
       <c r="D38" t="n">
-        <v>4336.1</v>
+        <v>4365.1</v>
       </c>
       <c r="E38" t="n">
-        <v>4361.8</v>
+        <v>4383</v>
       </c>
       <c r="F38" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>0.0049</v>
       </c>
       <c r="H38" t="n">
-        <v>54</v>
+        <v>43.5</v>
       </c>
       <c r="I38" t="n">
-        <v>4176.5</v>
+        <v>4282.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4252.18</v>
+        <v>4307.15</v>
       </c>
       <c r="K38" t="n">
-        <v>4291.95</v>
+        <v>4334.8</v>
       </c>
       <c r="L38" t="n">
-        <v>4331.73</v>
+        <v>4362.45</v>
       </c>
       <c r="M38" t="n">
-        <v>4389.45</v>
+        <v>4388.8</v>
       </c>
       <c r="N38" t="n">
-        <v>4447.18</v>
+        <v>4415.15</v>
       </c>
       <c r="O38" t="n">
-        <v>4469</v>
+        <v>4444.1</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3713,7 +3703,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3729,7 +3719,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3739,50 +3729,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4408.6</v>
+        <v>4406.5</v>
       </c>
       <c r="C39" t="n">
-        <v>4408.6</v>
+        <v>4434</v>
       </c>
       <c r="D39" t="n">
-        <v>4365.1</v>
+        <v>4406.3</v>
       </c>
       <c r="E39" t="n">
-        <v>4383</v>
+        <v>4408.9</v>
       </c>
       <c r="F39" t="n">
-        <v>21.2</v>
+        <v>25.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>43.5</v>
+        <v>27.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4282.1</v>
+        <v>4321.6</v>
       </c>
       <c r="J39" t="n">
-        <v>4307.15</v>
+        <v>4337.57</v>
       </c>
       <c r="K39" t="n">
-        <v>4334.8</v>
+        <v>4361.25</v>
       </c>
       <c r="L39" t="n">
-        <v>4362.45</v>
+        <v>4384.93</v>
       </c>
       <c r="M39" t="n">
-        <v>4388.8</v>
+        <v>4404.75</v>
       </c>
       <c r="N39" t="n">
-        <v>4415.15</v>
+        <v>4424.57</v>
       </c>
       <c r="O39" t="n">
-        <v>4444.1</v>
+        <v>4452.1</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3793,7 +3783,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3803,13 +3793,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3819,68 +3811,74 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4406.5</v>
+        <v>4403.5</v>
       </c>
       <c r="C40" t="n">
-        <v>4434</v>
+        <v>4445</v>
       </c>
       <c r="D40" t="n">
-        <v>4406.3</v>
+        <v>4350</v>
       </c>
       <c r="E40" t="n">
-        <v>4408.9</v>
+        <v>4363.6</v>
       </c>
       <c r="F40" t="n">
-        <v>25.9</v>
+        <v>-45.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0103</v>
       </c>
       <c r="H40" t="n">
-        <v>27.7</v>
+        <v>95</v>
       </c>
       <c r="I40" t="n">
-        <v>4321.6</v>
+        <v>4378.6</v>
       </c>
       <c r="J40" t="n">
-        <v>4337.57</v>
+        <v>4375.57</v>
       </c>
       <c r="K40" t="n">
-        <v>4361.25</v>
+        <v>4395.05</v>
       </c>
       <c r="L40" t="n">
-        <v>4384.93</v>
+        <v>4414.52</v>
       </c>
       <c r="M40" t="n">
-        <v>4404.75</v>
+        <v>4422.75</v>
       </c>
       <c r="N40" t="n">
-        <v>4424.57</v>
+        <v>4430.98</v>
       </c>
       <c r="O40" t="n">
-        <v>4452.1</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>4461.7</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="inlineStr">
@@ -3893,93 +3891,89 @@
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4403.5</v>
+        <v>4322.1</v>
       </c>
       <c r="C41" t="n">
-        <v>4445</v>
+        <v>4397.1</v>
       </c>
       <c r="D41" t="n">
-        <v>4350</v>
+        <v>4315</v>
       </c>
       <c r="E41" t="n">
-        <v>4363.6</v>
+        <v>4380.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-45.3</v>
+        <v>16.8</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0038</v>
       </c>
       <c r="H41" t="n">
-        <v>95</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>4378.6</v>
+        <v>4255</v>
       </c>
       <c r="J41" t="n">
-        <v>4375.57</v>
+        <v>4251.65</v>
       </c>
       <c r="K41" t="n">
-        <v>4395.05</v>
+        <v>4316.1</v>
       </c>
       <c r="L41" t="n">
-        <v>4414.52</v>
+        <v>4380.55</v>
       </c>
       <c r="M41" t="n">
-        <v>4422.75</v>
+        <v>4411.1</v>
       </c>
       <c r="N41" t="n">
-        <v>4430.98</v>
+        <v>4441.65</v>
       </c>
       <c r="O41" t="n">
-        <v>4461.7</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>4540</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3993,50 +3987,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4322.1</v>
+        <v>4394.8</v>
       </c>
       <c r="C42" t="n">
-        <v>4397.1</v>
+        <v>4428.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4315</v>
+        <v>4386.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4380.4</v>
+        <v>4417.8</v>
       </c>
       <c r="F42" t="n">
-        <v>16.8</v>
+        <v>37.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>82.09999999999999</v>
+        <v>42</v>
       </c>
       <c r="I42" t="n">
-        <v>4255</v>
+        <v>4232.9</v>
       </c>
       <c r="J42" t="n">
-        <v>4251.65</v>
+        <v>4310.47</v>
       </c>
       <c r="K42" t="n">
-        <v>4316.1</v>
+        <v>4339.35</v>
       </c>
       <c r="L42" t="n">
-        <v>4380.55</v>
+        <v>4368.22</v>
       </c>
       <c r="M42" t="n">
-        <v>4411.1</v>
+        <v>4421.45</v>
       </c>
       <c r="N42" t="n">
-        <v>4441.65</v>
+        <v>4474.67</v>
       </c>
       <c r="O42" t="n">
-        <v>4540</v>
+        <v>4479.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,18 +4038,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4063,83 +4057,87 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4394.8</v>
+        <v>4415.2</v>
       </c>
       <c r="C43" t="n">
-        <v>4428.5</v>
+        <v>4434.1</v>
       </c>
       <c r="D43" t="n">
-        <v>4386.5</v>
+        <v>4330.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4417.8</v>
+        <v>4366</v>
       </c>
       <c r="F43" t="n">
-        <v>37.4</v>
+        <v>-51.8</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0117</v>
       </c>
       <c r="H43" t="n">
-        <v>42</v>
+        <v>103.4</v>
       </c>
       <c r="I43" t="n">
-        <v>4232.9</v>
+        <v>4344.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4310.47</v>
+        <v>4380.95</v>
       </c>
       <c r="K43" t="n">
-        <v>4339.35</v>
+        <v>4396.8</v>
       </c>
       <c r="L43" t="n">
-        <v>4368.22</v>
+        <v>4412.65</v>
       </c>
       <c r="M43" t="n">
-        <v>4421.45</v>
+        <v>4438.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4474.67</v>
+        <v>4464.95</v>
       </c>
       <c r="O43" t="n">
-        <v>4479.2</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>4470.5</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4147,97 +4145,95 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4415.2</v>
+        <v>4339.8</v>
       </c>
       <c r="C44" t="n">
-        <v>4434.1</v>
+        <v>4524.1</v>
       </c>
       <c r="D44" t="n">
-        <v>4330.7</v>
+        <v>4327.6</v>
       </c>
       <c r="E44" t="n">
-        <v>4366</v>
+        <v>4489.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-51.8</v>
+        <v>123.4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0283</v>
       </c>
       <c r="H44" t="n">
-        <v>103.4</v>
+        <v>196.5</v>
       </c>
       <c r="I44" t="n">
-        <v>4344.5</v>
+        <v>4227.3</v>
       </c>
       <c r="J44" t="n">
-        <v>4380.95</v>
+        <v>4254.4</v>
       </c>
       <c r="K44" t="n">
-        <v>4396.8</v>
+        <v>4314.3</v>
       </c>
       <c r="L44" t="n">
-        <v>4412.65</v>
+        <v>4374.2</v>
       </c>
       <c r="M44" t="n">
-        <v>4438.8</v>
+        <v>4417.7</v>
       </c>
       <c r="N44" t="n">
-        <v>4464.95</v>
+        <v>4461.2</v>
       </c>
       <c r="O44" t="n">
-        <v>4470.5</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>4537.5</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
@@ -4249,50 +4245,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4339.8</v>
+        <v>4506.8</v>
       </c>
       <c r="C45" t="n">
-        <v>4524.1</v>
+        <v>4530</v>
       </c>
       <c r="D45" t="n">
-        <v>4327.6</v>
+        <v>4486</v>
       </c>
       <c r="E45" t="n">
-        <v>4489.4</v>
+        <v>4516.3</v>
       </c>
       <c r="F45" t="n">
-        <v>123.4</v>
+        <v>26.9</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.006</v>
       </c>
       <c r="H45" t="n">
-        <v>196.5</v>
+        <v>44</v>
       </c>
       <c r="I45" t="n">
-        <v>4227.3</v>
+        <v>4131.1</v>
       </c>
       <c r="J45" t="n">
-        <v>4254.4</v>
+        <v>4324.67</v>
       </c>
       <c r="K45" t="n">
-        <v>4314.3</v>
+        <v>4391.15</v>
       </c>
       <c r="L45" t="n">
-        <v>4374.2</v>
+        <v>4457.62</v>
       </c>
       <c r="M45" t="n">
-        <v>4417.7</v>
+        <v>4587.65</v>
       </c>
       <c r="N45" t="n">
-        <v>4461.2</v>
+        <v>4717.67</v>
       </c>
       <c r="O45" t="n">
-        <v>4537.5</v>
+        <v>4720.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4303,82 +4299,74 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4506.8</v>
+        <v>4560</v>
       </c>
       <c r="C46" t="n">
-        <v>4530</v>
+        <v>4624.1</v>
       </c>
       <c r="D46" t="n">
-        <v>4486</v>
+        <v>4560</v>
       </c>
       <c r="E46" t="n">
-        <v>4516.3</v>
+        <v>4624.1</v>
       </c>
       <c r="F46" t="n">
-        <v>26.9</v>
+        <v>107.8</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0239</v>
       </c>
       <c r="H46" t="n">
-        <v>44</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>4131.1</v>
+        <v>4442</v>
       </c>
       <c r="J46" t="n">
-        <v>4324.67</v>
+        <v>4476.45</v>
       </c>
       <c r="K46" t="n">
-        <v>4391.15</v>
+        <v>4494.3</v>
       </c>
       <c r="L46" t="n">
-        <v>4457.62</v>
+        <v>4512.15</v>
       </c>
       <c r="M46" t="n">
-        <v>4587.65</v>
+        <v>4538.3</v>
       </c>
       <c r="N46" t="n">
-        <v>4717.67</v>
+        <v>4564.45</v>
       </c>
       <c r="O46" t="n">
-        <v>4720.6</v>
+        <v>4574</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4389,21 +4377,27 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4413,50 +4407,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4560</v>
+        <v>4638</v>
       </c>
       <c r="C47" t="n">
-        <v>4624.1</v>
+        <v>4670.9</v>
       </c>
       <c r="D47" t="n">
-        <v>4560</v>
+        <v>4635.1</v>
       </c>
       <c r="E47" t="n">
-        <v>4624.1</v>
+        <v>4640.8</v>
       </c>
       <c r="F47" t="n">
-        <v>107.8</v>
+        <v>16.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0036</v>
       </c>
       <c r="H47" t="n">
-        <v>64.09999999999999</v>
+        <v>35.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4442</v>
+        <v>4495.9</v>
       </c>
       <c r="J47" t="n">
-        <v>4476.45</v>
+        <v>4576.03</v>
       </c>
       <c r="K47" t="n">
-        <v>4494.3</v>
+        <v>4592.05</v>
       </c>
       <c r="L47" t="n">
-        <v>4512.15</v>
+        <v>4608.08</v>
       </c>
       <c r="M47" t="n">
-        <v>4538.3</v>
+        <v>4656.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4564.45</v>
+        <v>4704.23</v>
       </c>
       <c r="O47" t="n">
-        <v>4574</v>
+        <v>4688.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4467,27 +4461,23 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4497,50 +4487,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4638</v>
+        <v>4630.5</v>
       </c>
       <c r="C48" t="n">
-        <v>4670.9</v>
+        <v>4638.1</v>
       </c>
       <c r="D48" t="n">
-        <v>4635.1</v>
+        <v>4626.2</v>
       </c>
       <c r="E48" t="n">
-        <v>4640.8</v>
+        <v>4638.1</v>
       </c>
       <c r="F48" t="n">
-        <v>16.7</v>
+        <v>-2.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>35.8</v>
+        <v>11.9</v>
       </c>
       <c r="I48" t="n">
-        <v>4495.9</v>
+        <v>4599.3</v>
       </c>
       <c r="J48" t="n">
-        <v>4576.03</v>
+        <v>4598.9</v>
       </c>
       <c r="K48" t="n">
-        <v>4592.05</v>
+        <v>4622.9</v>
       </c>
       <c r="L48" t="n">
-        <v>4608.08</v>
+        <v>4646.9</v>
       </c>
       <c r="M48" t="n">
-        <v>4656.15</v>
+        <v>4658.7</v>
       </c>
       <c r="N48" t="n">
-        <v>4704.23</v>
+        <v>4670.5</v>
       </c>
       <c r="O48" t="n">
-        <v>4688.2</v>
+        <v>4706.7</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,13 +4543,11 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4567,73 +4555,83 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4630.5</v>
+        <v>4615.3</v>
       </c>
       <c r="C49" t="n">
-        <v>4638.1</v>
+        <v>4615.3</v>
       </c>
       <c r="D49" t="n">
-        <v>4626.2</v>
+        <v>4598.2</v>
       </c>
       <c r="E49" t="n">
-        <v>4638.1</v>
+        <v>4598.2</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.7</v>
+        <v>-39.9</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0086</v>
       </c>
       <c r="H49" t="n">
-        <v>11.9</v>
+        <v>17.1</v>
       </c>
       <c r="I49" t="n">
-        <v>4599.3</v>
+        <v>4614.3</v>
       </c>
       <c r="J49" t="n">
-        <v>4598.9</v>
+        <v>4629.18</v>
       </c>
       <c r="K49" t="n">
-        <v>4622.9</v>
+        <v>4632.15</v>
       </c>
       <c r="L49" t="n">
-        <v>4646.9</v>
+        <v>4635.13</v>
       </c>
       <c r="M49" t="n">
-        <v>4658.7</v>
+        <v>4644.05</v>
       </c>
       <c r="N49" t="n">
-        <v>4670.5</v>
+        <v>4652.97</v>
       </c>
       <c r="O49" t="n">
-        <v>4706.7</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4650</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4647,159 +4645,163 @@
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4615.3</v>
+        <v>4609.7</v>
       </c>
       <c r="C50" t="n">
-        <v>4615.3</v>
+        <v>4609.7</v>
       </c>
       <c r="D50" t="n">
-        <v>4598.2</v>
+        <v>4609.7</v>
       </c>
       <c r="E50" t="n">
-        <v>4598.2</v>
+        <v>4609.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-39.9</v>
+        <v>11.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0025</v>
       </c>
       <c r="H50" t="n">
-        <v>17.1</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>4614.3</v>
+        <v>4581.1</v>
       </c>
       <c r="J50" t="n">
-        <v>4629.18</v>
+        <v>4576.83</v>
       </c>
       <c r="K50" t="n">
-        <v>4632.15</v>
+        <v>4589.65</v>
       </c>
       <c r="L50" t="n">
-        <v>4635.13</v>
+        <v>4602.48</v>
       </c>
       <c r="M50" t="n">
-        <v>4644.05</v>
+        <v>4606.75</v>
       </c>
       <c r="N50" t="n">
-        <v>4652.97</v>
+        <v>4611.02</v>
       </c>
       <c r="O50" t="n">
-        <v>4650</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>4632.4</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
+        <v>4599.3</v>
+      </c>
+      <c r="C51" t="n">
+        <v>4625.5</v>
+      </c>
+      <c r="D51" t="n">
+        <v>4451.8</v>
+      </c>
+      <c r="E51" t="n">
+        <v>4478.1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-131.6</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>-0.0285</v>
+      </c>
+      <c r="H51" t="n">
+        <v>173.7</v>
+      </c>
+      <c r="I51" t="n">
         <v>4609.7</v>
       </c>
-      <c r="C51" t="n">
+      <c r="J51" t="n">
         <v>4609.7</v>
       </c>
-      <c r="D51" t="n">
+      <c r="K51" t="n">
         <v>4609.7</v>
       </c>
-      <c r="E51" t="n">
+      <c r="L51" t="n">
         <v>4609.7</v>
       </c>
-      <c r="F51" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="G51" s="5" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>4581.1</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4576.83</v>
-      </c>
-      <c r="K51" t="n">
-        <v>4589.65</v>
-      </c>
-      <c r="L51" t="n">
-        <v>4602.48</v>
-      </c>
       <c r="M51" t="n">
-        <v>4606.75</v>
+        <v>4609.7</v>
       </c>
       <c r="N51" t="n">
-        <v>4611.02</v>
+        <v>4609.7</v>
       </c>
       <c r="O51" t="n">
-        <v>4632.4</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>4609.7</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4809,177 +4811,169 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4599.3</v>
+        <v>4430</v>
       </c>
       <c r="C52" t="n">
-        <v>4625.5</v>
+        <v>4466.9</v>
       </c>
       <c r="D52" t="n">
-        <v>4451.8</v>
+        <v>4410.9</v>
       </c>
       <c r="E52" t="n">
-        <v>4478.1</v>
+        <v>4431.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-131.6</v>
+        <v>-47</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0105</v>
       </c>
       <c r="H52" t="n">
-        <v>173.7</v>
+        <v>56</v>
       </c>
       <c r="I52" t="n">
-        <v>4609.7</v>
+        <v>4278.1</v>
       </c>
       <c r="J52" t="n">
-        <v>4609.7</v>
+        <v>4274.12</v>
       </c>
       <c r="K52" t="n">
-        <v>4609.7</v>
+        <v>4391.25</v>
       </c>
       <c r="L52" t="n">
-        <v>4609.7</v>
+        <v>4508.38</v>
       </c>
       <c r="M52" t="n">
-        <v>4609.7</v>
+        <v>4564.95</v>
       </c>
       <c r="N52" t="n">
-        <v>4609.7</v>
+        <v>4621.53</v>
       </c>
       <c r="O52" t="n">
-        <v>4609.7</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
+        <v>4799.2</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4430</v>
+        <v>4402</v>
       </c>
       <c r="C53" t="n">
-        <v>4466.9</v>
+        <v>4402</v>
       </c>
       <c r="D53" t="n">
-        <v>4410.9</v>
+        <v>4329.1</v>
       </c>
       <c r="E53" t="n">
-        <v>4431.1</v>
+        <v>4348</v>
       </c>
       <c r="F53" t="n">
-        <v>-47</v>
+        <v>-83.09999999999999</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.0188</v>
       </c>
       <c r="H53" t="n">
-        <v>56</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>4278.1</v>
+        <v>4354.9</v>
       </c>
       <c r="J53" t="n">
-        <v>4274.12</v>
+        <v>4371.2</v>
       </c>
       <c r="K53" t="n">
-        <v>4391.25</v>
+        <v>4403.1</v>
       </c>
       <c r="L53" t="n">
-        <v>4508.38</v>
+        <v>4435</v>
       </c>
       <c r="M53" t="n">
-        <v>4564.95</v>
+        <v>4459.1</v>
       </c>
       <c r="N53" t="n">
-        <v>4621.53</v>
+        <v>4483.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4799.2</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>4522.9</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4993,7 +4987,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5003,60 +4997,56 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4402</v>
+        <v>4328</v>
       </c>
       <c r="C54" t="n">
-        <v>4402</v>
+        <v>4390.2</v>
       </c>
       <c r="D54" t="n">
-        <v>4329.1</v>
+        <v>4292.2</v>
       </c>
       <c r="E54" t="n">
-        <v>4348</v>
+        <v>4366.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-83.09999999999999</v>
+        <v>18.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0188</v>
+        <v>0.0042</v>
       </c>
       <c r="H54" t="n">
-        <v>72.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="I54" t="n">
-        <v>4354.9</v>
+        <v>4256.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4371.2</v>
+        <v>4266.33</v>
       </c>
       <c r="K54" t="n">
-        <v>4403.1</v>
+        <v>4311.55</v>
       </c>
       <c r="L54" t="n">
-        <v>4435</v>
+        <v>4356.78</v>
       </c>
       <c r="M54" t="n">
-        <v>4459.1</v>
+        <v>4384.45</v>
       </c>
       <c r="N54" t="n">
-        <v>4483.2</v>
+        <v>4412.12</v>
       </c>
       <c r="O54" t="n">
-        <v>4522.9</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4474.9</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5065,11 +5055,13 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5077,60 +5069,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4328</v>
+        <v>4426.3</v>
       </c>
       <c r="C55" t="n">
-        <v>4390.2</v>
+        <v>4510</v>
       </c>
       <c r="D55" t="n">
-        <v>4292.2</v>
+        <v>4426</v>
       </c>
       <c r="E55" t="n">
-        <v>4366.3</v>
+        <v>4491.7</v>
       </c>
       <c r="F55" t="n">
-        <v>18.3</v>
+        <v>125.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0287</v>
       </c>
       <c r="H55" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I55" t="n">
-        <v>4256.2</v>
+        <v>4194.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4266.33</v>
+        <v>4280.85</v>
       </c>
       <c r="K55" t="n">
-        <v>4311.55</v>
+        <v>4317.3</v>
       </c>
       <c r="L55" t="n">
-        <v>4356.78</v>
+        <v>4353.75</v>
       </c>
       <c r="M55" t="n">
-        <v>4384.45</v>
+        <v>4415.3</v>
       </c>
       <c r="N55" t="n">
-        <v>4412.12</v>
+        <v>4476.85</v>
       </c>
       <c r="O55" t="n">
-        <v>4474.9</v>
+        <v>4488.2</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5138,14 +5134,12 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5153,161 +5147,165 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4426.3</v>
+        <v>4429.8</v>
       </c>
       <c r="C56" t="n">
-        <v>4510</v>
+        <v>4429.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4426</v>
+        <v>4429.8</v>
       </c>
       <c r="E56" t="n">
-        <v>4491.7</v>
+        <v>4429.8</v>
       </c>
       <c r="F56" t="n">
-        <v>125.4</v>
+        <v>-61.9</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0287</v>
+        <v>-0.0138</v>
       </c>
       <c r="H56" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>4194.2</v>
+        <v>4342</v>
       </c>
       <c r="J56" t="n">
-        <v>4280.85</v>
+        <v>4419.55</v>
       </c>
       <c r="K56" t="n">
-        <v>4317.3</v>
+        <v>4449.7</v>
       </c>
       <c r="L56" t="n">
-        <v>4353.75</v>
+        <v>4479.85</v>
       </c>
       <c r="M56" t="n">
-        <v>4415.3</v>
+        <v>4533.7</v>
       </c>
       <c r="N56" t="n">
-        <v>4476.85</v>
+        <v>4587.55</v>
       </c>
       <c r="O56" t="n">
-        <v>4488.2</v>
+        <v>4594</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
+        <v>4391.9</v>
+      </c>
+      <c r="C57" t="n">
+        <v>4406.1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>4384.4</v>
+      </c>
+      <c r="E57" t="n">
+        <v>4393.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-35.9</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0081</v>
+      </c>
+      <c r="H57" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="I57" t="n">
         <v>4429.8</v>
       </c>
-      <c r="C57" t="n">
+      <c r="J57" t="n">
         <v>4429.8</v>
       </c>
-      <c r="D57" t="n">
+      <c r="K57" t="n">
         <v>4429.8</v>
       </c>
-      <c r="E57" t="n">
+      <c r="L57" t="n">
         <v>4429.8</v>
       </c>
-      <c r="F57" t="n">
-        <v>-61.9</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0138</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>4342</v>
-      </c>
-      <c r="J57" t="n">
-        <v>4419.55</v>
-      </c>
-      <c r="K57" t="n">
-        <v>4449.7</v>
-      </c>
-      <c r="L57" t="n">
-        <v>4479.85</v>
-      </c>
       <c r="M57" t="n">
-        <v>4533.7</v>
+        <v>4429.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4587.55</v>
+        <v>4429.8</v>
       </c>
       <c r="O57" t="n">
-        <v>4594</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
+        <v>4429.8</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5315,7 +5313,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5331,95 +5329,89 @@
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4391.9</v>
+        <v>4398.7</v>
       </c>
       <c r="C58" t="n">
-        <v>4406.1</v>
+        <v>4416</v>
       </c>
       <c r="D58" t="n">
-        <v>4384.4</v>
+        <v>4397.4</v>
       </c>
       <c r="E58" t="n">
-        <v>4393.9</v>
+        <v>4416</v>
       </c>
       <c r="F58" t="n">
-        <v>-35.9</v>
+        <v>22.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.005</v>
       </c>
       <c r="H58" t="n">
-        <v>21.7</v>
+        <v>18.6</v>
       </c>
       <c r="I58" t="n">
-        <v>4429.8</v>
+        <v>4362.7</v>
       </c>
       <c r="J58" t="n">
-        <v>4429.8</v>
+        <v>4371.52</v>
       </c>
       <c r="K58" t="n">
-        <v>4429.8</v>
+        <v>4383.05</v>
       </c>
       <c r="L58" t="n">
-        <v>4429.8</v>
+        <v>4394.57</v>
       </c>
       <c r="M58" t="n">
-        <v>4429.8</v>
+        <v>4404.75</v>
       </c>
       <c r="N58" t="n">
-        <v>4429.8</v>
+        <v>4414.93</v>
       </c>
       <c r="O58" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
+        <v>4427.8</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr"/>
@@ -5427,239 +5419,243 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4398.7</v>
+        <v>4418.9</v>
       </c>
       <c r="C59" t="n">
-        <v>4416</v>
+        <v>4420</v>
       </c>
       <c r="D59" t="n">
-        <v>4397.4</v>
+        <v>4330.7</v>
       </c>
       <c r="E59" t="n">
-        <v>4416</v>
+        <v>4364.5</v>
       </c>
       <c r="F59" t="n">
-        <v>22.1</v>
+        <v>-51.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.0117</v>
       </c>
       <c r="H59" t="n">
-        <v>18.6</v>
+        <v>89.3</v>
       </c>
       <c r="I59" t="n">
-        <v>4362.7</v>
+        <v>4378.8</v>
       </c>
       <c r="J59" t="n">
-        <v>4371.52</v>
+        <v>4402.05</v>
       </c>
       <c r="K59" t="n">
-        <v>4383.05</v>
+        <v>4406.7</v>
       </c>
       <c r="L59" t="n">
-        <v>4394.57</v>
+        <v>4411.35</v>
       </c>
       <c r="M59" t="n">
-        <v>4404.75</v>
+        <v>4425.3</v>
       </c>
       <c r="N59" t="n">
-        <v>4414.93</v>
+        <v>4439.25</v>
       </c>
       <c r="O59" t="n">
-        <v>4427.8</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+        <v>4434.6</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr"/>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4418.9</v>
+        <v>4359.4</v>
       </c>
       <c r="C60" t="n">
-        <v>4420</v>
+        <v>4444.9</v>
       </c>
       <c r="D60" t="n">
-        <v>4330.7</v>
+        <v>4333</v>
       </c>
       <c r="E60" t="n">
-        <v>4364.5</v>
+        <v>4408.9</v>
       </c>
       <c r="F60" t="n">
-        <v>-51.5</v>
+        <v>44.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0102</v>
       </c>
       <c r="H60" t="n">
-        <v>89.3</v>
+        <v>111.9</v>
       </c>
       <c r="I60" t="n">
-        <v>4378.8</v>
+        <v>4241.4</v>
       </c>
       <c r="J60" t="n">
-        <v>4402.05</v>
+        <v>4269.78</v>
       </c>
       <c r="K60" t="n">
-        <v>4406.7</v>
+        <v>4319.85</v>
       </c>
       <c r="L60" t="n">
-        <v>4411.35</v>
+        <v>4369.93</v>
       </c>
       <c r="M60" t="n">
-        <v>4425.3</v>
+        <v>4409.15</v>
       </c>
       <c r="N60" t="n">
-        <v>4439.25</v>
+        <v>4448.37</v>
       </c>
       <c r="O60" t="n">
-        <v>4434.6</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
+        <v>4509.3</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C61" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D61" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E61" t="n">
-        <v>4408.9</v>
+        <v>4340</v>
       </c>
       <c r="F61" t="n">
-        <v>44.4</v>
+        <v>-68.90000000000001</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0156</v>
       </c>
       <c r="H61" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I61" t="n">
-        <v>4241.4</v>
+        <v>4221.1</v>
       </c>
       <c r="J61" t="n">
-        <v>4269.78</v>
+        <v>4306.97</v>
       </c>
       <c r="K61" t="n">
-        <v>4319.85</v>
+        <v>4352.95</v>
       </c>
       <c r="L61" t="n">
-        <v>4369.93</v>
+        <v>4398.92</v>
       </c>
       <c r="M61" t="n">
-        <v>4409.15</v>
+        <v>4464.85</v>
       </c>
       <c r="N61" t="n">
-        <v>4448.37</v>
+        <v>4530.77</v>
       </c>
       <c r="O61" t="n">
-        <v>4509.3</v>
+        <v>4556.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5667,16 +5663,12 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5685,25 +5677,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4306.97</v>
+        <v>4233.75</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4352.95</v>
+        <v>4288.1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4398.92</v>
+        <v>4342.45</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4464.85</v>
+        <v>4391.9</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4530.77</v>
+        <v>4441.35</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5595,25 +5595,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C61" t="n">
-        <v>4396.8</v>
+        <v>4347</v>
       </c>
       <c r="D61" t="n">
-        <v>4293</v>
+        <v>4323.8</v>
       </c>
       <c r="E61" t="n">
-        <v>4340</v>
+        <v>4340.7</v>
       </c>
       <c r="F61" t="n">
-        <v>-68.90000000000001</v>
+        <v>-68.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0156</v>
+        <v>-0.0155</v>
       </c>
       <c r="H61" t="n">
-        <v>103.8</v>
+        <v>23.2</v>
       </c>
       <c r="I61" t="n">
         <v>4221.1</v>
@@ -5639,10 +5639,8 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5677,25 +5675,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4189.2</v>
+        <v>4300.6</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4233.75</v>
+        <v>4320.15</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4288.1</v>
+        <v>4329.1</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4342.45</v>
+        <v>4338.05</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4391.9</v>
+        <v>4352.3</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4441.35</v>
+        <v>4366.55</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4500.6</v>
+        <v>4370.2</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5598,22 +5598,22 @@
         <v>4340.3</v>
       </c>
       <c r="C61" t="n">
-        <v>4347</v>
+        <v>4352.1</v>
       </c>
       <c r="D61" t="n">
         <v>4323.8</v>
       </c>
       <c r="E61" t="n">
-        <v>4340.7</v>
+        <v>4346.7</v>
       </c>
       <c r="F61" t="n">
-        <v>-68.2</v>
+        <v>-62.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0155</v>
+        <v>-0.0141</v>
       </c>
       <c r="H61" t="n">
-        <v>23.2</v>
+        <v>28.3</v>
       </c>
       <c r="I61" t="n">
         <v>4221.1</v>
@@ -5675,25 +5675,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4300.6</v>
+        <v>4295.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4320.15</v>
+        <v>4322.78</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4329.1</v>
+        <v>4332.55</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4338.05</v>
+        <v>4342.33</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4352.3</v>
+        <v>4360.85</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4366.55</v>
+        <v>4379.38</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4370.2</v>
+        <v>4380.4</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5598,22 +5598,22 @@
         <v>4340.3</v>
       </c>
       <c r="C61" t="n">
-        <v>4352.1</v>
+        <v>4358.2</v>
       </c>
       <c r="D61" t="n">
         <v>4323.8</v>
       </c>
       <c r="E61" t="n">
-        <v>4346.7</v>
+        <v>4353.8</v>
       </c>
       <c r="F61" t="n">
-        <v>-62.2</v>
+        <v>-55.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0125</v>
       </c>
       <c r="H61" t="n">
-        <v>28.3</v>
+        <v>34.4</v>
       </c>
       <c r="I61" t="n">
         <v>4221.1</v>
@@ -5675,25 +5675,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4295.5</v>
+        <v>4289.4</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4322.78</v>
+        <v>4325.8</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4332.55</v>
+        <v>4336.6</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4342.33</v>
+        <v>4347.4</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4360.85</v>
+        <v>4371</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4379.38</v>
+        <v>4394.6</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4380.4</v>
+        <v>4392.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5595,25 +5595,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4340.3</v>
+        <v>4375</v>
       </c>
       <c r="C61" t="n">
-        <v>4358.2</v>
+        <v>4396.8</v>
       </c>
       <c r="D61" t="n">
-        <v>4323.8</v>
+        <v>4293</v>
       </c>
       <c r="E61" t="n">
-        <v>4353.8</v>
+        <v>4351.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-55.1</v>
+        <v>-57</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0125</v>
+        <v>-0.0129</v>
       </c>
       <c r="H61" t="n">
-        <v>34.4</v>
+        <v>103.8</v>
       </c>
       <c r="I61" t="n">
         <v>4221.1</v>
@@ -5639,8 +5639,10 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
@@ -5669,30 +5671,112 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4340.3</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4358.2</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4323.8</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4343.2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="H62" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4189.2</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4251.6</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4300</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4348.4</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4403.8</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4459.2</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4500.6</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>4289.4</v>
       </c>
-      <c r="J62" s="13" t="n">
-        <v>4325.8</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>4336.6</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>4347.4</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>4371</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>4394.6</v>
-      </c>
-      <c r="O62" s="13" t="n">
+      <c r="J63" s="13" t="n">
+        <v>4309.9</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>4326</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>4342.1</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>4360.4</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>4378.7</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>4392.6</v>
       </c>
     </row>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,66 +641,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4279.8</v>
+        <v>4163.9</v>
       </c>
       <c r="C2" t="n">
-        <v>4323.2</v>
+        <v>4238.1</v>
       </c>
       <c r="D2" t="n">
-        <v>4223.7</v>
+        <v>4151.4</v>
       </c>
       <c r="E2" t="n">
-        <v>4224.1</v>
+        <v>4202.7</v>
       </c>
       <c r="F2" t="n">
-        <v>-134.8</v>
+        <v>-43.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0309</v>
+        <v>-0.0102</v>
       </c>
       <c r="H2" t="n">
-        <v>99.5</v>
+        <v>86.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4215</v>
+        <v>4090.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4289.1</v>
+        <v>4096.32</v>
       </c>
       <c r="K2" t="n">
-        <v>4318.4</v>
+        <v>4180.95</v>
       </c>
       <c r="L2" t="n">
-        <v>4347.7</v>
+        <v>4265.57</v>
       </c>
       <c r="M2" t="n">
-        <v>4399.4</v>
+        <v>4310.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4451.1</v>
+        <v>4356.13</v>
       </c>
       <c r="O2" t="n">
-        <v>4458</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>4480.1</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -717,64 +713,70 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4138.8</v>
+        <v>4210.8</v>
       </c>
       <c r="C3" t="n">
-        <v>4216.4</v>
+        <v>4216</v>
       </c>
       <c r="D3" t="n">
-        <v>4134.8</v>
+        <v>4108.2</v>
       </c>
       <c r="E3" t="n">
-        <v>4181.9</v>
+        <v>4149.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-42.2</v>
+        <v>-53.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0127</v>
       </c>
       <c r="H3" t="n">
-        <v>81.59999999999999</v>
+        <v>107.8</v>
       </c>
       <c r="I3" t="n">
-        <v>4124.2</v>
+        <v>4064.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4099.93</v>
+        <v>4119.98</v>
       </c>
       <c r="K3" t="n">
-        <v>4174.35</v>
+        <v>4159.35</v>
       </c>
       <c r="L3" t="n">
-        <v>4248.78</v>
+        <v>4198.73</v>
       </c>
       <c r="M3" t="n">
-        <v>4273.85</v>
+        <v>4246.05</v>
       </c>
       <c r="N3" t="n">
-        <v>4298.93</v>
+        <v>4293.38</v>
       </c>
       <c r="O3" t="n">
-        <v>4422.7</v>
+        <v>4324.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
@@ -797,68 +799,76 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4127.1</v>
+        <v>4130</v>
       </c>
       <c r="C4" t="n">
-        <v>4135.2</v>
+        <v>4132.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4118.5</v>
+        <v>3975.7</v>
       </c>
       <c r="E4" t="n">
-        <v>4129.9</v>
+        <v>4008.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-52</v>
+        <v>-140.6</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0339</v>
       </c>
       <c r="H4" t="n">
-        <v>16.7</v>
+        <v>156.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4053.2</v>
+        <v>4000.4</v>
       </c>
       <c r="J4" t="n">
-        <v>4103.45</v>
+        <v>4035.25</v>
       </c>
       <c r="K4" t="n">
-        <v>4141.1</v>
+        <v>4095.5</v>
       </c>
       <c r="L4" t="n">
-        <v>4178.75</v>
+        <v>4155.75</v>
       </c>
       <c r="M4" t="n">
-        <v>4222.7</v>
+        <v>4203.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4266.65</v>
+        <v>4250.85</v>
       </c>
       <c r="O4" t="n">
-        <v>4298</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>4323.8</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -875,7 +885,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -885,69 +895,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4104.4</v>
+        <v>4019</v>
       </c>
       <c r="C5" t="n">
-        <v>4104.7</v>
+        <v>4060</v>
       </c>
       <c r="D5" t="n">
-        <v>3963.3</v>
+        <v>3976.3</v>
       </c>
       <c r="E5" t="n">
-        <v>3990.3</v>
+        <v>4047.6</v>
       </c>
       <c r="F5" t="n">
-        <v>-139.6</v>
+        <v>38.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0338</v>
+        <v>0.0097</v>
       </c>
       <c r="H5" t="n">
-        <v>141.4</v>
+        <v>83.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4101.8</v>
+        <v>3819</v>
       </c>
       <c r="J5" t="n">
-        <v>4114.72</v>
+        <v>3829.48</v>
       </c>
       <c r="K5" t="n">
-        <v>4121.55</v>
+        <v>3930.45</v>
       </c>
       <c r="L5" t="n">
-        <v>4128.38</v>
+        <v>4031.42</v>
       </c>
       <c r="M5" t="n">
-        <v>4138.25</v>
+        <v>4087.15</v>
       </c>
       <c r="N5" t="n">
-        <v>4148.12</v>
+        <v>4142.88</v>
       </c>
       <c r="O5" t="n">
-        <v>4151.9</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4289.1</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -959,60 +963,64 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3988.4</v>
+        <v>4044.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4030.5</v>
+        <v>4111.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3986.7</v>
+        <v>3998.1</v>
       </c>
       <c r="E6" t="n">
-        <v>4030.5</v>
+        <v>4096.3</v>
       </c>
       <c r="F6" t="n">
-        <v>40.2</v>
+        <v>48.7</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.012</v>
       </c>
       <c r="H6" t="n">
-        <v>43.8</v>
+        <v>113.4</v>
       </c>
       <c r="I6" t="n">
-        <v>3821.9</v>
+        <v>3892.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3827.05</v>
+        <v>3978.63</v>
       </c>
       <c r="K6" t="n">
-        <v>3919.6</v>
+        <v>4005.75</v>
       </c>
       <c r="L6" t="n">
-        <v>4012.15</v>
+        <v>4032.88</v>
       </c>
       <c r="M6" t="n">
-        <v>4061</v>
+        <v>4089.45</v>
       </c>
       <c r="N6" t="n">
-        <v>4109.85</v>
+        <v>4146.03</v>
       </c>
       <c r="O6" t="n">
-        <v>4246.1</v>
+        <v>4143.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,16 +1028,20 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1037,64 +1049,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4078.7</v>
+        <v>4101.1</v>
       </c>
       <c r="C7" t="n">
-        <v>4078.7</v>
+        <v>4102.9</v>
       </c>
       <c r="D7" t="n">
-        <v>4078.7</v>
+        <v>4012</v>
       </c>
       <c r="E7" t="n">
-        <v>4078.7</v>
+        <v>4038.9</v>
       </c>
       <c r="F7" t="n">
-        <v>48.2</v>
+        <v>-57.4</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3942.9</v>
+        <v>3884.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3997.65</v>
+        <v>4003.65</v>
       </c>
       <c r="K7" t="n">
-        <v>4008.6</v>
+        <v>4039.6</v>
       </c>
       <c r="L7" t="n">
-        <v>4019.55</v>
+        <v>4075.55</v>
       </c>
       <c r="M7" t="n">
-        <v>4052.4</v>
+        <v>4153</v>
       </c>
       <c r="N7" t="n">
-        <v>4085.25</v>
+        <v>4230.45</v>
       </c>
       <c r="O7" t="n">
-        <v>4074.3</v>
+        <v>4224.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,104 +1114,98 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4057.5</v>
+        <v>4032.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4070</v>
+        <v>4078.1</v>
       </c>
       <c r="D8" t="n">
-        <v>4003.2</v>
+        <v>3955.4</v>
       </c>
       <c r="E8" t="n">
-        <v>4022.3</v>
+        <v>4038.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-56.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.0001</v>
       </c>
       <c r="H8" t="n">
-        <v>66.8</v>
+        <v>122.7</v>
       </c>
       <c r="I8" t="n">
-        <v>4078.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J8" t="n">
-        <v>4078.7</v>
+        <v>3938.72</v>
       </c>
       <c r="K8" t="n">
-        <v>4078.7</v>
+        <v>3993.45</v>
       </c>
       <c r="L8" t="n">
-        <v>4078.7</v>
+        <v>4048.17</v>
       </c>
       <c r="M8" t="n">
-        <v>4078.7</v>
+        <v>4084.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4078.7</v>
+        <v>4120.52</v>
       </c>
       <c r="O8" t="n">
-        <v>4078.7</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>4193.8</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1211,7 +1217,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1221,50 +1227,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4002.6</v>
+        <v>4025</v>
       </c>
       <c r="C9" t="n">
-        <v>4049.7</v>
+        <v>4131</v>
       </c>
       <c r="D9" t="n">
-        <v>3962.5</v>
+        <v>3973</v>
       </c>
       <c r="E9" t="n">
-        <v>4022.9</v>
+        <v>4082.4</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6</v>
+        <v>43.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H9" t="n">
-        <v>87.2</v>
+        <v>158</v>
       </c>
       <c r="I9" t="n">
-        <v>3936.4</v>
+        <v>3832.7</v>
       </c>
       <c r="J9" t="n">
-        <v>3948.35</v>
+        <v>3926.67</v>
       </c>
       <c r="K9" t="n">
-        <v>3988.9</v>
+        <v>3977.15</v>
       </c>
       <c r="L9" t="n">
-        <v>4029.45</v>
+        <v>4027.62</v>
       </c>
       <c r="M9" t="n">
-        <v>4055.7</v>
+        <v>4099.85</v>
       </c>
       <c r="N9" t="n">
-        <v>4081.95</v>
+        <v>4172.08</v>
       </c>
       <c r="O9" t="n">
-        <v>4136.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,13 +1283,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1291,64 +1299,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4013.1</v>
+        <v>4049.2</v>
       </c>
       <c r="C10" t="n">
-        <v>4100</v>
+        <v>4157.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3963</v>
+        <v>4042.8</v>
       </c>
       <c r="E10" t="n">
-        <v>4068.3</v>
+        <v>4125.7</v>
       </c>
       <c r="F10" t="n">
-        <v>45.4</v>
+        <v>43.3</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0113</v>
+        <v>0.0106</v>
       </c>
       <c r="H10" t="n">
-        <v>137</v>
+        <v>114.3</v>
       </c>
       <c r="I10" t="n">
-        <v>3875.3</v>
+        <v>3815</v>
       </c>
       <c r="J10" t="n">
-        <v>3944.1</v>
+        <v>3939.6</v>
       </c>
       <c r="K10" t="n">
-        <v>3979.3</v>
+        <v>4003.4</v>
       </c>
       <c r="L10" t="n">
-        <v>4014.5</v>
+        <v>4067.2</v>
       </c>
       <c r="M10" t="n">
-        <v>4066.5</v>
+        <v>4161.4</v>
       </c>
       <c r="N10" t="n">
-        <v>4118.5</v>
+        <v>4255.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4136.9</v>
+        <v>4289</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,12 +1364,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1377,7 +1383,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1391,50 +1397,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4067.5</v>
+        <v>4187.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4140.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D11" t="n">
-        <v>4062</v>
+        <v>4140.6</v>
       </c>
       <c r="E11" t="n">
-        <v>4112.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F11" t="n">
-        <v>44.4</v>
+        <v>41.8</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0101</v>
       </c>
       <c r="H11" t="n">
-        <v>78.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3826</v>
+        <v>3928.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3949.7</v>
+        <v>4024.28</v>
       </c>
       <c r="K11" t="n">
-        <v>3999.8</v>
+        <v>4068.55</v>
       </c>
       <c r="L11" t="n">
-        <v>4049.9</v>
+        <v>4112.83</v>
       </c>
       <c r="M11" t="n">
-        <v>4136.8</v>
+        <v>4182.85</v>
       </c>
       <c r="N11" t="n">
-        <v>4223.7</v>
+        <v>4252.88</v>
       </c>
       <c r="O11" t="n">
-        <v>4237</v>
+        <v>4271.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,7 +1451,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1461,7 +1467,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1475,50 +1481,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4175.4</v>
+        <v>4176.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4199.7</v>
+        <v>4192.4</v>
       </c>
       <c r="D12" t="n">
-        <v>4134.2</v>
+        <v>4102.7</v>
       </c>
       <c r="E12" t="n">
-        <v>4155.1</v>
+        <v>4157.4</v>
       </c>
       <c r="F12" t="n">
-        <v>42.4</v>
+        <v>-10.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0103</v>
+        <v>-0.0024</v>
       </c>
       <c r="H12" t="n">
-        <v>65.5</v>
+        <v>89.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3983.9</v>
+        <v>4065.7</v>
       </c>
       <c r="J12" t="n">
-        <v>4040.43</v>
+        <v>4087.33</v>
       </c>
       <c r="K12" t="n">
-        <v>4073.65</v>
+        <v>4130.05</v>
       </c>
       <c r="L12" t="n">
-        <v>4106.88</v>
+        <v>4172.78</v>
       </c>
       <c r="M12" t="n">
-        <v>4151.75</v>
+        <v>4204.95</v>
       </c>
       <c r="N12" t="n">
-        <v>4196.63</v>
+        <v>4237.12</v>
       </c>
       <c r="O12" t="n">
-        <v>4218.2</v>
+        <v>4290.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,91 +1532,87 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4126.5</v>
+        <v>4106.5</v>
       </c>
       <c r="C13" t="n">
-        <v>4167.2</v>
+        <v>4144.7</v>
       </c>
       <c r="D13" t="n">
-        <v>4107.2</v>
+        <v>4032.5</v>
       </c>
       <c r="E13" t="n">
-        <v>4145.3</v>
+        <v>4082.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.800000000000001</v>
+        <v>-75</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H13" t="n">
-        <v>60</v>
+        <v>112.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4068.7</v>
+        <v>4013</v>
       </c>
       <c r="J13" t="n">
-        <v>4083.68</v>
+        <v>4072.63</v>
       </c>
       <c r="K13" t="n">
-        <v>4122.35</v>
+        <v>4112.55</v>
       </c>
       <c r="L13" t="n">
-        <v>4161.03</v>
+        <v>4152.47</v>
       </c>
       <c r="M13" t="n">
-        <v>4187.85</v>
+        <v>4202.25</v>
       </c>
       <c r="N13" t="n">
-        <v>4214.68</v>
+        <v>4252.02</v>
       </c>
       <c r="O13" t="n">
-        <v>4265.2</v>
+        <v>4282.1</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
@@ -1619,7 +1621,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1631,7 +1633,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1641,132 +1643,134 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4116.3</v>
+        <v>4087.6</v>
       </c>
       <c r="C14" t="n">
-        <v>4120.3</v>
+        <v>4148.4</v>
       </c>
       <c r="D14" t="n">
-        <v>4053</v>
+        <v>4063.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4070.9</v>
+        <v>4140.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-74.40000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.0143</v>
       </c>
       <c r="H14" t="n">
-        <v>67.3</v>
+        <v>85</v>
       </c>
       <c r="I14" t="n">
-        <v>4047.2</v>
+        <v>3920.3</v>
       </c>
       <c r="J14" t="n">
-        <v>4089.35</v>
+        <v>3967.1</v>
       </c>
       <c r="K14" t="n">
-        <v>4115.3</v>
+        <v>4026.3</v>
       </c>
       <c r="L14" t="n">
-        <v>4141.25</v>
+        <v>4085.5</v>
       </c>
       <c r="M14" t="n">
-        <v>4175.3</v>
+        <v>4138.5</v>
       </c>
       <c r="N14" t="n">
-        <v>4209.35</v>
+        <v>4191.5</v>
       </c>
       <c r="O14" t="n">
-        <v>4227.2</v>
+        <v>4256.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4066.4</v>
+        <v>4135.4</v>
       </c>
       <c r="C15" t="n">
-        <v>4130.6</v>
+        <v>4144.6</v>
       </c>
       <c r="D15" t="n">
-        <v>4064.2</v>
+        <v>4081.7</v>
       </c>
       <c r="E15" t="n">
-        <v>4130.6</v>
+        <v>4113.7</v>
       </c>
       <c r="F15" t="n">
-        <v>59.7</v>
+        <v>-27.1</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0147</v>
+        <v>-0.0065</v>
       </c>
       <c r="H15" t="n">
-        <v>66.40000000000001</v>
+        <v>62.9</v>
       </c>
       <c r="I15" t="n">
-        <v>3985.7</v>
+        <v>3978.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3995.73</v>
+        <v>4073.25</v>
       </c>
       <c r="K15" t="n">
-        <v>4037.25</v>
+        <v>4098.3</v>
       </c>
       <c r="L15" t="n">
-        <v>4078.77</v>
+        <v>4123.35</v>
       </c>
       <c r="M15" t="n">
-        <v>4104.55</v>
+        <v>4183.3</v>
       </c>
       <c r="N15" t="n">
-        <v>4130.32</v>
+        <v>4243.25</v>
       </c>
       <c r="O15" t="n">
-        <v>4187.6</v>
+        <v>4233.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,91 +1778,97 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4122.3</v>
+        <v>4106.6</v>
       </c>
       <c r="C16" t="n">
-        <v>4125.8</v>
+        <v>4111.6</v>
       </c>
       <c r="D16" t="n">
-        <v>4090.6</v>
+        <v>3992.9</v>
       </c>
       <c r="E16" t="n">
-        <v>4104.1</v>
+        <v>4005.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-26.5</v>
+        <v>-108</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0064</v>
+        <v>-0.0263</v>
       </c>
       <c r="H16" t="n">
-        <v>35.2</v>
+        <v>118.7</v>
       </c>
       <c r="I16" t="n">
-        <v>3997.8</v>
+        <v>4018.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4080.8</v>
+        <v>4051.08</v>
       </c>
       <c r="K16" t="n">
-        <v>4097.4</v>
+        <v>4082.25</v>
       </c>
       <c r="L16" t="n">
-        <v>4114</v>
+        <v>4113.43</v>
       </c>
       <c r="M16" t="n">
-        <v>4163.8</v>
+        <v>4145.15</v>
       </c>
       <c r="N16" t="n">
-        <v>4213.6</v>
+        <v>4176.88</v>
       </c>
       <c r="O16" t="n">
-        <v>4197</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
@@ -1875,148 +1885,146 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4081</v>
+        <v>4005.9</v>
       </c>
       <c r="C17" t="n">
-        <v>4081</v>
+        <v>4112.5</v>
       </c>
       <c r="D17" t="n">
-        <v>3985.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E17" t="n">
-        <v>3997</v>
+        <v>4069.7</v>
       </c>
       <c r="F17" t="n">
-        <v>-107.1</v>
+        <v>64</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0261</v>
+        <v>0.016</v>
       </c>
       <c r="H17" t="n">
-        <v>95.09999999999999</v>
+        <v>122.1</v>
       </c>
       <c r="I17" t="n">
-        <v>4055.4</v>
+        <v>3874.2</v>
       </c>
       <c r="J17" t="n">
-        <v>4066.85</v>
+        <v>3863.72</v>
       </c>
       <c r="K17" t="n">
-        <v>4086.5</v>
+        <v>3946.35</v>
       </c>
       <c r="L17" t="n">
-        <v>4106.15</v>
+        <v>4028.97</v>
       </c>
       <c r="M17" t="n">
-        <v>4121.7</v>
+        <v>4065.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4137.25</v>
+        <v>4101.13</v>
       </c>
       <c r="O17" t="n">
-        <v>4161</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3995.7</v>
+        <v>4059.8</v>
       </c>
       <c r="C18" t="n">
-        <v>4091.2</v>
+        <v>4089.1</v>
       </c>
       <c r="D18" t="n">
-        <v>3986.5</v>
+        <v>4023.3</v>
       </c>
       <c r="E18" t="n">
-        <v>4061.1</v>
+        <v>4051.8</v>
       </c>
       <c r="F18" t="n">
-        <v>64.09999999999999</v>
+        <v>-17.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H18" t="n">
-        <v>104.7</v>
+        <v>65.8</v>
       </c>
       <c r="I18" t="n">
-        <v>3890.8</v>
+        <v>3868.3</v>
       </c>
       <c r="J18" t="n">
-        <v>3883.67</v>
+        <v>3956.72</v>
       </c>
       <c r="K18" t="n">
-        <v>3949.45</v>
+        <v>4008.65</v>
       </c>
       <c r="L18" t="n">
-        <v>4015.22</v>
+        <v>4060.57</v>
       </c>
       <c r="M18" t="n">
-        <v>4044.55</v>
+        <v>4130.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4073.88</v>
+        <v>4200.93</v>
       </c>
       <c r="O18" t="n">
-        <v>4176.1</v>
+        <v>4234.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2027,95 +2035,95 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4049.1</v>
+        <v>4068.9</v>
       </c>
       <c r="C19" t="n">
-        <v>4070.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D19" t="n">
-        <v>4019.4</v>
+        <v>3973.4</v>
       </c>
       <c r="E19" t="n">
-        <v>4044</v>
+        <v>3992.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-17.1</v>
+        <v>-59.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0042</v>
+        <v>-0.0147</v>
       </c>
       <c r="H19" t="n">
-        <v>50.7</v>
+        <v>98.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3881.8</v>
+        <v>3957.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3967.53</v>
+        <v>3983.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4008.75</v>
+        <v>4018.9</v>
       </c>
       <c r="L19" t="n">
-        <v>4049.98</v>
+        <v>4054</v>
       </c>
       <c r="M19" t="n">
-        <v>4113.45</v>
+        <v>4084.7</v>
       </c>
       <c r="N19" t="n">
-        <v>4176.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4195.9</v>
+        <v>4154.9</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2127,81 +2135,73 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4030.5</v>
+        <v>3980.1</v>
       </c>
       <c r="C20" t="n">
-        <v>4030.5</v>
+        <v>4028.9</v>
       </c>
       <c r="D20" t="n">
-        <v>3972.6</v>
+        <v>3963</v>
       </c>
       <c r="E20" t="n">
-        <v>3985.6</v>
+        <v>4018.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-58.4</v>
+        <v>26.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0144</v>
+        <v>0.0067</v>
       </c>
       <c r="H20" t="n">
-        <v>57.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>3968.7</v>
+        <v>3874.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3992.92</v>
+        <v>3878.33</v>
       </c>
       <c r="K20" t="n">
-        <v>4018.65</v>
+        <v>3942.85</v>
       </c>
       <c r="L20" t="n">
-        <v>4044.38</v>
+        <v>4007.38</v>
       </c>
       <c r="M20" t="n">
-        <v>4069.35</v>
+        <v>4041.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4094.33</v>
+        <v>4075.33</v>
       </c>
       <c r="O20" t="n">
-        <v>4120.8</v>
+        <v>4170.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2213,60 +2213,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3975.5</v>
+        <v>4005.6</v>
       </c>
       <c r="C21" t="n">
-        <v>4017.2</v>
+        <v>4046</v>
       </c>
       <c r="D21" t="n">
-        <v>3964.2</v>
+        <v>3986.5</v>
       </c>
       <c r="E21" t="n">
-        <v>4012.7</v>
+        <v>4015.9</v>
       </c>
       <c r="F21" t="n">
-        <v>27.1</v>
+        <v>-2.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0068</v>
+        <v>-0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>53</v>
+        <v>59.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3914.7</v>
+        <v>3897.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3919.73</v>
+        <v>3964.33</v>
       </c>
       <c r="K21" t="n">
-        <v>3956.65</v>
+        <v>3985.85</v>
       </c>
       <c r="L21" t="n">
-        <v>3993.58</v>
+        <v>4007.38</v>
       </c>
       <c r="M21" t="n">
-        <v>4014.55</v>
+        <v>4051.75</v>
       </c>
       <c r="N21" t="n">
-        <v>4035.53</v>
+        <v>4096.12</v>
       </c>
       <c r="O21" t="n">
-        <v>4088.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2277,15 +2281,13 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2293,64 +2295,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4003.4</v>
+        <v>4013.4</v>
       </c>
       <c r="C22" t="n">
-        <v>4018.9</v>
+        <v>4092.5</v>
       </c>
       <c r="D22" t="n">
-        <v>4002.7</v>
+        <v>4003.3</v>
       </c>
       <c r="E22" t="n">
-        <v>4010.3</v>
+        <v>4076.4</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4</v>
+        <v>60.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0151</v>
       </c>
       <c r="H22" t="n">
-        <v>16.2</v>
+        <v>89.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3911.2</v>
+        <v>3927</v>
       </c>
       <c r="J22" t="n">
-        <v>3970.7</v>
+        <v>3956.22</v>
       </c>
       <c r="K22" t="n">
-        <v>3986.2</v>
+        <v>3986.15</v>
       </c>
       <c r="L22" t="n">
-        <v>4001.7</v>
+        <v>4016.07</v>
       </c>
       <c r="M22" t="n">
-        <v>4039.2</v>
+        <v>4045.65</v>
       </c>
       <c r="N22" t="n">
-        <v>4076.7</v>
+        <v>4075.22</v>
       </c>
       <c r="O22" t="n">
-        <v>4070.2</v>
+        <v>4105.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2361,78 +2363,78 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4002.1</v>
+        <v>4084.7</v>
       </c>
       <c r="C23" t="n">
-        <v>4071.1</v>
+        <v>4171.4</v>
       </c>
       <c r="D23" t="n">
-        <v>3999.7</v>
+        <v>4081</v>
       </c>
       <c r="E23" t="n">
-        <v>4071.1</v>
+        <v>4151.9</v>
       </c>
       <c r="F23" t="n">
-        <v>60.8</v>
+        <v>75.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0185</v>
       </c>
       <c r="H23" t="n">
-        <v>71.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>3986.5</v>
+        <v>3914.1</v>
       </c>
       <c r="J23" t="n">
-        <v>3993.85</v>
+        <v>4001.45</v>
       </c>
       <c r="K23" t="n">
-        <v>4002.2</v>
+        <v>4031.8</v>
       </c>
       <c r="L23" t="n">
-        <v>4010.55</v>
+        <v>4062.15</v>
       </c>
       <c r="M23" t="n">
-        <v>4018.4</v>
+        <v>4121</v>
       </c>
       <c r="N23" t="n">
-        <v>4026.25</v>
+        <v>4179.85</v>
       </c>
       <c r="O23" t="n">
-        <v>4035.1</v>
+        <v>4181.7</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,120 +2442,112 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4096.2</v>
+        <v>4126</v>
       </c>
       <c r="C24" t="n">
-        <v>4152.1</v>
+        <v>4144</v>
       </c>
       <c r="D24" t="n">
-        <v>4096.2</v>
+        <v>4042.5</v>
       </c>
       <c r="E24" t="n">
-        <v>4146.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F24" t="n">
-        <v>75.8</v>
+        <v>-101.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0186</v>
+        <v>-0.0245</v>
       </c>
       <c r="H24" t="n">
-        <v>55.9</v>
+        <v>101.5</v>
       </c>
       <c r="I24" t="n">
-        <v>3928.3</v>
+        <v>3990.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4017.55</v>
+        <v>4074.35</v>
       </c>
       <c r="K24" t="n">
-        <v>4035.4</v>
+        <v>4106.7</v>
       </c>
       <c r="L24" t="n">
-        <v>4053.25</v>
+        <v>4139.05</v>
       </c>
       <c r="M24" t="n">
-        <v>4106.8</v>
+        <v>4197.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4160.35</v>
+        <v>4255.15</v>
       </c>
       <c r="O24" t="n">
-        <v>4142.5</v>
+        <v>4261.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2561,69 +2555,63 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4129.9</v>
+        <v>4053.4</v>
       </c>
       <c r="C25" t="n">
-        <v>4130.9</v>
+        <v>4085.2</v>
       </c>
       <c r="D25" t="n">
-        <v>4046.6</v>
+        <v>4024</v>
       </c>
       <c r="E25" t="n">
-        <v>4046.6</v>
+        <v>4070.8</v>
       </c>
       <c r="F25" t="n">
-        <v>-100.3</v>
+        <v>20.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0242</v>
+        <v>0.0051</v>
       </c>
       <c r="H25" t="n">
-        <v>84.3</v>
+        <v>61.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4040.3</v>
+        <v>3941</v>
       </c>
       <c r="J25" t="n">
-        <v>4102.37</v>
+        <v>3927.17</v>
       </c>
       <c r="K25" t="n">
-        <v>4118.95</v>
+        <v>3999.45</v>
       </c>
       <c r="L25" t="n">
-        <v>4135.53</v>
+        <v>4071.72</v>
       </c>
       <c r="M25" t="n">
-        <v>4174.85</v>
+        <v>4100.95</v>
       </c>
       <c r="N25" t="n">
-        <v>4214.17</v>
+        <v>4130.17</v>
       </c>
       <c r="O25" t="n">
-        <v>4208</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4245.5</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2635,60 +2623,64 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4067.6</v>
+        <v>4097.5</v>
       </c>
       <c r="C26" t="n">
-        <v>4068</v>
+        <v>4119.3</v>
       </c>
       <c r="D26" t="n">
-        <v>4067.6</v>
+        <v>4067.1</v>
       </c>
       <c r="E26" t="n">
-        <v>4067.6</v>
+        <v>4077</v>
       </c>
       <c r="F26" t="n">
-        <v>21</v>
+        <v>6.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0015</v>
       </c>
       <c r="H26" t="n">
-        <v>0.4</v>
+        <v>52.2</v>
       </c>
       <c r="I26" t="n">
-        <v>3962.3</v>
+        <v>3962.8</v>
       </c>
       <c r="J26" t="n">
-        <v>3941.23</v>
+        <v>4017.7</v>
       </c>
       <c r="K26" t="n">
-        <v>4004.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L26" t="n">
-        <v>4067.68</v>
+        <v>4062.7</v>
       </c>
       <c r="M26" t="n">
-        <v>4088.75</v>
+        <v>4101.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4109.82</v>
+        <v>4140.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4215.2</v>
+        <v>4146.4</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2699,13 +2691,15 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2713,97 +2707,97 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4090.1</v>
+        <v>4083</v>
       </c>
       <c r="C27" t="n">
-        <v>4107.9</v>
+        <v>4085.7</v>
       </c>
       <c r="D27" t="n">
-        <v>4072.7</v>
+        <v>4011.1</v>
       </c>
       <c r="E27" t="n">
-        <v>4074.5</v>
+        <v>4038.7</v>
       </c>
       <c r="F27" t="n">
-        <v>6.9</v>
+        <v>-38.3</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.0094</v>
       </c>
       <c r="H27" t="n">
-        <v>35.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>4067.2</v>
+        <v>4014.9</v>
       </c>
       <c r="J27" t="n">
-        <v>4067.1</v>
+        <v>4016.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4067.4</v>
+        <v>4050.9</v>
       </c>
       <c r="L27" t="n">
-        <v>4067.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M27" t="n">
-        <v>4067.8</v>
+        <v>4103.1</v>
       </c>
       <c r="N27" t="n">
-        <v>4067.9</v>
+        <v>4121.1</v>
       </c>
       <c r="O27" t="n">
-        <v>4068.4</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V27" s="8" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2811,159 +2805,157 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4025.7</v>
+        <v>4020.9</v>
       </c>
       <c r="C28" t="n">
-        <v>4036.3</v>
+        <v>4115.2</v>
       </c>
       <c r="D28" t="n">
-        <v>4025.7</v>
+        <v>3993.8</v>
       </c>
       <c r="E28" t="n">
         <v>4036.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-38.2</v>
+        <v>-2.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>10.6</v>
+        <v>121.4</v>
       </c>
       <c r="I28" t="n">
-        <v>4037.5</v>
+        <v>3936.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4031.4</v>
+        <v>3959.25</v>
       </c>
       <c r="K28" t="n">
-        <v>4056.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L28" t="n">
-        <v>4082.4</v>
+        <v>4043.55</v>
       </c>
       <c r="M28" t="n">
-        <v>4092.1</v>
+        <v>4076</v>
       </c>
       <c r="N28" t="n">
-        <v>4101.8</v>
+        <v>4108.45</v>
       </c>
       <c r="O28" t="n">
-        <v>4143.1</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4018.1</v>
+        <v>4060.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4034.7</v>
+        <v>4118.5</v>
       </c>
       <c r="D29" t="n">
-        <v>4017.9</v>
+        <v>4028.5</v>
       </c>
       <c r="E29" t="n">
-        <v>4034.7</v>
+        <v>4100.1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.6</v>
+        <v>63.8</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0004</v>
+        <v>0.0158</v>
       </c>
       <c r="H29" t="n">
-        <v>16.8</v>
+        <v>90</v>
       </c>
       <c r="I29" t="n">
-        <v>4015.1</v>
+        <v>3872.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4028.35</v>
+        <v>3905.8</v>
       </c>
       <c r="K29" t="n">
-        <v>4031</v>
+        <v>3975.6</v>
       </c>
       <c r="L29" t="n">
-        <v>4033.65</v>
+        <v>4045.4</v>
       </c>
       <c r="M29" t="n">
-        <v>4041.6</v>
+        <v>4097</v>
       </c>
       <c r="N29" t="n">
-        <v>4049.55</v>
+        <v>4148.6</v>
       </c>
       <c r="O29" t="n">
-        <v>4046.9</v>
+        <v>4236.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2971,9 +2963,9 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W29" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -2985,50 +2977,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C30" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D30" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E30" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F30" t="n">
-        <v>65.40000000000001</v>
+        <v>6.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0162</v>
+        <v>0.0017</v>
       </c>
       <c r="H30" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4001.1</v>
+        <v>3938.5</v>
       </c>
       <c r="J30" t="n">
-        <v>4022.1</v>
+        <v>4023.4</v>
       </c>
       <c r="K30" t="n">
-        <v>4026.3</v>
+        <v>4055.1</v>
       </c>
       <c r="L30" t="n">
-        <v>4030.5</v>
+        <v>4086.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4043.1</v>
+        <v>4145.1</v>
       </c>
       <c r="N30" t="n">
-        <v>4055.7</v>
+        <v>4203.4</v>
       </c>
       <c r="O30" t="n">
-        <v>4051.5</v>
+        <v>4208.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3039,9 +3031,9 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
@@ -3049,87 +3041,83 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4102.4</v>
+        <v>4135.2</v>
       </c>
       <c r="C31" t="n">
-        <v>4102.4</v>
+        <v>4145.5</v>
       </c>
       <c r="D31" t="n">
-        <v>4022.4</v>
+        <v>4074</v>
       </c>
       <c r="E31" t="n">
-        <v>4049.1</v>
+        <v>4090.5</v>
       </c>
       <c r="F31" t="n">
-        <v>-51</v>
+        <v>-16.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>80</v>
+        <v>71.5</v>
       </c>
       <c r="I31" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J31" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K31" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L31" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M31" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N31" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O31" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3141,64 +3129,60 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4083.4</v>
+        <v>4109.6</v>
       </c>
       <c r="C32" t="n">
-        <v>4083.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4026.5</v>
+        <v>4098.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4033.7</v>
+        <v>4152.6</v>
       </c>
       <c r="F32" t="n">
-        <v>-15.4</v>
+        <v>62.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0038</v>
+        <v>0.0152</v>
       </c>
       <c r="H32" t="n">
-        <v>57</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>3942.4</v>
+        <v>4002.5</v>
       </c>
       <c r="J32" t="n">
-        <v>3962.45</v>
+        <v>4009.38</v>
       </c>
       <c r="K32" t="n">
-        <v>4009.1</v>
+        <v>4054.75</v>
       </c>
       <c r="L32" t="n">
-        <v>4055.75</v>
+        <v>4100.12</v>
       </c>
       <c r="M32" t="n">
-        <v>4089.1</v>
+        <v>4126.25</v>
       </c>
       <c r="N32" t="n">
-        <v>4122.45</v>
+        <v>4152.38</v>
       </c>
       <c r="O32" t="n">
-        <v>4182.4</v>
+        <v>4217</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,78 +3193,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4050.5</v>
+        <v>4133.8</v>
       </c>
       <c r="C33" t="n">
-        <v>4095.4</v>
+        <v>4328.2</v>
       </c>
       <c r="D33" t="n">
-        <v>4048.8</v>
+        <v>4121.6</v>
       </c>
       <c r="E33" t="n">
-        <v>4095.4</v>
+        <v>4305.2</v>
       </c>
       <c r="F33" t="n">
-        <v>61.7</v>
+        <v>152.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0153</v>
+        <v>0.0367</v>
       </c>
       <c r="H33" t="n">
-        <v>46.6</v>
+        <v>206.6</v>
       </c>
       <c r="I33" t="n">
-        <v>3969.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J33" t="n">
-        <v>3966.05</v>
+        <v>4097.8</v>
       </c>
       <c r="K33" t="n">
-        <v>4005.2</v>
+        <v>4119.8</v>
       </c>
       <c r="L33" t="n">
-        <v>4044.35</v>
+        <v>4141.8</v>
       </c>
       <c r="M33" t="n">
-        <v>4062.2</v>
+        <v>4185.4</v>
       </c>
       <c r="N33" t="n">
-        <v>4080.05</v>
+        <v>4229</v>
       </c>
       <c r="O33" t="n">
-        <v>4140.5</v>
+        <v>4229.4</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,7 +3275,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3303,13 +3287,15 @@
       </c>
       <c r="U33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3319,50 +3305,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4130</v>
+        <v>4307</v>
       </c>
       <c r="C34" t="n">
-        <v>4262.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D34" t="n">
-        <v>4129.5</v>
+        <v>4281.2</v>
       </c>
       <c r="E34" t="n">
-        <v>4245.8</v>
+        <v>4299.6</v>
       </c>
       <c r="F34" t="n">
-        <v>150.4</v>
+        <v>-5.6</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H34" t="n">
-        <v>132.7</v>
+        <v>82.5</v>
       </c>
       <c r="I34" t="n">
-        <v>4002.2</v>
+        <v>3915</v>
       </c>
       <c r="J34" t="n">
-        <v>4060.45</v>
+        <v>4138.75</v>
       </c>
       <c r="K34" t="n">
-        <v>4072.1</v>
+        <v>4201.9</v>
       </c>
       <c r="L34" t="n">
-        <v>4083.75</v>
+        <v>4265.05</v>
       </c>
       <c r="M34" t="n">
-        <v>4118.7</v>
+        <v>4408.5</v>
       </c>
       <c r="N34" t="n">
-        <v>4153.65</v>
+        <v>4551.95</v>
       </c>
       <c r="O34" t="n">
-        <v>4142</v>
+        <v>4534.8</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3373,80 +3359,78 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4297</v>
+        <v>4298.3</v>
       </c>
       <c r="C35" t="n">
-        <v>4297</v>
+        <v>4432.3</v>
       </c>
       <c r="D35" t="n">
-        <v>4228</v>
+        <v>4288</v>
       </c>
       <c r="E35" t="n">
-        <v>4242</v>
+        <v>4399.7</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.8</v>
+        <v>100.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0009</v>
+        <v>0.0233</v>
       </c>
       <c r="H35" t="n">
-        <v>69</v>
+        <v>144.3</v>
       </c>
       <c r="I35" t="n">
-        <v>3996.8</v>
+        <v>4198.7</v>
       </c>
       <c r="J35" t="n">
-        <v>4138.07</v>
+        <v>4205.68</v>
       </c>
       <c r="K35" t="n">
-        <v>4179.45</v>
+        <v>4258.35</v>
       </c>
       <c r="L35" t="n">
-        <v>4220.82</v>
+        <v>4311.03</v>
       </c>
       <c r="M35" t="n">
-        <v>4312.15</v>
+        <v>4340.85</v>
       </c>
       <c r="N35" t="n">
-        <v>4403.47</v>
+        <v>4370.68</v>
       </c>
       <c r="O35" t="n">
-        <v>4394.9</v>
+        <v>4446.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3457,78 +3441,78 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4277</v>
+        <v>4400</v>
       </c>
       <c r="C36" t="n">
-        <v>4371.5</v>
+        <v>4453.8</v>
       </c>
       <c r="D36" t="n">
-        <v>4274</v>
+        <v>4373.9</v>
       </c>
       <c r="E36" t="n">
-        <v>4340.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F36" t="n">
-        <v>98.7</v>
+        <v>20</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H36" t="n">
-        <v>97.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>4159</v>
+        <v>4143.7</v>
       </c>
       <c r="J36" t="n">
-        <v>4162.75</v>
+        <v>4275.18</v>
       </c>
       <c r="K36" t="n">
-        <v>4207.5</v>
+        <v>4327.55</v>
       </c>
       <c r="L36" t="n">
-        <v>4252.25</v>
+        <v>4379.93</v>
       </c>
       <c r="M36" t="n">
-        <v>4276.5</v>
+        <v>4471.85</v>
       </c>
       <c r="N36" t="n">
-        <v>4300.75</v>
+        <v>4563.78</v>
       </c>
       <c r="O36" t="n">
-        <v>4366</v>
+        <v>4576.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3539,27 +3523,21 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3569,50 +3547,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4336.1</v>
+        <v>4446.9</v>
       </c>
       <c r="C37" t="n">
-        <v>4390.1</v>
+        <v>4495</v>
       </c>
       <c r="D37" t="n">
-        <v>4336.1</v>
+        <v>4415.7</v>
       </c>
       <c r="E37" t="n">
-        <v>4361.8</v>
+        <v>4441.1</v>
       </c>
       <c r="F37" t="n">
-        <v>21.1</v>
+        <v>21.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="H37" t="n">
-        <v>54</v>
+        <v>79.3</v>
       </c>
       <c r="I37" t="n">
-        <v>4176.5</v>
+        <v>4294</v>
       </c>
       <c r="J37" t="n">
-        <v>4252.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K37" t="n">
-        <v>4291.95</v>
+        <v>4379.75</v>
       </c>
       <c r="L37" t="n">
-        <v>4331.73</v>
+        <v>4416.78</v>
       </c>
       <c r="M37" t="n">
-        <v>4389.45</v>
+        <v>4459.65</v>
       </c>
       <c r="N37" t="n">
-        <v>4447.18</v>
+        <v>4502.53</v>
       </c>
       <c r="O37" t="n">
-        <v>4469</v>
+        <v>4533.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,7 +3601,7 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3639,7 +3617,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3649,50 +3627,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4408.6</v>
+        <v>4430</v>
       </c>
       <c r="C38" t="n">
-        <v>4408.6</v>
+        <v>4502.7</v>
       </c>
       <c r="D38" t="n">
-        <v>4365.1</v>
+        <v>4421.4</v>
       </c>
       <c r="E38" t="n">
-        <v>4383</v>
+        <v>4467.5</v>
       </c>
       <c r="F38" t="n">
-        <v>21.2</v>
+        <v>26.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0049</v>
+        <v>0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>43.5</v>
+        <v>81.3</v>
       </c>
       <c r="I38" t="n">
-        <v>4282.1</v>
+        <v>4336.4</v>
       </c>
       <c r="J38" t="n">
-        <v>4307.15</v>
+        <v>4354.68</v>
       </c>
       <c r="K38" t="n">
-        <v>4334.8</v>
+        <v>4401.45</v>
       </c>
       <c r="L38" t="n">
-        <v>4362.45</v>
+        <v>4448.23</v>
       </c>
       <c r="M38" t="n">
-        <v>4388.8</v>
+        <v>4480.75</v>
       </c>
       <c r="N38" t="n">
-        <v>4415.15</v>
+        <v>4513.27</v>
       </c>
       <c r="O38" t="n">
-        <v>4444.1</v>
+        <v>4574.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3703,7 +3681,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3719,7 +3697,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3729,50 +3707,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4406.5</v>
+        <v>4468.8</v>
       </c>
       <c r="C39" t="n">
-        <v>4434</v>
+        <v>4509.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4406.3</v>
+        <v>4400</v>
       </c>
       <c r="E39" t="n">
-        <v>4408.9</v>
+        <v>4420.4</v>
       </c>
       <c r="F39" t="n">
-        <v>25.9</v>
+        <v>-47.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H39" t="n">
-        <v>27.7</v>
+        <v>109.1</v>
       </c>
       <c r="I39" t="n">
-        <v>4321.6</v>
+        <v>4340.1</v>
       </c>
       <c r="J39" t="n">
-        <v>4337.57</v>
+        <v>4388.92</v>
       </c>
       <c r="K39" t="n">
-        <v>4361.25</v>
+        <v>4426.85</v>
       </c>
       <c r="L39" t="n">
-        <v>4384.93</v>
+        <v>4464.78</v>
       </c>
       <c r="M39" t="n">
-        <v>4404.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N39" t="n">
-        <v>4424.57</v>
+        <v>4551.53</v>
       </c>
       <c r="O39" t="n">
-        <v>4452.1</v>
+        <v>4584</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3780,173 +3758,169 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4403.5</v>
+        <v>4408.2</v>
       </c>
       <c r="C40" t="n">
-        <v>4445</v>
+        <v>4454.6</v>
       </c>
       <c r="D40" t="n">
-        <v>4350</v>
+        <v>4365.5</v>
       </c>
       <c r="E40" t="n">
-        <v>4363.6</v>
+        <v>4437.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-45.3</v>
+        <v>16.9</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0038</v>
       </c>
       <c r="H40" t="n">
-        <v>95</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>4378.6</v>
+        <v>4290.9</v>
       </c>
       <c r="J40" t="n">
-        <v>4375.57</v>
+        <v>4294.22</v>
       </c>
       <c r="K40" t="n">
-        <v>4395.05</v>
+        <v>4365.85</v>
       </c>
       <c r="L40" t="n">
-        <v>4414.52</v>
+        <v>4437.47</v>
       </c>
       <c r="M40" t="n">
-        <v>4422.75</v>
+        <v>4474.95</v>
       </c>
       <c r="N40" t="n">
-        <v>4430.98</v>
+        <v>4512.42</v>
       </c>
       <c r="O40" t="n">
-        <v>4461.7</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>4618.2</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4322.1</v>
+        <v>4440</v>
       </c>
       <c r="C41" t="n">
-        <v>4397.1</v>
+        <v>4486.5</v>
       </c>
       <c r="D41" t="n">
-        <v>4315</v>
+        <v>4422.3</v>
       </c>
       <c r="E41" t="n">
-        <v>4380.4</v>
+        <v>4473.7</v>
       </c>
       <c r="F41" t="n">
-        <v>16.8</v>
+        <v>36.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>82.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I41" t="n">
-        <v>4255</v>
+        <v>4276.4</v>
       </c>
       <c r="J41" t="n">
-        <v>4251.65</v>
+        <v>4361.82</v>
       </c>
       <c r="K41" t="n">
-        <v>4316.1</v>
+        <v>4392.75</v>
       </c>
       <c r="L41" t="n">
-        <v>4380.55</v>
+        <v>4423.67</v>
       </c>
       <c r="M41" t="n">
-        <v>4411.1</v>
+        <v>4481.85</v>
       </c>
       <c r="N41" t="n">
-        <v>4441.65</v>
+        <v>4540.02</v>
       </c>
       <c r="O41" t="n">
-        <v>4540</v>
+        <v>4543.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,18 +3928,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3975,82 +3949,80 @@
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4394.8</v>
+        <v>4473.4</v>
       </c>
       <c r="C42" t="n">
-        <v>4428.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D42" t="n">
-        <v>4386.5</v>
+        <v>4383.3</v>
       </c>
       <c r="E42" t="n">
-        <v>4417.8</v>
+        <v>4420.6</v>
       </c>
       <c r="F42" t="n">
-        <v>37.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H42" t="n">
-        <v>42</v>
+        <v>109.8</v>
       </c>
       <c r="I42" t="n">
-        <v>4232.9</v>
+        <v>4358.1</v>
       </c>
       <c r="J42" t="n">
-        <v>4310.47</v>
+        <v>4419.15</v>
       </c>
       <c r="K42" t="n">
-        <v>4339.35</v>
+        <v>4441.6</v>
       </c>
       <c r="L42" t="n">
-        <v>4368.22</v>
+        <v>4464.05</v>
       </c>
       <c r="M42" t="n">
-        <v>4421.45</v>
+        <v>4505.8</v>
       </c>
       <c r="N42" t="n">
-        <v>4474.67</v>
+        <v>4547.55</v>
       </c>
       <c r="O42" t="n">
-        <v>4479.2</v>
+        <v>4550.7</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4059,95 +4031,93 @@
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4415.2</v>
+        <v>4391.4</v>
       </c>
       <c r="C43" t="n">
-        <v>4434.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D43" t="n">
-        <v>4330.7</v>
+        <v>4378</v>
       </c>
       <c r="E43" t="n">
-        <v>4366</v>
+        <v>4545.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-51.8</v>
+        <v>124.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0282</v>
       </c>
       <c r="H43" t="n">
-        <v>103.4</v>
+        <v>204.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4344.5</v>
+        <v>4273.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4380.95</v>
+        <v>4302</v>
       </c>
       <c r="K43" t="n">
-        <v>4396.8</v>
+        <v>4365.7</v>
       </c>
       <c r="L43" t="n">
-        <v>4412.65</v>
+        <v>4429.4</v>
       </c>
       <c r="M43" t="n">
-        <v>4438.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N43" t="n">
-        <v>4464.95</v>
+        <v>4521.6</v>
       </c>
       <c r="O43" t="n">
-        <v>4470.5</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>4602.9</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="U43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
@@ -4159,50 +4129,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4339.8</v>
+        <v>4580</v>
       </c>
       <c r="C44" t="n">
-        <v>4524.1</v>
+        <v>4597.1</v>
       </c>
       <c r="D44" t="n">
-        <v>4327.6</v>
+        <v>4506</v>
       </c>
       <c r="E44" t="n">
-        <v>4489.4</v>
+        <v>4571.4</v>
       </c>
       <c r="F44" t="n">
-        <v>123.4</v>
+        <v>26.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.0057</v>
       </c>
       <c r="H44" t="n">
-        <v>196.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>4227.3</v>
+        <v>4173.2</v>
       </c>
       <c r="J44" t="n">
-        <v>4254.4</v>
+        <v>4372.95</v>
       </c>
       <c r="K44" t="n">
-        <v>4314.3</v>
+        <v>4442.9</v>
       </c>
       <c r="L44" t="n">
-        <v>4374.2</v>
+        <v>4512.85</v>
       </c>
       <c r="M44" t="n">
-        <v>4417.7</v>
+        <v>4647.7</v>
       </c>
       <c r="N44" t="n">
-        <v>4461.2</v>
+        <v>4782.55</v>
       </c>
       <c r="O44" t="n">
-        <v>4537.5</v>
+        <v>4787.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4213,82 +4183,74 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4506.8</v>
+        <v>4577</v>
       </c>
       <c r="C45" t="n">
-        <v>4530</v>
+        <v>4690.4</v>
       </c>
       <c r="D45" t="n">
-        <v>4486</v>
+        <v>4565.5</v>
       </c>
       <c r="E45" t="n">
-        <v>4516.3</v>
+        <v>4680.6</v>
       </c>
       <c r="F45" t="n">
-        <v>26.9</v>
+        <v>109.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.006</v>
+        <v>0.0239</v>
       </c>
       <c r="H45" t="n">
-        <v>44</v>
+        <v>124.9</v>
       </c>
       <c r="I45" t="n">
-        <v>4131.1</v>
+        <v>4414.9</v>
       </c>
       <c r="J45" t="n">
-        <v>4324.67</v>
+        <v>4490.22</v>
       </c>
       <c r="K45" t="n">
-        <v>4391.15</v>
+        <v>4525.85</v>
       </c>
       <c r="L45" t="n">
-        <v>4457.62</v>
+        <v>4561.47</v>
       </c>
       <c r="M45" t="n">
-        <v>4587.65</v>
+        <v>4616.95</v>
       </c>
       <c r="N45" t="n">
-        <v>4717.67</v>
+        <v>4672.42</v>
       </c>
       <c r="O45" t="n">
-        <v>4720.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4299,21 +4261,27 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4323,50 +4291,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4560</v>
+        <v>4673.4</v>
       </c>
       <c r="C46" t="n">
-        <v>4624.1</v>
+        <v>4738.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4560</v>
+        <v>4651.8</v>
       </c>
       <c r="E46" t="n">
-        <v>4624.1</v>
+        <v>4697.8</v>
       </c>
       <c r="F46" t="n">
-        <v>107.8</v>
+        <v>17.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H46" t="n">
-        <v>64.09999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="I46" t="n">
-        <v>4442</v>
+        <v>4440.6</v>
       </c>
       <c r="J46" t="n">
-        <v>4476.45</v>
+        <v>4582.03</v>
       </c>
       <c r="K46" t="n">
-        <v>4494.3</v>
+        <v>4618.15</v>
       </c>
       <c r="L46" t="n">
-        <v>4512.15</v>
+        <v>4654.28</v>
       </c>
       <c r="M46" t="n">
-        <v>4538.3</v>
+        <v>4743.05</v>
       </c>
       <c r="N46" t="n">
-        <v>4564.45</v>
+        <v>4831.83</v>
       </c>
       <c r="O46" t="n">
-        <v>4574</v>
+        <v>4815.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4377,27 +4345,21 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4407,50 +4369,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4638</v>
+        <v>4710.1</v>
       </c>
       <c r="C47" t="n">
-        <v>4670.9</v>
+        <v>4755</v>
       </c>
       <c r="D47" t="n">
-        <v>4635.1</v>
+        <v>4659.5</v>
       </c>
       <c r="E47" t="n">
-        <v>4640.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F47" t="n">
-        <v>16.7</v>
+        <v>-3.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>35.8</v>
+        <v>95.5</v>
       </c>
       <c r="I47" t="n">
-        <v>4495.9</v>
+        <v>4565.1</v>
       </c>
       <c r="J47" t="n">
-        <v>4576.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K47" t="n">
-        <v>4592.05</v>
+        <v>4654.45</v>
       </c>
       <c r="L47" t="n">
-        <v>4608.08</v>
+        <v>4696.47</v>
       </c>
       <c r="M47" t="n">
-        <v>4656.15</v>
+        <v>4741.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4704.23</v>
+        <v>4785.82</v>
       </c>
       <c r="O47" t="n">
-        <v>4688.2</v>
+        <v>4825.2</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4461,14 +4423,14 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U47" s="8" t="n">
@@ -4477,60 +4439,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4630.5</v>
+        <v>4715.7</v>
       </c>
       <c r="C48" t="n">
-        <v>4638.1</v>
+        <v>4730.9</v>
       </c>
       <c r="D48" t="n">
-        <v>4626.2</v>
+        <v>4638.2</v>
       </c>
       <c r="E48" t="n">
-        <v>4638.1</v>
+        <v>4653.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.7</v>
+        <v>-41.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>11.9</v>
+        <v>92.7</v>
       </c>
       <c r="I48" t="n">
-        <v>4599.3</v>
+        <v>4564</v>
       </c>
       <c r="J48" t="n">
-        <v>4598.9</v>
+        <v>4592.62</v>
       </c>
       <c r="K48" t="n">
-        <v>4622.9</v>
+        <v>4646.75</v>
       </c>
       <c r="L48" t="n">
-        <v>4646.9</v>
+        <v>4700.88</v>
       </c>
       <c r="M48" t="n">
-        <v>4658.7</v>
+        <v>4742.25</v>
       </c>
       <c r="N48" t="n">
-        <v>4670.5</v>
+        <v>4783.62</v>
       </c>
       <c r="O48" t="n">
-        <v>4706.7</v>
+        <v>4850.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4538,12 +4504,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4555,7 +4523,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4569,69 +4537,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4615.3</v>
+        <v>4650</v>
       </c>
       <c r="C49" t="n">
-        <v>4615.3</v>
+        <v>4697.7</v>
       </c>
       <c r="D49" t="n">
-        <v>4598.2</v>
+        <v>4616</v>
       </c>
       <c r="E49" t="n">
-        <v>4598.2</v>
+        <v>4664</v>
       </c>
       <c r="F49" t="n">
-        <v>-39.9</v>
+        <v>10.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0086</v>
+        <v>0.0023</v>
       </c>
       <c r="H49" t="n">
-        <v>17.1</v>
+        <v>81.7</v>
       </c>
       <c r="I49" t="n">
-        <v>4614.3</v>
+        <v>4545.5</v>
       </c>
       <c r="J49" t="n">
-        <v>4629.18</v>
+        <v>4544.97</v>
       </c>
       <c r="K49" t="n">
-        <v>4632.15</v>
+        <v>4606.95</v>
       </c>
       <c r="L49" t="n">
-        <v>4635.13</v>
+        <v>4668.92</v>
       </c>
       <c r="M49" t="n">
-        <v>4644.05</v>
+        <v>4699.65</v>
       </c>
       <c r="N49" t="n">
-        <v>4652.97</v>
+        <v>4730.37</v>
       </c>
       <c r="O49" t="n">
-        <v>4650</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4823.6</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4645,248 +4607,240 @@
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4609.7</v>
+        <v>4656</v>
       </c>
       <c r="C50" t="n">
-        <v>4609.7</v>
+        <v>4688</v>
       </c>
       <c r="D50" t="n">
-        <v>4609.7</v>
+        <v>4495</v>
       </c>
       <c r="E50" t="n">
-        <v>4609.7</v>
+        <v>4529.9</v>
       </c>
       <c r="F50" t="n">
-        <v>11.5</v>
+        <v>-134.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0288</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>193</v>
       </c>
       <c r="I50" t="n">
-        <v>4581.1</v>
+        <v>4534.3</v>
       </c>
       <c r="J50" t="n">
-        <v>4576.83</v>
+        <v>4585.87</v>
       </c>
       <c r="K50" t="n">
-        <v>4589.65</v>
+        <v>4623.15</v>
       </c>
       <c r="L50" t="n">
-        <v>4602.48</v>
+        <v>4660.43</v>
       </c>
       <c r="M50" t="n">
-        <v>4606.75</v>
+        <v>4704.85</v>
       </c>
       <c r="N50" t="n">
-        <v>4611.02</v>
+        <v>4749.28</v>
       </c>
       <c r="O50" t="n">
-        <v>4632.4</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+        <v>4779.4</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4599.3</v>
+        <v>4483.2</v>
       </c>
       <c r="C51" t="n">
-        <v>4625.5</v>
+        <v>4521.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4451.8</v>
+        <v>4445.6</v>
       </c>
       <c r="E51" t="n">
-        <v>4478.1</v>
+        <v>4481.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-131.6</v>
+        <v>-48.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0285</v>
+        <v>-0.0107</v>
       </c>
       <c r="H51" t="n">
-        <v>173.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>4609.7</v>
+        <v>4302</v>
       </c>
       <c r="J51" t="n">
-        <v>4609.7</v>
+        <v>4306.1</v>
       </c>
       <c r="K51" t="n">
-        <v>4609.7</v>
+        <v>4433.4</v>
       </c>
       <c r="L51" t="n">
-        <v>4609.7</v>
+        <v>4560.7</v>
       </c>
       <c r="M51" t="n">
-        <v>4609.7</v>
+        <v>4626.4</v>
       </c>
       <c r="N51" t="n">
-        <v>4609.7</v>
+        <v>4692.1</v>
       </c>
       <c r="O51" t="n">
-        <v>4609.7</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4430</v>
+        <v>4498.7</v>
       </c>
       <c r="C52" t="n">
-        <v>4466.9</v>
+        <v>4510.5</v>
       </c>
       <c r="D52" t="n">
-        <v>4410.9</v>
+        <v>4369.7</v>
       </c>
       <c r="E52" t="n">
-        <v>4431.1</v>
+        <v>4396.4</v>
       </c>
       <c r="F52" t="n">
-        <v>-47</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0105</v>
+        <v>-0.019</v>
       </c>
       <c r="H52" t="n">
-        <v>56</v>
+        <v>140.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4278.1</v>
+        <v>4369.7</v>
       </c>
       <c r="J52" t="n">
-        <v>4274.12</v>
+        <v>4404.58</v>
       </c>
       <c r="K52" t="n">
-        <v>4391.25</v>
+        <v>4443.55</v>
       </c>
       <c r="L52" t="n">
-        <v>4508.38</v>
+        <v>4482.53</v>
       </c>
       <c r="M52" t="n">
-        <v>4564.95</v>
+        <v>4519.45</v>
       </c>
       <c r="N52" t="n">
-        <v>4621.53</v>
+        <v>4556.37</v>
       </c>
       <c r="O52" t="n">
-        <v>4799.2</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
@@ -4903,7 +4857,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4913,69 +4867,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4402</v>
+        <v>4377.2</v>
       </c>
       <c r="C53" t="n">
-        <v>4402</v>
+        <v>4444.4</v>
       </c>
       <c r="D53" t="n">
-        <v>4329.1</v>
+        <v>4329.2</v>
       </c>
       <c r="E53" t="n">
-        <v>4348</v>
+        <v>4414.6</v>
       </c>
       <c r="F53" t="n">
-        <v>-83.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0188</v>
+        <v>0.0041</v>
       </c>
       <c r="H53" t="n">
-        <v>72.90000000000001</v>
+        <v>115.2</v>
       </c>
       <c r="I53" t="n">
-        <v>4354.9</v>
+        <v>4228.9</v>
       </c>
       <c r="J53" t="n">
-        <v>4371.2</v>
+        <v>4233.75</v>
       </c>
       <c r="K53" t="n">
-        <v>4403.1</v>
+        <v>4326</v>
       </c>
       <c r="L53" t="n">
-        <v>4435</v>
+        <v>4418.25</v>
       </c>
       <c r="M53" t="n">
-        <v>4459.1</v>
+        <v>4466.8</v>
       </c>
       <c r="N53" t="n">
-        <v>4483.2</v>
+        <v>4515.35</v>
       </c>
       <c r="O53" t="n">
-        <v>4522.9</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4987,60 +4935,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4328</v>
+        <v>4436.4</v>
       </c>
       <c r="C54" t="n">
-        <v>4390.2</v>
+        <v>4558.5</v>
       </c>
       <c r="D54" t="n">
-        <v>4292.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E54" t="n">
-        <v>4366.3</v>
+        <v>4539.9</v>
       </c>
       <c r="F54" t="n">
-        <v>18.3</v>
+        <v>125.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0284</v>
       </c>
       <c r="H54" t="n">
-        <v>98</v>
+        <v>131.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4256.2</v>
+        <v>4214</v>
       </c>
       <c r="J54" t="n">
-        <v>4266.33</v>
+        <v>4313.3</v>
       </c>
       <c r="K54" t="n">
-        <v>4311.55</v>
+        <v>4357</v>
       </c>
       <c r="L54" t="n">
-        <v>4356.78</v>
+        <v>4400.7</v>
       </c>
       <c r="M54" t="n">
-        <v>4384.45</v>
+        <v>4472.2</v>
       </c>
       <c r="N54" t="n">
-        <v>4412.12</v>
+        <v>4543.7</v>
       </c>
       <c r="O54" t="n">
-        <v>4474.9</v>
+        <v>4559.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5048,118 +5000,116 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4426.3</v>
+        <v>4522</v>
       </c>
       <c r="C55" t="n">
-        <v>4510</v>
+        <v>4537.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4426</v>
+        <v>4412</v>
       </c>
       <c r="E55" t="n">
-        <v>4491.7</v>
+        <v>4476.6</v>
       </c>
       <c r="F55" t="n">
-        <v>125.4</v>
+        <v>-63.3</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0287</v>
+        <v>-0.0139</v>
       </c>
       <c r="H55" t="n">
-        <v>84</v>
+        <v>125.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4194.2</v>
+        <v>4294.9</v>
       </c>
       <c r="J55" t="n">
-        <v>4280.85</v>
+        <v>4431.75</v>
       </c>
       <c r="K55" t="n">
-        <v>4317.3</v>
+        <v>4474</v>
       </c>
       <c r="L55" t="n">
-        <v>4353.75</v>
+        <v>4516.25</v>
       </c>
       <c r="M55" t="n">
-        <v>4415.3</v>
+        <v>4605.8</v>
       </c>
       <c r="N55" t="n">
-        <v>4476.85</v>
+        <v>4695.35</v>
       </c>
       <c r="O55" t="n">
-        <v>4488.2</v>
+        <v>4690.3</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr"/>
@@ -5167,64 +5117,62 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4429.8</v>
+        <v>4466.5</v>
       </c>
       <c r="C56" t="n">
-        <v>4429.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4429.8</v>
+        <v>4381</v>
       </c>
       <c r="E56" t="n">
-        <v>4429.8</v>
+        <v>4439</v>
       </c>
       <c r="F56" t="n">
-        <v>-61.9</v>
+        <v>-37.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0138</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>107.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4342</v>
+        <v>4286.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4419.55</v>
+        <v>4351.65</v>
       </c>
       <c r="K56" t="n">
-        <v>4449.7</v>
+        <v>4413.7</v>
       </c>
       <c r="L56" t="n">
-        <v>4479.85</v>
+        <v>4475.75</v>
       </c>
       <c r="M56" t="n">
-        <v>4533.7</v>
+        <v>4539.5</v>
       </c>
       <c r="N56" t="n">
-        <v>4587.55</v>
+        <v>4603.25</v>
       </c>
       <c r="O56" t="n">
-        <v>4594</v>
+        <v>4663.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5239,83 +5187,75 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4391.9</v>
+        <v>4399</v>
       </c>
       <c r="C57" t="n">
-        <v>4406.1</v>
+        <v>4479</v>
       </c>
       <c r="D57" t="n">
-        <v>4384.4</v>
+        <v>4384.1</v>
       </c>
       <c r="E57" t="n">
-        <v>4393.9</v>
+        <v>4460.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-35.9</v>
+        <v>21.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0081</v>
+        <v>0.0049</v>
       </c>
       <c r="H57" t="n">
-        <v>21.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>4429.8</v>
+        <v>4273.2</v>
       </c>
       <c r="J57" t="n">
-        <v>4429.8</v>
+        <v>4333.25</v>
       </c>
       <c r="K57" t="n">
-        <v>4429.8</v>
+        <v>4385.1</v>
       </c>
       <c r="L57" t="n">
-        <v>4429.8</v>
+        <v>4436.95</v>
       </c>
       <c r="M57" t="n">
-        <v>4429.8</v>
+        <v>4492.9</v>
       </c>
       <c r="N57" t="n">
-        <v>4429.8</v>
+        <v>4548.85</v>
       </c>
       <c r="O57" t="n">
-        <v>4429.8</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
+        <v>4596.6</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S57" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5327,161 +5267,165 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4398.7</v>
+        <v>4448</v>
       </c>
       <c r="C58" t="n">
-        <v>4416</v>
+        <v>4479.9</v>
       </c>
       <c r="D58" t="n">
-        <v>4397.4</v>
+        <v>4354.7</v>
       </c>
       <c r="E58" t="n">
-        <v>4416</v>
+        <v>4407.3</v>
       </c>
       <c r="F58" t="n">
-        <v>22.1</v>
+        <v>-53.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.005</v>
+        <v>-0.012</v>
       </c>
       <c r="H58" t="n">
-        <v>18.6</v>
+        <v>125.2</v>
       </c>
       <c r="I58" t="n">
-        <v>4362.7</v>
+        <v>4289.2</v>
       </c>
       <c r="J58" t="n">
-        <v>4371.52</v>
+        <v>4380.38</v>
       </c>
       <c r="K58" t="n">
-        <v>4383.05</v>
+        <v>4413.25</v>
       </c>
       <c r="L58" t="n">
-        <v>4394.57</v>
+        <v>4446.13</v>
       </c>
       <c r="M58" t="n">
-        <v>4404.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N58" t="n">
-        <v>4414.93</v>
+        <v>4570.18</v>
       </c>
       <c r="O58" t="n">
-        <v>4427.8</v>
+        <v>4573.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4418.9</v>
+        <v>4359.4</v>
       </c>
       <c r="C59" t="n">
-        <v>4420</v>
+        <v>4444.9</v>
       </c>
       <c r="D59" t="n">
-        <v>4330.7</v>
+        <v>4333</v>
       </c>
       <c r="E59" t="n">
-        <v>4364.5</v>
+        <v>4408.9</v>
       </c>
       <c r="F59" t="n">
-        <v>-51.5</v>
+        <v>1.6</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0117</v>
+        <v>0.0004</v>
       </c>
       <c r="H59" t="n">
-        <v>89.3</v>
+        <v>111.9</v>
       </c>
       <c r="I59" t="n">
-        <v>4378.8</v>
+        <v>4229.5</v>
       </c>
       <c r="J59" t="n">
-        <v>4402.05</v>
+        <v>4277.1</v>
       </c>
       <c r="K59" t="n">
-        <v>4406.7</v>
+        <v>4344.7</v>
       </c>
       <c r="L59" t="n">
-        <v>4411.35</v>
+        <v>4412.3</v>
       </c>
       <c r="M59" t="n">
-        <v>4425.3</v>
+        <v>4469.9</v>
       </c>
       <c r="N59" t="n">
-        <v>4439.25</v>
+        <v>4527.5</v>
       </c>
       <c r="O59" t="n">
-        <v>4434.6</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
+        <v>4605.1</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5493,7 +5437,7 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5507,151 +5451,145 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C60" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D60" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E60" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F60" t="n">
-        <v>44.4</v>
+        <v>-57</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0102</v>
+        <v>-0.0129</v>
       </c>
       <c r="H60" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I60" t="n">
-        <v>4241.4</v>
+        <v>4221.1</v>
       </c>
       <c r="J60" t="n">
-        <v>4269.78</v>
+        <v>4306.97</v>
       </c>
       <c r="K60" t="n">
-        <v>4319.85</v>
+        <v>4352.95</v>
       </c>
       <c r="L60" t="n">
-        <v>4369.93</v>
+        <v>4398.92</v>
       </c>
       <c r="M60" t="n">
-        <v>4409.15</v>
+        <v>4464.85</v>
       </c>
       <c r="N60" t="n">
-        <v>4448.37</v>
+        <v>4530.77</v>
       </c>
       <c r="O60" t="n">
-        <v>4509.3</v>
+        <v>4556.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C61" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D61" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E61" t="n">
-        <v>4351.9</v>
+        <v>4333.4</v>
       </c>
       <c r="F61" t="n">
-        <v>-57</v>
+        <v>-18.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0043</v>
       </c>
       <c r="H61" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I61" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J61" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K61" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L61" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M61" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N61" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O61" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5663,121 +5601,43 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4340.3</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4358.2</v>
-      </c>
-      <c r="D62" t="n">
-        <v>4323.8</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4343.2</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-8.699999999999999</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="H62" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4189.2</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4251.6</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4300</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4348.4</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4403.8</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4459.2</v>
-      </c>
-      <c r="O62" t="n">
-        <v>4500.6</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>4289.4</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>4309.9</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>4326</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>4342.1</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>4360.4</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>4378.7</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>4392.6</v>
+      <c r="I62" s="13" t="n">
+        <v>4245</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>4278.55</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>4305.1</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>4331.65</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>4361.7</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>4391.75</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>4414.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5537,25 +5537,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C61" t="n">
-        <v>4358.2</v>
+        <v>4339.5</v>
       </c>
       <c r="D61" t="n">
-        <v>4301.6</v>
+        <v>4315.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4333.4</v>
+        <v>4324.9</v>
       </c>
       <c r="F61" t="n">
-        <v>-18.5</v>
+        <v>-27</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0062</v>
       </c>
       <c r="H61" t="n">
-        <v>56.6</v>
+        <v>24.3</v>
       </c>
       <c r="I61" t="n">
         <v>4189.2</v>
@@ -5619,25 +5619,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4245</v>
+        <v>4290.9</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4278.55</v>
+        <v>4299.38</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4305.1</v>
+        <v>4312.75</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4331.65</v>
+        <v>4326.12</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4361.7</v>
+        <v>4337.05</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4391.75</v>
+        <v>4347.97</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4414.8</v>
+        <v>4363.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5537,25 +5537,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4333.5</v>
+        <v>4340.3</v>
       </c>
       <c r="C61" t="n">
-        <v>4339.5</v>
+        <v>4358.2</v>
       </c>
       <c r="D61" t="n">
-        <v>4315.2</v>
+        <v>4301.6</v>
       </c>
       <c r="E61" t="n">
-        <v>4324.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F61" t="n">
-        <v>-27</v>
+        <v>-19.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0062</v>
+        <v>-0.0044</v>
       </c>
       <c r="H61" t="n">
-        <v>24.3</v>
+        <v>56.6</v>
       </c>
       <c r="I61" t="n">
         <v>4189.2</v>
@@ -5613,31 +5613,115 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4333.5</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4381.9</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4315.2</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4371</v>
+      </c>
+      <c r="F62" t="n">
+        <v>38.2</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.008800000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4245</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4277.65</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4304.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4331.35</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4361.1</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4390.85</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4414.8</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>4290.9</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>4299.38</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>4312.75</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>4326.12</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>4337.05</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>4347.97</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>4363.8</v>
+      <c r="I63" s="13" t="n">
+        <v>4248.5</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>4315.53</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>4337.65</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>4359.78</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>4404.35</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>4448.92</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>4448.6</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5622,22 +5622,22 @@
         <v>4333.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4381.9</v>
+        <v>4394.5</v>
       </c>
       <c r="D62" t="n">
         <v>4315.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4371</v>
+        <v>4389.8</v>
       </c>
       <c r="F62" t="n">
-        <v>38.2</v>
+        <v>57</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0132</v>
       </c>
       <c r="H62" t="n">
-        <v>66.7</v>
+        <v>79.3</v>
       </c>
       <c r="I62" t="n">
         <v>4245</v>
@@ -5676,11 +5676,13 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5703,25 +5705,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>4248.5</v>
+        <v>4235.9</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>4315.53</v>
+        <v>4327.97</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>4337.65</v>
+        <v>4350.15</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>4359.78</v>
+        <v>4372.32</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>4404.35</v>
+        <v>4429.45</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>4448.92</v>
+        <v>4486.57</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>4448.6</v>
+        <v>4473.8</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5622,22 +5622,22 @@
         <v>4333.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4394.5</v>
+        <v>4394.8</v>
       </c>
       <c r="D62" t="n">
         <v>4315.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4389.8</v>
+        <v>4384.9</v>
       </c>
       <c r="F62" t="n">
-        <v>57</v>
+        <v>52.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0132</v>
+        <v>0.012</v>
       </c>
       <c r="H62" t="n">
-        <v>79.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I62" t="n">
         <v>4245</v>
@@ -5705,25 +5705,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>4235.9</v>
+        <v>4235.6</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>4327.97</v>
+        <v>4320.25</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>4350.15</v>
+        <v>4345.1</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>4372.32</v>
+        <v>4369.95</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>4429.45</v>
+        <v>4424.7</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>4486.57</v>
+        <v>4479.45</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>4473.8</v>
+        <v>4474.4</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5628,13 +5628,13 @@
         <v>4315.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4384.9</v>
+        <v>4387.5</v>
       </c>
       <c r="F62" t="n">
-        <v>52.1</v>
+        <v>54.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.012</v>
+        <v>0.0126</v>
       </c>
       <c r="H62" t="n">
         <v>79.59999999999999</v>
@@ -5708,19 +5708,19 @@
         <v>4235.6</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>4320.25</v>
+        <v>4324.15</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>4345.1</v>
+        <v>4347.7</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>4369.95</v>
+        <v>4371.25</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>4424.7</v>
+        <v>4427.3</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>4479.45</v>
+        <v>4483.35</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>4474.4</v>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,56 +641,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4163.9</v>
+        <v>4210.8</v>
       </c>
       <c r="C2" t="n">
-        <v>4238.1</v>
+        <v>4216</v>
       </c>
       <c r="D2" t="n">
-        <v>4151.4</v>
+        <v>4108.2</v>
       </c>
       <c r="E2" t="n">
-        <v>4202.7</v>
+        <v>4149.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-43.2</v>
+        <v>-53.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0102</v>
+        <v>-0.0127</v>
       </c>
       <c r="H2" t="n">
-        <v>86.7</v>
+        <v>107.8</v>
       </c>
       <c r="I2" t="n">
-        <v>4090.4</v>
+        <v>4064.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4096.32</v>
+        <v>4119.98</v>
       </c>
       <c r="K2" t="n">
-        <v>4180.95</v>
+        <v>4159.35</v>
       </c>
       <c r="L2" t="n">
-        <v>4265.57</v>
+        <v>4198.73</v>
       </c>
       <c r="M2" t="n">
-        <v>4310.85</v>
+        <v>4246.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4356.13</v>
+        <v>4293.38</v>
       </c>
       <c r="O2" t="n">
-        <v>4480.1</v>
+        <v>4324.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -725,53 +727,55 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4210.8</v>
+        <v>4130</v>
       </c>
       <c r="C3" t="n">
-        <v>4216</v>
+        <v>4132.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4108.2</v>
+        <v>3975.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4149.4</v>
+        <v>4008.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-53.3</v>
+        <v>-140.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0339</v>
       </c>
       <c r="H3" t="n">
-        <v>107.8</v>
+        <v>156.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4064.7</v>
+        <v>4000.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4119.98</v>
+        <v>4035.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4159.35</v>
+        <v>4095.5</v>
       </c>
       <c r="L3" t="n">
-        <v>4198.73</v>
+        <v>4155.75</v>
       </c>
       <c r="M3" t="n">
-        <v>4246.05</v>
+        <v>4203.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4293.38</v>
+        <v>4250.85</v>
       </c>
       <c r="O3" t="n">
-        <v>4324.8</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
+        <v>4323.8</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q3" s="6" t="inlineStr">
         <is>
@@ -780,7 +784,7 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -797,83 +801,73 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4130</v>
+        <v>4019</v>
       </c>
       <c r="C4" t="n">
-        <v>4132.4</v>
+        <v>4060</v>
       </c>
       <c r="D4" t="n">
-        <v>3975.7</v>
+        <v>3976.3</v>
       </c>
       <c r="E4" t="n">
-        <v>4008.8</v>
+        <v>4047.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-140.6</v>
+        <v>38.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0339</v>
+        <v>0.0097</v>
       </c>
       <c r="H4" t="n">
-        <v>156.7</v>
+        <v>83.7</v>
       </c>
       <c r="I4" t="n">
-        <v>4000.4</v>
+        <v>3819</v>
       </c>
       <c r="J4" t="n">
-        <v>4035.25</v>
+        <v>3829.48</v>
       </c>
       <c r="K4" t="n">
-        <v>4095.5</v>
+        <v>3930.45</v>
       </c>
       <c r="L4" t="n">
-        <v>4155.75</v>
+        <v>4031.42</v>
       </c>
       <c r="M4" t="n">
-        <v>4203.3</v>
+        <v>4087.15</v>
       </c>
       <c r="N4" t="n">
-        <v>4250.85</v>
+        <v>4142.88</v>
       </c>
       <c r="O4" t="n">
-        <v>4323.8</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4289.1</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -890,55 +884,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4019</v>
+        <v>4044.4</v>
       </c>
       <c r="C5" t="n">
-        <v>4060</v>
+        <v>4111.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3976.3</v>
+        <v>3998.1</v>
       </c>
       <c r="E5" t="n">
-        <v>4047.6</v>
+        <v>4096.3</v>
       </c>
       <c r="F5" t="n">
-        <v>38.8</v>
+        <v>48.7</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.012</v>
       </c>
       <c r="H5" t="n">
-        <v>83.7</v>
+        <v>113.4</v>
       </c>
       <c r="I5" t="n">
-        <v>3819</v>
+        <v>3892.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3829.48</v>
+        <v>3978.63</v>
       </c>
       <c r="K5" t="n">
-        <v>3930.45</v>
+        <v>4005.75</v>
       </c>
       <c r="L5" t="n">
-        <v>4031.42</v>
+        <v>4032.88</v>
       </c>
       <c r="M5" t="n">
-        <v>4087.15</v>
+        <v>4089.45</v>
       </c>
       <c r="N5" t="n">
-        <v>4142.88</v>
+        <v>4146.03</v>
       </c>
       <c r="O5" t="n">
-        <v>4289.1</v>
+        <v>4143.7</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -946,16 +944,20 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -970,57 +972,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4044.4</v>
+        <v>4101.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4111.5</v>
+        <v>4102.9</v>
       </c>
       <c r="D6" t="n">
-        <v>3998.1</v>
+        <v>4012</v>
       </c>
       <c r="E6" t="n">
-        <v>4096.3</v>
+        <v>4038.9</v>
       </c>
       <c r="F6" t="n">
-        <v>48.7</v>
+        <v>-57.4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H6" t="n">
-        <v>113.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3892.6</v>
+        <v>3884.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3978.63</v>
+        <v>4003.65</v>
       </c>
       <c r="K6" t="n">
-        <v>4005.75</v>
+        <v>4039.6</v>
       </c>
       <c r="L6" t="n">
-        <v>4032.88</v>
+        <v>4075.55</v>
       </c>
       <c r="M6" t="n">
-        <v>4089.45</v>
+        <v>4153</v>
       </c>
       <c r="N6" t="n">
-        <v>4146.03</v>
+        <v>4230.45</v>
       </c>
       <c r="O6" t="n">
-        <v>4143.7</v>
+        <v>4224.9</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1030,19 +1032,17 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1056,57 +1056,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C7" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D7" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E7" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H7" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K7" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L7" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M7" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N7" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O7" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1138,59 +1138,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C8" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D8" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E8" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H8" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I8" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J8" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K8" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L8" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M8" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N8" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O8" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1203,13 +1199,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1222,55 +1220,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C9" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E9" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F9" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H9" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I9" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J9" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K9" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L9" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M9" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N9" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,10 +1280,8 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="11" t="inlineStr">
         <is>
@@ -1313,50 +1313,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C10" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D10" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E10" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F10" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H10" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K10" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L10" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M10" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O10" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1397,50 +1397,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C11" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D11" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E11" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F11" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H11" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J11" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K11" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L11" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M11" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N11" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O11" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1448,18 +1448,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1472,65 +1472,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C12" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D12" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E12" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H12" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J12" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K12" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L12" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M12" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N12" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O12" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1539,7 +1537,7 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1561,72 +1559,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C13" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D13" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H13" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I13" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J13" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K13" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L13" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M13" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N13" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O13" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1638,55 +1634,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C14" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D14" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E14" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F14" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H14" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I14" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K14" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L14" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M14" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N14" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O14" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,18 +1694,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1720,63 +1720,67 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C15" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D15" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E15" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H15" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I15" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J15" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K15" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L15" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M15" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N15" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O15" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1785,7 +1789,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1802,86 +1806,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C16" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D16" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E16" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F16" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H16" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I16" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J16" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K16" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L16" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M16" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O16" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1890,55 +1888,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C17" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D17" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E17" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F17" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H17" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I17" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K17" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L17" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M17" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O17" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,20 +1951,16 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1974,70 +1972,74 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C18" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D18" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E18" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H18" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L18" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M18" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N18" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2054,76 +2056,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C19" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D19" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E19" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H19" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K19" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L19" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M19" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N19" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O19" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2140,55 +2134,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C20" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D20" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E20" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F20" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K20" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L20" t="n">
         <v>4007.38</v>
       </c>
       <c r="M20" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N20" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O20" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2220,57 +2218,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C21" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E21" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H21" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J21" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K21" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L21" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M21" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N21" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O21" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2283,76 +2281,76 @@
       </c>
       <c r="S21" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C22" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D22" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E22" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F22" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H22" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J22" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K22" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L22" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M22" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N22" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O22" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2391,81 +2389,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C23" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D23" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E23" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F23" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H23" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K23" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L23" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M23" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O23" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2473,67 +2471,63 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C24" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D24" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E24" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F24" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H24" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J24" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K24" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L24" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M24" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N24" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O24" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2550,55 +2544,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C25" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D25" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E25" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F25" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H25" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I25" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K25" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L25" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M25" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O25" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2609,13 +2607,15 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2630,77 +2630,81 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C26" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D26" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E26" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F26" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H26" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J26" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K26" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L26" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O26" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2712,85 +2716,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C27" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D27" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E27" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F27" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I27" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K27" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L27" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M27" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N27" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O27" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2800,55 +2800,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C28" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D28" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E28" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H28" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I28" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J28" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L28" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N28" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,25 +2860,21 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2886,57 +2886,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C29" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E29" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F29" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H29" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I29" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J29" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L29" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N29" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O29" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2949,12 +2949,12 @@
       </c>
       <c r="S29" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2977,50 +2977,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C30" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D30" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E30" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F30" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H30" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I30" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K30" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L30" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M30" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N30" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O30" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,15 +3031,13 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3052,59 +3050,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C31" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D31" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E31" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F31" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H31" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K31" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L31" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M31" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N31" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O31" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3115,23 +3109,27 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3139,50 +3137,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C32" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D32" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E32" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F32" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H32" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I32" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J32" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K32" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L32" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M32" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N32" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O32" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3205,11 +3203,13 @@
       </c>
       <c r="U32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3221,50 +3221,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C33" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D33" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E33" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F33" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H33" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I33" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J33" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K33" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L33" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M33" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O33" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3277,78 +3277,76 @@
       </c>
       <c r="S33" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C34" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D34" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E34" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H34" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I34" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J34" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K34" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L34" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M34" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N34" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O34" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3361,14 +3359,18 @@
       </c>
       <c r="S34" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3378,59 +3380,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C35" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D35" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E35" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F35" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H35" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J35" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K35" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L35" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M35" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N35" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O35" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,18 +3441,14 @@
       </c>
       <c r="S35" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3469,50 +3463,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C36" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D36" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E36" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F36" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H36" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J36" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K36" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L36" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M36" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N36" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O36" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3525,11 +3519,13 @@
       </c>
       <c r="S36" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3547,50 +3543,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C37" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E37" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F37" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H37" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I37" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J37" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K37" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L37" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M37" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N37" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O37" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,50 +3623,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C38" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D38" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E38" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F38" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H38" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I38" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K38" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L38" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M38" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N38" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O38" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3678,17 +3674,19 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3702,55 +3700,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C39" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D39" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E39" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H39" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J39" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K39" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L39" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M39" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N39" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O39" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3760,18 +3762,16 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3793,50 +3793,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C40" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E40" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F40" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I40" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J40" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K40" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L40" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M40" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N40" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O40" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3844,18 +3844,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3868,79 +3868,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C41" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D41" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E41" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F41" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H41" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I41" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J41" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K41" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L41" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M41" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O41" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+      <c r="Q41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3952,80 +3950,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C42" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D42" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E42" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H42" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I42" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J42" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K42" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L42" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M42" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N42" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O42" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4036,57 +4038,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C43" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D43" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E43" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F43" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H43" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J43" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K43" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L43" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M43" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N43" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O43" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4099,18 +4101,14 @@
       </c>
       <c r="S43" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4120,59 +4118,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C44" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D44" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E44" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F44" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H44" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I44" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J44" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K44" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L44" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M44" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N44" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O44" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4185,17 +4179,23 @@
       </c>
       <c r="S44" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
@@ -4207,50 +4207,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C45" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E45" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F45" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H45" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I45" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J45" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K45" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L45" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M45" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N45" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O45" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4263,23 +4263,17 @@
       </c>
       <c r="S45" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4291,50 +4285,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C46" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D46" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E46" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F46" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I46" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J46" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K46" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L46" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M46" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N46" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O46" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4345,13 +4339,15 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4364,55 +4360,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C47" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D47" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E47" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I47" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J47" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K47" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L47" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M47" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N47" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O47" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4420,18 +4420,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4446,57 +4446,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C48" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D48" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E48" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F48" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H48" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I48" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J48" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K48" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L48" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M48" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N48" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O48" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4504,14 +4504,12 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4530,70 +4528,76 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C49" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D49" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E49" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F49" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H49" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I49" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J49" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K49" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L49" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M49" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N49" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O49" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4605,78 +4609,70 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C50" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D50" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E50" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H50" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J50" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K50" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L50" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M50" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N50" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O50" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -4703,60 +4699,64 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C51" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E51" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F51" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H51" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J51" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K51" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L51" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M51" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N51" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O51" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
@@ -4783,69 +4783,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C52" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D52" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E52" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F52" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H52" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I52" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J52" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K52" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L52" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M52" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N52" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O52" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4862,55 +4856,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C53" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D53" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E53" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F53" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H53" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J53" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K53" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L53" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M53" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N53" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O53" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4921,16 +4919,20 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4942,82 +4944,82 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C54" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E54" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F54" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H54" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J54" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K54" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L54" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M54" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N54" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O54" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5026,67 +5028,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C55" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E55" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F55" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K55" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L55" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M55" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N55" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O55" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5117,50 +5113,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C56" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D56" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E56" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F56" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H56" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K56" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L56" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M56" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N56" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O56" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5170,12 +5166,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5192,70 +5188,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C57" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D57" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E57" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F57" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H57" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I57" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J57" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K57" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L57" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M57" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N57" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O57" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5274,74 +5276,72 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D58" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E58" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F58" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H58" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I58" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J58" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K58" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L58" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M58" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N58" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O58" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5367,65 +5367,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C59" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D59" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E59" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F59" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H59" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J59" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K59" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L59" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M59" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N59" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O59" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5442,76 +5444,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C60" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D60" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E60" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F60" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H60" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I60" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J60" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K60" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L60" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M60" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N60" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O60" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5528,55 +5522,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4340.3</v>
+        <v>4301.4</v>
       </c>
       <c r="C61" t="n">
-        <v>4358.2</v>
+        <v>4302.7</v>
       </c>
       <c r="D61" t="n">
-        <v>4301.6</v>
+        <v>4296.3</v>
       </c>
       <c r="E61" t="n">
-        <v>4332.8</v>
+        <v>4296.6</v>
       </c>
       <c r="F61" t="n">
-        <v>-19.1</v>
+        <v>-36.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>56.6</v>
+        <v>6.4</v>
       </c>
       <c r="I61" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J61" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K61" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L61" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M61" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N61" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O61" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5584,12 +5582,14 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5606,124 +5606,34 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4333.5</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4394.8</v>
-      </c>
-      <c r="D62" t="n">
-        <v>4315.2</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4387.5</v>
-      </c>
-      <c r="F62" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0126</v>
-      </c>
-      <c r="H62" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4245</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4277.65</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4304.5</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4331.35</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4361.1</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4390.85</v>
-      </c>
-      <c r="O62" t="n">
-        <v>4414.8</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>4235.6</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>4324.15</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>4347.7</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>4371.25</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>4427.3</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>4483.35</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>4474.4</v>
+      <c r="I62" s="13" t="n">
+        <v>4289.9</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>4288.75</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>4293.4</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>4298.05</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>4299.8</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>4301.55</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>4309.1</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5538,22 +5538,22 @@
         <v>4301.4</v>
       </c>
       <c r="C61" t="n">
-        <v>4302.7</v>
+        <v>4330.4</v>
       </c>
       <c r="D61" t="n">
-        <v>4296.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E61" t="n">
-        <v>4296.6</v>
+        <v>4318.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-36.2</v>
+        <v>-14.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0033</v>
       </c>
       <c r="H61" t="n">
-        <v>6.4</v>
+        <v>35.9</v>
       </c>
       <c r="I61" t="n">
         <v>4245</v>
@@ -5584,12 +5584,12 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5615,25 +5615,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>4289.9</v>
+        <v>4258.6</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>4288.75</v>
+        <v>4285.63</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>4293.4</v>
+        <v>4300.55</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>4298.05</v>
+        <v>4315.47</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>4299.8</v>
+        <v>4336.45</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>4301.55</v>
+        <v>4357.42</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>4309.1</v>
+        <v>4366.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5535,25 +5535,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4301.4</v>
+        <v>4333.5</v>
       </c>
       <c r="C61" t="n">
-        <v>4330.4</v>
+        <v>4413.1</v>
       </c>
       <c r="D61" t="n">
-        <v>4294.5</v>
+        <v>4273.3</v>
       </c>
       <c r="E61" t="n">
-        <v>4318.5</v>
+        <v>4387.5</v>
       </c>
       <c r="F61" t="n">
-        <v>-14.3</v>
+        <v>54.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0033</v>
+        <v>0.0126</v>
       </c>
       <c r="H61" t="n">
-        <v>35.9</v>
+        <v>139.8</v>
       </c>
       <c r="I61" t="n">
         <v>4245</v>
@@ -5579,24 +5579,30 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5606,34 +5612,120 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4381.6</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4384.1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4380.9</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4382.2</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0012</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4133.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4269.85</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4317.6</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4365.35</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4457.4</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4549.45</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4552.9</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>4258.6</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>4285.63</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>4300.55</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>4315.47</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>4336.45</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>4357.42</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>4366.3</v>
+      <c r="I63" s="13" t="n">
+        <v>4377.7</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>4378.85</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>4380.6</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>4382.35</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>4383.8</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>4385.25</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>4387.3</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5628,22 +5628,22 @@
         <v>4381.6</v>
       </c>
       <c r="C62" t="n">
-        <v>4384.1</v>
+        <v>4388.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4380.9</v>
+        <v>4378.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4382.2</v>
+        <v>4383.1</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.3</v>
+        <v>-4.4</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.001</v>
       </c>
       <c r="H62" t="n">
-        <v>3.2</v>
+        <v>10.2</v>
       </c>
       <c r="I62" t="n">
         <v>4133.5</v>
@@ -5707,25 +5707,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>4377.7</v>
+        <v>4368.1</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>4378.85</v>
+        <v>4372.75</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>4380.6</v>
+        <v>4378</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>4382.35</v>
+        <v>4383.25</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>4383.8</v>
+        <v>4388.2</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>4385.25</v>
+        <v>4393.15</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>4387.3</v>
+        <v>4398.7</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5628,22 +5621,22 @@
         <v>4381.6</v>
       </c>
       <c r="C62" t="n">
-        <v>4388.5</v>
+        <v>4396.3</v>
       </c>
       <c r="D62" t="n">
         <v>4378.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4383.1</v>
+        <v>4391.6</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.4</v>
+        <v>4.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="H62" t="n">
-        <v>10.2</v>
+        <v>18</v>
       </c>
       <c r="I62" t="n">
         <v>4133.5</v>
@@ -5696,36 +5689,8 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>4368.1</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>4372.75</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>4378</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>4383.25</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>4388.2</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>4393.15</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>4398.7</v>
+          <t>中警訊</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5621,22 +5621,22 @@
         <v>4381.6</v>
       </c>
       <c r="C62" t="n">
-        <v>4396.3</v>
+        <v>4399.5</v>
       </c>
       <c r="D62" t="n">
         <v>4378.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4391.6</v>
+        <v>4395</v>
       </c>
       <c r="F62" t="n">
-        <v>4.1</v>
+        <v>7.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0009</v>
+        <v>0.0017</v>
       </c>
       <c r="H62" t="n">
-        <v>18</v>
+        <v>21.2</v>
       </c>
       <c r="I62" t="n">
         <v>4133.5</v>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,53 +634,55 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4210.8</v>
+        <v>4130</v>
       </c>
       <c r="C2" t="n">
-        <v>4216</v>
+        <v>4132.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4108.2</v>
+        <v>3975.7</v>
       </c>
       <c r="E2" t="n">
-        <v>4149.4</v>
+        <v>4008.8</v>
       </c>
       <c r="F2" t="n">
-        <v>-53.3</v>
+        <v>-140.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0127</v>
+        <v>-0.0339</v>
       </c>
       <c r="H2" t="n">
-        <v>107.8</v>
+        <v>156.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4064.7</v>
+        <v>4000.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4119.98</v>
+        <v>4035.25</v>
       </c>
       <c r="K2" t="n">
-        <v>4159.35</v>
+        <v>4095.5</v>
       </c>
       <c r="L2" t="n">
-        <v>4198.73</v>
+        <v>4155.75</v>
       </c>
       <c r="M2" t="n">
-        <v>4246.05</v>
+        <v>4203.3</v>
       </c>
       <c r="N2" t="n">
-        <v>4293.38</v>
+        <v>4250.85</v>
       </c>
       <c r="O2" t="n">
-        <v>4324.8</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>4323.8</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="inlineStr">
         <is>
@@ -689,7 +691,7 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -708,81 +710,71 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4130</v>
+        <v>4019</v>
       </c>
       <c r="C3" t="n">
-        <v>4132.4</v>
+        <v>4060</v>
       </c>
       <c r="D3" t="n">
-        <v>3975.7</v>
+        <v>3976.3</v>
       </c>
       <c r="E3" t="n">
-        <v>4008.8</v>
+        <v>4047.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-140.6</v>
+        <v>38.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0339</v>
+        <v>0.0097</v>
       </c>
       <c r="H3" t="n">
-        <v>156.7</v>
+        <v>83.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4000.4</v>
+        <v>3819</v>
       </c>
       <c r="J3" t="n">
-        <v>4035.25</v>
+        <v>3829.48</v>
       </c>
       <c r="K3" t="n">
-        <v>4095.5</v>
+        <v>3930.45</v>
       </c>
       <c r="L3" t="n">
-        <v>4155.75</v>
+        <v>4031.42</v>
       </c>
       <c r="M3" t="n">
-        <v>4203.3</v>
+        <v>4087.15</v>
       </c>
       <c r="N3" t="n">
-        <v>4250.85</v>
+        <v>4142.88</v>
       </c>
       <c r="O3" t="n">
-        <v>4323.8</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4289.1</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -794,60 +786,64 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4019</v>
+        <v>4044.4</v>
       </c>
       <c r="C4" t="n">
-        <v>4060</v>
+        <v>4111.5</v>
       </c>
       <c r="D4" t="n">
-        <v>3976.3</v>
+        <v>3998.1</v>
       </c>
       <c r="E4" t="n">
-        <v>4047.6</v>
+        <v>4096.3</v>
       </c>
       <c r="F4" t="n">
-        <v>38.8</v>
+        <v>48.7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.012</v>
       </c>
       <c r="H4" t="n">
-        <v>83.7</v>
+        <v>113.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3819</v>
+        <v>3892.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3829.48</v>
+        <v>3978.63</v>
       </c>
       <c r="K4" t="n">
-        <v>3930.45</v>
+        <v>4005.75</v>
       </c>
       <c r="L4" t="n">
-        <v>4031.42</v>
+        <v>4032.88</v>
       </c>
       <c r="M4" t="n">
-        <v>4087.15</v>
+        <v>4089.45</v>
       </c>
       <c r="N4" t="n">
-        <v>4142.88</v>
+        <v>4146.03</v>
       </c>
       <c r="O4" t="n">
-        <v>4289.1</v>
+        <v>4143.7</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,16 +851,20 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -872,64 +872,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4044.4</v>
+        <v>4101.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4111.5</v>
+        <v>4102.9</v>
       </c>
       <c r="D5" t="n">
-        <v>3998.1</v>
+        <v>4012</v>
       </c>
       <c r="E5" t="n">
-        <v>4096.3</v>
+        <v>4038.9</v>
       </c>
       <c r="F5" t="n">
-        <v>48.7</v>
+        <v>-57.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H5" t="n">
-        <v>113.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3892.6</v>
+        <v>3884.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3978.63</v>
+        <v>4003.65</v>
       </c>
       <c r="K5" t="n">
-        <v>4005.75</v>
+        <v>4039.6</v>
       </c>
       <c r="L5" t="n">
-        <v>4032.88</v>
+        <v>4075.55</v>
       </c>
       <c r="M5" t="n">
-        <v>4089.45</v>
+        <v>4153</v>
       </c>
       <c r="N5" t="n">
-        <v>4146.03</v>
+        <v>4230.45</v>
       </c>
       <c r="O5" t="n">
-        <v>4143.7</v>
+        <v>4224.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,83 +939,81 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D6" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E6" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H6" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J6" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K6" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L6" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M6" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N6" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O6" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,12 +1023,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1042,64 +1040,60 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C7" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D7" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E7" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H7" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I7" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K7" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L7" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M7" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O7" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,13 +1106,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1126,60 +1122,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C8" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D8" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E8" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F8" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H8" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I8" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J8" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K8" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L8" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M8" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N8" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,12 +1187,10 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1208,7 +1206,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1222,50 +1220,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D9" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E9" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F9" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H9" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K9" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L9" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M9" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N9" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O9" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1276,7 +1274,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="11" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1292,7 +1290,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1306,50 +1304,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D10" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E10" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F10" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H10" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K10" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L10" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M10" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N10" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O10" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1357,18 +1355,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1376,70 +1374,68 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C11" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D11" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E11" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H11" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I11" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J11" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K11" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L11" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M11" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N11" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O11" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
@@ -1448,7 +1444,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1460,7 +1456,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1470,132 +1466,134 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C12" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D12" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H12" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I12" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J12" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L12" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M12" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O12" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D13" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E13" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F13" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H13" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I13" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J13" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K13" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L13" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M13" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N13" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O13" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,18 +1601,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1622,70 +1620,74 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C14" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D14" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E14" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H14" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I14" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J14" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K14" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L14" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M14" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N14" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O14" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1694,7 +1696,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1706,148 +1708,146 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C15" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F15" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H15" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I15" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K15" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L15" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M15" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N15" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O15" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C16" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D16" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E16" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F16" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H16" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I16" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J16" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K16" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L16" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M16" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O16" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,95 +1858,95 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C17" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D17" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E17" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H17" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J17" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L17" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M17" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N17" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1958,81 +1958,73 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="10" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C18" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D18" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E18" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H18" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K18" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L18" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M18" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N18" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O18" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2044,60 +2036,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="10" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C19" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D19" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E19" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F19" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K19" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L19" t="n">
         <v>4007.38</v>
       </c>
       <c r="M19" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N19" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O19" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,7 +2104,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2122,64 +2118,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="10" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C20" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D20" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E20" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H20" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J20" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K20" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L20" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M20" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N20" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O20" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,78 +2186,78 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C21" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D21" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E21" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F21" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H21" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J21" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L21" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M21" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N21" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O21" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,7 +2268,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2290,7 +2286,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2300,81 +2296,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C22" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D22" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E22" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F22" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H22" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I22" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K22" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L22" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M22" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O22" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2382,67 +2378,63 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C23" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D23" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E23" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F23" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H23" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J23" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K23" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L23" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M23" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N23" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O23" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2454,60 +2446,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="10" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C24" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D24" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E24" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F24" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H24" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I24" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L24" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M24" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N24" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,13 +2514,15 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2532,232 +2530,236 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="10" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C25" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D25" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E25" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F25" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H25" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J25" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K25" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L25" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M25" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O25" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C26" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D26" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E26" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F26" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I26" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K26" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L26" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M26" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N26" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O26" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="10" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C27" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D27" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E27" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H27" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I27" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L27" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M27" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N27" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O27" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2765,87 +2767,83 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="10" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C28" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D28" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E28" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F28" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H28" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L28" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N28" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O28" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,14 +2854,14 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2872,7 +2870,7 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2886,50 +2884,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C29" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D29" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E29" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F29" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H29" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I29" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K29" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L29" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M29" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N29" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O29" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,15 +2938,13 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2956,64 +2952,60 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C30" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D30" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E30" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H30" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J30" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K30" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L30" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M30" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N30" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O30" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3024,23 +3016,27 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3048,50 +3044,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C31" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D31" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E31" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F31" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H31" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I31" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J31" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K31" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L31" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N31" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O31" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3102,7 +3098,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="11" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3114,13 +3110,15 @@
       </c>
       <c r="U31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3130,50 +3128,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C32" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D32" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E32" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F32" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H32" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I32" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J32" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K32" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L32" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M32" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O32" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,80 +3182,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C33" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D33" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E33" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H33" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I33" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J33" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K33" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L33" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M33" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N33" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O33" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3268,78 +3264,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C34" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E34" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F34" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H34" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I34" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J34" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K34" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L34" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M34" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N34" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O34" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,25 +3346,21 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3378,50 +3370,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C35" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D35" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E35" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H35" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I35" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J35" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K35" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L35" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M35" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N35" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O35" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3432,13 +3424,15 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3446,7 +3440,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3456,50 +3450,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C36" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D36" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E36" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F36" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H36" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I36" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J36" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K36" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L36" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M36" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N36" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O36" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,7 +3504,7 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="11" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3526,7 +3520,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3536,50 +3530,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C37" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D37" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E37" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F37" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H37" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I37" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J37" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K37" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L37" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M37" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N37" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O37" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3587,17 +3581,19 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3606,60 +3602,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C38" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D38" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E38" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H38" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J38" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K38" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L38" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M38" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N38" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O38" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3669,18 +3669,16 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3688,7 +3686,7 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3702,50 +3700,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C39" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D39" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E39" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F39" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I39" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J39" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K39" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L39" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M39" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N39" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O39" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3753,18 +3751,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3772,230 +3770,232 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C40" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D40" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E40" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F40" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H40" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I40" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J40" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K40" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L40" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M40" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N40" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O40" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C41" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D41" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E41" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H41" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I41" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J41" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K41" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L41" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M41" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N41" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O41" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C42" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D42" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E42" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F42" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H42" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J42" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K42" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L42" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M42" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N42" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O42" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4006,82 +4006,74 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C43" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D43" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E43" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F43" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H43" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I43" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K43" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L43" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M43" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N43" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O43" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4092,21 +4084,27 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4116,50 +4114,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C44" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D44" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E44" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F44" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H44" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I44" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J44" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K44" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L44" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M44" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N44" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O44" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4170,27 +4168,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4200,50 +4192,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C45" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D45" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E45" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F45" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I45" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J45" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K45" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L45" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M45" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N45" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O45" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4254,13 +4246,15 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4268,60 +4262,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C46" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D46" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E46" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I46" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J46" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K46" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L46" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M46" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N46" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O46" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4329,18 +4327,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4348,64 +4346,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C47" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D47" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E47" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F47" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H47" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I47" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J47" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K47" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L47" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M47" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N47" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O47" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4413,14 +4411,12 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4432,77 +4428,83 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C48" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D48" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E48" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F48" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H48" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I48" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J48" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K48" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L48" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M48" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N48" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O48" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4516,78 +4518,70 @@
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C49" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D49" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E49" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F49" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H49" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J49" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K49" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L49" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M49" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N49" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O49" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4602,7 +4596,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4612,60 +4606,64 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C50" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D50" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E50" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F50" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H50" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J50" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K50" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L50" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M50" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N50" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O50" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -4682,7 +4680,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4692,69 +4690,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C51" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D51" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E51" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F51" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H51" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I51" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J51" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K51" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L51" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M51" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N51" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O51" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4766,60 +4758,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C52" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D52" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E52" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F52" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H52" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J52" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K52" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L52" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M52" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N52" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O52" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4830,172 +4826,170 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C53" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E53" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F53" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H53" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J53" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K53" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L53" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M53" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N53" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O53" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C54" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E54" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F54" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K54" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L54" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M54" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N54" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O54" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5016,7 +5010,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="10" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5026,50 +5020,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C55" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D55" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E55" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F55" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H55" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K55" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L55" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M55" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N55" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O55" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5079,12 +5073,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5096,75 +5090,81 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="10" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C56" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D56" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E56" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F56" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H56" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I56" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K56" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L56" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M56" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N56" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O56" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5176,81 +5176,79 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="10" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D57" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E57" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F57" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H57" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I57" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J57" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K57" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L57" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M57" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N57" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O57" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5262,7 +5260,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="10" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5276,65 +5274,67 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C58" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D58" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E58" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F58" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H58" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J58" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K58" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L58" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M58" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N58" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O58" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5346,81 +5346,73 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="10" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C59" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D59" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E59" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F59" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H59" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I59" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J59" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K59" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L59" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M59" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N59" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O59" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5432,232 +5424,238 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="10" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C60" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D60" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E60" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H60" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I60" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J60" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K60" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L60" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M60" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N60" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O60" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="10" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C61" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D61" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E61" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F61" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H61" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I61" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J61" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K61" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L61" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M61" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N61" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O61" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>4381.6</v>
       </c>
       <c r="C62" t="n">
-        <v>4399.5</v>
+        <v>4439.8</v>
       </c>
       <c r="D62" t="n">
-        <v>4378.3</v>
+        <v>4372.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4395</v>
+        <v>4424.9</v>
       </c>
       <c r="F62" t="n">
-        <v>7.5</v>
+        <v>25.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0057</v>
       </c>
       <c r="H62" t="n">
-        <v>21.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J62" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K62" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L62" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M62" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N62" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O62" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5668,28 +5666,112 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="11" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4413</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4416.9</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4411</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4424.9</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4304.6</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4366.75</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4391.1</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4415.45</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4458.7</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4501.95</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4507.4</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="10" t="inlineStr">
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4130</v>
+        <v>4019</v>
       </c>
       <c r="C2" t="n">
-        <v>4132.4</v>
+        <v>4060</v>
       </c>
       <c r="D2" t="n">
-        <v>3975.7</v>
+        <v>3976.3</v>
       </c>
       <c r="E2" t="n">
-        <v>4008.8</v>
+        <v>4047.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-140.6</v>
+        <v>38.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0339</v>
+        <v>0.0097</v>
       </c>
       <c r="H2" t="n">
-        <v>156.7</v>
+        <v>83.7</v>
       </c>
       <c r="I2" t="n">
-        <v>4000.4</v>
+        <v>3819</v>
       </c>
       <c r="J2" t="n">
-        <v>4035.25</v>
+        <v>3829.48</v>
       </c>
       <c r="K2" t="n">
-        <v>4095.5</v>
+        <v>3930.45</v>
       </c>
       <c r="L2" t="n">
-        <v>4155.75</v>
+        <v>4031.42</v>
       </c>
       <c r="M2" t="n">
-        <v>4203.3</v>
+        <v>4087.15</v>
       </c>
       <c r="N2" t="n">
-        <v>4250.85</v>
+        <v>4142.88</v>
       </c>
       <c r="O2" t="n">
-        <v>4323.8</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4289.1</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4019</v>
+        <v>4044.4</v>
       </c>
       <c r="C3" t="n">
-        <v>4060</v>
+        <v>4111.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3976.3</v>
+        <v>3998.1</v>
       </c>
       <c r="E3" t="n">
-        <v>4047.6</v>
+        <v>4096.3</v>
       </c>
       <c r="F3" t="n">
-        <v>38.8</v>
+        <v>48.7</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.012</v>
       </c>
       <c r="H3" t="n">
-        <v>83.7</v>
+        <v>113.4</v>
       </c>
       <c r="I3" t="n">
-        <v>3819</v>
+        <v>3892.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3829.48</v>
+        <v>3978.63</v>
       </c>
       <c r="K3" t="n">
-        <v>3930.45</v>
+        <v>4005.75</v>
       </c>
       <c r="L3" t="n">
-        <v>4031.42</v>
+        <v>4032.88</v>
       </c>
       <c r="M3" t="n">
-        <v>4087.15</v>
+        <v>4089.45</v>
       </c>
       <c r="N3" t="n">
-        <v>4142.88</v>
+        <v>4146.03</v>
       </c>
       <c r="O3" t="n">
-        <v>4289.1</v>
+        <v>4143.7</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,16 +767,20 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -788,62 +790,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4044.4</v>
+        <v>4101.1</v>
       </c>
       <c r="C4" t="n">
-        <v>4111.5</v>
+        <v>4102.9</v>
       </c>
       <c r="D4" t="n">
-        <v>3998.1</v>
+        <v>4012</v>
       </c>
       <c r="E4" t="n">
-        <v>4096.3</v>
+        <v>4038.9</v>
       </c>
       <c r="F4" t="n">
-        <v>48.7</v>
+        <v>-57.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H4" t="n">
-        <v>113.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3892.6</v>
+        <v>3884.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3978.63</v>
+        <v>4003.65</v>
       </c>
       <c r="K4" t="n">
-        <v>4005.75</v>
+        <v>4039.6</v>
       </c>
       <c r="L4" t="n">
-        <v>4032.88</v>
+        <v>4075.55</v>
       </c>
       <c r="M4" t="n">
-        <v>4089.45</v>
+        <v>4153</v>
       </c>
       <c r="N4" t="n">
-        <v>4146.03</v>
+        <v>4230.45</v>
       </c>
       <c r="O4" t="n">
-        <v>4143.7</v>
+        <v>4224.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,18 +851,16 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -874,62 +870,62 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D5" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E5" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H5" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K5" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L5" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M5" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N5" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O5" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,12 +935,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -958,62 +954,62 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C6" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D6" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E6" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H6" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I6" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K6" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L6" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M6" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O6" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,11 +1024,13 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1042,7 +1040,7 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1050,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C7" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E7" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F7" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H7" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J7" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L7" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M7" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N7" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,12 +1099,10 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1124,62 +1120,58 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D8" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E8" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F8" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H8" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K8" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L8" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M8" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N8" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O8" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,7 +1182,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1208,62 +1200,58 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C9" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E9" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F9" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H9" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J9" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K9" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L9" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M9" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N9" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O9" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,18 +1259,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1292,7 +1280,7 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -1304,65 +1292,67 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C10" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D10" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H10" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I10" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J10" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K10" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L10" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M10" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N10" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O10" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1376,80 +1366,82 @@
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C11" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D11" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E11" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H11" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I11" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J11" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K11" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L11" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O11" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1458,7 +1450,7 @@
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr"/>
@@ -1466,50 +1458,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D12" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E12" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F12" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H12" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I12" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K12" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L12" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M12" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O12" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,18 +1509,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1538,77 +1530,81 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C13" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D13" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E13" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H13" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I13" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K13" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L13" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M13" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N13" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O13" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1620,148 +1616,146 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C14" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F14" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H14" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I14" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J14" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K14" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L14" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M14" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N14" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O14" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="U14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C15" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D15" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E15" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F15" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H15" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J15" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K15" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L15" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M15" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O15" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,93 +1768,93 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C16" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D16" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E16" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F16" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H16" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L16" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M16" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N16" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1872,81 +1866,73 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C17" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D17" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E17" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H17" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K17" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L17" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M17" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N17" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O17" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1958,60 +1944,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C18" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D18" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E18" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F18" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K18" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L18" t="n">
         <v>4007.38</v>
       </c>
       <c r="M18" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N18" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O18" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,7 +2012,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2036,64 +2026,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C19" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D19" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E19" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H19" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J19" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K19" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L19" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M19" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N19" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O19" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2104,78 +2094,78 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C20" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D20" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E20" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F20" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H20" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J20" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L20" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M20" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N20" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O20" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,7 +2176,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2204,7 +2194,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2214,81 +2204,81 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C21" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D21" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E21" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F21" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H21" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K21" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L21" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M21" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O21" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2296,67 +2286,63 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C22" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D22" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E22" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H22" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J22" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K22" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L22" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M22" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N22" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O22" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2368,60 +2354,64 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C23" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D23" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E23" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F23" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H23" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I23" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K23" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L23" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M23" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,11 +2424,13 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2446,83 +2438,87 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C24" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D24" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E24" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F24" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H24" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J24" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K24" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L24" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M24" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O24" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>4171.5</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2530,148 +2526,148 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C25" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D25" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E25" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I25" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K25" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L25" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M25" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N25" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O25" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C26" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D26" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E26" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H26" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I26" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K26" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L26" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N26" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O26" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2679,87 +2675,83 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C27" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D27" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E27" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F27" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H27" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I27" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J27" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L27" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M27" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N27" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O27" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,14 +2762,14 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2786,7 +2778,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2800,50 +2792,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C28" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D28" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E28" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F28" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H28" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I28" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J28" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K28" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L28" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M28" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N28" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O28" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2856,13 +2848,11 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2870,64 +2860,60 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C29" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E29" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F29" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H29" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J29" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K29" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L29" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M29" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N29" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O29" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2940,21 +2926,25 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2962,50 +2952,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C30" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D30" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E30" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F30" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H30" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I30" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J30" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K30" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L30" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M30" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N30" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O30" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3016,7 +3006,7 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3028,13 +3018,15 @@
       </c>
       <c r="U30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3044,50 +3036,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C31" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D31" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E31" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F31" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H31" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I31" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J31" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K31" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L31" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M31" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O31" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3098,80 +3090,78 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C32" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D32" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E32" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H32" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J32" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K32" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L32" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M32" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N32" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O32" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,78 +3172,78 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C33" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E33" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F33" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H33" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J33" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K33" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L33" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M33" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N33" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O33" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3264,25 +3254,21 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3292,50 +3278,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C34" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D34" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E34" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F34" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H34" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I34" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J34" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K34" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L34" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M34" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N34" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O34" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3346,13 +3332,15 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3360,7 +3348,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3370,50 +3358,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C35" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D35" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E35" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F35" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H35" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I35" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K35" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L35" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M35" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N35" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O35" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3424,7 +3412,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3440,7 +3428,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3450,50 +3438,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C36" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D36" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E36" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F36" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H36" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I36" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J36" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K36" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L36" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M36" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N36" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O36" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3501,17 +3489,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3520,60 +3510,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C37" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D37" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E37" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H37" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J37" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K37" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L37" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M37" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N37" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O37" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3583,26 +3577,24 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3616,50 +3608,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C38" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D38" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E38" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F38" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I38" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J38" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K38" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L38" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M38" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N38" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O38" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3667,18 +3659,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3686,83 +3678,81 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C39" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E39" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F39" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H39" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I39" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J39" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K39" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L39" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M39" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O39" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3770,146 +3760,150 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C40" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D40" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E40" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H40" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I40" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J40" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K40" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L40" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M40" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N40" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O40" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C41" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D41" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E41" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F41" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H41" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J41" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K41" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L41" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M41" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N41" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O41" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3920,82 +3914,74 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C42" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D42" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F42" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H42" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I42" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J42" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K42" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L42" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M42" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N42" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O42" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4006,21 +3992,27 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4030,50 +4022,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C43" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E43" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F43" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H43" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I43" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J43" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K43" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L43" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M43" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N43" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O43" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4084,27 +4076,21 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4114,50 +4100,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C44" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D44" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E44" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F44" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I44" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J44" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K44" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L44" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M44" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N44" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O44" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4170,11 +4156,13 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4182,60 +4170,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C45" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D45" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E45" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I45" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J45" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K45" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L45" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M45" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N45" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O45" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4243,18 +4235,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4262,64 +4254,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C46" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D46" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E46" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F46" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H46" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I46" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J46" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K46" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L46" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M46" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N46" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O46" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4327,14 +4319,12 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4346,77 +4336,83 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C47" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D47" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E47" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F47" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H47" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I47" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J47" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K47" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L47" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M47" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N47" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O47" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4779.4</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4430,79 +4426,71 @@
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C48" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E48" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F48" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H48" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J48" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K48" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L48" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M48" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N48" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O48" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4516,7 +4504,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4526,63 +4514,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C49" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D49" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E49" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F49" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H49" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J49" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K49" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L49" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M49" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N49" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O49" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4596,7 +4588,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4606,69 +4598,63 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C50" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D50" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E50" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F50" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H50" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I50" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J50" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K50" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L50" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M50" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N50" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O50" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4651.3</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4680,60 +4666,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C51" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D51" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E51" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F51" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H51" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J51" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K51" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L51" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M51" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N51" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O51" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4746,177 +4736,175 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C52" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E52" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F52" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H52" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J52" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K52" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L52" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M52" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N52" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O52" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C53" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E53" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F53" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K53" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L53" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M53" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N53" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O53" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4930,7 +4918,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4940,50 +4928,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C54" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D54" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E54" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H54" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K54" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L54" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M54" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N54" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O54" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -4993,12 +4981,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5010,75 +4998,81 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C55" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D55" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E55" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F55" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H55" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K55" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L55" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M55" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N55" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O55" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5090,81 +5084,79 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C56" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D56" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E56" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F56" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H56" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I56" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K56" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L56" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M56" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N56" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O56" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5176,7 +5168,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5190,65 +5182,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C57" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D57" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E57" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F57" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H57" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J57" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K57" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L57" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M57" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N57" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O57" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5260,81 +5254,73 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C58" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D58" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F58" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I58" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J58" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K58" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L58" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M58" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N58" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O58" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5346,232 +5332,238 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C59" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D59" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E59" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H59" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J59" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K59" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L59" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M59" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N59" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O59" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C60" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D60" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E60" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F60" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H60" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I60" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J60" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K60" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L60" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M60" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N60" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O60" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C61" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D61" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F61" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H61" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J61" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K61" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L61" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M61" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N61" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O61" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5579,18 +5571,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5598,7 +5590,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5612,50 +5604,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4381.6</v>
+        <v>4382.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4439.8</v>
+        <v>4386.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4372.2</v>
+        <v>4382</v>
       </c>
       <c r="E62" t="n">
-        <v>4424.9</v>
+        <v>4385.2</v>
       </c>
       <c r="F62" t="n">
-        <v>25.2</v>
+        <v>-39.7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>67.59999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="I62" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J62" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K62" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L62" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M62" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N62" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O62" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5663,18 +5655,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5682,94 +5674,12 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4413</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4416.9</v>
-      </c>
-      <c r="D63" t="n">
-        <v>4411</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4424.9</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4304.6</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4366.75</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4391.1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>4415.45</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4458.7</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4501.95</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4507.4</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5608,25 +5608,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4382.5</v>
+        <v>4413</v>
       </c>
       <c r="C62" t="n">
-        <v>4386.5</v>
+        <v>4422.1</v>
       </c>
       <c r="D62" t="n">
-        <v>4382</v>
+        <v>4360.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4385.2</v>
+        <v>4383.9</v>
       </c>
       <c r="F62" t="n">
-        <v>-39.7</v>
+        <v>-41</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>4.5</v>
+        <v>61.8</v>
       </c>
       <c r="I62" t="n">
         <v>4304.6</v>
@@ -5652,8 +5652,10 @@
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
@@ -5679,11 +5681,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4382.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4414.1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4327.6</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4374.7</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-9.199999999999999</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="H63" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4298.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4318.45</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4353</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4387.55</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4414.8</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4442.05</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4483.9</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5699,13 +5699,13 @@
         <v>4327.6</v>
       </c>
       <c r="E63" t="n">
-        <v>4374.7</v>
+        <v>4359.7</v>
       </c>
       <c r="F63" t="n">
-        <v>-9.199999999999999</v>
+        <v>-24.2</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0021</v>
+        <v>-0.0055</v>
       </c>
       <c r="H63" t="n">
         <v>86.5</v>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4019</v>
+        <v>4044.4</v>
       </c>
       <c r="C2" t="n">
-        <v>4060</v>
+        <v>4111.5</v>
       </c>
       <c r="D2" t="n">
-        <v>3976.3</v>
+        <v>3998.1</v>
       </c>
       <c r="E2" t="n">
-        <v>4047.6</v>
+        <v>4096.3</v>
       </c>
       <c r="F2" t="n">
-        <v>38.8</v>
+        <v>48.7</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.012</v>
       </c>
       <c r="H2" t="n">
-        <v>83.7</v>
+        <v>113.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3819</v>
+        <v>3892.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3829.48</v>
+        <v>3978.63</v>
       </c>
       <c r="K2" t="n">
-        <v>3930.45</v>
+        <v>4005.75</v>
       </c>
       <c r="L2" t="n">
-        <v>4031.42</v>
+        <v>4032.88</v>
       </c>
       <c r="M2" t="n">
-        <v>4087.15</v>
+        <v>4089.45</v>
       </c>
       <c r="N2" t="n">
-        <v>4142.88</v>
+        <v>4146.03</v>
       </c>
       <c r="O2" t="n">
-        <v>4289.1</v>
+        <v>4143.7</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,16 +685,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4044.4</v>
+        <v>4101.1</v>
       </c>
       <c r="C3" t="n">
-        <v>4111.5</v>
+        <v>4102.9</v>
       </c>
       <c r="D3" t="n">
-        <v>3998.1</v>
+        <v>4012</v>
       </c>
       <c r="E3" t="n">
-        <v>4096.3</v>
+        <v>4038.9</v>
       </c>
       <c r="F3" t="n">
-        <v>48.7</v>
+        <v>-57.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H3" t="n">
-        <v>113.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3892.6</v>
+        <v>3884.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3978.63</v>
+        <v>4003.65</v>
       </c>
       <c r="K3" t="n">
-        <v>4005.75</v>
+        <v>4039.6</v>
       </c>
       <c r="L3" t="n">
-        <v>4032.88</v>
+        <v>4075.55</v>
       </c>
       <c r="M3" t="n">
-        <v>4089.45</v>
+        <v>4153</v>
       </c>
       <c r="N3" t="n">
-        <v>4146.03</v>
+        <v>4230.45</v>
       </c>
       <c r="O3" t="n">
-        <v>4143.7</v>
+        <v>4224.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,19 +769,17 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -793,55 +791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D4" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H4" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J4" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K4" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L4" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M4" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N4" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O4" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,12 +853,12 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -875,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C5" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D5" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E5" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H5" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I5" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K5" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L5" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M5" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O5" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,13 +940,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -957,59 +961,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C6" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E6" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F6" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H6" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I6" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J6" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L6" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M6" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N6" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,10 +1017,8 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
@@ -1048,50 +1046,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C7" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D7" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E7" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F7" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H7" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K7" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L7" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M7" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N7" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O7" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1128,50 +1126,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C8" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D8" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F8" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H8" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K8" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L8" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M8" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N8" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O8" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1179,18 +1177,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1203,61 +1201,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C9" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D9" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E9" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H9" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I9" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J9" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K9" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L9" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M9" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N9" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O9" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
@@ -1266,7 +1270,7 @@
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1292,72 +1296,70 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C10" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D10" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H10" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I10" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J10" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L10" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M10" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O10" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1369,59 +1371,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C11" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D11" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E11" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F11" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H11" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I11" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J11" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K11" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L11" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M11" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O11" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,18 +1427,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1453,61 +1451,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C12" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D12" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E12" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H12" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I12" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K12" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L12" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M12" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N12" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O12" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1516,7 +1522,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1528,91 +1534,85 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C13" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D13" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F13" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H13" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I13" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J13" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K13" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L13" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M13" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O13" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="U13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1621,55 +1621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C14" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D14" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E14" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H14" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J14" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K14" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L14" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M14" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O14" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1680,20 +1684,16 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1705,70 +1705,74 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C15" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D15" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E15" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F15" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H15" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K15" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L15" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M15" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N15" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O15" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1785,76 +1789,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C16" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D16" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E16" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H16" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K16" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L16" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N16" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O16" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1871,55 +1867,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C17" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D17" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E17" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F17" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K17" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L17" t="n">
         <v>4007.38</v>
       </c>
       <c r="M17" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N17" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O17" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,57 +1951,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C18" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D18" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E18" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H18" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I18" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J18" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K18" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L18" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M18" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N18" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O18" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2014,76 +2014,76 @@
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C19" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D19" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E19" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F19" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H19" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J19" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L19" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M19" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N19" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O19" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2122,81 +2122,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C20" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D20" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E20" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F20" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H20" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K20" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L20" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M20" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2204,67 +2204,63 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C21" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D21" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E21" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F21" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H21" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J21" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K21" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L21" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M21" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N21" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O21" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2281,55 +2277,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C22" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D22" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E22" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F22" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H22" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I22" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J22" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K22" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L22" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M22" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N22" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O22" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2340,13 +2340,15 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2361,77 +2363,81 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C23" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D23" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E23" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F23" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H23" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J23" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L23" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M23" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O23" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2443,85 +2449,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C24" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D24" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E24" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F24" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K24" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L24" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M24" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N24" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O24" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2531,55 +2533,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C25" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D25" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E25" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H25" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I25" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K25" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L25" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M25" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N25" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O25" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2587,25 +2593,21 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2617,57 +2619,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C26" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D26" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E26" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F26" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H26" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J26" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L26" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M26" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O26" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2680,12 +2682,12 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
@@ -2708,50 +2710,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C27" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D27" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E27" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F27" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H27" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I27" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J27" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K27" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L27" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M27" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N27" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O27" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2762,15 +2764,13 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2783,59 +2783,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C28" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D28" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E28" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H28" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J28" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K28" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L28" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M28" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N28" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O28" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2846,23 +2842,27 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2870,50 +2870,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C29" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D29" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E29" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F29" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H29" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I29" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K29" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L29" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M29" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N29" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O29" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2936,11 +2936,13 @@
       </c>
       <c r="U29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2952,50 +2954,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C30" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D30" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E30" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F30" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H30" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I30" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J30" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K30" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L30" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M30" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N30" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O30" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3008,78 +3010,76 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C31" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D31" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E31" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H31" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J31" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K31" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L31" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M31" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N31" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O31" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3092,14 +3092,18 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3109,59 +3113,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C32" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E32" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F32" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H32" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J32" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K32" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L32" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M32" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N32" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O32" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3174,18 +3174,14 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3200,50 +3196,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C33" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D33" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E33" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F33" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H33" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I33" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J33" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K33" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L33" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M33" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N33" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O33" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3256,11 +3252,13 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3278,50 +3276,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C34" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D34" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E34" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F34" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H34" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I34" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J34" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K34" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L34" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M34" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N34" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O34" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3358,50 +3356,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C35" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D35" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E35" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F35" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H35" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J35" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K35" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L35" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M35" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N35" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O35" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3409,17 +3407,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3433,55 +3433,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C36" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D36" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E36" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F36" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H36" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J36" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K36" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L36" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M36" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O36" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3491,18 +3495,16 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3524,50 +3526,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C37" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D37" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E37" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F37" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I37" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J37" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K37" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L37" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M37" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N37" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O37" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3575,18 +3577,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3599,79 +3601,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C38" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D38" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E38" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F38" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H38" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I38" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K38" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L38" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M38" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N38" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O38" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="Q38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3683,80 +3683,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C39" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D39" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E39" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H39" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I39" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K39" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L39" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M39" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N39" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O39" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3767,57 +3771,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C40" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D40" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E40" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F40" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H40" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J40" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K40" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L40" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M40" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N40" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O40" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3830,18 +3834,14 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3851,59 +3851,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C41" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D41" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F41" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H41" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I41" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J41" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K41" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L41" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M41" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N41" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O41" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3916,17 +3912,23 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3938,50 +3940,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C42" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E42" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F42" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H42" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J42" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K42" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L42" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M42" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N42" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O42" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3994,23 +3996,17 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4022,50 +4018,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C43" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D43" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E43" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F43" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I43" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J43" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K43" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L43" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M43" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N43" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O43" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4076,13 +4072,15 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4095,55 +4093,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C44" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D44" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E44" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I44" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J44" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K44" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L44" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M44" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N44" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O44" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4151,18 +4153,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4177,57 +4179,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C45" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D45" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E45" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F45" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H45" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I45" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J45" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K45" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L45" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M45" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N45" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O45" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4235,14 +4237,12 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4261,70 +4261,76 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C46" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D46" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E46" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F46" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H46" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I46" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J46" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K46" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L46" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M46" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N46" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O46" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4336,78 +4342,70 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C47" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D47" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E47" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F47" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H47" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J47" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K47" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L47" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M47" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N47" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O47" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
@@ -4434,60 +4432,64 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C48" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E48" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F48" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H48" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J48" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K48" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L48" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M48" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N48" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O48" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
@@ -4514,69 +4516,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C49" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D49" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E49" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F49" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H49" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I49" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J49" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K49" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L49" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M49" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N49" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O49" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4593,55 +4589,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C50" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D50" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E50" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F50" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H50" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J50" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K50" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L50" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M50" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N50" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O50" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4652,16 +4652,20 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4673,82 +4677,82 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C51" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E51" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F51" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H51" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J51" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K51" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L51" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M51" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N51" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O51" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4757,67 +4761,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C52" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E52" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F52" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H52" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K52" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L52" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M52" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N52" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O52" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4848,50 +4846,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C53" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D53" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E53" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H53" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K53" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L53" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M53" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N53" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O53" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4901,12 +4899,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4923,70 +4921,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C54" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D54" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E54" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F54" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H54" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I54" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K54" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L54" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M54" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N54" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O54" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5005,74 +5009,72 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C55" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D55" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E55" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F55" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H55" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I55" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J55" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K55" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L55" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M55" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N55" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O55" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5098,65 +5100,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C56" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E56" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F56" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H56" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J56" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K56" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L56" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M56" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N56" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O56" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5173,76 +5177,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C57" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D57" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E57" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F57" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H57" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I57" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J57" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K57" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L57" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M57" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O57" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5259,75 +5255,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C58" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H58" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J58" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K58" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L58" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M58" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N58" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O58" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5339,85 +5347,79 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C59" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D59" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E59" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F59" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H59" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J59" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K59" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L59" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M59" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N59" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O59" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5429,57 +5431,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C60" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D60" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E60" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F60" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H60" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J60" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K60" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L60" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M60" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N60" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O60" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5487,18 +5489,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5520,70 +5522,72 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C61" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D61" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E61" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F61" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I61" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J61" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K61" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L61" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M61" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N61" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O61" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5595,76 +5599,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4413</v>
+        <v>4394.7</v>
       </c>
       <c r="C62" t="n">
-        <v>4422.1</v>
+        <v>4400.8</v>
       </c>
       <c r="D62" t="n">
-        <v>4360.3</v>
+        <v>4394.7</v>
       </c>
       <c r="E62" t="n">
-        <v>4383.9</v>
+        <v>4399.8</v>
       </c>
       <c r="F62" t="n">
-        <v>-41</v>
+        <v>15.9</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.0036</v>
       </c>
       <c r="H62" t="n">
-        <v>61.8</v>
+        <v>6.1</v>
       </c>
       <c r="I62" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J62" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K62" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L62" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M62" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N62" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O62" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5681,87 +5677,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4382.5</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4414.1</v>
-      </c>
-      <c r="D63" t="n">
-        <v>4327.6</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4359.7</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-24.2</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0055</v>
-      </c>
-      <c r="H63" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4298.5</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4318.45</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4353</v>
-      </c>
-      <c r="L63" t="n">
-        <v>4387.55</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4414.8</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4442.05</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4483.9</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5611,22 +5611,22 @@
         <v>4394.7</v>
       </c>
       <c r="C62" t="n">
-        <v>4400.8</v>
+        <v>4407.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4394.7</v>
+        <v>4380.3</v>
       </c>
       <c r="E62" t="n">
-        <v>4399.8</v>
+        <v>4380.8</v>
       </c>
       <c r="F62" t="n">
-        <v>15.9</v>
+        <v>-3.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0036</v>
+        <v>-0.0007</v>
       </c>
       <c r="H62" t="n">
-        <v>6.1</v>
+        <v>27.2</v>
       </c>
       <c r="I62" t="n">
         <v>4298.5</v>
@@ -5658,9 +5658,9 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5614,19 +5614,19 @@
         <v>4407.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4380.3</v>
+        <v>4378.6</v>
       </c>
       <c r="E62" t="n">
-        <v>4380.8</v>
+        <v>4381.8</v>
       </c>
       <c r="F62" t="n">
-        <v>-3.1</v>
+        <v>-2.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0005</v>
       </c>
       <c r="H62" t="n">
-        <v>27.2</v>
+        <v>28.9</v>
       </c>
       <c r="I62" t="n">
         <v>4298.5</v>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5614,19 +5614,19 @@
         <v>4407.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4378.6</v>
+        <v>4370.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4381.8</v>
+        <v>4374</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.1</v>
+        <v>-9.9</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0005</v>
+        <v>-0.0023</v>
       </c>
       <c r="H62" t="n">
-        <v>28.9</v>
+        <v>37.3</v>
       </c>
       <c r="I62" t="n">
         <v>4298.5</v>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -5614,19 +5614,19 @@
         <v>4407.5</v>
       </c>
       <c r="D62" t="n">
-        <v>4370.2</v>
+        <v>4370</v>
       </c>
       <c r="E62" t="n">
-        <v>4374</v>
+        <v>4373.9</v>
       </c>
       <c r="F62" t="n">
-        <v>-9.9</v>
+        <v>-10</v>
       </c>
       <c r="G62" s="5" t="n">
         <v>-0.0023</v>
       </c>
       <c r="H62" t="n">
-        <v>37.3</v>
+        <v>37.5</v>
       </c>
       <c r="I62" t="n">
         <v>4298.5</v>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5608,25 +5608,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4394.7</v>
+        <v>4382.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4407.5</v>
+        <v>4414.1</v>
       </c>
       <c r="D62" t="n">
-        <v>4370</v>
+        <v>4327.6</v>
       </c>
       <c r="E62" t="n">
-        <v>4373.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F62" t="n">
-        <v>-10</v>
+        <v>-7.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0023</v>
+        <v>-0.0017</v>
       </c>
       <c r="H62" t="n">
-        <v>37.5</v>
+        <v>86.5</v>
       </c>
       <c r="I62" t="n">
         <v>4298.5</v>
@@ -5655,8 +5655,10 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
@@ -5677,7 +5679,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4394.7</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4407.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4330.9</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4336.6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-39.8</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0091</v>
+      </c>
+      <c r="H63" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4241.1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4292.67</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4333.15</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4373.62</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4419.65</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4465.67</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4500.6</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4044.4</v>
+        <v>4101.1</v>
       </c>
       <c r="C2" t="n">
-        <v>4111.5</v>
+        <v>4102.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3998.1</v>
+        <v>4012</v>
       </c>
       <c r="E2" t="n">
-        <v>4096.3</v>
+        <v>4038.9</v>
       </c>
       <c r="F2" t="n">
-        <v>48.7</v>
+        <v>-57.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="H2" t="n">
-        <v>113.4</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3892.6</v>
+        <v>3884.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3978.63</v>
+        <v>4003.65</v>
       </c>
       <c r="K2" t="n">
-        <v>4005.75</v>
+        <v>4039.6</v>
       </c>
       <c r="L2" t="n">
-        <v>4032.88</v>
+        <v>4075.55</v>
       </c>
       <c r="M2" t="n">
-        <v>4089.45</v>
+        <v>4153</v>
       </c>
       <c r="N2" t="n">
-        <v>4146.03</v>
+        <v>4230.45</v>
       </c>
       <c r="O2" t="n">
-        <v>4143.7</v>
+        <v>4224.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,18 +687,16 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D3" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E3" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H3" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J3" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K3" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L3" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M3" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N3" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O3" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,12 +771,12 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -793,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C4" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D4" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E4" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H4" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I4" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J4" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K4" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L4" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M4" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O4" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,11 +860,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C5" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D5" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E5" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F5" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H5" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J5" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K5" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L5" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N5" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,12 +935,10 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -966,50 +964,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D6" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E6" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F6" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H6" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K6" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L6" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M6" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O6" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,7 +1018,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1046,50 +1044,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D7" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F7" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H7" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K7" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L7" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M7" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N7" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O7" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,18 +1095,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1121,70 +1119,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C8" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D8" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E8" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F8" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H8" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J8" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K8" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L8" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M8" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N8" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O8" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1210,72 +1214,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D9" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E9" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H9" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J9" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L9" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N9" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O9" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1287,59 +1289,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E10" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F10" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H10" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I10" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J10" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K10" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L10" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M10" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N10" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O10" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,18 +1345,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1371,70 +1369,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C11" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D11" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E11" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H11" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J11" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K11" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L11" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M11" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N11" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O11" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1446,91 +1452,85 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W11" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C12" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D12" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F12" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H12" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J12" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K12" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L12" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M12" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O12" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="U12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
@@ -1539,55 +1539,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C13" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D13" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E13" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F13" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H13" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J13" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K13" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L13" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M13" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O13" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,18 +1604,14 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
@@ -1623,70 +1623,74 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C14" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D14" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E14" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F14" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H14" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J14" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K14" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L14" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M14" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N14" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1703,76 +1707,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C15" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D15" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E15" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H15" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K15" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L15" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M15" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N15" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O15" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1789,55 +1785,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C16" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D16" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E16" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F16" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K16" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L16" t="n">
         <v>4007.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N16" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O16" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,7 +1848,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1869,57 +1869,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C17" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D17" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E17" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H17" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J17" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K17" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L17" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M17" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N17" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O17" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1930,78 +1930,78 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C18" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D18" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E18" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F18" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H18" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K18" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L18" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M18" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N18" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O18" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2012,7 +2012,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2040,81 +2040,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C19" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D19" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E19" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F19" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H19" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J19" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K19" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L19" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M19" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2122,67 +2122,63 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C20" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E20" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F20" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H20" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J20" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K20" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L20" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M20" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N20" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O20" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2199,55 +2195,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C21" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D21" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E21" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F21" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H21" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I21" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K21" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L21" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M21" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2260,11 +2260,13 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2279,76 +2281,80 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C22" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D22" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E22" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F22" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H22" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J22" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K22" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L22" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M22" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O22" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+        <v>4171.5</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2361,85 +2367,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C23" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D23" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E23" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F23" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I23" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K23" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L23" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M23" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N23" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O23" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2449,55 +2451,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C24" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D24" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E24" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H24" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I24" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J24" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L24" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M24" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N24" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O24" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2505,25 +2511,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2535,57 +2537,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C25" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D25" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E25" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F25" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H25" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I25" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J25" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K25" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L25" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M25" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N25" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O25" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,14 +2598,14 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2626,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C26" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D26" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E26" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F26" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H26" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I26" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J26" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K26" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L26" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M26" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N26" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O26" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2682,13 +2684,11 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2701,59 +2701,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C27" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D27" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E27" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H27" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J27" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K27" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L27" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M27" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N27" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O27" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2766,21 +2762,25 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2788,50 +2788,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C28" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D28" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E28" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F28" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H28" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I28" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J28" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K28" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L28" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M28" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N28" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O28" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2842,7 +2842,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2854,11 +2854,13 @@
       </c>
       <c r="U28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2870,50 +2872,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C29" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E29" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F29" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H29" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I29" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J29" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K29" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L29" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M29" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N29" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O29" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2924,80 +2926,78 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C30" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D30" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E30" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F30" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H30" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I30" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J30" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K30" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L30" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M30" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N30" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O30" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3008,16 +3008,20 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3027,59 +3031,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C31" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D31" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E31" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F31" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H31" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J31" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K31" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L31" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M31" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N31" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O31" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3090,20 +3090,16 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3118,50 +3114,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C32" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D32" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E32" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F32" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H32" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J32" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K32" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L32" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M32" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N32" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O32" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3172,13 +3168,15 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3196,50 +3194,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C33" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D33" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E33" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F33" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H33" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I33" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J33" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K33" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L33" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M33" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N33" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O33" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3250,7 +3248,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3276,50 +3274,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C34" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D34" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E34" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F34" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H34" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I34" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J34" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K34" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L34" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M34" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N34" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O34" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3327,17 +3325,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3351,55 +3351,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C35" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D35" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E35" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F35" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H35" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J35" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K35" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L35" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N35" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O35" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3409,18 +3413,16 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3442,50 +3444,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C36" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D36" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E36" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F36" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I36" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J36" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K36" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L36" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M36" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N36" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O36" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3493,18 +3495,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3517,78 +3519,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C37" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D37" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E37" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F37" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H37" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I37" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J37" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K37" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L37" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M37" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N37" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O37" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3601,80 +3601,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C38" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D38" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E38" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H38" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I38" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K38" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L38" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M38" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N38" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O38" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3685,57 +3689,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C39" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D39" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E39" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F39" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H39" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J39" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K39" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L39" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M39" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N39" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O39" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3746,20 +3750,16 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3769,59 +3769,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C40" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D40" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E40" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F40" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H40" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I40" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J40" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K40" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L40" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M40" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N40" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O40" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3832,19 +3828,25 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3856,50 +3858,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C41" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D41" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E41" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F41" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H41" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I41" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J41" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K41" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L41" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M41" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N41" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O41" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3910,25 +3912,19 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3940,50 +3936,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C42" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D42" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E42" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F42" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I42" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J42" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K42" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L42" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M42" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N42" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O42" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3996,11 +3992,13 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4013,55 +4011,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C43" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D43" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E43" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I43" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J43" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K43" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L43" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M43" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N43" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O43" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4069,18 +4071,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4095,57 +4097,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C44" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D44" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E44" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F44" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H44" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I44" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J44" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K44" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L44" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M44" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N44" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O44" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4153,14 +4155,12 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4179,70 +4179,76 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C45" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D45" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E45" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F45" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H45" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I45" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J45" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K45" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L45" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M45" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N45" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O45" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4779.4</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4254,81 +4260,73 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C46" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E46" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H46" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J46" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K46" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L46" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M46" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N46" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O46" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4352,63 +4350,67 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C47" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D47" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E47" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F47" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H47" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J47" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K47" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L47" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M47" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N47" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O47" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4432,69 +4434,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C48" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D48" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E48" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F48" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H48" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I48" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J48" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K48" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L48" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M48" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N48" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O48" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4651.3</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4511,55 +4507,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C49" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D49" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E49" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F49" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H49" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J49" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K49" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L49" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M49" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N49" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O49" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4572,14 +4572,18 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4591,81 +4595,81 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C50" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D50" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E50" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F50" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H50" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J50" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K50" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L50" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M50" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N50" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O50" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4675,74 +4679,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C51" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E51" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F51" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J51" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K51" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L51" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M51" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N51" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O51" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4766,50 +4764,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C52" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D52" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E52" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H52" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K52" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L52" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M52" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N52" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O52" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4819,12 +4817,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4841,70 +4839,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C53" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D53" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E53" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F53" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H53" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I53" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K53" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L53" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M53" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N53" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O53" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4923,74 +4927,72 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C54" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D54" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E54" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F54" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H54" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I54" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J54" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K54" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L54" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M54" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N54" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O54" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5016,65 +5018,67 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C55" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E55" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F55" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H55" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J55" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K55" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L55" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M55" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N55" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O55" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5091,76 +5095,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C56" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D56" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E56" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F56" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H56" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I56" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J56" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K56" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L56" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M56" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N56" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O56" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5177,75 +5173,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C57" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D57" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H57" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J57" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K57" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L57" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M57" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N57" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O57" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5257,85 +5265,79 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D58" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E58" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F58" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H58" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J58" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K58" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L58" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M58" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N58" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O58" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5347,57 +5349,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C59" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D59" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E59" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F59" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H59" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I59" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J59" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K59" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L59" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M59" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N59" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O59" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5405,18 +5407,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5438,69 +5440,71 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C60" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D60" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E60" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F60" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I60" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J60" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K60" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L60" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M60" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N60" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O60" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5513,76 +5517,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C61" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D61" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E61" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F61" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H61" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I61" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J61" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K61" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L61" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M61" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N61" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O61" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5604,50 +5602,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4382.5</v>
+        <v>4324.4</v>
       </c>
       <c r="C62" t="n">
-        <v>4414.1</v>
+        <v>4328.6</v>
       </c>
       <c r="D62" t="n">
-        <v>4327.6</v>
+        <v>4324</v>
       </c>
       <c r="E62" t="n">
-        <v>4376.4</v>
+        <v>4328.6</v>
       </c>
       <c r="F62" t="n">
-        <v>-7.5</v>
+        <v>-47.8</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0109</v>
       </c>
       <c r="H62" t="n">
-        <v>86.5</v>
+        <v>4.6</v>
       </c>
       <c r="I62" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J62" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K62" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L62" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M62" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N62" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O62" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5657,12 +5655,12 @@
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5680,90 +5678,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4394.7</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4407.5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>4330.9</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4336.6</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-39.8</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0091</v>
-      </c>
-      <c r="H63" t="n">
-        <v>76.59999999999999</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4241.1</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4292.67</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4333.15</v>
-      </c>
-      <c r="L63" t="n">
-        <v>4373.62</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4419.65</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4465.67</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4500.6</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4101.1</v>
+        <v>4032.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4102.9</v>
+        <v>4078.1</v>
       </c>
       <c r="D2" t="n">
-        <v>4012</v>
+        <v>3955.4</v>
       </c>
       <c r="E2" t="n">
-        <v>4038.9</v>
+        <v>4038.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-57.4</v>
+        <v>-0.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.014</v>
+        <v>-0.0001</v>
       </c>
       <c r="H2" t="n">
-        <v>90.90000000000001</v>
+        <v>122.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3884.7</v>
+        <v>3921.1</v>
       </c>
       <c r="J2" t="n">
-        <v>4003.65</v>
+        <v>3938.72</v>
       </c>
       <c r="K2" t="n">
-        <v>4039.6</v>
+        <v>3993.45</v>
       </c>
       <c r="L2" t="n">
-        <v>4075.55</v>
+        <v>4048.17</v>
       </c>
       <c r="M2" t="n">
-        <v>4153</v>
+        <v>4084.35</v>
       </c>
       <c r="N2" t="n">
-        <v>4230.45</v>
+        <v>4120.52</v>
       </c>
       <c r="O2" t="n">
-        <v>4224.9</v>
+        <v>4193.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,12 +687,12 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C3" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D3" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E3" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H3" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I3" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J3" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K3" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L3" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M3" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O3" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,13 +774,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C4" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D4" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E4" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F4" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H4" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I4" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J4" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L4" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M4" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N4" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O4" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,10 +851,8 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
@@ -884,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D5" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E5" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F5" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H5" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K5" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L5" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M5" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O5" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -964,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E6" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F6" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H6" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J6" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K6" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L6" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M6" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N6" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O6" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,18 +1011,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,61 +1035,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C7" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D7" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E7" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H7" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I7" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J7" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K7" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L7" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M7" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N7" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O7" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
@@ -1102,7 +1104,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1128,72 +1130,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C8" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D8" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E8" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H8" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I8" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J8" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K8" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L8" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M8" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N8" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O8" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1205,59 +1205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C9" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D9" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E9" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F9" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H9" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I9" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K9" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L9" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M9" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N9" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O9" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1265,18 +1261,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1289,61 +1285,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C10" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D10" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E10" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H10" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I10" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K10" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L10" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M10" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N10" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O10" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
@@ -1352,7 +1356,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1364,91 +1368,85 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C11" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E11" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F11" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H11" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I11" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J11" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K11" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L11" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M11" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O11" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
@@ -1457,55 +1455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C12" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D12" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E12" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F12" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H12" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K12" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L12" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M12" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N12" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O12" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1516,20 +1518,16 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
@@ -1541,70 +1539,74 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C13" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D13" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E13" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F13" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H13" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K13" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L13" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M13" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N13" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O13" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1621,76 +1623,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C14" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D14" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E14" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H14" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K14" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L14" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M14" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N14" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O14" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,55 +1701,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C15" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D15" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E15" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F15" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H15" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K15" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L15" t="n">
         <v>4007.38</v>
       </c>
       <c r="M15" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N15" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O15" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,57 +1785,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C16" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D16" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E16" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H16" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J16" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K16" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L16" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M16" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N16" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O16" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1850,76 +1848,76 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C17" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D17" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E17" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F17" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H17" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J17" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K17" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L17" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M17" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N17" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O17" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1958,81 +1956,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C18" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D18" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E18" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F18" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H18" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I18" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J18" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K18" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L18" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M18" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2040,67 +2038,63 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C19" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D19" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E19" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F19" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H19" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J19" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K19" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L19" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M19" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N19" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O19" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2117,55 +2111,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C20" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D20" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E20" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F20" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H20" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I20" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J20" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K20" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L20" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M20" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2176,13 +2174,15 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2197,77 +2197,81 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C21" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D21" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E21" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F21" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H21" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J21" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K21" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L21" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M21" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O21" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2279,85 +2283,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C22" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D22" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E22" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F22" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I22" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K22" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L22" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M22" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N22" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O22" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2367,55 +2367,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C23" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D23" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E23" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H23" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I23" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J23" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K23" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L23" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M23" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N23" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O23" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2423,25 +2427,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2453,57 +2453,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C24" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D24" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E24" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F24" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H24" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J24" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K24" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L24" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O24" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2544,50 +2544,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C25" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D25" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E25" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F25" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I25" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J25" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K25" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L25" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M25" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N25" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O25" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2598,15 +2598,13 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2619,59 +2617,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C26" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D26" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E26" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F26" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H26" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K26" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L26" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M26" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N26" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O26" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2682,23 +2676,27 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2706,50 +2704,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C27" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D27" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E27" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F27" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H27" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I27" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J27" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L27" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M27" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N27" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O27" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,11 +2770,13 @@
       </c>
       <c r="U27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2788,50 +2788,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C28" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D28" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E28" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F28" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H28" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I28" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J28" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K28" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L28" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M28" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N28" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O28" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2844,78 +2844,76 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C29" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D29" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E29" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H29" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I29" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J29" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K29" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L29" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M29" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N29" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O29" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2928,14 +2926,18 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2945,59 +2947,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C30" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D30" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E30" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F30" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H30" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J30" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K30" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L30" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M30" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N30" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O30" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3010,18 +3008,14 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3036,50 +3030,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C31" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D31" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E31" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F31" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H31" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I31" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J31" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K31" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L31" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M31" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N31" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O31" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3092,11 +3086,13 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3114,50 +3110,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C32" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D32" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E32" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F32" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H32" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I32" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K32" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L32" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M32" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N32" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O32" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3194,50 +3190,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C33" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D33" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E33" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F33" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H33" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I33" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J33" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K33" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L33" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M33" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N33" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O33" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3245,17 +3241,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3269,55 +3267,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C34" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D34" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E34" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F34" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H34" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J34" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K34" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L34" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M34" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N34" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O34" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3327,18 +3329,16 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3360,50 +3360,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C35" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D35" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E35" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F35" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I35" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K35" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L35" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M35" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N35" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O35" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3411,18 +3411,18 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3435,79 +3435,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C36" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D36" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E36" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F36" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H36" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J36" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K36" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L36" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M36" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N36" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O36" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3519,80 +3517,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C37" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D37" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E37" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H37" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I37" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K37" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L37" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M37" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N37" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O37" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3603,57 +3605,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C38" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D38" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E38" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F38" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H38" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J38" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K38" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L38" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M38" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N38" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O38" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3666,18 +3668,14 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3687,59 +3685,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C39" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D39" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E39" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F39" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H39" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I39" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J39" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K39" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L39" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M39" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N39" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O39" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3752,17 +3746,23 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3774,50 +3774,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C40" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E40" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F40" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H40" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J40" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K40" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L40" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M40" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N40" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O40" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3830,23 +3830,17 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3858,50 +3852,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C41" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D41" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E41" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F41" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I41" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J41" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K41" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L41" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M41" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N41" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O41" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3912,13 +3906,15 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3931,55 +3927,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C42" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D42" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E42" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J42" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K42" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L42" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M42" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N42" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O42" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3987,18 +3987,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C43" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D43" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E43" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F43" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H43" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I43" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J43" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K43" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L43" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M43" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N43" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O43" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4071,14 +4071,12 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4097,70 +4095,76 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C44" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D44" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E44" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F44" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H44" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I44" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J44" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K44" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L44" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M44" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N44" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O44" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4172,78 +4176,70 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C45" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E45" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H45" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J45" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K45" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L45" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M45" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N45" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O45" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
@@ -4270,60 +4266,64 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C46" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E46" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F46" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H46" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I46" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J46" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K46" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L46" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M46" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N46" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O46" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
@@ -4350,69 +4350,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C47" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D47" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E47" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F47" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H47" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I47" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J47" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K47" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L47" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M47" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N47" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O47" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4429,55 +4423,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C48" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D48" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E48" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F48" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H48" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J48" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K48" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L48" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M48" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N48" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O48" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4488,16 +4486,20 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4509,82 +4511,82 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C49" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D49" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E49" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F49" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H49" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J49" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K49" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L49" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M49" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N49" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O49" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4593,67 +4595,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C50" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D50" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E50" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F50" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H50" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J50" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K50" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L50" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M50" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N50" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O50" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4684,50 +4680,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C51" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D51" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E51" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H51" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J51" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K51" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L51" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M51" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N51" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O51" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4737,12 +4733,12 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4759,70 +4755,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C52" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D52" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E52" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F52" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H52" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I52" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K52" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L52" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M52" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N52" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O52" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4841,74 +4843,72 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C53" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D53" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E53" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F53" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H53" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I53" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J53" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K53" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L53" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M53" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N53" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O53" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4934,65 +4934,67 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C54" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E54" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F54" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H54" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J54" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K54" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L54" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M54" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N54" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O54" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5009,76 +5011,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C55" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D55" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E55" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F55" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H55" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I55" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J55" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K55" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L55" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M55" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N55" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O55" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5095,75 +5089,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C56" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D56" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H56" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J56" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K56" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L56" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M56" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N56" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O56" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5175,85 +5181,79 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D57" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E57" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F57" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H57" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J57" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K57" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L57" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M57" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N57" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O57" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5265,57 +5265,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C58" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D58" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E58" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F58" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J58" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K58" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L58" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M58" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N58" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O58" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5323,18 +5323,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5356,70 +5356,72 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C59" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D59" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E59" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F59" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J59" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K59" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L59" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M59" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N59" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O59" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5431,76 +5433,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C60" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D60" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E60" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F60" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H60" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I60" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J60" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K60" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L60" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M60" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N60" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O60" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5522,50 +5518,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C61" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D61" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E61" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F61" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H61" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I61" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J61" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K61" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L61" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M61" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N61" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O61" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5575,12 +5571,12 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5602,50 +5598,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4328.6</v>
+        <v>4312.8</v>
       </c>
       <c r="D62" t="n">
-        <v>4324</v>
+        <v>4307.1</v>
       </c>
       <c r="E62" t="n">
-        <v>4328.6</v>
+        <v>4308.1</v>
       </c>
       <c r="F62" t="n">
-        <v>-47.8</v>
+        <v>-10.3</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0109</v>
+        <v>-0.0024</v>
       </c>
       <c r="H62" t="n">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="I62" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J62" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K62" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L62" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M62" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N62" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O62" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5653,14 +5649,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4032.5</v>
+        <v>4025</v>
       </c>
       <c r="C2" t="n">
-        <v>4078.1</v>
+        <v>4131</v>
       </c>
       <c r="D2" t="n">
-        <v>3955.4</v>
+        <v>3973</v>
       </c>
       <c r="E2" t="n">
-        <v>4038.5</v>
+        <v>4082.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4</v>
+        <v>43.9</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0001</v>
+        <v>0.0109</v>
       </c>
       <c r="H2" t="n">
-        <v>122.7</v>
+        <v>158</v>
       </c>
       <c r="I2" t="n">
-        <v>3921.1</v>
+        <v>3832.7</v>
       </c>
       <c r="J2" t="n">
-        <v>3938.72</v>
+        <v>3926.67</v>
       </c>
       <c r="K2" t="n">
-        <v>3993.45</v>
+        <v>3977.15</v>
       </c>
       <c r="L2" t="n">
-        <v>4048.17</v>
+        <v>4027.62</v>
       </c>
       <c r="M2" t="n">
-        <v>4084.35</v>
+        <v>4099.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4120.52</v>
+        <v>4172.08</v>
       </c>
       <c r="O2" t="n">
-        <v>4193.8</v>
+        <v>4200.8</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,11 +692,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C3" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E3" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F3" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H3" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I3" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J3" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L3" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N3" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O3" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,12 +767,10 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D4" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E4" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F4" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H4" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K4" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L4" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M4" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N4" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O4" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,7 +850,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -880,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C5" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E5" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F5" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H5" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K5" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L5" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M5" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N5" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O5" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,18 +927,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,70 +951,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C6" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D6" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E6" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F6" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H6" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J6" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K6" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L6" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M6" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N6" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O6" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1044,72 +1046,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C7" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D7" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E7" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F7" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H7" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I7" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J7" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K7" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L7" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M7" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N7" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O7" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1121,59 +1121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C8" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E8" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F8" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H8" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I8" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L8" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M8" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N8" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O8" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1181,18 +1177,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1205,70 +1201,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D9" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E9" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H9" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I9" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K9" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L9" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M9" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N9" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O9" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1280,91 +1284,85 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C10" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H10" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J10" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K10" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L10" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M10" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O10" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="U10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
@@ -1373,55 +1371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C11" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D11" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F11" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H11" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K11" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L11" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M11" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O11" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1434,18 +1436,14 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1457,70 +1455,74 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C12" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D12" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E12" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H12" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K12" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L12" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M12" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N12" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1537,76 +1539,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C13" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D13" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E13" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H13" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J13" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K13" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L13" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M13" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N13" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O13" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1623,55 +1617,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C14" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D14" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E14" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F14" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H14" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K14" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L14" t="n">
         <v>4007.38</v>
       </c>
       <c r="M14" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N14" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O14" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,7 +1680,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1703,57 +1701,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C15" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D15" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E15" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H15" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J15" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K15" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L15" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M15" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N15" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O15" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,78 +1762,78 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C16" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D16" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E16" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F16" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H16" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J16" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K16" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L16" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M16" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N16" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O16" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1846,7 +1844,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1874,81 +1872,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C17" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D17" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E17" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F17" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H17" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I17" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J17" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K17" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L17" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M17" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1956,67 +1954,63 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C18" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D18" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E18" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F18" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H18" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I18" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J18" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K18" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L18" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M18" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N18" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O18" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2033,55 +2027,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C19" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D19" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E19" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F19" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H19" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I19" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J19" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L19" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M19" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N19" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O19" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2094,11 +2092,13 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2113,76 +2113,80 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C20" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D20" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E20" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F20" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H20" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J20" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K20" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L20" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M20" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O20" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>4171.5</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2195,85 +2199,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C21" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D21" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E21" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F21" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I21" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K21" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L21" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M21" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N21" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O21" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2283,55 +2283,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C22" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D22" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E22" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H22" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I22" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J22" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L22" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M22" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N22" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O22" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,25 +2343,21 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2369,57 +2369,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C23" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D23" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E23" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F23" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H23" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J23" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K23" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L23" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N23" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O23" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,14 +2430,14 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2460,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C24" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D24" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E24" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F24" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H24" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I24" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J24" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K24" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L24" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M24" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N24" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O24" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,13 +2516,11 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2535,59 +2533,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C25" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D25" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E25" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F25" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H25" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J25" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K25" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L25" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M25" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O25" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,21 +2594,25 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2622,50 +2620,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C26" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D26" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F26" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H26" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I26" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K26" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L26" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M26" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N26" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O26" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2676,7 +2674,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2688,11 +2686,13 @@
       </c>
       <c r="U26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2704,50 +2704,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C27" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D27" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E27" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F27" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H27" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I27" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J27" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K27" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L27" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M27" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N27" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O27" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2758,80 +2758,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C28" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D28" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E28" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H28" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J28" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K28" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L28" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M28" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N28" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O28" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2842,16 +2840,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2861,59 +2863,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C29" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D29" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E29" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F29" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H29" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J29" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K29" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L29" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M29" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N29" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O29" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2924,20 +2922,16 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2952,50 +2946,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C30" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D30" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E30" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H30" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J30" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K30" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L30" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M30" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N30" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O30" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3006,13 +3000,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3030,50 +3026,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C31" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D31" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E31" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F31" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H31" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I31" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K31" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L31" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M31" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N31" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O31" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3084,7 +3080,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3110,50 +3106,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C32" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D32" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E32" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F32" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H32" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I32" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J32" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K32" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L32" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M32" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N32" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O32" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3161,17 +3157,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3185,55 +3183,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C33" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D33" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H33" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J33" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K33" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L33" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M33" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N33" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O33" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3243,18 +3245,16 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3276,50 +3276,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C34" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D34" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E34" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F34" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I34" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J34" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K34" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L34" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M34" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N34" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O34" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3327,18 +3327,18 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3351,78 +3351,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C35" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D35" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E35" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F35" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H35" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I35" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J35" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K35" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L35" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M35" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N35" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O35" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3435,80 +3433,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C36" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D36" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E36" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F36" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H36" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I36" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K36" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L36" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M36" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N36" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O36" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3519,57 +3521,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C37" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D37" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E37" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F37" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H37" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J37" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K37" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L37" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M37" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N37" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O37" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3580,20 +3582,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3603,59 +3601,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C38" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D38" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E38" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F38" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H38" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I38" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J38" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K38" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L38" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M38" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N38" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O38" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3666,19 +3660,25 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3690,50 +3690,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C39" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D39" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E39" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F39" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H39" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J39" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K39" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L39" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M39" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N39" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O39" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3744,25 +3744,19 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3774,50 +3768,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C40" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D40" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E40" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I40" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J40" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K40" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L40" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M40" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N40" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O40" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3830,11 +3824,13 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3847,55 +3843,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C41" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D41" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E41" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I41" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J41" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K41" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L41" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M41" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N41" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O41" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3903,18 +3903,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3929,57 +3929,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C42" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D42" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E42" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F42" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H42" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I42" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J42" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K42" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L42" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M42" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O42" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3987,14 +3987,12 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4013,70 +4011,76 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C43" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D43" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E43" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F43" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H43" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I43" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J43" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K43" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L43" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M43" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N43" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O43" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4779.4</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4088,81 +4092,73 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C44" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D44" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E44" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H44" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J44" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K44" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L44" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M44" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N44" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O44" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4186,63 +4182,67 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C45" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E45" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F45" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H45" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I45" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J45" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K45" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L45" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M45" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N45" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O45" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4266,69 +4266,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C46" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D46" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E46" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F46" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H46" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I46" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J46" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K46" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L46" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M46" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N46" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O46" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4651.3</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4345,55 +4339,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C47" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D47" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E47" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F47" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H47" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J47" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K47" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L47" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M47" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O47" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4406,14 +4404,18 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4425,81 +4427,81 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C48" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D48" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E48" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F48" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H48" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J48" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K48" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L48" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M48" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N48" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O48" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4509,74 +4511,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C49" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D49" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E49" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F49" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H49" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J49" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K49" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L49" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M49" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N49" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O49" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4600,50 +4596,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C50" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D50" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E50" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H50" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J50" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K50" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L50" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M50" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N50" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O50" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4653,12 +4649,12 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4675,70 +4671,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C51" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D51" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E51" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F51" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H51" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I51" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J51" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K51" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L51" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M51" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N51" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O51" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4757,74 +4759,72 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C52" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D52" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E52" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F52" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H52" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I52" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J52" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K52" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L52" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M52" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N52" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O52" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4850,65 +4850,67 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C53" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E53" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F53" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H53" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J53" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K53" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L53" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M53" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N53" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O53" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4925,76 +4927,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C54" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D54" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E54" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F54" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H54" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I54" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J54" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K54" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L54" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M54" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N54" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O54" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5011,75 +5005,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C55" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D55" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E55" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H55" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J55" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K55" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L55" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M55" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O55" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5091,85 +5097,79 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C56" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D56" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E56" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F56" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H56" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K56" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L56" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M56" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N56" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O56" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5181,57 +5181,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C57" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D57" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F57" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H57" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I57" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J57" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K57" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L57" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M57" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N57" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O57" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5239,18 +5239,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5272,69 +5272,71 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C58" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F58" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J58" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K58" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L58" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M58" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N58" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O58" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5347,76 +5349,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C59" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D59" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E59" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H59" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I59" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J59" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K59" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L59" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M59" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N59" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O59" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5438,50 +5434,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C60" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D60" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E60" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F60" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H60" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I60" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J60" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K60" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L60" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M60" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N60" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O60" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5491,12 +5487,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5518,50 +5514,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C61" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D61" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E61" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F61" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H61" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I61" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J61" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K61" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L61" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M61" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N61" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O61" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5574,7 +5570,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5598,50 +5594,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>4309.5</v>
       </c>
       <c r="C62" t="n">
-        <v>4312.8</v>
+        <v>4351.6</v>
       </c>
       <c r="D62" t="n">
-        <v>4307.1</v>
+        <v>4289.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4308.1</v>
+        <v>4321.2</v>
       </c>
       <c r="F62" t="n">
-        <v>-10.3</v>
+        <v>23.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0024</v>
+        <v>0.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>5.7</v>
+        <v>62.4</v>
       </c>
       <c r="I62" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J62" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K62" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L62" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M62" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N62" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O62" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5654,11 +5650,13 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5671,7 +5669,93 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4315</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4315.6</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4300.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4321.2</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4226.8</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4259.2</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4290</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4320.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4352.4</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4384</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4414</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4025</v>
+        <v>4049.2</v>
       </c>
       <c r="C2" t="n">
-        <v>4131</v>
+        <v>4157.1</v>
       </c>
       <c r="D2" t="n">
-        <v>3973</v>
+        <v>4042.8</v>
       </c>
       <c r="E2" t="n">
-        <v>4082.4</v>
+        <v>4125.7</v>
       </c>
       <c r="F2" t="n">
-        <v>43.9</v>
+        <v>43.3</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0109</v>
+        <v>0.0106</v>
       </c>
       <c r="H2" t="n">
-        <v>158</v>
+        <v>114.3</v>
       </c>
       <c r="I2" t="n">
-        <v>3832.7</v>
+        <v>3815</v>
       </c>
       <c r="J2" t="n">
-        <v>3926.67</v>
+        <v>3939.6</v>
       </c>
       <c r="K2" t="n">
-        <v>3977.15</v>
+        <v>4003.4</v>
       </c>
       <c r="L2" t="n">
-        <v>4027.62</v>
+        <v>4067.2</v>
       </c>
       <c r="M2" t="n">
-        <v>4099.85</v>
+        <v>4161.4</v>
       </c>
       <c r="N2" t="n">
-        <v>4172.08</v>
+        <v>4255.6</v>
       </c>
       <c r="O2" t="n">
-        <v>4200.8</v>
+        <v>4289</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D3" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E3" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F3" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H3" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K3" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L3" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M3" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N3" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O3" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -796,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C4" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E4" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F4" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H4" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L4" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M4" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N4" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O4" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,18 +845,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -871,61 +869,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C5" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D5" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E5" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F5" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H5" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I5" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J5" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K5" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L5" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M5" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N5" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O5" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
@@ -934,7 +938,7 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -960,72 +964,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D6" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E6" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F6" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H6" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I6" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J6" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K6" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L6" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M6" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N6" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O6" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1037,59 +1039,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C7" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E7" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F7" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H7" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I7" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J7" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K7" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L7" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M7" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N7" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O7" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,18 +1095,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1121,61 +1119,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C8" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D8" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E8" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H8" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I8" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K8" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L8" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M8" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N8" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O8" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
@@ -1184,7 +1190,7 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1196,91 +1202,85 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C9" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D9" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E9" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F9" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H9" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I9" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J9" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K9" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L9" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M9" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O9" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
@@ -1289,55 +1289,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C10" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D10" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F10" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H10" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K10" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L10" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M10" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N10" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O10" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1348,20 +1352,16 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1373,70 +1373,74 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C11" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D11" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E11" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H11" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K11" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L11" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M11" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N11" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1453,76 +1457,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C12" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D12" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E12" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F12" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H12" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J12" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K12" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L12" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M12" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N12" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O12" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1539,55 +1535,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C13" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D13" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E13" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F13" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H13" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K13" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L13" t="n">
         <v>4007.38</v>
       </c>
       <c r="M13" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N13" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O13" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,57 +1619,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C14" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D14" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E14" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H14" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J14" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K14" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L14" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M14" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N14" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O14" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,76 +1682,76 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C15" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D15" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E15" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F15" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H15" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K15" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L15" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M15" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N15" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O15" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1790,81 +1790,81 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C16" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D16" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E16" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F16" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H16" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J16" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K16" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L16" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M16" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1872,67 +1872,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C17" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E17" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F17" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H17" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J17" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K17" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L17" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M17" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N17" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O17" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1949,55 +1945,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C18" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D18" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E18" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F18" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H18" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I18" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K18" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L18" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M18" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N18" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2008,13 +2008,15 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2029,77 +2031,81 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C19" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D19" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E19" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F19" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H19" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J19" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L19" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M19" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O19" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2111,85 +2117,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C20" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D20" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E20" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F20" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I20" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K20" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L20" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M20" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N20" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O20" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2199,55 +2201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C21" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D21" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E21" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H21" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K21" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L21" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M21" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N21" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O21" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2255,25 +2261,21 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2285,57 +2287,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C22" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D22" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E22" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F22" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H22" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J22" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L22" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N22" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O22" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,12 +2350,12 @@
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2376,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C23" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D23" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E23" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F23" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I23" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J23" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K23" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L23" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M23" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N23" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O23" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,15 +2432,13 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2451,59 +2451,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C24" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D24" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H24" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J24" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K24" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L24" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M24" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O24" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2514,23 +2510,27 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2538,50 +2538,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C25" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D25" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E25" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F25" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H25" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I25" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K25" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L25" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M25" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N25" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O25" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,11 +2604,13 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2620,50 +2622,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C26" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D26" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E26" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F26" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H26" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I26" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J26" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K26" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L26" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M26" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N26" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O26" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2676,78 +2678,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C27" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D27" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E27" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H27" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I27" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J27" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K27" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L27" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M27" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N27" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O27" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,14 +2760,18 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2777,59 +2781,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C28" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D28" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E28" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F28" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H28" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J28" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K28" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L28" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M28" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N28" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O28" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2842,18 +2842,14 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2868,50 +2864,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C29" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D29" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E29" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F29" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H29" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I29" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J29" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K29" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L29" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M29" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O29" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2924,11 +2920,13 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2946,50 +2944,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C30" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D30" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E30" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F30" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H30" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I30" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J30" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K30" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L30" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M30" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N30" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O30" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3026,50 +3024,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C31" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D31" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E31" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F31" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H31" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I31" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J31" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K31" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L31" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M31" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N31" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O31" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3077,17 +3075,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3101,55 +3101,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C32" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D32" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E32" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H32" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J32" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K32" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L32" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M32" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N32" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O32" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3159,18 +3163,16 @@
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3192,50 +3194,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C33" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D33" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E33" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F33" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I33" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J33" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K33" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L33" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M33" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N33" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O33" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3243,18 +3245,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3267,79 +3269,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C34" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D34" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E34" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F34" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H34" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I34" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J34" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K34" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L34" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M34" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N34" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O34" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3351,80 +3351,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C35" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D35" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E35" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F35" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H35" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I35" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J35" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K35" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L35" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M35" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N35" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O35" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3435,57 +3439,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C36" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D36" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E36" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F36" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H36" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J36" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K36" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L36" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M36" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N36" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O36" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3498,18 +3502,14 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3519,59 +3519,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C37" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D37" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E37" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F37" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H37" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I37" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J37" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K37" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L37" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M37" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N37" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O37" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3584,17 +3580,23 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3606,50 +3608,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C38" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D38" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E38" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F38" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H38" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J38" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K38" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L38" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M38" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N38" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O38" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3662,23 +3664,17 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3690,50 +3686,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C39" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D39" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E39" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H39" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I39" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J39" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K39" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L39" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M39" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N39" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O39" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3744,13 +3740,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3763,55 +3761,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C40" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D40" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E40" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J40" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K40" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L40" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M40" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N40" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O40" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3819,18 +3821,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3845,57 +3847,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C41" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D41" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E41" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F41" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H41" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I41" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J41" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K41" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L41" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M41" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N41" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O41" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3903,14 +3905,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3929,70 +3929,76 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C42" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D42" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E42" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F42" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H42" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I42" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J42" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K42" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L42" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M42" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N42" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O42" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4004,78 +4010,70 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C43" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E43" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H43" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J43" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K43" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L43" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N43" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O43" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4102,60 +4100,64 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C44" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D44" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H44" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I44" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J44" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K44" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L44" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M44" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N44" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O44" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4182,69 +4184,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C45" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D45" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E45" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F45" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H45" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I45" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J45" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K45" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L45" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M45" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O45" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4261,55 +4257,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C46" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D46" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E46" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F46" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H46" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I46" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J46" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K46" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L46" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M46" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O46" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4320,16 +4320,20 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4341,82 +4345,82 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C47" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D47" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E47" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F47" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H47" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J47" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K47" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L47" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M47" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N47" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O47" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4425,67 +4429,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C48" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D48" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E48" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F48" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K48" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L48" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M48" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N48" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O48" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4516,50 +4514,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C49" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D49" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E49" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F49" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H49" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J49" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K49" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L49" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M49" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N49" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O49" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4569,12 +4567,12 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4591,70 +4589,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C50" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D50" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E50" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F50" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H50" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I50" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J50" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K50" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L50" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M50" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N50" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O50" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4673,74 +4677,72 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C51" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D51" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E51" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F51" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H51" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I51" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J51" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K51" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L51" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M51" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N51" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O51" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4766,65 +4768,67 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C52" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E52" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F52" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H52" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J52" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K52" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L52" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M52" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N52" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O52" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4841,76 +4845,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C53" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D53" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E53" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F53" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H53" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I53" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J53" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K53" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L53" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M53" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N53" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O53" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4927,75 +4923,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C54" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D54" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E54" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H54" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J54" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K54" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L54" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M54" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O54" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5007,85 +5015,79 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C55" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D55" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E55" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F55" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H55" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J55" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K55" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L55" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M55" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N55" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O55" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5097,57 +5099,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C56" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D56" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E56" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F56" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H56" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J56" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K56" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L56" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M56" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N56" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O56" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5155,18 +5157,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5188,70 +5190,72 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C57" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D57" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F57" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J57" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K57" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L57" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M57" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N57" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O57" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5263,76 +5267,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C58" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D58" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E58" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H58" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I58" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J58" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K58" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L58" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M58" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N58" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O58" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5354,50 +5352,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C59" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D59" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E59" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F59" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H59" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I59" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J59" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K59" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L59" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M59" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N59" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O59" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5407,12 +5405,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5434,50 +5432,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C60" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D60" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E60" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F60" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H60" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I60" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J60" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K60" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L60" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M60" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N60" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O60" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5514,50 +5512,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C61" t="n">
-        <v>4338</v>
+        <v>4351.6</v>
       </c>
       <c r="D61" t="n">
-        <v>4278.3</v>
+        <v>4289.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4298</v>
+        <v>4321.2</v>
       </c>
       <c r="F61" t="n">
-        <v>-20.4</v>
+        <v>23.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0054</v>
       </c>
       <c r="H61" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="I61" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J61" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K61" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L61" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M61" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N61" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O61" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5565,19 +5563,19 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5589,75 +5587,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4309.5</v>
+        <v>4150.1</v>
       </c>
       <c r="C62" t="n">
-        <v>4351.6</v>
+        <v>4153.9</v>
       </c>
       <c r="D62" t="n">
-        <v>4289.2</v>
+        <v>4147.8</v>
       </c>
       <c r="E62" t="n">
-        <v>4321.2</v>
+        <v>4153.7</v>
       </c>
       <c r="F62" t="n">
-        <v>23.2</v>
+        <v>-167.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0388</v>
       </c>
       <c r="H62" t="n">
-        <v>62.4</v>
+        <v>6.1</v>
       </c>
       <c r="I62" t="n">
-        <v>4218.6</v>
+        <v>4226.8</v>
       </c>
       <c r="J62" t="n">
-        <v>4233.22</v>
+        <v>4259.2</v>
       </c>
       <c r="K62" t="n">
-        <v>4268.15</v>
+        <v>4290</v>
       </c>
       <c r="L62" t="n">
-        <v>4303.07</v>
+        <v>4320.8</v>
       </c>
       <c r="M62" t="n">
-        <v>4327.85</v>
+        <v>4352.4</v>
       </c>
       <c r="N62" t="n">
-        <v>4352.63</v>
+        <v>4384</v>
       </c>
       <c r="O62" t="n">
-        <v>4397.7</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+        <v>4414</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5669,93 +5675,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>4315</v>
-      </c>
-      <c r="C63" t="n">
-        <v>4315.6</v>
-      </c>
-      <c r="D63" t="n">
-        <v>4300.5</v>
-      </c>
-      <c r="E63" t="n">
-        <v>4321.2</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>15.1</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4226.8</v>
-      </c>
-      <c r="J63" t="n">
-        <v>4259.2</v>
-      </c>
-      <c r="K63" t="n">
-        <v>4290</v>
-      </c>
-      <c r="L63" t="n">
-        <v>4320.8</v>
-      </c>
-      <c r="M63" t="n">
-        <v>4352.4</v>
-      </c>
-      <c r="N63" t="n">
-        <v>4384</v>
-      </c>
-      <c r="O63" t="n">
-        <v>4414</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4049.2</v>
+        <v>4187.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4157.1</v>
+        <v>4215.5</v>
       </c>
       <c r="D2" t="n">
-        <v>4042.8</v>
+        <v>4140.6</v>
       </c>
       <c r="E2" t="n">
-        <v>4125.7</v>
+        <v>4167.5</v>
       </c>
       <c r="F2" t="n">
-        <v>43.3</v>
+        <v>41.8</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0106</v>
+        <v>0.0101</v>
       </c>
       <c r="H2" t="n">
-        <v>114.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>3815</v>
+        <v>3928.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3939.6</v>
+        <v>4024.28</v>
       </c>
       <c r="K2" t="n">
-        <v>4003.4</v>
+        <v>4068.55</v>
       </c>
       <c r="L2" t="n">
-        <v>4067.2</v>
+        <v>4112.83</v>
       </c>
       <c r="M2" t="n">
-        <v>4161.4</v>
+        <v>4182.85</v>
       </c>
       <c r="N2" t="n">
-        <v>4255.6</v>
+        <v>4252.88</v>
       </c>
       <c r="O2" t="n">
-        <v>4289</v>
+        <v>4271.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -714,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C3" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F3" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H3" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I3" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K3" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L3" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M3" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N3" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O3" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,61 +789,67 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C4" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D4" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E4" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F4" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H4" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I4" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J4" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K4" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L4" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M4" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N4" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O4" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
@@ -852,7 +858,7 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -878,72 +884,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C5" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D5" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E5" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F5" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H5" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I5" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J5" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K5" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L5" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M5" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N5" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O5" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -955,59 +959,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C6" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D6" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E6" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F6" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H6" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I6" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L6" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M6" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N6" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O6" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1015,18 +1015,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,61 +1039,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C7" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D7" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E7" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H7" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I7" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J7" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K7" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L7" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M7" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N7" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O7" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
@@ -1102,7 +1110,7 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1114,91 +1122,85 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C8" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D8" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E8" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F8" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H8" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J8" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K8" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L8" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M8" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N8" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O8" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
@@ -1207,55 +1209,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C9" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D9" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E9" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F9" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H9" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K9" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L9" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M9" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O9" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,20 +1272,16 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1291,70 +1293,74 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C10" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D10" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E10" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H10" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J10" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L10" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M10" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N10" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1371,76 +1377,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C11" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D11" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E11" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F11" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H11" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J11" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K11" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L11" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N11" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O11" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1457,55 +1455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C12" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D12" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E12" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F12" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H12" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K12" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L12" t="n">
         <v>4007.38</v>
       </c>
       <c r="M12" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N12" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O12" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1537,57 +1539,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D13" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E13" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H13" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J13" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K13" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L13" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M13" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N13" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O13" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,76 +1602,76 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C14" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D14" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E14" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F14" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H14" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L14" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M14" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N14" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O14" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1708,81 +1710,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C15" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D15" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E15" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F15" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H15" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J15" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K15" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L15" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M15" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
@@ -1790,67 +1792,63 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C16" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D16" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E16" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F16" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H16" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J16" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K16" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L16" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M16" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N16" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O16" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1867,55 +1865,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C17" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D17" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E17" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F17" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H17" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I17" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K17" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L17" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M17" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O17" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1926,13 +1928,15 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1947,77 +1951,81 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C18" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D18" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E18" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F18" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H18" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J18" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L18" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M18" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O18" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2029,85 +2037,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C19" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D19" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E19" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F19" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I19" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J19" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K19" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L19" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M19" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N19" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O19" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2117,55 +2121,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C20" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D20" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E20" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H20" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J20" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K20" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L20" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M20" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N20" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O20" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2173,25 +2181,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2203,57 +2207,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C21" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D21" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E21" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F21" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L21" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M21" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O21" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,12 +2270,12 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2294,50 +2298,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C22" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D22" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E22" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H22" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I22" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J22" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K22" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L22" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M22" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N22" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O22" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,15 +2352,13 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2369,59 +2371,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C23" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D23" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E23" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F23" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H23" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J23" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K23" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L23" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M23" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N23" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O23" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2432,23 +2430,27 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2456,50 +2458,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C24" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D24" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E24" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F24" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H24" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J24" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K24" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L24" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M24" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N24" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O24" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,11 +2524,13 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2538,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C25" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D25" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E25" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F25" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H25" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I25" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J25" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K25" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L25" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M25" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N25" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O25" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2594,78 +2598,76 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C26" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D26" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E26" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H26" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J26" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K26" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L26" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M26" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N26" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O26" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2678,14 +2680,18 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2695,59 +2701,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C27" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D27" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E27" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F27" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H27" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J27" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K27" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L27" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M27" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N27" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O27" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,18 +2762,14 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2786,50 +2784,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C28" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D28" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E28" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F28" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H28" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I28" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J28" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K28" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L28" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M28" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N28" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O28" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2842,11 +2840,13 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2864,50 +2864,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C29" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D29" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E29" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F29" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H29" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I29" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K29" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L29" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M29" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N29" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O29" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,50 +2944,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C30" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D30" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E30" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F30" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H30" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I30" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K30" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L30" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M30" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N30" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O30" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -2995,17 +2995,19 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3019,55 +3021,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C31" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D31" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E31" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F31" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H31" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J31" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K31" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L31" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M31" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N31" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O31" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3077,18 +3083,16 @@
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3110,50 +3114,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C32" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D32" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E32" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F32" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I32" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J32" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K32" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L32" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M32" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N32" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O32" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3161,18 +3165,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3185,79 +3189,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C33" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D33" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E33" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F33" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H33" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J33" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K33" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L33" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M33" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N33" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O33" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="Q33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3269,80 +3271,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C34" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D34" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E34" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F34" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H34" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I34" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J34" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K34" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L34" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M34" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N34" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O34" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3353,57 +3359,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C35" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D35" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E35" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F35" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H35" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J35" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K35" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L35" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M35" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N35" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O35" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3416,18 +3422,14 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3437,59 +3439,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C36" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D36" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E36" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F36" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H36" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I36" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J36" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K36" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L36" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M36" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N36" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O36" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3502,17 +3500,23 @@
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3524,50 +3528,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C37" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D37" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E37" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F37" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H37" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I37" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K37" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L37" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M37" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N37" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O37" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3580,23 +3584,17 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3608,50 +3606,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C38" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D38" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E38" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F38" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H38" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I38" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J38" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K38" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L38" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M38" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N38" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O38" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3662,13 +3660,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3681,55 +3681,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C39" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D39" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E39" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J39" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K39" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L39" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M39" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N39" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O39" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3737,18 +3741,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3763,57 +3767,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C40" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D40" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E40" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F40" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H40" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I40" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J40" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K40" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L40" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M40" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N40" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O40" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3821,14 +3825,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3847,70 +3849,76 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C41" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D41" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E41" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F41" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H41" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I41" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J41" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K41" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L41" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M41" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N41" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O41" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3922,78 +3930,70 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C42" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E42" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H42" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I42" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J42" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K42" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L42" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M42" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N42" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O42" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4020,60 +4020,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C43" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H43" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J43" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K43" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L43" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M43" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N43" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O43" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4100,69 +4104,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C44" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D44" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E44" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F44" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H44" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I44" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J44" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K44" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L44" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N44" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O44" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4179,55 +4177,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C45" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D45" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E45" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F45" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H45" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I45" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J45" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L45" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M45" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N45" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O45" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4238,16 +4240,20 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4259,82 +4265,82 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C46" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D46" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E46" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F46" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H46" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I46" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J46" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K46" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L46" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M46" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N46" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O46" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4343,67 +4349,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C47" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D47" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E47" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F47" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I47" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J47" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K47" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L47" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M47" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N47" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O47" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4434,50 +4434,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C48" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D48" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E48" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H48" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K48" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L48" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M48" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N48" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O48" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4509,70 +4509,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C49" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D49" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E49" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F49" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H49" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I49" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J49" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K49" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L49" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M49" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N49" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O49" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4591,74 +4597,72 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C50" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D50" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E50" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F50" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H50" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I50" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J50" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K50" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L50" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M50" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N50" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O50" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4684,65 +4688,67 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C51" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D51" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E51" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F51" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H51" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J51" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K51" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L51" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M51" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N51" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O51" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4759,76 +4765,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C52" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D52" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E52" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F52" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H52" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I52" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J52" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K52" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L52" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M52" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N52" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O52" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4845,75 +4843,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C53" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D53" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E53" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H53" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J53" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K53" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L53" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M53" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N53" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O53" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4925,85 +4935,79 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C54" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D54" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E54" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F54" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H54" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J54" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K54" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L54" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M54" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N54" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O54" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5015,57 +5019,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C55" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D55" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E55" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F55" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H55" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J55" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K55" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L55" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M55" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N55" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O55" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5073,18 +5077,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5106,70 +5110,72 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C56" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D56" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F56" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J56" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K56" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L56" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M56" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N56" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O56" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5181,76 +5187,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C57" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D57" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E57" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H57" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I57" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J57" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K57" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L57" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M57" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O57" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5272,50 +5272,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C58" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D58" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E58" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F58" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H58" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I58" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J58" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K58" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L58" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M58" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N58" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O58" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5325,12 +5325,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5352,50 +5352,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C59" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D59" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E59" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F59" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H59" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I59" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J59" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K59" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L59" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M59" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N59" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O59" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5432,50 +5432,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C60" t="n">
-        <v>4338</v>
+        <v>4351.6</v>
       </c>
       <c r="D60" t="n">
-        <v>4278.3</v>
+        <v>4289.2</v>
       </c>
       <c r="E60" t="n">
-        <v>4298</v>
+        <v>4321.2</v>
       </c>
       <c r="F60" t="n">
-        <v>-20.4</v>
+        <v>23.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0054</v>
       </c>
       <c r="H60" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="I60" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J60" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K60" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L60" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M60" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N60" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O60" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5483,19 +5483,19 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5507,75 +5507,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4309.5</v>
+        <v>4216.2</v>
       </c>
       <c r="C61" t="n">
-        <v>4351.6</v>
+        <v>4217.3</v>
       </c>
       <c r="D61" t="n">
-        <v>4289.2</v>
+        <v>4212.8</v>
       </c>
       <c r="E61" t="n">
-        <v>4321.2</v>
+        <v>4214.9</v>
       </c>
       <c r="F61" t="n">
-        <v>23.2</v>
+        <v>-106.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0246</v>
       </c>
       <c r="H61" t="n">
-        <v>62.4</v>
+        <v>4.5</v>
       </c>
       <c r="I61" t="n">
-        <v>4218.6</v>
+        <v>4226.8</v>
       </c>
       <c r="J61" t="n">
-        <v>4233.22</v>
+        <v>4259.2</v>
       </c>
       <c r="K61" t="n">
-        <v>4268.15</v>
+        <v>4290</v>
       </c>
       <c r="L61" t="n">
-        <v>4303.07</v>
+        <v>4320.8</v>
       </c>
       <c r="M61" t="n">
-        <v>4327.85</v>
+        <v>4352.4</v>
       </c>
       <c r="N61" t="n">
-        <v>4352.63</v>
+        <v>4384</v>
       </c>
       <c r="O61" t="n">
-        <v>4397.7</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+        <v>4414</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5587,95 +5595,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>4150.1</v>
-      </c>
-      <c r="C62" t="n">
-        <v>4153.9</v>
-      </c>
-      <c r="D62" t="n">
-        <v>4147.8</v>
-      </c>
-      <c r="E62" t="n">
-        <v>4153.7</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-167.5</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0388</v>
-      </c>
-      <c r="H62" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="I62" t="n">
-        <v>4226.8</v>
-      </c>
-      <c r="J62" t="n">
-        <v>4259.2</v>
-      </c>
-      <c r="K62" t="n">
-        <v>4290</v>
-      </c>
-      <c r="L62" t="n">
-        <v>4320.8</v>
-      </c>
-      <c r="M62" t="n">
-        <v>4352.4</v>
-      </c>
-      <c r="N62" t="n">
-        <v>4384</v>
-      </c>
-      <c r="O62" t="n">
-        <v>4414</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4187.5</v>
+        <v>4176.4</v>
       </c>
       <c r="C2" t="n">
-        <v>4215.5</v>
+        <v>4192.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4140.6</v>
+        <v>4102.7</v>
       </c>
       <c r="E2" t="n">
-        <v>4167.5</v>
+        <v>4157.4</v>
       </c>
       <c r="F2" t="n">
-        <v>41.8</v>
+        <v>-10.1</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0101</v>
+        <v>-0.0024</v>
       </c>
       <c r="H2" t="n">
-        <v>74.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="I2" t="n">
-        <v>3928.5</v>
+        <v>4065.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4024.28</v>
+        <v>4087.33</v>
       </c>
       <c r="K2" t="n">
-        <v>4068.55</v>
+        <v>4130.05</v>
       </c>
       <c r="L2" t="n">
-        <v>4112.83</v>
+        <v>4172.78</v>
       </c>
       <c r="M2" t="n">
-        <v>4182.85</v>
+        <v>4204.95</v>
       </c>
       <c r="N2" t="n">
-        <v>4252.88</v>
+        <v>4237.12</v>
       </c>
       <c r="O2" t="n">
-        <v>4271.4</v>
+        <v>4290.4</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,70 +709,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C3" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D3" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E3" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H3" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I3" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J3" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K3" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L3" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M3" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N3" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O3" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -798,72 +804,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C4" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D4" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H4" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I4" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L4" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M4" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N4" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O4" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -875,59 +879,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C5" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D5" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E5" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F5" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H5" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I5" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K5" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L5" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M5" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N5" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O5" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,18 +935,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -959,70 +959,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C6" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D6" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E6" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H6" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J6" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K6" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L6" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M6" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N6" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O6" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1034,91 +1042,85 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C7" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D7" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E7" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F7" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H7" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K7" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L7" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M7" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O7" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1127,55 +1129,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C8" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D8" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E8" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F8" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H8" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J8" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K8" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L8" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M8" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N8" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O8" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,18 +1194,14 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1211,70 +1213,74 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C9" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D9" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E9" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H9" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K9" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L9" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M9" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N9" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O9" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1291,76 +1297,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C10" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D10" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E10" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H10" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K10" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L10" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M10" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N10" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O10" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1377,55 +1375,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C11" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D11" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E11" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F11" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H11" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K11" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L11" t="n">
         <v>4007.38</v>
       </c>
       <c r="M11" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N11" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O11" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,7 +1438,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1457,57 +1459,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C12" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D12" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E12" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H12" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I12" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J12" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K12" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L12" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M12" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N12" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O12" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,78 +1520,78 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C13" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D13" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E13" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F13" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H13" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K13" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L13" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M13" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N13" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O13" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,7 +1602,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,81 +1630,81 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C14" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D14" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E14" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F14" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H14" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I14" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J14" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K14" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L14" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N14" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
@@ -1710,67 +1712,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C15" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D15" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E15" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F15" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H15" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J15" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K15" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L15" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M15" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N15" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O15" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1787,55 +1785,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C16" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D16" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E16" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F16" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H16" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K16" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L16" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M16" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N16" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1848,11 +1850,13 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1867,76 +1871,80 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C17" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D17" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E17" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F17" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H17" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J17" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L17" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M17" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N17" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O17" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>4171.5</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1949,85 +1957,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C18" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D18" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E18" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F18" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K18" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L18" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M18" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N18" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O18" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2037,55 +2041,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C19" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D19" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E19" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H19" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K19" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L19" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M19" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N19" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O19" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2093,25 +2101,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2123,57 +2127,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C20" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D20" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E20" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F20" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J20" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K20" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L20" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M20" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N20" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2184,14 +2188,14 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2214,50 +2218,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C21" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D21" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E21" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F21" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I21" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J21" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K21" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L21" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M21" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O21" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,13 +2274,11 @@
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2289,59 +2291,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C22" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D22" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H22" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J22" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K22" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L22" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M22" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O22" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2354,21 +2352,25 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2376,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C23" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D23" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E23" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F23" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H23" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I23" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J23" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K23" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L23" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M23" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N23" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O23" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,7 +2432,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2442,11 +2444,13 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2458,50 +2462,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C24" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D24" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E24" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F24" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H24" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I24" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J24" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K24" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L24" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M24" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N24" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O24" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2512,80 +2516,78 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C25" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D25" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E25" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H25" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I25" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J25" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K25" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L25" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M25" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N25" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O25" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,16 +2598,20 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2615,59 +2621,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C26" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D26" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E26" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F26" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H26" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J26" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K26" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L26" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M26" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N26" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O26" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2678,20 +2680,16 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2706,50 +2704,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C27" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D27" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E27" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F27" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H27" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J27" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K27" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L27" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M27" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N27" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O27" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,13 +2758,15 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2784,50 +2784,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C28" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D28" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E28" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F28" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H28" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I28" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J28" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K28" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L28" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M28" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N28" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O28" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2838,7 +2838,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2864,50 +2864,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C29" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D29" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E29" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F29" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H29" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I29" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J29" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K29" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L29" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M29" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N29" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O29" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2915,17 +2915,19 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2939,55 +2941,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C30" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D30" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E30" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H30" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J30" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K30" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L30" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M30" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N30" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O30" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -2997,18 +3003,16 @@
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3030,50 +3034,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C31" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D31" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E31" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F31" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I31" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J31" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K31" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L31" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M31" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N31" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O31" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3081,18 +3085,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3105,78 +3109,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D32" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E32" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F32" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H32" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J32" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K32" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L32" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M32" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N32" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O32" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3189,80 +3191,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C33" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D33" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E33" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H33" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I33" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J33" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K33" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L33" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M33" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N33" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O33" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3273,57 +3279,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C34" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D34" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E34" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F34" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H34" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J34" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K34" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L34" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M34" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N34" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O34" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3334,20 +3340,16 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3357,59 +3359,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C35" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D35" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E35" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F35" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H35" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I35" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J35" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K35" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L35" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N35" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O35" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3420,19 +3418,25 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3444,50 +3448,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C36" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D36" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E36" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F36" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H36" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J36" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K36" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L36" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M36" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O36" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3498,25 +3502,19 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3528,50 +3526,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C37" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D37" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E37" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F37" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H37" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I37" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J37" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K37" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L37" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M37" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N37" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O37" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3584,11 +3582,13 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3601,55 +3601,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C38" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D38" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E38" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J38" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K38" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L38" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M38" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N38" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O38" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3657,18 +3661,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3683,57 +3687,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C39" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D39" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E39" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F39" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H39" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I39" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J39" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K39" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L39" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M39" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N39" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O39" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3741,14 +3745,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3767,70 +3769,76 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C40" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D40" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E40" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F40" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H40" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I40" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J40" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K40" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L40" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M40" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N40" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O40" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4779.4</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3842,81 +3850,73 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C41" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D41" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E41" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H41" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J41" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K41" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L41" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M41" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N41" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O41" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3940,63 +3940,67 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C42" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E42" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H42" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I42" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J42" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K42" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L42" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M42" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N42" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O42" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4020,69 +4024,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C43" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D43" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E43" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F43" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H43" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I43" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L43" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O43" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4651.3</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4099,55 +4097,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C44" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D44" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E44" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F44" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H44" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I44" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J44" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K44" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L44" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M44" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O44" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4160,14 +4162,18 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4179,81 +4185,81 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C45" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D45" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E45" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F45" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H45" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I45" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J45" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K45" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L45" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M45" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N45" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O45" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4263,74 +4269,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C46" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D46" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E46" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F46" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I46" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J46" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K46" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L46" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M46" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N46" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4354,50 +4354,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C47" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D47" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E47" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F47" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H47" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I47" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J47" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K47" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L47" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M47" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N47" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O47" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4407,12 +4407,12 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4429,70 +4429,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C48" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D48" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E48" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F48" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H48" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I48" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J48" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K48" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L48" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M48" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N48" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O48" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4511,74 +4517,72 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C49" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D49" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E49" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F49" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H49" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I49" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J49" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K49" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L49" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M49" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N49" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O49" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4604,65 +4608,67 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C50" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D50" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E50" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F50" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H50" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J50" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K50" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L50" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M50" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N50" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O50" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4679,76 +4685,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C51" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D51" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E51" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F51" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H51" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I51" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J51" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K51" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L51" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M51" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N51" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O51" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4765,75 +4763,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C52" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D52" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E52" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H52" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J52" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K52" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L52" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M52" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N52" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O52" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4845,85 +4855,79 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C53" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D53" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E53" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F53" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H53" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J53" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K53" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L53" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M53" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N53" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O53" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4935,57 +4939,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C54" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D54" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E54" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F54" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H54" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I54" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J54" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K54" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L54" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M54" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N54" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O54" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -4993,18 +4997,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5026,69 +5030,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C55" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D55" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E55" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F55" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J55" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K55" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L55" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M55" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N55" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O55" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5101,76 +5107,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C56" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D56" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E56" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F56" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H56" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I56" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J56" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K56" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L56" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M56" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N56" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O56" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5192,50 +5192,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C57" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D57" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E57" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F57" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H57" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I57" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J57" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K57" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L57" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M57" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N57" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O57" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5245,12 +5245,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5272,50 +5272,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C58" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D58" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E58" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F58" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H58" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I58" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J58" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K58" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L58" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M58" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N58" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O58" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5328,7 +5328,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5352,50 +5352,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C59" t="n">
-        <v>4338</v>
+        <v>4351.6</v>
       </c>
       <c r="D59" t="n">
-        <v>4278.3</v>
+        <v>4289.2</v>
       </c>
       <c r="E59" t="n">
-        <v>4298</v>
+        <v>4321.2</v>
       </c>
       <c r="F59" t="n">
-        <v>-20.4</v>
+        <v>23.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0054</v>
       </c>
       <c r="H59" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="I59" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J59" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K59" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L59" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M59" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N59" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O59" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5403,19 +5403,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5427,74 +5427,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4309.5</v>
+        <v>4315</v>
       </c>
       <c r="C60" t="n">
-        <v>4351.6</v>
+        <v>4315.6</v>
       </c>
       <c r="D60" t="n">
-        <v>4289.2</v>
+        <v>4143.1</v>
       </c>
       <c r="E60" t="n">
-        <v>4321.2</v>
+        <v>4168.4</v>
       </c>
       <c r="F60" t="n">
-        <v>23.2</v>
+        <v>-152.8</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0354</v>
       </c>
       <c r="H60" t="n">
-        <v>62.4</v>
+        <v>172.5</v>
       </c>
       <c r="I60" t="n">
-        <v>4218.6</v>
+        <v>4226.8</v>
       </c>
       <c r="J60" t="n">
-        <v>4233.22</v>
+        <v>4259.2</v>
       </c>
       <c r="K60" t="n">
-        <v>4268.15</v>
+        <v>4290</v>
       </c>
       <c r="L60" t="n">
-        <v>4303.07</v>
+        <v>4320.8</v>
       </c>
       <c r="M60" t="n">
-        <v>4327.85</v>
+        <v>4352.4</v>
       </c>
       <c r="N60" t="n">
-        <v>4352.63</v>
+        <v>4384</v>
       </c>
       <c r="O60" t="n">
-        <v>4397.7</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>4414</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5507,11 +5515,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5520,65 +5524,59 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4216.2</v>
+        <v>4150.1</v>
       </c>
       <c r="C61" t="n">
-        <v>4217.3</v>
+        <v>4218.1</v>
       </c>
       <c r="D61" t="n">
-        <v>4212.8</v>
+        <v>4145.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4214.9</v>
+        <v>4179.7</v>
       </c>
       <c r="F61" t="n">
-        <v>-106.3</v>
+        <v>11.3</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0246</v>
+        <v>0.0027</v>
       </c>
       <c r="H61" t="n">
-        <v>4.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>4226.8</v>
+        <v>3970.6</v>
       </c>
       <c r="J61" t="n">
-        <v>4259.2</v>
+        <v>3965.42</v>
       </c>
       <c r="K61" t="n">
-        <v>4290</v>
+        <v>4082.15</v>
       </c>
       <c r="L61" t="n">
-        <v>4320.8</v>
+        <v>4198.88</v>
       </c>
       <c r="M61" t="n">
-        <v>4352.4</v>
+        <v>4254.65</v>
       </c>
       <c r="N61" t="n">
-        <v>4384</v>
+        <v>4310.42</v>
       </c>
       <c r="O61" t="n">
-        <v>4414</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4488.1</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5595,7 +5593,93 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>4190.1</v>
+      </c>
+      <c r="C62" t="n">
+        <v>4192</v>
+      </c>
+      <c r="D62" t="n">
+        <v>4188.5</v>
+      </c>
+      <c r="E62" t="n">
+        <v>4190.6</v>
+      </c>
+      <c r="F62" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>4072.3</v>
+      </c>
+      <c r="J62" t="n">
+        <v>4105.83</v>
+      </c>
+      <c r="K62" t="n">
+        <v>4143.25</v>
+      </c>
+      <c r="L62" t="n">
+        <v>4180.68</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4216.15</v>
+      </c>
+      <c r="N62" t="n">
+        <v>4251.63</v>
+      </c>
+      <c r="O62" t="n">
+        <v>4291</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5606,25 +5606,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4190.1</v>
+        <v>4216.2</v>
       </c>
       <c r="C62" t="n">
-        <v>4192</v>
+        <v>4251.1</v>
       </c>
       <c r="D62" t="n">
-        <v>4188.5</v>
+        <v>4178.2</v>
       </c>
       <c r="E62" t="n">
-        <v>4190.6</v>
+        <v>4186.7</v>
       </c>
       <c r="F62" t="n">
-        <v>10.9</v>
+        <v>7</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0017</v>
       </c>
       <c r="H62" t="n">
-        <v>3.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I62" t="n">
         <v>4072.3</v>
@@ -5661,8 +5661,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5676,6 +5678,88 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>4204.6</v>
+      </c>
+      <c r="C63" t="n">
+        <v>4207.2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>4203.5</v>
+      </c>
+      <c r="E63" t="n">
+        <v>4205.3</v>
+      </c>
+      <c r="F63" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0044</v>
+      </c>
+      <c r="H63" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="I63" t="n">
+        <v>4105.3</v>
+      </c>
+      <c r="J63" t="n">
+        <v>4099.83</v>
+      </c>
+      <c r="K63" t="n">
+        <v>4150.25</v>
+      </c>
+      <c r="L63" t="n">
+        <v>4200.68</v>
+      </c>
+      <c r="M63" t="n">
+        <v>4223.15</v>
+      </c>
+      <c r="N63" t="n">
+        <v>4245.63</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4324</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4176.4</v>
+        <v>4106.5</v>
       </c>
       <c r="C2" t="n">
-        <v>4192.4</v>
+        <v>4144.7</v>
       </c>
       <c r="D2" t="n">
-        <v>4102.7</v>
+        <v>4032.5</v>
       </c>
       <c r="E2" t="n">
-        <v>4157.4</v>
+        <v>4082.4</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.1</v>
+        <v>-75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0024</v>
+        <v>-0.018</v>
       </c>
       <c r="H2" t="n">
-        <v>89.7</v>
+        <v>112.2</v>
       </c>
       <c r="I2" t="n">
-        <v>4065.7</v>
+        <v>4013</v>
       </c>
       <c r="J2" t="n">
-        <v>4087.33</v>
+        <v>4072.63</v>
       </c>
       <c r="K2" t="n">
-        <v>4130.05</v>
+        <v>4112.55</v>
       </c>
       <c r="L2" t="n">
-        <v>4172.78</v>
+        <v>4152.47</v>
       </c>
       <c r="M2" t="n">
-        <v>4204.95</v>
+        <v>4202.25</v>
       </c>
       <c r="N2" t="n">
-        <v>4237.12</v>
+        <v>4252.02</v>
       </c>
       <c r="O2" t="n">
-        <v>4290.4</v>
+        <v>4282.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,7 +694,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -718,72 +720,70 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C3" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D3" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E3" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H3" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I3" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J3" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L3" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M3" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N3" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O3" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -795,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C4" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D4" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E4" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F4" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K4" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L4" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M4" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N4" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O4" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,18 +851,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -879,61 +875,69 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C5" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D5" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E5" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H5" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I5" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J5" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K5" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L5" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M5" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N5" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O5" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
@@ -942,7 +946,7 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -954,91 +958,85 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C6" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D6" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E6" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F6" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H6" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K6" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L6" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M6" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N6" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O6" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1047,55 +1045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C7" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D7" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E7" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F7" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H7" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K7" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L7" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M7" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N7" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O7" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1106,20 +1108,16 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
@@ -1131,70 +1129,74 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C8" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D8" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E8" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F8" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H8" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I8" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K8" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L8" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M8" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N8" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1211,76 +1213,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C9" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D9" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E9" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F9" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H9" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K9" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L9" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M9" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N9" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O9" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1297,55 +1291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C10" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D10" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E10" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F10" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H10" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I10" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K10" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L10" t="n">
         <v>4007.38</v>
       </c>
       <c r="M10" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N10" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O10" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1377,57 +1375,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C11" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D11" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E11" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H11" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I11" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J11" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K11" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L11" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M11" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N11" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O11" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,76 +1438,76 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C12" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D12" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E12" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F12" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H12" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L12" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M12" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N12" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O12" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1548,81 +1546,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C13" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D13" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E13" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F13" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H13" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J13" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K13" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L13" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M13" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
@@ -1630,67 +1628,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C14" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D14" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E14" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F14" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H14" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J14" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K14" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L14" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M14" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N14" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O14" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,55 +1701,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C15" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D15" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E15" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F15" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H15" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K15" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L15" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M15" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N15" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1766,13 +1764,15 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1787,77 +1787,81 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C16" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D16" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E16" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F16" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H16" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J16" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K16" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L16" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M16" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N16" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>4171.5</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1869,85 +1873,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C17" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D17" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E17" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F17" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I17" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J17" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K17" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L17" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M17" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N17" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O17" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1957,55 +1957,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C18" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D18" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E18" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H18" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K18" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L18" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M18" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N18" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O18" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,25 +2017,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2043,57 +2043,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C19" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D19" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E19" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F19" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J19" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L19" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M19" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N19" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,12 +2106,12 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2134,50 +2134,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C20" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D20" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E20" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F20" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H20" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J20" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K20" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L20" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M20" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N20" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O20" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,15 +2188,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2209,59 +2207,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C21" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D21" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E21" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F21" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H21" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J21" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K21" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L21" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M21" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N21" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O21" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,23 +2266,27 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2296,50 +2294,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C22" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D22" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E22" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F22" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H22" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I22" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J22" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K22" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L22" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N22" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O22" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,11 +2360,13 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2378,50 +2378,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C23" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D23" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E23" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F23" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H23" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I23" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J23" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K23" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L23" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M23" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O23" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,78 +2434,76 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C24" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D24" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E24" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H24" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J24" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K24" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L24" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M24" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N24" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O24" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,14 +2516,18 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2535,59 +2537,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C25" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D25" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E25" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F25" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H25" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J25" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K25" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L25" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M25" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N25" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O25" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,18 +2598,14 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2626,50 +2620,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C26" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D26" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E26" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H26" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I26" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J26" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K26" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L26" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M26" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N26" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O26" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2682,11 +2676,13 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2704,50 +2700,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C27" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D27" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E27" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F27" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H27" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I27" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J27" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K27" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L27" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M27" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N27" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O27" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2784,50 +2780,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C28" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D28" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E28" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F28" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H28" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I28" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J28" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K28" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L28" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M28" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N28" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O28" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2835,17 +2831,19 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
@@ -2859,55 +2857,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C29" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D29" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E29" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H29" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I29" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J29" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K29" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L29" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M29" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N29" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O29" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2917,18 +2919,16 @@
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2950,50 +2950,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C30" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D30" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E30" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F30" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I30" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J30" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K30" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L30" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M30" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N30" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O30" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3001,18 +3001,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3025,79 +3025,77 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C31" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D31" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E31" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F31" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H31" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I31" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J31" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K31" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L31" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M31" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N31" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O31" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3109,80 +3107,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C32" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D32" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E32" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H32" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I32" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K32" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L32" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M32" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N32" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O32" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3193,57 +3195,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C33" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D33" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E33" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F33" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H33" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J33" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K33" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L33" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M33" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N33" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O33" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3256,18 +3258,14 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3277,59 +3275,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C34" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D34" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E34" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F34" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H34" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I34" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J34" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K34" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L34" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M34" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N34" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O34" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3342,17 +3336,23 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3364,50 +3364,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C35" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D35" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E35" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F35" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H35" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I35" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K35" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L35" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M35" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O35" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3420,23 +3420,17 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3448,50 +3442,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C36" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D36" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E36" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F36" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H36" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I36" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J36" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K36" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L36" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M36" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N36" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O36" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3502,13 +3496,15 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3521,55 +3517,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C37" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D37" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E37" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I37" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J37" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K37" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L37" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M37" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N37" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O37" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3577,18 +3577,18 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3603,57 +3603,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C38" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D38" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E38" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F38" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H38" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I38" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K38" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L38" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M38" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N38" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O38" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3661,14 +3661,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3687,70 +3685,76 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C39" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D39" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E39" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F39" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H39" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I39" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J39" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K39" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L39" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M39" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N39" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O39" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+        <v>4779.4</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3762,78 +3766,70 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C40" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E40" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H40" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J40" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K40" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L40" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M40" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N40" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O40" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
@@ -3860,60 +3856,64 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C41" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D41" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E41" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H41" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I41" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J41" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K41" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L41" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M41" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N41" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O41" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
@@ -3940,69 +3940,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C42" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D42" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E42" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F42" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H42" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I42" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J42" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K42" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L42" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M42" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N42" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O42" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4651.3</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4019,55 +4013,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C43" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D43" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E43" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F43" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H43" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J43" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K43" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L43" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M43" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N43" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O43" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4078,16 +4076,20 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4099,82 +4101,82 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C44" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D44" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E44" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F44" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H44" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I44" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J44" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K44" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L44" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M44" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N44" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O44" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4183,67 +4185,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C45" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D45" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E45" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F45" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I45" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J45" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K45" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L45" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M45" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N45" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O45" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
@@ -4274,50 +4270,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C46" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D46" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E46" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F46" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H46" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J46" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K46" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L46" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M46" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N46" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O46" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4327,12 +4323,12 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4349,70 +4345,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C47" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D47" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E47" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F47" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H47" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I47" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J47" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K47" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L47" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M47" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N47" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O47" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4431,74 +4433,72 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C48" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D48" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E48" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F48" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I48" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J48" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K48" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L48" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M48" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N48" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O48" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4524,65 +4524,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C49" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D49" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E49" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F49" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H49" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I49" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J49" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K49" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L49" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M49" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N49" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O49" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4599,76 +4601,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C50" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D50" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E50" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F50" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H50" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I50" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J50" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K50" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L50" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M50" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N50" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O50" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4685,75 +4679,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C51" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D51" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E51" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H51" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J51" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K51" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L51" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M51" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N51" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O51" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4765,85 +4771,79 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C52" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D52" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E52" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F52" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H52" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I52" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J52" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K52" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L52" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M52" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N52" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O52" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4855,57 +4855,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C53" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D53" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E53" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F53" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H53" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I53" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J53" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K53" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L53" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M53" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N53" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O53" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4913,18 +4913,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4946,70 +4946,72 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C54" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D54" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E54" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F54" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H54" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I54" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J54" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K54" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L54" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M54" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N54" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O54" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5021,76 +5023,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C55" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D55" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E55" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F55" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H55" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I55" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J55" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K55" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L55" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M55" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N55" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O55" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5112,50 +5108,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C56" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D56" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E56" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F56" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H56" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I56" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J56" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K56" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L56" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M56" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N56" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O56" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5165,12 +5161,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5192,50 +5188,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C57" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D57" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E57" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F57" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H57" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I57" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J57" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K57" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L57" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M57" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N57" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O57" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5272,50 +5268,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C58" t="n">
-        <v>4338</v>
+        <v>4351.6</v>
       </c>
       <c r="D58" t="n">
-        <v>4278.3</v>
+        <v>4289.2</v>
       </c>
       <c r="E58" t="n">
-        <v>4298</v>
+        <v>4321.2</v>
       </c>
       <c r="F58" t="n">
-        <v>-20.4</v>
+        <v>23.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0054</v>
       </c>
       <c r="H58" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="I58" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J58" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K58" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L58" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M58" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N58" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O58" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5323,19 +5319,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5347,75 +5343,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4309.5</v>
+        <v>4315</v>
       </c>
       <c r="C59" t="n">
-        <v>4351.6</v>
+        <v>4315.6</v>
       </c>
       <c r="D59" t="n">
-        <v>4289.2</v>
+        <v>4143.1</v>
       </c>
       <c r="E59" t="n">
-        <v>4321.2</v>
+        <v>4168.4</v>
       </c>
       <c r="F59" t="n">
-        <v>23.2</v>
+        <v>-152.8</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0054</v>
+        <v>-0.0354</v>
       </c>
       <c r="H59" t="n">
-        <v>62.4</v>
+        <v>172.5</v>
       </c>
       <c r="I59" t="n">
-        <v>4218.6</v>
+        <v>4226.8</v>
       </c>
       <c r="J59" t="n">
-        <v>4233.22</v>
+        <v>4259.2</v>
       </c>
       <c r="K59" t="n">
-        <v>4268.15</v>
+        <v>4290</v>
       </c>
       <c r="L59" t="n">
-        <v>4303.07</v>
+        <v>4320.8</v>
       </c>
       <c r="M59" t="n">
-        <v>4327.85</v>
+        <v>4352.4</v>
       </c>
       <c r="N59" t="n">
-        <v>4352.63</v>
+        <v>4384</v>
       </c>
       <c r="O59" t="n">
-        <v>4397.7</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+        <v>4414</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5427,78 +5431,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4315</v>
+        <v>4150.1</v>
       </c>
       <c r="C60" t="n">
-        <v>4315.6</v>
+        <v>4218.1</v>
       </c>
       <c r="D60" t="n">
-        <v>4143.1</v>
+        <v>4145.2</v>
       </c>
       <c r="E60" t="n">
-        <v>4168.4</v>
+        <v>4179.7</v>
       </c>
       <c r="F60" t="n">
-        <v>-152.8</v>
+        <v>11.3</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0354</v>
+        <v>0.0027</v>
       </c>
       <c r="H60" t="n">
-        <v>172.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I60" t="n">
-        <v>4226.8</v>
+        <v>3970.6</v>
       </c>
       <c r="J60" t="n">
-        <v>4259.2</v>
+        <v>3965.42</v>
       </c>
       <c r="K60" t="n">
-        <v>4290</v>
+        <v>4082.15</v>
       </c>
       <c r="L60" t="n">
-        <v>4320.8</v>
+        <v>4198.88</v>
       </c>
       <c r="M60" t="n">
-        <v>4352.4</v>
+        <v>4254.65</v>
       </c>
       <c r="N60" t="n">
-        <v>4384</v>
+        <v>4310.42</v>
       </c>
       <c r="O60" t="n">
-        <v>4414</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4488.1</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5515,55 +5509,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>4150.1</v>
+        <v>4216.2</v>
       </c>
       <c r="C61" t="n">
-        <v>4218.1</v>
+        <v>4251.1</v>
       </c>
       <c r="D61" t="n">
-        <v>4145.2</v>
+        <v>4178.2</v>
       </c>
       <c r="E61" t="n">
-        <v>4179.7</v>
+        <v>4186.7</v>
       </c>
       <c r="F61" t="n">
-        <v>11.3</v>
+        <v>7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0017</v>
       </c>
       <c r="H61" t="n">
         <v>72.90000000000001</v>
       </c>
       <c r="I61" t="n">
-        <v>3970.6</v>
+        <v>4072.3</v>
       </c>
       <c r="J61" t="n">
-        <v>3965.42</v>
+        <v>4105.83</v>
       </c>
       <c r="K61" t="n">
-        <v>4082.15</v>
+        <v>4143.25</v>
       </c>
       <c r="L61" t="n">
-        <v>4198.88</v>
+        <v>4180.68</v>
       </c>
       <c r="M61" t="n">
-        <v>4254.65</v>
+        <v>4216.15</v>
       </c>
       <c r="N61" t="n">
-        <v>4310.42</v>
+        <v>4251.63</v>
       </c>
       <c r="O61" t="n">
-        <v>4488.1</v>
+        <v>4291</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5574,13 +5572,15 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5595,57 +5595,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>4216.2</v>
+        <v>4190.1</v>
       </c>
       <c r="C62" t="n">
-        <v>4251.1</v>
+        <v>4222.8</v>
       </c>
       <c r="D62" t="n">
-        <v>4178.2</v>
+        <v>4169.4</v>
       </c>
       <c r="E62" t="n">
-        <v>4186.7</v>
+        <v>4202.3</v>
       </c>
       <c r="F62" t="n">
-        <v>7</v>
+        <v>15.6</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0017</v>
+        <v>0.0037</v>
       </c>
       <c r="H62" t="n">
-        <v>72.90000000000001</v>
+        <v>53.4</v>
       </c>
       <c r="I62" t="n">
-        <v>4072.3</v>
+        <v>4105.3</v>
       </c>
       <c r="J62" t="n">
-        <v>4105.83</v>
+        <v>4099.83</v>
       </c>
       <c r="K62" t="n">
-        <v>4143.25</v>
+        <v>4150.25</v>
       </c>
       <c r="L62" t="n">
-        <v>4180.68</v>
+        <v>4200.68</v>
       </c>
       <c r="M62" t="n">
-        <v>4216.15</v>
+        <v>4223.15</v>
       </c>
       <c r="N62" t="n">
-        <v>4251.63</v>
+        <v>4245.63</v>
       </c>
       <c r="O62" t="n">
-        <v>4291</v>
+        <v>4324</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5661,10 +5661,8 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5679,77 +5677,85 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>4204.6</v>
       </c>
       <c r="C63" t="n">
-        <v>4207.2</v>
+        <v>4259</v>
       </c>
       <c r="D63" t="n">
-        <v>4203.5</v>
+        <v>4153.8</v>
       </c>
       <c r="E63" t="n">
-        <v>4205.3</v>
+        <v>4162.3</v>
       </c>
       <c r="F63" t="n">
-        <v>18.6</v>
+        <v>-40</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0095</v>
       </c>
       <c r="H63" t="n">
-        <v>3.7</v>
+        <v>105.2</v>
       </c>
       <c r="I63" t="n">
-        <v>4105.3</v>
+        <v>4116</v>
       </c>
       <c r="J63" t="n">
-        <v>4099.83</v>
+        <v>4152</v>
       </c>
       <c r="K63" t="n">
-        <v>4150.25</v>
+        <v>4175.6</v>
       </c>
       <c r="L63" t="n">
-        <v>4200.68</v>
+        <v>4199.2</v>
       </c>
       <c r="M63" t="n">
-        <v>4223.15</v>
+        <v>4229</v>
       </c>
       <c r="N63" t="n">
-        <v>4245.63</v>
+        <v>4258.8</v>
       </c>
       <c r="O63" t="n">
-        <v>4324</v>
+        <v>4276.2</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5761,7 +5767,89 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>4169.4</v>
+      </c>
+      <c r="C64" t="n">
+        <v>4174.5</v>
+      </c>
+      <c r="D64" t="n">
+        <v>4160</v>
+      </c>
+      <c r="E64" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="I64" t="n">
+        <v>4048.6</v>
+      </c>
+      <c r="J64" t="n">
+        <v>4035.05</v>
+      </c>
+      <c r="K64" t="n">
+        <v>4109.7</v>
+      </c>
+      <c r="L64" t="n">
+        <v>4184.35</v>
+      </c>
+      <c r="M64" t="n">
+        <v>4214.9</v>
+      </c>
+      <c r="N64" t="n">
+        <v>4245.45</v>
+      </c>
+      <c r="O64" t="n">
+        <v>4364.2</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/GC_daily.xlsx
+++ b/three_gate/analysis/GC_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4106.5</v>
+        <v>4087.6</v>
       </c>
       <c r="C2" t="n">
-        <v>4144.7</v>
+        <v>4148.4</v>
       </c>
       <c r="D2" t="n">
-        <v>4032.5</v>
+        <v>4063.4</v>
       </c>
       <c r="E2" t="n">
-        <v>4082.4</v>
+        <v>4140.8</v>
       </c>
       <c r="F2" t="n">
-        <v>-75</v>
+        <v>58.4</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.018</v>
+        <v>0.0143</v>
       </c>
       <c r="H2" t="n">
-        <v>112.2</v>
+        <v>85</v>
       </c>
       <c r="I2" t="n">
-        <v>4013</v>
+        <v>3920.3</v>
       </c>
       <c r="J2" t="n">
-        <v>4072.63</v>
+        <v>3967.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4112.55</v>
+        <v>4026.3</v>
       </c>
       <c r="L2" t="n">
-        <v>4152.47</v>
+        <v>4085.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4202.25</v>
+        <v>4138.5</v>
       </c>
       <c r="N2" t="n">
-        <v>4252.02</v>
+        <v>4191.5</v>
       </c>
       <c r="O2" t="n">
-        <v>4282.1</v>
+        <v>4256.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -711,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4087.6</v>
+        <v>4135.4</v>
       </c>
       <c r="C3" t="n">
-        <v>4148.4</v>
+        <v>4144.6</v>
       </c>
       <c r="D3" t="n">
-        <v>4063.4</v>
+        <v>4081.7</v>
       </c>
       <c r="E3" t="n">
-        <v>4140.8</v>
+        <v>4113.7</v>
       </c>
       <c r="F3" t="n">
-        <v>58.4</v>
+        <v>-27.1</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0143</v>
+        <v>-0.0065</v>
       </c>
       <c r="H3" t="n">
-        <v>85</v>
+        <v>62.9</v>
       </c>
       <c r="I3" t="n">
-        <v>3920.3</v>
+        <v>3978.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3967.1</v>
+        <v>4073.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4026.3</v>
+        <v>4098.3</v>
       </c>
       <c r="L3" t="n">
-        <v>4085.5</v>
+        <v>4123.35</v>
       </c>
       <c r="M3" t="n">
-        <v>4138.5</v>
+        <v>4183.3</v>
       </c>
       <c r="N3" t="n">
-        <v>4191.5</v>
+        <v>4243.25</v>
       </c>
       <c r="O3" t="n">
-        <v>4256.9</v>
+        <v>4233.4</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -771,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -795,70 +789,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4135.4</v>
+        <v>4106.6</v>
       </c>
       <c r="C4" t="n">
-        <v>4144.6</v>
+        <v>4111.6</v>
       </c>
       <c r="D4" t="n">
-        <v>4081.7</v>
+        <v>3992.9</v>
       </c>
       <c r="E4" t="n">
-        <v>4113.7</v>
+        <v>4005.7</v>
       </c>
       <c r="F4" t="n">
-        <v>-27.1</v>
+        <v>-108</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0263</v>
       </c>
       <c r="H4" t="n">
-        <v>62.9</v>
+        <v>118.7</v>
       </c>
       <c r="I4" t="n">
-        <v>3978.4</v>
+        <v>4018.8</v>
       </c>
       <c r="J4" t="n">
-        <v>4073.25</v>
+        <v>4051.08</v>
       </c>
       <c r="K4" t="n">
-        <v>4098.3</v>
+        <v>4082.25</v>
       </c>
       <c r="L4" t="n">
-        <v>4123.35</v>
+        <v>4113.43</v>
       </c>
       <c r="M4" t="n">
-        <v>4183.3</v>
+        <v>4145.15</v>
       </c>
       <c r="N4" t="n">
-        <v>4243.25</v>
+        <v>4176.88</v>
       </c>
       <c r="O4" t="n">
-        <v>4233.4</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>4207.5</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -870,91 +872,85 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4106.6</v>
+        <v>4005.9</v>
       </c>
       <c r="C5" t="n">
-        <v>4111.6</v>
+        <v>4112.5</v>
       </c>
       <c r="D5" t="n">
-        <v>3992.9</v>
+        <v>3990.4</v>
       </c>
       <c r="E5" t="n">
-        <v>4005.7</v>
+        <v>4069.7</v>
       </c>
       <c r="F5" t="n">
-        <v>-108</v>
+        <v>64</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0263</v>
+        <v>0.016</v>
       </c>
       <c r="H5" t="n">
-        <v>118.7</v>
+        <v>122.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4018.8</v>
+        <v>3874.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4051.08</v>
+        <v>3863.72</v>
       </c>
       <c r="K5" t="n">
-        <v>4082.25</v>
+        <v>3946.35</v>
       </c>
       <c r="L5" t="n">
-        <v>4113.43</v>
+        <v>4028.97</v>
       </c>
       <c r="M5" t="n">
-        <v>4145.15</v>
+        <v>4065.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4176.88</v>
+        <v>4101.13</v>
       </c>
       <c r="O5" t="n">
-        <v>4207.5</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>4230.3</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
@@ -963,55 +959,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4005.9</v>
+        <v>4059.8</v>
       </c>
       <c r="C6" t="n">
-        <v>4112.5</v>
+        <v>4089.1</v>
       </c>
       <c r="D6" t="n">
-        <v>3990.4</v>
+        <v>4023.3</v>
       </c>
       <c r="E6" t="n">
-        <v>4069.7</v>
+        <v>4051.8</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>-17.9</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.016</v>
+        <v>-0.0044</v>
       </c>
       <c r="H6" t="n">
-        <v>122.1</v>
+        <v>65.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3874.2</v>
+        <v>3868.3</v>
       </c>
       <c r="J6" t="n">
-        <v>3863.72</v>
+        <v>3956.72</v>
       </c>
       <c r="K6" t="n">
-        <v>3946.35</v>
+        <v>4008.65</v>
       </c>
       <c r="L6" t="n">
-        <v>4028.97</v>
+        <v>4060.57</v>
       </c>
       <c r="M6" t="n">
-        <v>4065.05</v>
+        <v>4130.75</v>
       </c>
       <c r="N6" t="n">
-        <v>4101.13</v>
+        <v>4200.93</v>
       </c>
       <c r="O6" t="n">
-        <v>4230.3</v>
+        <v>4234.6</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1024,18 +1024,14 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
@@ -1047,70 +1043,74 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4059.8</v>
+        <v>4068.9</v>
       </c>
       <c r="C7" t="n">
-        <v>4089.1</v>
+        <v>4071.9</v>
       </c>
       <c r="D7" t="n">
-        <v>4023.3</v>
+        <v>3973.4</v>
       </c>
       <c r="E7" t="n">
-        <v>4051.8</v>
+        <v>3992.1</v>
       </c>
       <c r="F7" t="n">
-        <v>-17.9</v>
+        <v>-59.7</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0044</v>
+        <v>-0.0147</v>
       </c>
       <c r="H7" t="n">
-        <v>65.8</v>
+        <v>98.5</v>
       </c>
       <c r="I7" t="n">
-        <v>3868.3</v>
+        <v>3957.5</v>
       </c>
       <c r="J7" t="n">
-        <v>3956.72</v>
+        <v>3983.8</v>
       </c>
       <c r="K7" t="n">
-        <v>4008.65</v>
+        <v>4018.9</v>
       </c>
       <c r="L7" t="n">
-        <v>4060.57</v>
+        <v>4054</v>
       </c>
       <c r="M7" t="n">
-        <v>4130.75</v>
+        <v>4084.7</v>
       </c>
       <c r="N7" t="n">
-        <v>4200.93</v>
+        <v>4115.4</v>
       </c>
       <c r="O7" t="n">
-        <v>4234.6</v>
+        <v>4154.9</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1127,76 +1127,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4068.9</v>
+        <v>3980.1</v>
       </c>
       <c r="C8" t="n">
-        <v>4071.9</v>
+        <v>4028.9</v>
       </c>
       <c r="D8" t="n">
-        <v>3973.4</v>
+        <v>3963</v>
       </c>
       <c r="E8" t="n">
-        <v>3992.1</v>
+        <v>4018.8</v>
       </c>
       <c r="F8" t="n">
-        <v>-59.7</v>
+        <v>26.7</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0147</v>
+        <v>0.0067</v>
       </c>
       <c r="H8" t="n">
-        <v>98.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>3957.5</v>
+        <v>3874.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3983.8</v>
+        <v>3878.33</v>
       </c>
       <c r="K8" t="n">
-        <v>4018.9</v>
+        <v>3942.85</v>
       </c>
       <c r="L8" t="n">
-        <v>4054</v>
+        <v>4007.38</v>
       </c>
       <c r="M8" t="n">
-        <v>4084.7</v>
+        <v>4041.35</v>
       </c>
       <c r="N8" t="n">
-        <v>4115.4</v>
+        <v>4075.33</v>
       </c>
       <c r="O8" t="n">
-        <v>4154.9</v>
+        <v>4170.4</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1213,55 +1205,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3980.1</v>
+        <v>4005.6</v>
       </c>
       <c r="C9" t="n">
-        <v>4028.9</v>
+        <v>4046</v>
       </c>
       <c r="D9" t="n">
-        <v>3963</v>
+        <v>3986.5</v>
       </c>
       <c r="E9" t="n">
-        <v>4018.8</v>
+        <v>4015.9</v>
       </c>
       <c r="F9" t="n">
-        <v>26.7</v>
+        <v>-2.9</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0007</v>
       </c>
       <c r="H9" t="n">
-        <v>65.90000000000001</v>
+        <v>59.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3874.9</v>
+        <v>3897.1</v>
       </c>
       <c r="J9" t="n">
-        <v>3878.33</v>
+        <v>3964.33</v>
       </c>
       <c r="K9" t="n">
-        <v>3942.85</v>
+        <v>3985.85</v>
       </c>
       <c r="L9" t="n">
         <v>4007.38</v>
       </c>
       <c r="M9" t="n">
-        <v>4041.35</v>
+        <v>4051.75</v>
       </c>
       <c r="N9" t="n">
-        <v>4075.33</v>
+        <v>4096.12</v>
       </c>
       <c r="O9" t="n">
-        <v>4170.4</v>
+        <v>4094.8</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,7 +1268,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1293,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4005.6</v>
+        <v>4013.4</v>
       </c>
       <c r="C10" t="n">
-        <v>4046</v>
+        <v>4092.5</v>
       </c>
       <c r="D10" t="n">
-        <v>3986.5</v>
+        <v>4003.3</v>
       </c>
       <c r="E10" t="n">
-        <v>4015.9</v>
+        <v>4076.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9</v>
+        <v>60.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0007</v>
+        <v>0.0151</v>
       </c>
       <c r="H10" t="n">
-        <v>59.5</v>
+        <v>89.2</v>
       </c>
       <c r="I10" t="n">
-        <v>3897.1</v>
+        <v>3927</v>
       </c>
       <c r="J10" t="n">
-        <v>3964.33</v>
+        <v>3956.22</v>
       </c>
       <c r="K10" t="n">
-        <v>3985.85</v>
+        <v>3986.15</v>
       </c>
       <c r="L10" t="n">
-        <v>4007.38</v>
+        <v>4016.07</v>
       </c>
       <c r="M10" t="n">
-        <v>4051.75</v>
+        <v>4045.65</v>
       </c>
       <c r="N10" t="n">
-        <v>4096.12</v>
+        <v>4075.22</v>
       </c>
       <c r="O10" t="n">
-        <v>4094.8</v>
+        <v>4105.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,78 +1350,78 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4013.4</v>
+        <v>4084.7</v>
       </c>
       <c r="C11" t="n">
-        <v>4092.5</v>
+        <v>4171.4</v>
       </c>
       <c r="D11" t="n">
-        <v>4003.3</v>
+        <v>4081</v>
       </c>
       <c r="E11" t="n">
-        <v>4076.4</v>
+        <v>4151.9</v>
       </c>
       <c r="F11" t="n">
-        <v>60.5</v>
+        <v>75.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0151</v>
+        <v>0.0185</v>
       </c>
       <c r="H11" t="n">
-        <v>89.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>3927</v>
+        <v>3914.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3956.22</v>
+        <v>4001.45</v>
       </c>
       <c r="K11" t="n">
-        <v>3986.15</v>
+        <v>4031.8</v>
       </c>
       <c r="L11" t="n">
-        <v>4016.07</v>
+        <v>4062.15</v>
       </c>
       <c r="M11" t="n">
-        <v>4045.65</v>
+        <v>4121</v>
       </c>
       <c r="N11" t="n">
-        <v>4075.22</v>
+        <v>4179.85</v>
       </c>
       <c r="O11" t="n">
-        <v>4105.5</v>
+        <v>4181.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,7 +1432,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1464,81 +1460,81 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4084.7</v>
+        <v>4126</v>
       </c>
       <c r="C12" t="n">
-        <v>4171.4</v>
+        <v>4144</v>
       </c>
       <c r="D12" t="n">
-        <v>4081</v>
+        <v>4042.5</v>
       </c>
       <c r="E12" t="n">
-        <v>4151.9</v>
+        <v>4050.2</v>
       </c>
       <c r="F12" t="n">
-        <v>75.5</v>
+        <v>-101.7</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0185</v>
+        <v>-0.0245</v>
       </c>
       <c r="H12" t="n">
-        <v>90.40000000000001</v>
+        <v>101.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3914.1</v>
+        <v>3990.6</v>
       </c>
       <c r="J12" t="n">
-        <v>4001.45</v>
+        <v>4074.35</v>
       </c>
       <c r="K12" t="n">
-        <v>4031.8</v>
+        <v>4106.7</v>
       </c>
       <c r="L12" t="n">
-        <v>4062.15</v>
+        <v>4139.05</v>
       </c>
       <c r="M12" t="n">
-        <v>4121</v>
+        <v>4197.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4179.85</v>
+        <v>4255.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4181.7</v>
+        <v>4261.8</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
@@ -1546,67 +1542,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4126</v>
+        <v>4053.4</v>
       </c>
       <c r="C13" t="n">
-        <v>4144</v>
+        <v>4085.2</v>
       </c>
       <c r="D13" t="n">
-        <v>4042.5</v>
+        <v>4024</v>
       </c>
       <c r="E13" t="n">
-        <v>4050.2</v>
+        <v>4070.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-101.7</v>
+        <v>20.6</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0245</v>
+        <v>0.0051</v>
       </c>
       <c r="H13" t="n">
-        <v>101.5</v>
+        <v>61.2</v>
       </c>
       <c r="I13" t="n">
-        <v>3990.6</v>
+        <v>3941</v>
       </c>
       <c r="J13" t="n">
-        <v>4074.35</v>
+        <v>3927.17</v>
       </c>
       <c r="K13" t="n">
-        <v>4106.7</v>
+        <v>3999.45</v>
       </c>
       <c r="L13" t="n">
-        <v>4139.05</v>
+        <v>4071.72</v>
       </c>
       <c r="M13" t="n">
-        <v>4197.1</v>
+        <v>4100.95</v>
       </c>
       <c r="N13" t="n">
-        <v>4255.15</v>
+        <v>4130.17</v>
       </c>
       <c r="O13" t="n">
-        <v>4261.8</v>
+        <v>4245.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1623,55 +1615,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4053.4</v>
+        <v>4097.5</v>
       </c>
       <c r="C14" t="n">
-        <v>4085.2</v>
+        <v>4119.3</v>
       </c>
       <c r="D14" t="n">
-        <v>4024</v>
+        <v>4067.1</v>
       </c>
       <c r="E14" t="n">
-        <v>4070.8</v>
+        <v>4077</v>
       </c>
       <c r="F14" t="n">
-        <v>20.6</v>
+        <v>6.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0051</v>
+        <v>0.0015</v>
       </c>
       <c r="H14" t="n">
-        <v>61.2</v>
+        <v>52.2</v>
       </c>
       <c r="I14" t="n">
-        <v>3941</v>
+        <v>3962.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3927.17</v>
+        <v>4017.7</v>
       </c>
       <c r="K14" t="n">
-        <v>3999.45</v>
+        <v>4040.2</v>
       </c>
       <c r="L14" t="n">
-        <v>4071.72</v>
+        <v>4062.7</v>
       </c>
       <c r="M14" t="n">
-        <v>4100.95</v>
+        <v>4101.4</v>
       </c>
       <c r="N14" t="n">
-        <v>4130.17</v>
+        <v>4140.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4245.5</v>
+        <v>4146.4</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,11 +1680,13 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1703,76 +1701,80 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4097.5</v>
+        <v>4083</v>
       </c>
       <c r="C15" t="n">
-        <v>4119.3</v>
+        <v>4085.7</v>
       </c>
       <c r="D15" t="n">
-        <v>4067.1</v>
+        <v>4011.1</v>
       </c>
       <c r="E15" t="n">
-        <v>4077</v>
+        <v>4038.7</v>
       </c>
       <c r="F15" t="n">
-        <v>6.2</v>
+        <v>-38.3</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0015</v>
+        <v>-0.0094</v>
       </c>
       <c r="H15" t="n">
-        <v>52.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>3962.8</v>
+        <v>4014.9</v>
       </c>
       <c r="J15" t="n">
-        <v>4017.7</v>
+        <v>4016.7</v>
       </c>
       <c r="K15" t="n">
-        <v>4040.2</v>
+        <v>4050.9</v>
       </c>
       <c r="L15" t="n">
-        <v>4062.7</v>
+        <v>4085.1</v>
       </c>
       <c r="M15" t="n">
-        <v>4101.4</v>
+        <v>4103.1</v>
       </c>
       <c r="N15" t="n">
-        <v>4140.1</v>
+        <v>4121.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4146.4</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>4171.5</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1785,85 +1787,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4083</v>
+        <v>4020.9</v>
       </c>
       <c r="C16" t="n">
-        <v>4085.7</v>
+        <v>4115.2</v>
       </c>
       <c r="D16" t="n">
-        <v>4011.1</v>
+        <v>3993.8</v>
       </c>
       <c r="E16" t="n">
-        <v>4038.7</v>
+        <v>4036.3</v>
       </c>
       <c r="F16" t="n">
-        <v>-38.3</v>
+        <v>-2.4</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0094</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>74.59999999999999</v>
+        <v>121.4</v>
       </c>
       <c r="I16" t="n">
-        <v>4014.9</v>
+        <v>3936.5</v>
       </c>
       <c r="J16" t="n">
-        <v>4016.7</v>
+        <v>3959.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4050.9</v>
+        <v>4001.4</v>
       </c>
       <c r="L16" t="n">
-        <v>4085.1</v>
+        <v>4043.55</v>
       </c>
       <c r="M16" t="n">
-        <v>4103.1</v>
+        <v>4076</v>
       </c>
       <c r="N16" t="n">
-        <v>4121.1</v>
+        <v>4108.45</v>
       </c>
       <c r="O16" t="n">
-        <v>4171.5</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>4160.3</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1873,55 +1871,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4020.9</v>
+        <v>4060.7</v>
       </c>
       <c r="C17" t="n">
-        <v>4115.2</v>
+        <v>4118.5</v>
       </c>
       <c r="D17" t="n">
-        <v>3993.8</v>
+        <v>4028.5</v>
       </c>
       <c r="E17" t="n">
-        <v>4036.3</v>
+        <v>4100.1</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4</v>
+        <v>63.8</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.0158</v>
       </c>
       <c r="H17" t="n">
-        <v>121.4</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>3936.5</v>
+        <v>3872.4</v>
       </c>
       <c r="J17" t="n">
-        <v>3959.25</v>
+        <v>3905.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4001.4</v>
+        <v>3975.6</v>
       </c>
       <c r="L17" t="n">
-        <v>4043.55</v>
+        <v>4045.4</v>
       </c>
       <c r="M17" t="n">
-        <v>4076</v>
+        <v>4097</v>
       </c>
       <c r="N17" t="n">
-        <v>4108.45</v>
+        <v>4148.6</v>
       </c>
       <c r="O17" t="n">
-        <v>4160.3</v>
+        <v>4236.6</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,25 +1931,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1959,57 +1957,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4060.7</v>
+        <v>4163.9</v>
       </c>
       <c r="C18" t="n">
-        <v>4118.5</v>
+        <v>4170.7</v>
       </c>
       <c r="D18" t="n">
-        <v>4028.5</v>
+        <v>4076.4</v>
       </c>
       <c r="E18" t="n">
-        <v>4100.1</v>
+        <v>4107</v>
       </c>
       <c r="F18" t="n">
-        <v>63.8</v>
+        <v>6.9</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0017</v>
       </c>
       <c r="H18" t="n">
-        <v>90</v>
+        <v>94.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3872.4</v>
+        <v>3938.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3905.8</v>
+        <v>4023.4</v>
       </c>
       <c r="K18" t="n">
-        <v>3975.6</v>
+        <v>4055.1</v>
       </c>
       <c r="L18" t="n">
-        <v>4045.4</v>
+        <v>4086.8</v>
       </c>
       <c r="M18" t="n">
-        <v>4097</v>
+        <v>4145.1</v>
       </c>
       <c r="N18" t="n">
-        <v>4148.6</v>
+        <v>4203.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4236.6</v>
+        <v>4208.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2020,14 +2018,14 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2050,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4163.9</v>
+        <v>4135.2</v>
       </c>
       <c r="C19" t="n">
-        <v>4170.7</v>
+        <v>4145.5</v>
       </c>
       <c r="D19" t="n">
-        <v>4076.4</v>
+        <v>4074</v>
       </c>
       <c r="E19" t="n">
-        <v>4107</v>
+        <v>4090.5</v>
       </c>
       <c r="F19" t="n">
-        <v>6.9</v>
+        <v>-16.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0017</v>
+        <v>-0.004</v>
       </c>
       <c r="H19" t="n">
-        <v>94.3</v>
+        <v>71.5</v>
       </c>
       <c r="I19" t="n">
-        <v>3938.5</v>
+        <v>3982.1</v>
       </c>
       <c r="J19" t="n">
-        <v>4023.4</v>
+        <v>4004.42</v>
       </c>
       <c r="K19" t="n">
-        <v>4055.1</v>
+        <v>4059.85</v>
       </c>
       <c r="L19" t="n">
-        <v>4086.8</v>
+        <v>4115.28</v>
       </c>
       <c r="M19" t="n">
-        <v>4145.1</v>
+        <v>4154.15</v>
       </c>
       <c r="N19" t="n">
-        <v>4203.4</v>
+        <v>4193.03</v>
       </c>
       <c r="O19" t="n">
-        <v>4208.5</v>
+        <v>4265</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,13 +2104,11 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2125,59 +2121,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4135.2</v>
+        <v>4109.6</v>
       </c>
       <c r="C20" t="n">
-        <v>4145.5</v>
+        <v>4163.8</v>
       </c>
       <c r="D20" t="n">
-        <v>4074</v>
+        <v>4098.2</v>
       </c>
       <c r="E20" t="n">
-        <v>4090.5</v>
+        <v>4152.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-16.5</v>
+        <v>62.1</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.004</v>
+        <v>0.0152</v>
       </c>
       <c r="H20" t="n">
-        <v>71.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3982.1</v>
+        <v>4002.5</v>
       </c>
       <c r="J20" t="n">
-        <v>4004.42</v>
+        <v>4009.38</v>
       </c>
       <c r="K20" t="n">
-        <v>4059.85</v>
+        <v>4054.75</v>
       </c>
       <c r="L20" t="n">
-        <v>4115.28</v>
+        <v>4100.12</v>
       </c>
       <c r="M20" t="n">
-        <v>4154.15</v>
+        <v>4126.25</v>
       </c>
       <c r="N20" t="n">
-        <v>4193.03</v>
+        <v>4152.38</v>
       </c>
       <c r="O20" t="n">
-        <v>4265</v>
+        <v>4217</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,21 +2182,25 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2212,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4109.6</v>
+        <v>4133.8</v>
       </c>
       <c r="C21" t="n">
-        <v>4163.8</v>
+        <v>4328.2</v>
       </c>
       <c r="D21" t="n">
-        <v>4098.2</v>
+        <v>4121.6</v>
       </c>
       <c r="E21" t="n">
-        <v>4152.6</v>
+        <v>4305.2</v>
       </c>
       <c r="F21" t="n">
-        <v>62.1</v>
+        <v>152.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0152</v>
+        <v>0.0367</v>
       </c>
       <c r="H21" t="n">
-        <v>65.59999999999999</v>
+        <v>206.6</v>
       </c>
       <c r="I21" t="n">
-        <v>4002.5</v>
+        <v>4032.6</v>
       </c>
       <c r="J21" t="n">
-        <v>4009.38</v>
+        <v>4097.8</v>
       </c>
       <c r="K21" t="n">
-        <v>4054.75</v>
+        <v>4119.8</v>
       </c>
       <c r="L21" t="n">
-        <v>4100.12</v>
+        <v>4141.8</v>
       </c>
       <c r="M21" t="n">
-        <v>4126.25</v>
+        <v>4185.4</v>
       </c>
       <c r="N21" t="n">
-        <v>4152.38</v>
+        <v>4229</v>
       </c>
       <c r="O21" t="n">
-        <v>4217</v>
+        <v>4229.4</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,7 +2262,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2278,11 +2274,13 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2294,50 +2292,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4133.8</v>
+        <v>4307</v>
       </c>
       <c r="C22" t="n">
-        <v>4328.2</v>
+        <v>4363.7</v>
       </c>
       <c r="D22" t="n">
-        <v>4121.6</v>
+        <v>4281.2</v>
       </c>
       <c r="E22" t="n">
-        <v>4305.2</v>
+        <v>4299.6</v>
       </c>
       <c r="F22" t="n">
-        <v>152.6</v>
+        <v>-5.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0367</v>
+        <v>-0.0013</v>
       </c>
       <c r="H22" t="n">
-        <v>206.6</v>
+        <v>82.5</v>
       </c>
       <c r="I22" t="n">
-        <v>4032.6</v>
+        <v>3915</v>
       </c>
       <c r="J22" t="n">
-        <v>4097.8</v>
+        <v>4138.75</v>
       </c>
       <c r="K22" t="n">
-        <v>4119.8</v>
+        <v>4201.9</v>
       </c>
       <c r="L22" t="n">
-        <v>4141.8</v>
+        <v>4265.05</v>
       </c>
       <c r="M22" t="n">
-        <v>4185.4</v>
+        <v>4408.5</v>
       </c>
       <c r="N22" t="n">
-        <v>4229</v>
+        <v>4551.95</v>
       </c>
       <c r="O22" t="n">
-        <v>4229.4</v>
+        <v>4534.8</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,80 +2346,78 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4307</v>
+        <v>4298.3</v>
       </c>
       <c r="C23" t="n">
-        <v>4363.7</v>
+        <v>4432.3</v>
       </c>
       <c r="D23" t="n">
-        <v>4281.2</v>
+        <v>4288</v>
       </c>
       <c r="E23" t="n">
-        <v>4299.6</v>
+        <v>4399.7</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.6</v>
+        <v>100.1</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0013</v>
+        <v>0.0233</v>
       </c>
       <c r="H23" t="n">
-        <v>82.5</v>
+        <v>144.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3915</v>
+        <v>4198.7</v>
       </c>
       <c r="J23" t="n">
-        <v>4138.75</v>
+        <v>4205.68</v>
       </c>
       <c r="K23" t="n">
-        <v>4201.9</v>
+        <v>4258.35</v>
       </c>
       <c r="L23" t="n">
-        <v>4265.05</v>
+        <v>4311.03</v>
       </c>
       <c r="M23" t="n">
-        <v>4408.5</v>
+        <v>4340.85</v>
       </c>
       <c r="N23" t="n">
-        <v>4551.95</v>
+        <v>4370.68</v>
       </c>
       <c r="O23" t="n">
-        <v>4534.8</v>
+        <v>4446.2</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2432,16 +2428,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2451,59 +2451,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4298.3</v>
+        <v>4400</v>
       </c>
       <c r="C24" t="n">
-        <v>4432.3</v>
+        <v>4453.8</v>
       </c>
       <c r="D24" t="n">
-        <v>4288</v>
+        <v>4373.9</v>
       </c>
       <c r="E24" t="n">
-        <v>4399.7</v>
+        <v>4419.7</v>
       </c>
       <c r="F24" t="n">
-        <v>100.1</v>
+        <v>20</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0045</v>
       </c>
       <c r="H24" t="n">
-        <v>144.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>4198.7</v>
+        <v>4143.7</v>
       </c>
       <c r="J24" t="n">
-        <v>4205.68</v>
+        <v>4275.18</v>
       </c>
       <c r="K24" t="n">
-        <v>4258.35</v>
+        <v>4327.55</v>
       </c>
       <c r="L24" t="n">
-        <v>4311.03</v>
+        <v>4379.93</v>
       </c>
       <c r="M24" t="n">
-        <v>4340.85</v>
+        <v>4471.85</v>
       </c>
       <c r="N24" t="n">
-        <v>4370.68</v>
+        <v>4563.78</v>
       </c>
       <c r="O24" t="n">
-        <v>4446.2</v>
+        <v>4576.6</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2514,20 +2510,16 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2542,50 +2534,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4400</v>
+        <v>4446.9</v>
       </c>
       <c r="C25" t="n">
-        <v>4453.8</v>
+        <v>4495</v>
       </c>
       <c r="D25" t="n">
-        <v>4373.9</v>
+        <v>4415.7</v>
       </c>
       <c r="E25" t="n">
-        <v>4419.7</v>
+        <v>4441.1</v>
       </c>
       <c r="F25" t="n">
-        <v>20</v>
+        <v>21.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="H25" t="n">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="I25" t="n">
-        <v>4143.7</v>
+        <v>4294</v>
       </c>
       <c r="J25" t="n">
-        <v>4275.18</v>
+        <v>4342.73</v>
       </c>
       <c r="K25" t="n">
-        <v>4327.55</v>
+        <v>4379.75</v>
       </c>
       <c r="L25" t="n">
-        <v>4379.93</v>
+        <v>4416.78</v>
       </c>
       <c r="M25" t="n">
-        <v>4471.85</v>
+        <v>4459.65</v>
       </c>
       <c r="N25" t="n">
-        <v>4563.78</v>
+        <v>4502.53</v>
       </c>
       <c r="O25" t="n">
-        <v>4576.6</v>
+        <v>4533.7</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,13 +2588,15 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2620,50 +2614,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4446.9</v>
+        <v>4430</v>
       </c>
       <c r="C26" t="n">
-        <v>4495</v>
+        <v>4502.7</v>
       </c>
       <c r="D26" t="n">
-        <v>4415.7</v>
+        <v>4421.4</v>
       </c>
       <c r="E26" t="n">
-        <v>4441.1</v>
+        <v>4467.5</v>
       </c>
       <c r="F26" t="n">
-        <v>21.4</v>
+        <v>26.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0048</v>
+        <v>0.0059</v>
       </c>
       <c r="H26" t="n">
-        <v>79.3</v>
+        <v>81.3</v>
       </c>
       <c r="I26" t="n">
-        <v>4294</v>
+        <v>4336.4</v>
       </c>
       <c r="J26" t="n">
-        <v>4342.73</v>
+        <v>4354.68</v>
       </c>
       <c r="K26" t="n">
-        <v>4379.75</v>
+        <v>4401.45</v>
       </c>
       <c r="L26" t="n">
-        <v>4416.78</v>
+        <v>4448.23</v>
       </c>
       <c r="M26" t="n">
-        <v>4459.65</v>
+        <v>4480.75</v>
       </c>
       <c r="N26" t="n">
-        <v>4502.53</v>
+        <v>4513.27</v>
       </c>
       <c r="O26" t="n">
-        <v>4533.7</v>
+        <v>4574.3</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2674,7 +2668,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2700,50 +2694,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4430</v>
+        <v>4468.8</v>
       </c>
       <c r="C27" t="n">
-        <v>4502.7</v>
+        <v>4509.1</v>
       </c>
       <c r="D27" t="n">
-        <v>4421.4</v>
+        <v>4400</v>
       </c>
       <c r="E27" t="n">
-        <v>4467.5</v>
+        <v>4420.4</v>
       </c>
       <c r="F27" t="n">
-        <v>26.4</v>
+        <v>-47.1</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0059</v>
+        <v>-0.0105</v>
       </c>
       <c r="H27" t="n">
-        <v>81.3</v>
+        <v>109.1</v>
       </c>
       <c r="I27" t="n">
-        <v>4336.4</v>
+        <v>4340.1</v>
       </c>
       <c r="J27" t="n">
-        <v>4354.68</v>
+        <v>4388.92</v>
       </c>
       <c r="K27" t="n">
-        <v>4401.45</v>
+        <v>4426.85</v>
       </c>
       <c r="L27" t="n">
-        <v>4448.23</v>
+        <v>4464.78</v>
       </c>
       <c r="M27" t="n">
-        <v>4480.75</v>
+        <v>4508.15</v>
       </c>
       <c r="N27" t="n">
-        <v>4513.27</v>
+        <v>4551.53</v>
       </c>
       <c r="O27" t="n">
-        <v>4574.3</v>
+        <v>4584</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2751,17 +2745,19 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
@@ -2775,55 +2771,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4468.8</v>
+        <v>4408.2</v>
       </c>
       <c r="C28" t="n">
-        <v>4509.1</v>
+        <v>4454.6</v>
       </c>
       <c r="D28" t="n">
-        <v>4400</v>
+        <v>4365.5</v>
       </c>
       <c r="E28" t="n">
-        <v>4420.4</v>
+        <v>4437.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-47.1</v>
+        <v>16.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0038</v>
       </c>
       <c r="H28" t="n">
-        <v>109.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>4340.1</v>
+        <v>4290.9</v>
       </c>
       <c r="J28" t="n">
-        <v>4388.92</v>
+        <v>4294.22</v>
       </c>
       <c r="K28" t="n">
-        <v>4426.85</v>
+        <v>4365.85</v>
       </c>
       <c r="L28" t="n">
-        <v>4464.78</v>
+        <v>4437.47</v>
       </c>
       <c r="M28" t="n">
-        <v>4508.15</v>
+        <v>4474.95</v>
       </c>
       <c r="N28" t="n">
-        <v>4551.53</v>
+        <v>4512.42</v>
       </c>
       <c r="O28" t="n">
-        <v>4584</v>
+        <v>4618.2</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2833,18 +2833,16 @@
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
           <t>✓</t>
         </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2866,50 +2864,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4408.2</v>
+        <v>4440</v>
       </c>
       <c r="C29" t="n">
-        <v>4454.6</v>
+        <v>4486.5</v>
       </c>
       <c r="D29" t="n">
-        <v>4365.5</v>
+        <v>4422.3</v>
       </c>
       <c r="E29" t="n">
-        <v>4437.3</v>
+        <v>4473.7</v>
       </c>
       <c r="F29" t="n">
-        <v>16.9</v>
+        <v>36.4</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>89.09999999999999</v>
+        <v>64.2</v>
       </c>
       <c r="I29" t="n">
-        <v>4290.9</v>
+        <v>4276.4</v>
       </c>
       <c r="J29" t="n">
-        <v>4294.22</v>
+        <v>4361.82</v>
       </c>
       <c r="K29" t="n">
-        <v>4365.85</v>
+        <v>4392.75</v>
       </c>
       <c r="L29" t="n">
-        <v>4437.47</v>
+        <v>4423.67</v>
       </c>
       <c r="M29" t="n">
-        <v>4474.95</v>
+        <v>4481.85</v>
       </c>
       <c r="N29" t="n">
-        <v>4512.42</v>
+        <v>4540.02</v>
       </c>
       <c r="O29" t="n">
-        <v>4618.2</v>
+        <v>4543.7</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2917,18 +2915,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2941,78 +2939,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4440</v>
+        <v>4473.4</v>
       </c>
       <c r="C30" t="n">
-        <v>4486.5</v>
+        <v>4493.1</v>
       </c>
       <c r="D30" t="n">
-        <v>4422.3</v>
+        <v>4383.3</v>
       </c>
       <c r="E30" t="n">
-        <v>4473.7</v>
+        <v>4420.6</v>
       </c>
       <c r="F30" t="n">
-        <v>36.4</v>
+        <v>-53.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-0.0119</v>
       </c>
       <c r="H30" t="n">
-        <v>64.2</v>
+        <v>109.8</v>
       </c>
       <c r="I30" t="n">
-        <v>4276.4</v>
+        <v>4358.1</v>
       </c>
       <c r="J30" t="n">
-        <v>4361.82</v>
+        <v>4419.15</v>
       </c>
       <c r="K30" t="n">
-        <v>4392.75</v>
+        <v>4441.6</v>
       </c>
       <c r="L30" t="n">
-        <v>4423.67</v>
+        <v>4464.05</v>
       </c>
       <c r="M30" t="n">
-        <v>4481.85</v>
+        <v>4505.8</v>
       </c>
       <c r="N30" t="n">
-        <v>4540.02</v>
+        <v>4547.55</v>
       </c>
       <c r="O30" t="n">
-        <v>4543.7</v>
+        <v>4550.7</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3025,80 +3021,84 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4473.4</v>
+        <v>4391.4</v>
       </c>
       <c r="C31" t="n">
-        <v>4493.1</v>
+        <v>4582.8</v>
       </c>
       <c r="D31" t="n">
-        <v>4383.3</v>
+        <v>4378</v>
       </c>
       <c r="E31" t="n">
-        <v>4420.6</v>
+        <v>4545.3</v>
       </c>
       <c r="F31" t="n">
-        <v>-53.1</v>
+        <v>124.7</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0119</v>
+        <v>0.0282</v>
       </c>
       <c r="H31" t="n">
-        <v>109.8</v>
+        <v>204.8</v>
       </c>
       <c r="I31" t="n">
-        <v>4358.1</v>
+        <v>4273.5</v>
       </c>
       <c r="J31" t="n">
-        <v>4419.15</v>
+        <v>4302</v>
       </c>
       <c r="K31" t="n">
-        <v>4441.6</v>
+        <v>4365.7</v>
       </c>
       <c r="L31" t="n">
-        <v>4464.05</v>
+        <v>4429.4</v>
       </c>
       <c r="M31" t="n">
-        <v>4505.8</v>
+        <v>4475.5</v>
       </c>
       <c r="N31" t="n">
-        <v>4547.55</v>
+        <v>4521.6</v>
       </c>
       <c r="O31" t="n">
-        <v>4550.7</v>
+        <v>4602.9</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3109,57 +3109,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4391.4</v>
+        <v>4580</v>
       </c>
       <c r="C32" t="n">
-        <v>4582.8</v>
+        <v>4597.1</v>
       </c>
       <c r="D32" t="n">
-        <v>4378</v>
+        <v>4506</v>
       </c>
       <c r="E32" t="n">
-        <v>4545.3</v>
+        <v>4571.4</v>
       </c>
       <c r="F32" t="n">
-        <v>124.7</v>
+        <v>26.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0282</v>
+        <v>0.0057</v>
       </c>
       <c r="H32" t="n">
-        <v>204.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>4273.5</v>
+        <v>4173.2</v>
       </c>
       <c r="J32" t="n">
-        <v>4302</v>
+        <v>4372.95</v>
       </c>
       <c r="K32" t="n">
-        <v>4365.7</v>
+        <v>4442.9</v>
       </c>
       <c r="L32" t="n">
-        <v>4429.4</v>
+        <v>4512.85</v>
       </c>
       <c r="M32" t="n">
-        <v>4475.5</v>
+        <v>4647.7</v>
       </c>
       <c r="N32" t="n">
-        <v>4521.6</v>
+        <v>4782.55</v>
       </c>
       <c r="O32" t="n">
-        <v>4602.9</v>
+        <v>4787.6</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3170,20 +3170,16 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3193,59 +3189,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4580</v>
+        <v>4577</v>
       </c>
       <c r="C33" t="n">
-        <v>4597.1</v>
+        <v>4690.4</v>
       </c>
       <c r="D33" t="n">
-        <v>4506</v>
+        <v>4565.5</v>
       </c>
       <c r="E33" t="n">
-        <v>4571.4</v>
+        <v>4680.6</v>
       </c>
       <c r="F33" t="n">
-        <v>26.1</v>
+        <v>109.2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0239</v>
       </c>
       <c r="H33" t="n">
-        <v>91.09999999999999</v>
+        <v>124.9</v>
       </c>
       <c r="I33" t="n">
-        <v>4173.2</v>
+        <v>4414.9</v>
       </c>
       <c r="J33" t="n">
-        <v>4372.95</v>
+        <v>4490.22</v>
       </c>
       <c r="K33" t="n">
-        <v>4442.9</v>
+        <v>4525.85</v>
       </c>
       <c r="L33" t="n">
-        <v>4512.85</v>
+        <v>4561.47</v>
       </c>
       <c r="M33" t="n">
-        <v>4647.7</v>
+        <v>4616.95</v>
       </c>
       <c r="N33" t="n">
-        <v>4782.55</v>
+        <v>4672.42</v>
       </c>
       <c r="O33" t="n">
-        <v>4787.6</v>
+        <v>4688.2</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3256,19 +3248,25 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3280,50 +3278,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4577</v>
+        <v>4673.4</v>
       </c>
       <c r="C34" t="n">
-        <v>4690.4</v>
+        <v>4738.5</v>
       </c>
       <c r="D34" t="n">
-        <v>4565.5</v>
+        <v>4651.8</v>
       </c>
       <c r="E34" t="n">
-        <v>4680.6</v>
+        <v>4697.8</v>
       </c>
       <c r="F34" t="n">
-        <v>109.2</v>
+        <v>17.2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0239</v>
+        <v>0.0037</v>
       </c>
       <c r="H34" t="n">
-        <v>124.9</v>
+        <v>86.7</v>
       </c>
       <c r="I34" t="n">
-        <v>4414.9</v>
+        <v>4440.6</v>
       </c>
       <c r="J34" t="n">
-        <v>4490.22</v>
+        <v>4582.03</v>
       </c>
       <c r="K34" t="n">
-        <v>4525.85</v>
+        <v>4618.15</v>
       </c>
       <c r="L34" t="n">
-        <v>4561.47</v>
+        <v>4654.28</v>
       </c>
       <c r="M34" t="n">
-        <v>4616.95</v>
+        <v>4743.05</v>
       </c>
       <c r="N34" t="n">
-        <v>4672.42</v>
+        <v>4831.83</v>
       </c>
       <c r="O34" t="n">
-        <v>4688.2</v>
+        <v>4815.3</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3334,25 +3332,19 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3364,50 +3356,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4673.4</v>
+        <v>4710.1</v>
       </c>
       <c r="C35" t="n">
-        <v>4738.5</v>
+        <v>4755</v>
       </c>
       <c r="D35" t="n">
-        <v>4651.8</v>
+        <v>4659.5</v>
       </c>
       <c r="E35" t="n">
-        <v>4697.8</v>
+        <v>4694.5</v>
       </c>
       <c r="F35" t="n">
-        <v>17.2</v>
+        <v>-3.3</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0007</v>
       </c>
       <c r="H35" t="n">
-        <v>86.7</v>
+        <v>95.5</v>
       </c>
       <c r="I35" t="n">
-        <v>4440.6</v>
+        <v>4565.1</v>
       </c>
       <c r="J35" t="n">
-        <v>4582.03</v>
+        <v>4612.42</v>
       </c>
       <c r="K35" t="n">
-        <v>4618.15</v>
+        <v>4654.45</v>
       </c>
       <c r="L35" t="n">
-        <v>4654.28</v>
+        <v>4696.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4743.05</v>
+        <v>4741.15</v>
       </c>
       <c r="N35" t="n">
-        <v>4831.83</v>
+        <v>4785.82</v>
       </c>
       <c r="O35" t="n">
-        <v>4815.3</v>
+        <v>4825.2</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3420,11 +3412,13 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3437,55 +3431,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4710.1</v>
+        <v>4715.7</v>
       </c>
       <c r="C36" t="n">
-        <v>4755</v>
+        <v>4730.9</v>
       </c>
       <c r="D36" t="n">
-        <v>4659.5</v>
+        <v>4638.2</v>
       </c>
       <c r="E36" t="n">
-        <v>4694.5</v>
+        <v>4653.3</v>
       </c>
       <c r="F36" t="n">
-        <v>-3.3</v>
+        <v>-41.2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>95.5</v>
+        <v>92.7</v>
       </c>
       <c r="I36" t="n">
-        <v>4565.1</v>
+        <v>4564</v>
       </c>
       <c r="J36" t="n">
-        <v>4612.42</v>
+        <v>4592.62</v>
       </c>
       <c r="K36" t="n">
-        <v>4654.45</v>
+        <v>4646.75</v>
       </c>
       <c r="L36" t="n">
-        <v>4696.47</v>
+        <v>4700.88</v>
       </c>
       <c r="M36" t="n">
-        <v>4741.15</v>
+        <v>4742.25</v>
       </c>
       <c r="N36" t="n">
-        <v>4785.82</v>
+        <v>4783.62</v>
       </c>
       <c r="O36" t="n">
-        <v>4825.2</v>
+        <v>4850.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3493,18 +3491,18 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3519,57 +3517,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4715.7</v>
+        <v>4650</v>
       </c>
       <c r="C37" t="n">
-        <v>4730.9</v>
+        <v>4697.7</v>
       </c>
       <c r="D37" t="n">
-        <v>4638.2</v>
+        <v>4616</v>
       </c>
       <c r="E37" t="n">
-        <v>4653.3</v>
+        <v>4664</v>
       </c>
       <c r="F37" t="n">
-        <v>-41.2</v>
+        <v>10.7</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0023</v>
       </c>
       <c r="H37" t="n">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="I37" t="n">
-        <v>4564</v>
+        <v>4545.5</v>
       </c>
       <c r="J37" t="n">
-        <v>4592.62</v>
+        <v>4544.97</v>
       </c>
       <c r="K37" t="n">
-        <v>4646.75</v>
+        <v>4606.95</v>
       </c>
       <c r="L37" t="n">
-        <v>4700.88</v>
+        <v>4668.92</v>
       </c>
       <c r="M37" t="n">
-        <v>4742.25</v>
+        <v>4699.65</v>
       </c>
       <c r="N37" t="n">
-        <v>4783.62</v>
+        <v>4730.37</v>
       </c>
       <c r="O37" t="n">
-        <v>4850.5</v>
+        <v>4823.6</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3577,14 +3575,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3603,70 +3599,76 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4650</v>
+        <v>4656</v>
       </c>
       <c r="C38" t="n">
-        <v>4697.7</v>
+        <v>4688</v>
       </c>
       <c r="D38" t="n">
-        <v>4616</v>
+        <v>4495</v>
       </c>
       <c r="E38" t="n">
-        <v>4664</v>
+        <v>4529.9</v>
       </c>
       <c r="F38" t="n">
-        <v>10.7</v>
+        <v>-134.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0288</v>
       </c>
       <c r="H38" t="n">
-        <v>81.7</v>
+        <v>193</v>
       </c>
       <c r="I38" t="n">
-        <v>4545.5</v>
+        <v>4534.3</v>
       </c>
       <c r="J38" t="n">
-        <v>4544.97</v>
+        <v>4585.87</v>
       </c>
       <c r="K38" t="n">
-        <v>4606.95</v>
+        <v>4623.15</v>
       </c>
       <c r="L38" t="n">
-        <v>4668.92</v>
+        <v>4660.43</v>
       </c>
       <c r="M38" t="n">
-        <v>4699.65</v>
+        <v>4704.85</v>
       </c>
       <c r="N38" t="n">
-        <v>4730.37</v>
+        <v>4749.28</v>
       </c>
       <c r="O38" t="n">
-        <v>4823.6</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>4779.4</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3678,81 +3680,73 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4656</v>
+        <v>4483.2</v>
       </c>
       <c r="C39" t="n">
-        <v>4688</v>
+        <v>4521.5</v>
       </c>
       <c r="D39" t="n">
-        <v>4495</v>
+        <v>4445.6</v>
       </c>
       <c r="E39" t="n">
-        <v>4529.9</v>
+        <v>4481.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-134.1</v>
+        <v>-48.4</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0288</v>
+        <v>-0.0107</v>
       </c>
       <c r="H39" t="n">
-        <v>193</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I39" t="n">
-        <v>4534.3</v>
+        <v>4302</v>
       </c>
       <c r="J39" t="n">
-        <v>4585.87</v>
+        <v>4306.1</v>
       </c>
       <c r="K39" t="n">
-        <v>4623.15</v>
+        <v>4433.4</v>
       </c>
       <c r="L39" t="n">
-        <v>4660.43</v>
+        <v>4560.7</v>
       </c>
       <c r="M39" t="n">
-        <v>4704.85</v>
+        <v>4626.4</v>
       </c>
       <c r="N39" t="n">
-        <v>4749.28</v>
+        <v>4692.1</v>
       </c>
       <c r="O39" t="n">
-        <v>4779.4</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
+        <v>4881</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3776,63 +3770,67 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4483.2</v>
+        <v>4498.7</v>
       </c>
       <c r="C40" t="n">
-        <v>4521.5</v>
+        <v>4510.5</v>
       </c>
       <c r="D40" t="n">
-        <v>4445.6</v>
+        <v>4369.7</v>
       </c>
       <c r="E40" t="n">
-        <v>4481.5</v>
+        <v>4396.4</v>
       </c>
       <c r="F40" t="n">
-        <v>-48.4</v>
+        <v>-85.09999999999999</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0107</v>
+        <v>-0.019</v>
       </c>
       <c r="H40" t="n">
-        <v>75.90000000000001</v>
+        <v>140.8</v>
       </c>
       <c r="I40" t="n">
-        <v>4302</v>
+        <v>4369.7</v>
       </c>
       <c r="J40" t="n">
-        <v>4306.1</v>
+        <v>4404.58</v>
       </c>
       <c r="K40" t="n">
-        <v>4433.4</v>
+        <v>4443.55</v>
       </c>
       <c r="L40" t="n">
-        <v>4560.7</v>
+        <v>4482.53</v>
       </c>
       <c r="M40" t="n">
-        <v>4626.4</v>
+        <v>4519.45</v>
       </c>
       <c r="N40" t="n">
-        <v>4692.1</v>
+        <v>4556.37</v>
       </c>
       <c r="O40" t="n">
-        <v>4881</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>4597.4</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3856,69 +3854,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4498.7</v>
+        <v>4377.2</v>
       </c>
       <c r="C41" t="n">
-        <v>4510.5</v>
+        <v>4444.4</v>
       </c>
       <c r="D41" t="n">
-        <v>4369.7</v>
+        <v>4329.2</v>
       </c>
       <c r="E41" t="n">
-        <v>4396.4</v>
+        <v>4414.6</v>
       </c>
       <c r="F41" t="n">
-        <v>-85.09999999999999</v>
+        <v>18.2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.019</v>
+        <v>0.0041</v>
       </c>
       <c r="H41" t="n">
-        <v>140.8</v>
+        <v>115.2</v>
       </c>
       <c r="I41" t="n">
-        <v>4369.7</v>
+        <v>4228.9</v>
       </c>
       <c r="J41" t="n">
-        <v>4404.58</v>
+        <v>4233.75</v>
       </c>
       <c r="K41" t="n">
-        <v>4443.55</v>
+        <v>4326</v>
       </c>
       <c r="L41" t="n">
-        <v>4482.53</v>
+        <v>4418.25</v>
       </c>
       <c r="M41" t="n">
-        <v>4519.45</v>
+        <v>4466.8</v>
       </c>
       <c r="N41" t="n">
-        <v>4556.37</v>
+        <v>4515.35</v>
       </c>
       <c r="O41" t="n">
-        <v>4597.4</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4651.3</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3935,55 +3927,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4377.2</v>
+        <v>4436.4</v>
       </c>
       <c r="C42" t="n">
-        <v>4444.4</v>
+        <v>4558.5</v>
       </c>
       <c r="D42" t="n">
-        <v>4329.2</v>
+        <v>4426.7</v>
       </c>
       <c r="E42" t="n">
-        <v>4414.6</v>
+        <v>4539.9</v>
       </c>
       <c r="F42" t="n">
-        <v>18.2</v>
+        <v>125.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0041</v>
+        <v>0.0284</v>
       </c>
       <c r="H42" t="n">
-        <v>115.2</v>
+        <v>131.8</v>
       </c>
       <c r="I42" t="n">
-        <v>4228.9</v>
+        <v>4214</v>
       </c>
       <c r="J42" t="n">
-        <v>4233.75</v>
+        <v>4313.3</v>
       </c>
       <c r="K42" t="n">
-        <v>4326</v>
+        <v>4357</v>
       </c>
       <c r="L42" t="n">
-        <v>4418.25</v>
+        <v>4400.7</v>
       </c>
       <c r="M42" t="n">
-        <v>4466.8</v>
+        <v>4472.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4515.35</v>
+        <v>4543.7</v>
       </c>
       <c r="O42" t="n">
-        <v>4651.3</v>
+        <v>4559.6</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3996,14 +3992,18 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4015,81 +4015,81 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4436.4</v>
+        <v>4522</v>
       </c>
       <c r="C43" t="n">
-        <v>4558.5</v>
+        <v>4537.8</v>
       </c>
       <c r="D43" t="n">
-        <v>4426.7</v>
+        <v>4412</v>
       </c>
       <c r="E43" t="n">
-        <v>4539.9</v>
+        <v>4476.6</v>
       </c>
       <c r="F43" t="n">
-        <v>125.3</v>
+        <v>-63.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0284</v>
+        <v>-0.0139</v>
       </c>
       <c r="H43" t="n">
-        <v>131.8</v>
+        <v>125.8</v>
       </c>
       <c r="I43" t="n">
-        <v>4214</v>
+        <v>4294.9</v>
       </c>
       <c r="J43" t="n">
-        <v>4313.3</v>
+        <v>4431.75</v>
       </c>
       <c r="K43" t="n">
-        <v>4357</v>
+        <v>4474</v>
       </c>
       <c r="L43" t="n">
-        <v>4400.7</v>
+        <v>4516.25</v>
       </c>
       <c r="M43" t="n">
-        <v>4472.2</v>
+        <v>4605.8</v>
       </c>
       <c r="N43" t="n">
-        <v>4543.7</v>
+        <v>4695.35</v>
       </c>
       <c r="O43" t="n">
-        <v>4559.6</v>
+        <v>4690.3</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4099,74 +4099,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4522</v>
+        <v>4466.5</v>
       </c>
       <c r="C44" t="n">
-        <v>4537.8</v>
+        <v>4488.8</v>
       </c>
       <c r="D44" t="n">
-        <v>4412</v>
+        <v>4381</v>
       </c>
       <c r="E44" t="n">
-        <v>4476.6</v>
+        <v>4439</v>
       </c>
       <c r="F44" t="n">
-        <v>-63.3</v>
+        <v>-37.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0139</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>125.8</v>
+        <v>107.8</v>
       </c>
       <c r="I44" t="n">
-        <v>4294.9</v>
+        <v>4286.2</v>
       </c>
       <c r="J44" t="n">
-        <v>4431.75</v>
+        <v>4351.65</v>
       </c>
       <c r="K44" t="n">
-        <v>4474</v>
+        <v>4413.7</v>
       </c>
       <c r="L44" t="n">
-        <v>4516.25</v>
+        <v>4475.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4605.8</v>
+        <v>4539.5</v>
       </c>
       <c r="N44" t="n">
-        <v>4695.35</v>
+        <v>4603.25</v>
       </c>
       <c r="O44" t="n">
-        <v>4690.3</v>
+        <v>4663.6</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4190,50 +4184,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4466.5</v>
+        <v>4399</v>
       </c>
       <c r="C45" t="n">
-        <v>4488.8</v>
+        <v>4479</v>
       </c>
       <c r="D45" t="n">
-        <v>4381</v>
+        <v>4384.1</v>
       </c>
       <c r="E45" t="n">
-        <v>4439</v>
+        <v>4460.7</v>
       </c>
       <c r="F45" t="n">
-        <v>-37.6</v>
+        <v>21.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0049</v>
       </c>
       <c r="H45" t="n">
-        <v>107.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>4286.2</v>
+        <v>4273.2</v>
       </c>
       <c r="J45" t="n">
-        <v>4351.65</v>
+        <v>4333.25</v>
       </c>
       <c r="K45" t="n">
-        <v>4413.7</v>
+        <v>4385.1</v>
       </c>
       <c r="L45" t="n">
-        <v>4475.75</v>
+        <v>4436.95</v>
       </c>
       <c r="M45" t="n">
-        <v>4539.5</v>
+        <v>4492.9</v>
       </c>
       <c r="N45" t="n">
-        <v>4603.25</v>
+        <v>4548.85</v>
       </c>
       <c r="O45" t="n">
-        <v>4663.6</v>
+        <v>4596.6</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4243,12 +4237,12 @@
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4265,70 +4259,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>4399</v>
+        <v>4448</v>
       </c>
       <c r="C46" t="n">
-        <v>4479</v>
+        <v>4479.9</v>
       </c>
       <c r="D46" t="n">
-        <v>4384.1</v>
+        <v>4354.7</v>
       </c>
       <c r="E46" t="n">
-        <v>4460.7</v>
+        <v>4407.3</v>
       </c>
       <c r="F46" t="n">
-        <v>21.7</v>
+        <v>-53.4</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0049</v>
+        <v>-0.012</v>
       </c>
       <c r="H46" t="n">
-        <v>94.90000000000001</v>
+        <v>125.2</v>
       </c>
       <c r="I46" t="n">
-        <v>4273.2</v>
+        <v>4289.2</v>
       </c>
       <c r="J46" t="n">
-        <v>4333.25</v>
+        <v>4380.38</v>
       </c>
       <c r="K46" t="n">
-        <v>4385.1</v>
+        <v>4413.25</v>
       </c>
       <c r="L46" t="n">
-        <v>4436.95</v>
+        <v>4446.13</v>
       </c>
       <c r="M46" t="n">
-        <v>4492.9</v>
+        <v>4508.15</v>
       </c>
       <c r="N46" t="n">
-        <v>4548.85</v>
+        <v>4570.18</v>
       </c>
       <c r="O46" t="n">
-        <v>4596.6</v>
+        <v>4573.9</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4347,74 +4347,72 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4448</v>
+        <v>4359.4</v>
       </c>
       <c r="C47" t="n">
-        <v>4479.9</v>
+        <v>4444.9</v>
       </c>
       <c r="D47" t="n">
-        <v>4354.7</v>
+        <v>4333</v>
       </c>
       <c r="E47" t="n">
-        <v>4407.3</v>
+        <v>4408.9</v>
       </c>
       <c r="F47" t="n">
-        <v>-53.4</v>
+        <v>1.6</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>125.2</v>
+        <v>111.9</v>
       </c>
       <c r="I47" t="n">
-        <v>4289.2</v>
+        <v>4229.5</v>
       </c>
       <c r="J47" t="n">
-        <v>4380.38</v>
+        <v>4277.1</v>
       </c>
       <c r="K47" t="n">
-        <v>4413.25</v>
+        <v>4344.7</v>
       </c>
       <c r="L47" t="n">
-        <v>4446.13</v>
+        <v>4412.3</v>
       </c>
       <c r="M47" t="n">
-        <v>4508.15</v>
+        <v>4469.9</v>
       </c>
       <c r="N47" t="n">
-        <v>4570.18</v>
+        <v>4527.5</v>
       </c>
       <c r="O47" t="n">
-        <v>4573.9</v>
+        <v>4605.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4440,65 +4438,67 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>4359.4</v>
+        <v>4375</v>
       </c>
       <c r="C48" t="n">
-        <v>4444.9</v>
+        <v>4396.8</v>
       </c>
       <c r="D48" t="n">
-        <v>4333</v>
+        <v>4293</v>
       </c>
       <c r="E48" t="n">
-        <v>4408.9</v>
+        <v>4351.9</v>
       </c>
       <c r="F48" t="n">
-        <v>1.6</v>
+        <v>-57</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0129</v>
       </c>
       <c r="H48" t="n">
-        <v>111.9</v>
+        <v>103.8</v>
       </c>
       <c r="I48" t="n">
-        <v>4229.5</v>
+        <v>4221.1</v>
       </c>
       <c r="J48" t="n">
-        <v>4277.1</v>
+        <v>4306.97</v>
       </c>
       <c r="K48" t="n">
-        <v>4344.7</v>
+        <v>4352.95</v>
       </c>
       <c r="L48" t="n">
-        <v>4412.3</v>
+        <v>4398.92</v>
       </c>
       <c r="M48" t="n">
-        <v>4469.9</v>
+        <v>4464.85</v>
       </c>
       <c r="N48" t="n">
-        <v>4527.5</v>
+        <v>4530.77</v>
       </c>
       <c r="O48" t="n">
-        <v>4605.1</v>
+        <v>4556.8</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4515,76 +4515,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>4375</v>
+        <v>4340.3</v>
       </c>
       <c r="C49" t="n">
-        <v>4396.8</v>
+        <v>4358.2</v>
       </c>
       <c r="D49" t="n">
-        <v>4293</v>
+        <v>4301.6</v>
       </c>
       <c r="E49" t="n">
-        <v>4351.9</v>
+        <v>4332.8</v>
       </c>
       <c r="F49" t="n">
-        <v>-57</v>
+        <v>-19.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0129</v>
+        <v>-0.0044</v>
       </c>
       <c r="H49" t="n">
-        <v>103.8</v>
+        <v>56.6</v>
       </c>
       <c r="I49" t="n">
-        <v>4221.1</v>
+        <v>4189.2</v>
       </c>
       <c r="J49" t="n">
-        <v>4306.97</v>
+        <v>4251.6</v>
       </c>
       <c r="K49" t="n">
-        <v>4352.95</v>
+        <v>4300</v>
       </c>
       <c r="L49" t="n">
-        <v>4398.92</v>
+        <v>4348.4</v>
       </c>
       <c r="M49" t="n">
-        <v>4464.85</v>
+        <v>4403.8</v>
       </c>
       <c r="N49" t="n">
-        <v>4530.77</v>
+        <v>4459.2</v>
       </c>
       <c r="O49" t="n">
-        <v>4556.8</v>
+        <v>4500.6</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4601,75 +4593,87 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4340.3</v>
+        <v>4333.5</v>
       </c>
       <c r="C50" t="n">
-        <v>4358.2</v>
+        <v>4413.1</v>
       </c>
       <c r="D50" t="n">
-        <v>4301.6</v>
+        <v>4273.3</v>
       </c>
       <c r="E50" t="n">
-        <v>4332.8</v>
+        <v>4387.5</v>
       </c>
       <c r="F50" t="n">
-        <v>-19.1</v>
+        <v>54.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0044</v>
+        <v>0.0126</v>
       </c>
       <c r="H50" t="n">
-        <v>56.6</v>
+        <v>139.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4189.2</v>
+        <v>4245</v>
       </c>
       <c r="J50" t="n">
-        <v>4251.6</v>
+        <v>4277.65</v>
       </c>
       <c r="K50" t="n">
-        <v>4300</v>
+        <v>4304.5</v>
       </c>
       <c r="L50" t="n">
-        <v>4348.4</v>
+        <v>4331.35</v>
       </c>
       <c r="M50" t="n">
-        <v>4403.8</v>
+        <v>4361.1</v>
       </c>
       <c r="N50" t="n">
-        <v>4459.2</v>
+        <v>4390.85</v>
       </c>
       <c r="O50" t="n">
-        <v>4500.6</v>
+        <v>4414.8</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4681,85 +4685,79 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>4333.5</v>
+        <v>4301.4</v>
       </c>
       <c r="C51" t="n">
-        <v>4413.1</v>
+        <v>4423.3</v>
       </c>
       <c r="D51" t="n">
-        <v>4273.3</v>
+        <v>4294.5</v>
       </c>
       <c r="E51" t="n">
-        <v>4387.5</v>
+        <v>4399.7</v>
       </c>
       <c r="F51" t="n">
-        <v>54.7</v>
+        <v>12.2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0126</v>
+        <v>0.0028</v>
       </c>
       <c r="H51" t="n">
-        <v>139.8</v>
+        <v>128.8</v>
       </c>
       <c r="I51" t="n">
-        <v>4245</v>
+        <v>4133.5</v>
       </c>
       <c r="J51" t="n">
-        <v>4277.65</v>
+        <v>4269.85</v>
       </c>
       <c r="K51" t="n">
-        <v>4304.5</v>
+        <v>4317.6</v>
       </c>
       <c r="L51" t="n">
-        <v>4331.35</v>
+        <v>4365.35</v>
       </c>
       <c r="M51" t="n">
-        <v>4361.1</v>
+        <v>4457.4</v>
       </c>
       <c r="N51" t="n">
-        <v>4390.85</v>
+        <v>4549.45</v>
       </c>
       <c r="O51" t="n">
-        <v>4414.8</v>
+        <v>4552.9</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4771,57 +4769,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4301.4</v>
+        <v>4381.6</v>
       </c>
       <c r="C52" t="n">
-        <v>4423.3</v>
+        <v>4439.8</v>
       </c>
       <c r="D52" t="n">
-        <v>4294.5</v>
+        <v>4372.2</v>
       </c>
       <c r="E52" t="n">
-        <v>4399.7</v>
+        <v>4424.9</v>
       </c>
       <c r="F52" t="n">
-        <v>12.2</v>
+        <v>25.2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.0057</v>
       </c>
       <c r="H52" t="n">
-        <v>128.8</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>4133.5</v>
+        <v>4165.7</v>
       </c>
       <c r="J52" t="n">
-        <v>4269.85</v>
+        <v>4291.3</v>
       </c>
       <c r="K52" t="n">
-        <v>4317.6</v>
+        <v>4335.3</v>
       </c>
       <c r="L52" t="n">
-        <v>4365.35</v>
+        <v>4379.3</v>
       </c>
       <c r="M52" t="n">
-        <v>4457.4</v>
+        <v>4464.1</v>
       </c>
       <c r="N52" t="n">
-        <v>4549.45</v>
+        <v>4548.9</v>
       </c>
       <c r="O52" t="n">
-        <v>4552.9</v>
+        <v>4552.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4829,18 +4827,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4862,69 +4860,71 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>4381.6</v>
+        <v>4413</v>
       </c>
       <c r="C53" t="n">
-        <v>4439.8</v>
+        <v>4422.1</v>
       </c>
       <c r="D53" t="n">
-        <v>4372.2</v>
+        <v>4360.3</v>
       </c>
       <c r="E53" t="n">
-        <v>4424.9</v>
+        <v>4383.9</v>
       </c>
       <c r="F53" t="n">
-        <v>25.2</v>
+        <v>-41</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>67.59999999999999</v>
+        <v>61.8</v>
       </c>
       <c r="I53" t="n">
-        <v>4165.7</v>
+        <v>4304.6</v>
       </c>
       <c r="J53" t="n">
-        <v>4291.3</v>
+        <v>4366.75</v>
       </c>
       <c r="K53" t="n">
-        <v>4335.3</v>
+        <v>4391.1</v>
       </c>
       <c r="L53" t="n">
-        <v>4379.3</v>
+        <v>4415.45</v>
       </c>
       <c r="M53" t="n">
-        <v>4464.1</v>
+        <v>4458.7</v>
       </c>
       <c r="N53" t="n">
-        <v>4548.9</v>
+        <v>4501.95</v>
       </c>
       <c r="O53" t="n">
-        <v>4552.1</v>
+        <v>4507.4</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4937,76 +4937,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4413</v>
+        <v>4382.5</v>
       </c>
       <c r="C54" t="n">
-        <v>4422.1</v>
+        <v>4414.1</v>
       </c>
       <c r="D54" t="n">
-        <v>4360.3</v>
+        <v>4327.6</v>
       </c>
       <c r="E54" t="n">
-        <v>4383.9</v>
+        <v>4376.4</v>
       </c>
       <c r="F54" t="n">
-        <v>-41</v>
+        <v>-7.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0017</v>
       </c>
       <c r="H54" t="n">
-        <v>61.8</v>
+        <v>86.5</v>
       </c>
       <c r="I54" t="n">
-        <v>4304.6</v>
+        <v>4298.5</v>
       </c>
       <c r="J54" t="n">
-        <v>4366.75</v>
+        <v>4318.45</v>
       </c>
       <c r="K54" t="n">
-        <v>4391.1</v>
+        <v>4353</v>
       </c>
       <c r="L54" t="n">
-        <v>4415.45</v>
+        <v>4387.55</v>
       </c>
       <c r="M54" t="n">
-        <v>4458.7</v>
+        <v>4414.8</v>
       </c>
       <c r="N54" t="n">
-        <v>4501.95</v>
+        <v>4442.05</v>
       </c>
       <c r="O54" t="n">
-        <v>4507.4</v>
+        <v>4483.9</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5028,50 +5022,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4382.5</v>
+        <v>4394.7</v>
       </c>
       <c r="C55" t="n">
-        <v>4414.1</v>
+        <v>4407.5</v>
       </c>
       <c r="D55" t="n">
-        <v>4327.6</v>
+        <v>4310.7</v>
       </c>
       <c r="E55" t="n">
-        <v>4376.4</v>
+        <v>4318.4</v>
       </c>
       <c r="F55" t="n">
-        <v>-7.5</v>
+        <v>-58</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0017</v>
+        <v>-0.0133</v>
       </c>
       <c r="H55" t="n">
-        <v>86.5</v>
+        <v>96.8</v>
       </c>
       <c r="I55" t="n">
-        <v>4298.5</v>
+        <v>4241.1</v>
       </c>
       <c r="J55" t="n">
-        <v>4318.45</v>
+        <v>4292.67</v>
       </c>
       <c r="K55" t="n">
-        <v>4353</v>
+        <v>4333.15</v>
       </c>
       <c r="L55" t="n">
-        <v>4387.55</v>
+        <v>4373.62</v>
       </c>
       <c r="M55" t="n">
-        <v>4414.8</v>
+        <v>4419.65</v>
       </c>
       <c r="N55" t="n">
-        <v>4442.05</v>
+        <v>4465.67</v>
       </c>
       <c r="O55" t="n">
-        <v>4483.9</v>
+        <v>4500.6</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5081,12 +5075,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5108,50 +5102,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4394.7</v>
+        <v>4324.4</v>
       </c>
       <c r="C56" t="n">
-        <v>4407.5</v>
+        <v>4338</v>
       </c>
       <c r="D56" t="n">
-        <v>4310.7</v>
+        <v>4278.3</v>
       </c>
       <c r="E56" t="n">
-        <v>4318.4</v>
+        <v>4298</v>
       </c>
       <c r="F56" t="n">
-        <v>-58</v>
+        <v>-20.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0133</v>
+        <v>-0.0047</v>
       </c>
       <c r="H56" t="n">
-        <v>96.8</v>
+        <v>59.7</v>
       </c>
       <c r="I56" t="n">
-        <v>4241.1</v>
+        <v>4213.9</v>
       </c>
       <c r="J56" t="n">
-        <v>4292.67</v>
+        <v>4201.25</v>
       </c>
       <c r="K56" t="n">
-        <v>4333.15</v>
+        <v>4270</v>
       </c>
       <c r="L56" t="n">
-        <v>4373.62</v>
+        <v>4338.75</v>
       </c>
       <c r="M56" t="n">
-        <v>4419.65</v>
+        <v>4366.8</v>
       </c>
       <c r="N56" t="n">
-        <v>4465.67</v>
+        <v>4394.85</v>
       </c>
       <c r="O56" t="n">
-        <v>4500.6</v>
+        <v>4504.3</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5164,7 +5158,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5188,50 +5182,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4324.4</v>
+        <v>4309.5</v>
       </c>
       <c r="C57" t="n">
-        <v>4338</v>
+        <v>4351.6</v>
       </c>
       <c r="D57" t="n">
-        <v>4278.3</v>
+        <v>4289.2</v>
       </c>
       <c r="E57" t="n">
-        <v>4298</v>
+        <v>4321.2</v>
       </c>
       <c r="F57" t="n">
-        <v>-20.4</v>
+        <v>23.2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0047</v>
+        <v>0.0054</v>
       </c>
       <c r="H57" t="n">
-        <v>59.7</v>
+        <v>62.4</v>
       </c>
       <c r="I57" t="n">
-        <v>4213.9</v>
+        <v>4218.6</v>
       </c>
       <c r="J57" t="n">
-        <v>4201.25</v>
+        <v>4233.22</v>
       </c>
       <c r="K57" t="n">
-        <v>4270</v>
+        <v>4268.15</v>
       </c>
       <c r="L57" t="n">
-        <v>4338.75</v>
+        <v>4303.07</v>
       </c>
       <c r="M57" t="n">
-        <v>4366.8</v>
+        <v>4327.85</v>
       </c>
       <c r="N57" t="n">
-        <v>4394.85</v>
+        <v>4352.63</v>
       </c>
       <c r="O57" t="n">
-        <v>4504.3</v>
+        <v>4397.7</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5239,19 +5233,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5263,74 +5257,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r